--- a/交易管理系统.xlsx
+++ b/交易管理系统.xlsx
@@ -262,6 +262,11 @@
         <t>默认等于实际买入股数；本系统按一次卖出处理。</t>
       </text>
     </comment>
+    <comment ref="AE1" authorId="0" shapeId="0">
+      <text>
+        <t>实际盈亏金额÷买入时账户金额快照；用于账户口径统计与逐笔复利。</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -282,9 +287,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TradeRecords" displayName="TradeRecords" ref="A1:AD201" headerRowCount="1">
-  <autoFilter ref="A1:AD201"/>
-  <tableColumns count="30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TradeRecords" displayName="TradeRecords" ref="A1:AE201" headerRowCount="1">
+  <autoFilter ref="A1:AE201"/>
+  <tableColumns count="31">
     <tableColumn id="1" name="交易编号"/>
     <tableColumn id="2" name="股票代码"/>
     <tableColumn id="3" name="买入时账户金额"/>
@@ -309,12 +314,13 @@
     <tableColumn id="22" name="期望止损比例"/>
     <tableColumn id="23" name="盈亏比"/>
     <tableColumn id="24" name="实际盈亏金额"/>
-    <tableColumn id="25" name="实际收益率"/>
-    <tableColumn id="26" name="与平均盈利比例差值"/>
+    <tableColumn id="25" name="单笔仓位收益率"/>
+    <tableColumn id="26" name="账户收益率与平均盈利率差值"/>
     <tableColumn id="27" name="持有天数"/>
     <tableColumn id="28" name="复利容许平均亏损上限"/>
     <tableColumn id="29" name="复利风险判断"/>
     <tableColumn id="30" name="交易打分评价"/>
+    <tableColumn id="31" name="实际账户收益率"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -639,7 +645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD201"/>
+  <dimension ref="A1:AE201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -672,6 +678,7 @@
     <col width="22" customWidth="1" min="28" max="28"/>
     <col width="18" customWidth="1" min="29" max="29"/>
     <col width="18" customWidth="1" min="30" max="30"/>
+    <col width="18" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1" ht="42" customHeight="1">
@@ -797,12 +804,12 @@
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>实际收益率</t>
+          <t>单笔仓位收益率</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>与平均盈利比例差值</t>
+          <t>账户收益率与平均盈利率差值</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
@@ -823,6 +830,11 @@
       <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>交易打分评价</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>实际账户收益率</t>
         </is>
       </c>
     </row>
@@ -877,7 +889,7 @@
         <v/>
       </c>
       <c r="Z2" s="7">
-        <f>IF(OR(Y2="",'多次统计数据'!$B$8=""),"",Y2-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE2="",'多次统计数据'!$B$8=""),"",AE2-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA2" s="10">
@@ -893,6 +905,10 @@
         <v/>
       </c>
       <c r="AD2" s="2" t="n"/>
+      <c r="AE2" s="7">
+        <f>IF(OR(X2="",C2="",C2&lt;=0),"",X2/C2)</f>
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n"/>
@@ -945,7 +961,7 @@
         <v/>
       </c>
       <c r="Z3" s="7">
-        <f>IF(OR(Y3="",'多次统计数据'!$B$8=""),"",Y3-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE3="",'多次统计数据'!$B$8=""),"",AE3-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA3" s="10">
@@ -961,6 +977,10 @@
         <v/>
       </c>
       <c r="AD3" s="2" t="n"/>
+      <c r="AE3" s="7">
+        <f>IF(OR(X3="",C3="",C3&lt;=0),"",X3/C3)</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n"/>
@@ -1013,7 +1033,7 @@
         <v/>
       </c>
       <c r="Z4" s="7">
-        <f>IF(OR(Y4="",'多次统计数据'!$B$8=""),"",Y4-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE4="",'多次统计数据'!$B$8=""),"",AE4-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA4" s="10">
@@ -1029,6 +1049,10 @@
         <v/>
       </c>
       <c r="AD4" s="2" t="n"/>
+      <c r="AE4" s="7">
+        <f>IF(OR(X4="",C4="",C4&lt;=0),"",X4/C4)</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n"/>
@@ -1081,7 +1105,7 @@
         <v/>
       </c>
       <c r="Z5" s="7">
-        <f>IF(OR(Y5="",'多次统计数据'!$B$8=""),"",Y5-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE5="",'多次统计数据'!$B$8=""),"",AE5-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA5" s="10">
@@ -1097,6 +1121,10 @@
         <v/>
       </c>
       <c r="AD5" s="2" t="n"/>
+      <c r="AE5" s="7">
+        <f>IF(OR(X5="",C5="",C5&lt;=0),"",X5/C5)</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n"/>
@@ -1149,7 +1177,7 @@
         <v/>
       </c>
       <c r="Z6" s="7">
-        <f>IF(OR(Y6="",'多次统计数据'!$B$8=""),"",Y6-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE6="",'多次统计数据'!$B$8=""),"",AE6-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA6" s="10">
@@ -1165,6 +1193,10 @@
         <v/>
       </c>
       <c r="AD6" s="2" t="n"/>
+      <c r="AE6" s="7">
+        <f>IF(OR(X6="",C6="",C6&lt;=0),"",X6/C6)</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n"/>
@@ -1217,7 +1249,7 @@
         <v/>
       </c>
       <c r="Z7" s="7">
-        <f>IF(OR(Y7="",'多次统计数据'!$B$8=""),"",Y7-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE7="",'多次统计数据'!$B$8=""),"",AE7-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA7" s="10">
@@ -1233,6 +1265,10 @@
         <v/>
       </c>
       <c r="AD7" s="2" t="n"/>
+      <c r="AE7" s="7">
+        <f>IF(OR(X7="",C7="",C7&lt;=0),"",X7/C7)</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
@@ -1285,7 +1321,7 @@
         <v/>
       </c>
       <c r="Z8" s="7">
-        <f>IF(OR(Y8="",'多次统计数据'!$B$8=""),"",Y8-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE8="",'多次统计数据'!$B$8=""),"",AE8-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA8" s="10">
@@ -1301,6 +1337,10 @@
         <v/>
       </c>
       <c r="AD8" s="2" t="n"/>
+      <c r="AE8" s="7">
+        <f>IF(OR(X8="",C8="",C8&lt;=0),"",X8/C8)</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
@@ -1353,7 +1393,7 @@
         <v/>
       </c>
       <c r="Z9" s="7">
-        <f>IF(OR(Y9="",'多次统计数据'!$B$8=""),"",Y9-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE9="",'多次统计数据'!$B$8=""),"",AE9-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA9" s="10">
@@ -1369,6 +1409,10 @@
         <v/>
       </c>
       <c r="AD9" s="2" t="n"/>
+      <c r="AE9" s="7">
+        <f>IF(OR(X9="",C9="",C9&lt;=0),"",X9/C9)</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n"/>
@@ -1421,7 +1465,7 @@
         <v/>
       </c>
       <c r="Z10" s="7">
-        <f>IF(OR(Y10="",'多次统计数据'!$B$8=""),"",Y10-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE10="",'多次统计数据'!$B$8=""),"",AE10-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA10" s="10">
@@ -1437,6 +1481,10 @@
         <v/>
       </c>
       <c r="AD10" s="2" t="n"/>
+      <c r="AE10" s="7">
+        <f>IF(OR(X10="",C10="",C10&lt;=0),"",X10/C10)</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n"/>
@@ -1489,7 +1537,7 @@
         <v/>
       </c>
       <c r="Z11" s="7">
-        <f>IF(OR(Y11="",'多次统计数据'!$B$8=""),"",Y11-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE11="",'多次统计数据'!$B$8=""),"",AE11-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA11" s="10">
@@ -1505,6 +1553,10 @@
         <v/>
       </c>
       <c r="AD11" s="2" t="n"/>
+      <c r="AE11" s="7">
+        <f>IF(OR(X11="",C11="",C11&lt;=0),"",X11/C11)</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n"/>
@@ -1557,7 +1609,7 @@
         <v/>
       </c>
       <c r="Z12" s="7">
-        <f>IF(OR(Y12="",'多次统计数据'!$B$8=""),"",Y12-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE12="",'多次统计数据'!$B$8=""),"",AE12-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA12" s="10">
@@ -1573,6 +1625,10 @@
         <v/>
       </c>
       <c r="AD12" s="2" t="n"/>
+      <c r="AE12" s="7">
+        <f>IF(OR(X12="",C12="",C12&lt;=0),"",X12/C12)</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n"/>
@@ -1625,7 +1681,7 @@
         <v/>
       </c>
       <c r="Z13" s="7">
-        <f>IF(OR(Y13="",'多次统计数据'!$B$8=""),"",Y13-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE13="",'多次统计数据'!$B$8=""),"",AE13-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA13" s="10">
@@ -1641,6 +1697,10 @@
         <v/>
       </c>
       <c r="AD13" s="2" t="n"/>
+      <c r="AE13" s="7">
+        <f>IF(OR(X13="",C13="",C13&lt;=0),"",X13/C13)</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n"/>
@@ -1693,7 +1753,7 @@
         <v/>
       </c>
       <c r="Z14" s="7">
-        <f>IF(OR(Y14="",'多次统计数据'!$B$8=""),"",Y14-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE14="",'多次统计数据'!$B$8=""),"",AE14-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA14" s="10">
@@ -1709,6 +1769,10 @@
         <v/>
       </c>
       <c r="AD14" s="2" t="n"/>
+      <c r="AE14" s="7">
+        <f>IF(OR(X14="",C14="",C14&lt;=0),"",X14/C14)</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n"/>
@@ -1761,7 +1825,7 @@
         <v/>
       </c>
       <c r="Z15" s="7">
-        <f>IF(OR(Y15="",'多次统计数据'!$B$8=""),"",Y15-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE15="",'多次统计数据'!$B$8=""),"",AE15-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA15" s="10">
@@ -1777,6 +1841,10 @@
         <v/>
       </c>
       <c r="AD15" s="2" t="n"/>
+      <c r="AE15" s="7">
+        <f>IF(OR(X15="",C15="",C15&lt;=0),"",X15/C15)</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n"/>
@@ -1829,7 +1897,7 @@
         <v/>
       </c>
       <c r="Z16" s="7">
-        <f>IF(OR(Y16="",'多次统计数据'!$B$8=""),"",Y16-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE16="",'多次统计数据'!$B$8=""),"",AE16-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA16" s="10">
@@ -1845,6 +1913,10 @@
         <v/>
       </c>
       <c r="AD16" s="2" t="n"/>
+      <c r="AE16" s="7">
+        <f>IF(OR(X16="",C16="",C16&lt;=0),"",X16/C16)</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n"/>
@@ -1897,7 +1969,7 @@
         <v/>
       </c>
       <c r="Z17" s="7">
-        <f>IF(OR(Y17="",'多次统计数据'!$B$8=""),"",Y17-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE17="",'多次统计数据'!$B$8=""),"",AE17-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA17" s="10">
@@ -1913,6 +1985,10 @@
         <v/>
       </c>
       <c r="AD17" s="2" t="n"/>
+      <c r="AE17" s="7">
+        <f>IF(OR(X17="",C17="",C17&lt;=0),"",X17/C17)</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n"/>
@@ -1965,7 +2041,7 @@
         <v/>
       </c>
       <c r="Z18" s="7">
-        <f>IF(OR(Y18="",'多次统计数据'!$B$8=""),"",Y18-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE18="",'多次统计数据'!$B$8=""),"",AE18-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA18" s="10">
@@ -1981,6 +2057,10 @@
         <v/>
       </c>
       <c r="AD18" s="2" t="n"/>
+      <c r="AE18" s="7">
+        <f>IF(OR(X18="",C18="",C18&lt;=0),"",X18/C18)</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n"/>
@@ -2033,7 +2113,7 @@
         <v/>
       </c>
       <c r="Z19" s="7">
-        <f>IF(OR(Y19="",'多次统计数据'!$B$8=""),"",Y19-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE19="",'多次统计数据'!$B$8=""),"",AE19-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA19" s="10">
@@ -2049,6 +2129,10 @@
         <v/>
       </c>
       <c r="AD19" s="2" t="n"/>
+      <c r="AE19" s="7">
+        <f>IF(OR(X19="",C19="",C19&lt;=0),"",X19/C19)</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n"/>
@@ -2101,7 +2185,7 @@
         <v/>
       </c>
       <c r="Z20" s="7">
-        <f>IF(OR(Y20="",'多次统计数据'!$B$8=""),"",Y20-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE20="",'多次统计数据'!$B$8=""),"",AE20-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA20" s="10">
@@ -2117,6 +2201,10 @@
         <v/>
       </c>
       <c r="AD20" s="2" t="n"/>
+      <c r="AE20" s="7">
+        <f>IF(OR(X20="",C20="",C20&lt;=0),"",X20/C20)</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n"/>
@@ -2169,7 +2257,7 @@
         <v/>
       </c>
       <c r="Z21" s="7">
-        <f>IF(OR(Y21="",'多次统计数据'!$B$8=""),"",Y21-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE21="",'多次统计数据'!$B$8=""),"",AE21-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA21" s="10">
@@ -2185,6 +2273,10 @@
         <v/>
       </c>
       <c r="AD21" s="2" t="n"/>
+      <c r="AE21" s="7">
+        <f>IF(OR(X21="",C21="",C21&lt;=0),"",X21/C21)</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n"/>
@@ -2237,7 +2329,7 @@
         <v/>
       </c>
       <c r="Z22" s="7">
-        <f>IF(OR(Y22="",'多次统计数据'!$B$8=""),"",Y22-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE22="",'多次统计数据'!$B$8=""),"",AE22-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA22" s="10">
@@ -2253,6 +2345,10 @@
         <v/>
       </c>
       <c r="AD22" s="2" t="n"/>
+      <c r="AE22" s="7">
+        <f>IF(OR(X22="",C22="",C22&lt;=0),"",X22/C22)</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n"/>
@@ -2305,7 +2401,7 @@
         <v/>
       </c>
       <c r="Z23" s="7">
-        <f>IF(OR(Y23="",'多次统计数据'!$B$8=""),"",Y23-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE23="",'多次统计数据'!$B$8=""),"",AE23-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA23" s="10">
@@ -2321,6 +2417,10 @@
         <v/>
       </c>
       <c r="AD23" s="2" t="n"/>
+      <c r="AE23" s="7">
+        <f>IF(OR(X23="",C23="",C23&lt;=0),"",X23/C23)</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n"/>
@@ -2373,7 +2473,7 @@
         <v/>
       </c>
       <c r="Z24" s="7">
-        <f>IF(OR(Y24="",'多次统计数据'!$B$8=""),"",Y24-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE24="",'多次统计数据'!$B$8=""),"",AE24-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA24" s="10">
@@ -2389,6 +2489,10 @@
         <v/>
       </c>
       <c r="AD24" s="2" t="n"/>
+      <c r="AE24" s="7">
+        <f>IF(OR(X24="",C24="",C24&lt;=0),"",X24/C24)</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n"/>
@@ -2441,7 +2545,7 @@
         <v/>
       </c>
       <c r="Z25" s="7">
-        <f>IF(OR(Y25="",'多次统计数据'!$B$8=""),"",Y25-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE25="",'多次统计数据'!$B$8=""),"",AE25-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA25" s="10">
@@ -2457,6 +2561,10 @@
         <v/>
       </c>
       <c r="AD25" s="2" t="n"/>
+      <c r="AE25" s="7">
+        <f>IF(OR(X25="",C25="",C25&lt;=0),"",X25/C25)</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n"/>
@@ -2509,7 +2617,7 @@
         <v/>
       </c>
       <c r="Z26" s="7">
-        <f>IF(OR(Y26="",'多次统计数据'!$B$8=""),"",Y26-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE26="",'多次统计数据'!$B$8=""),"",AE26-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA26" s="10">
@@ -2525,6 +2633,10 @@
         <v/>
       </c>
       <c r="AD26" s="2" t="n"/>
+      <c r="AE26" s="7">
+        <f>IF(OR(X26="",C26="",C26&lt;=0),"",X26/C26)</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n"/>
@@ -2577,7 +2689,7 @@
         <v/>
       </c>
       <c r="Z27" s="7">
-        <f>IF(OR(Y27="",'多次统计数据'!$B$8=""),"",Y27-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE27="",'多次统计数据'!$B$8=""),"",AE27-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA27" s="10">
@@ -2593,6 +2705,10 @@
         <v/>
       </c>
       <c r="AD27" s="2" t="n"/>
+      <c r="AE27" s="7">
+        <f>IF(OR(X27="",C27="",C27&lt;=0),"",X27/C27)</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n"/>
@@ -2645,7 +2761,7 @@
         <v/>
       </c>
       <c r="Z28" s="7">
-        <f>IF(OR(Y28="",'多次统计数据'!$B$8=""),"",Y28-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE28="",'多次统计数据'!$B$8=""),"",AE28-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA28" s="10">
@@ -2661,6 +2777,10 @@
         <v/>
       </c>
       <c r="AD28" s="2" t="n"/>
+      <c r="AE28" s="7">
+        <f>IF(OR(X28="",C28="",C28&lt;=0),"",X28/C28)</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n"/>
@@ -2713,7 +2833,7 @@
         <v/>
       </c>
       <c r="Z29" s="7">
-        <f>IF(OR(Y29="",'多次统计数据'!$B$8=""),"",Y29-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE29="",'多次统计数据'!$B$8=""),"",AE29-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA29" s="10">
@@ -2729,6 +2849,10 @@
         <v/>
       </c>
       <c r="AD29" s="2" t="n"/>
+      <c r="AE29" s="7">
+        <f>IF(OR(X29="",C29="",C29&lt;=0),"",X29/C29)</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n"/>
@@ -2781,7 +2905,7 @@
         <v/>
       </c>
       <c r="Z30" s="7">
-        <f>IF(OR(Y30="",'多次统计数据'!$B$8=""),"",Y30-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE30="",'多次统计数据'!$B$8=""),"",AE30-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA30" s="10">
@@ -2797,6 +2921,10 @@
         <v/>
       </c>
       <c r="AD30" s="2" t="n"/>
+      <c r="AE30" s="7">
+        <f>IF(OR(X30="",C30="",C30&lt;=0),"",X30/C30)</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n"/>
@@ -2849,7 +2977,7 @@
         <v/>
       </c>
       <c r="Z31" s="7">
-        <f>IF(OR(Y31="",'多次统计数据'!$B$8=""),"",Y31-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE31="",'多次统计数据'!$B$8=""),"",AE31-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA31" s="10">
@@ -2865,6 +2993,10 @@
         <v/>
       </c>
       <c r="AD31" s="2" t="n"/>
+      <c r="AE31" s="7">
+        <f>IF(OR(X31="",C31="",C31&lt;=0),"",X31/C31)</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n"/>
@@ -2917,7 +3049,7 @@
         <v/>
       </c>
       <c r="Z32" s="7">
-        <f>IF(OR(Y32="",'多次统计数据'!$B$8=""),"",Y32-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE32="",'多次统计数据'!$B$8=""),"",AE32-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA32" s="10">
@@ -2933,6 +3065,10 @@
         <v/>
       </c>
       <c r="AD32" s="2" t="n"/>
+      <c r="AE32" s="7">
+        <f>IF(OR(X32="",C32="",C32&lt;=0),"",X32/C32)</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n"/>
@@ -2985,7 +3121,7 @@
         <v/>
       </c>
       <c r="Z33" s="7">
-        <f>IF(OR(Y33="",'多次统计数据'!$B$8=""),"",Y33-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE33="",'多次统计数据'!$B$8=""),"",AE33-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA33" s="10">
@@ -3001,6 +3137,10 @@
         <v/>
       </c>
       <c r="AD33" s="2" t="n"/>
+      <c r="AE33" s="7">
+        <f>IF(OR(X33="",C33="",C33&lt;=0),"",X33/C33)</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n"/>
@@ -3053,7 +3193,7 @@
         <v/>
       </c>
       <c r="Z34" s="7">
-        <f>IF(OR(Y34="",'多次统计数据'!$B$8=""),"",Y34-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE34="",'多次统计数据'!$B$8=""),"",AE34-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA34" s="10">
@@ -3069,6 +3209,10 @@
         <v/>
       </c>
       <c r="AD34" s="2" t="n"/>
+      <c r="AE34" s="7">
+        <f>IF(OR(X34="",C34="",C34&lt;=0),"",X34/C34)</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n"/>
@@ -3121,7 +3265,7 @@
         <v/>
       </c>
       <c r="Z35" s="7">
-        <f>IF(OR(Y35="",'多次统计数据'!$B$8=""),"",Y35-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE35="",'多次统计数据'!$B$8=""),"",AE35-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA35" s="10">
@@ -3137,6 +3281,10 @@
         <v/>
       </c>
       <c r="AD35" s="2" t="n"/>
+      <c r="AE35" s="7">
+        <f>IF(OR(X35="",C35="",C35&lt;=0),"",X35/C35)</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n"/>
@@ -3189,7 +3337,7 @@
         <v/>
       </c>
       <c r="Z36" s="7">
-        <f>IF(OR(Y36="",'多次统计数据'!$B$8=""),"",Y36-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE36="",'多次统计数据'!$B$8=""),"",AE36-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA36" s="10">
@@ -3205,6 +3353,10 @@
         <v/>
       </c>
       <c r="AD36" s="2" t="n"/>
+      <c r="AE36" s="7">
+        <f>IF(OR(X36="",C36="",C36&lt;=0),"",X36/C36)</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n"/>
@@ -3257,7 +3409,7 @@
         <v/>
       </c>
       <c r="Z37" s="7">
-        <f>IF(OR(Y37="",'多次统计数据'!$B$8=""),"",Y37-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE37="",'多次统计数据'!$B$8=""),"",AE37-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA37" s="10">
@@ -3273,6 +3425,10 @@
         <v/>
       </c>
       <c r="AD37" s="2" t="n"/>
+      <c r="AE37" s="7">
+        <f>IF(OR(X37="",C37="",C37&lt;=0),"",X37/C37)</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n"/>
@@ -3325,7 +3481,7 @@
         <v/>
       </c>
       <c r="Z38" s="7">
-        <f>IF(OR(Y38="",'多次统计数据'!$B$8=""),"",Y38-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE38="",'多次统计数据'!$B$8=""),"",AE38-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA38" s="10">
@@ -3341,6 +3497,10 @@
         <v/>
       </c>
       <c r="AD38" s="2" t="n"/>
+      <c r="AE38" s="7">
+        <f>IF(OR(X38="",C38="",C38&lt;=0),"",X38/C38)</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n"/>
@@ -3393,7 +3553,7 @@
         <v/>
       </c>
       <c r="Z39" s="7">
-        <f>IF(OR(Y39="",'多次统计数据'!$B$8=""),"",Y39-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE39="",'多次统计数据'!$B$8=""),"",AE39-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA39" s="10">
@@ -3409,6 +3569,10 @@
         <v/>
       </c>
       <c r="AD39" s="2" t="n"/>
+      <c r="AE39" s="7">
+        <f>IF(OR(X39="",C39="",C39&lt;=0),"",X39/C39)</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n"/>
@@ -3461,7 +3625,7 @@
         <v/>
       </c>
       <c r="Z40" s="7">
-        <f>IF(OR(Y40="",'多次统计数据'!$B$8=""),"",Y40-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE40="",'多次统计数据'!$B$8=""),"",AE40-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA40" s="10">
@@ -3477,6 +3641,10 @@
         <v/>
       </c>
       <c r="AD40" s="2" t="n"/>
+      <c r="AE40" s="7">
+        <f>IF(OR(X40="",C40="",C40&lt;=0),"",X40/C40)</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n"/>
@@ -3529,7 +3697,7 @@
         <v/>
       </c>
       <c r="Z41" s="7">
-        <f>IF(OR(Y41="",'多次统计数据'!$B$8=""),"",Y41-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE41="",'多次统计数据'!$B$8=""),"",AE41-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA41" s="10">
@@ -3545,6 +3713,10 @@
         <v/>
       </c>
       <c r="AD41" s="2" t="n"/>
+      <c r="AE41" s="7">
+        <f>IF(OR(X41="",C41="",C41&lt;=0),"",X41/C41)</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n"/>
@@ -3597,7 +3769,7 @@
         <v/>
       </c>
       <c r="Z42" s="7">
-        <f>IF(OR(Y42="",'多次统计数据'!$B$8=""),"",Y42-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE42="",'多次统计数据'!$B$8=""),"",AE42-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA42" s="10">
@@ -3613,6 +3785,10 @@
         <v/>
       </c>
       <c r="AD42" s="2" t="n"/>
+      <c r="AE42" s="7">
+        <f>IF(OR(X42="",C42="",C42&lt;=0),"",X42/C42)</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n"/>
@@ -3665,7 +3841,7 @@
         <v/>
       </c>
       <c r="Z43" s="7">
-        <f>IF(OR(Y43="",'多次统计数据'!$B$8=""),"",Y43-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE43="",'多次统计数据'!$B$8=""),"",AE43-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA43" s="10">
@@ -3681,6 +3857,10 @@
         <v/>
       </c>
       <c r="AD43" s="2" t="n"/>
+      <c r="AE43" s="7">
+        <f>IF(OR(X43="",C43="",C43&lt;=0),"",X43/C43)</f>
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n"/>
@@ -3733,7 +3913,7 @@
         <v/>
       </c>
       <c r="Z44" s="7">
-        <f>IF(OR(Y44="",'多次统计数据'!$B$8=""),"",Y44-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE44="",'多次统计数据'!$B$8=""),"",AE44-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA44" s="10">
@@ -3749,6 +3929,10 @@
         <v/>
       </c>
       <c r="AD44" s="2" t="n"/>
+      <c r="AE44" s="7">
+        <f>IF(OR(X44="",C44="",C44&lt;=0),"",X44/C44)</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n"/>
@@ -3801,7 +3985,7 @@
         <v/>
       </c>
       <c r="Z45" s="7">
-        <f>IF(OR(Y45="",'多次统计数据'!$B$8=""),"",Y45-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE45="",'多次统计数据'!$B$8=""),"",AE45-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA45" s="10">
@@ -3817,6 +4001,10 @@
         <v/>
       </c>
       <c r="AD45" s="2" t="n"/>
+      <c r="AE45" s="7">
+        <f>IF(OR(X45="",C45="",C45&lt;=0),"",X45/C45)</f>
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n"/>
@@ -3869,7 +4057,7 @@
         <v/>
       </c>
       <c r="Z46" s="7">
-        <f>IF(OR(Y46="",'多次统计数据'!$B$8=""),"",Y46-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE46="",'多次统计数据'!$B$8=""),"",AE46-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA46" s="10">
@@ -3885,6 +4073,10 @@
         <v/>
       </c>
       <c r="AD46" s="2" t="n"/>
+      <c r="AE46" s="7">
+        <f>IF(OR(X46="",C46="",C46&lt;=0),"",X46/C46)</f>
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n"/>
@@ -3937,7 +4129,7 @@
         <v/>
       </c>
       <c r="Z47" s="7">
-        <f>IF(OR(Y47="",'多次统计数据'!$B$8=""),"",Y47-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE47="",'多次统计数据'!$B$8=""),"",AE47-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA47" s="10">
@@ -3953,6 +4145,10 @@
         <v/>
       </c>
       <c r="AD47" s="2" t="n"/>
+      <c r="AE47" s="7">
+        <f>IF(OR(X47="",C47="",C47&lt;=0),"",X47/C47)</f>
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n"/>
@@ -4005,7 +4201,7 @@
         <v/>
       </c>
       <c r="Z48" s="7">
-        <f>IF(OR(Y48="",'多次统计数据'!$B$8=""),"",Y48-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE48="",'多次统计数据'!$B$8=""),"",AE48-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA48" s="10">
@@ -4021,6 +4217,10 @@
         <v/>
       </c>
       <c r="AD48" s="2" t="n"/>
+      <c r="AE48" s="7">
+        <f>IF(OR(X48="",C48="",C48&lt;=0),"",X48/C48)</f>
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n"/>
@@ -4073,7 +4273,7 @@
         <v/>
       </c>
       <c r="Z49" s="7">
-        <f>IF(OR(Y49="",'多次统计数据'!$B$8=""),"",Y49-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE49="",'多次统计数据'!$B$8=""),"",AE49-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA49" s="10">
@@ -4089,6 +4289,10 @@
         <v/>
       </c>
       <c r="AD49" s="2" t="n"/>
+      <c r="AE49" s="7">
+        <f>IF(OR(X49="",C49="",C49&lt;=0),"",X49/C49)</f>
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n"/>
@@ -4141,7 +4345,7 @@
         <v/>
       </c>
       <c r="Z50" s="7">
-        <f>IF(OR(Y50="",'多次统计数据'!$B$8=""),"",Y50-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE50="",'多次统计数据'!$B$8=""),"",AE50-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA50" s="10">
@@ -4157,6 +4361,10 @@
         <v/>
       </c>
       <c r="AD50" s="2" t="n"/>
+      <c r="AE50" s="7">
+        <f>IF(OR(X50="",C50="",C50&lt;=0),"",X50/C50)</f>
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n"/>
@@ -4209,7 +4417,7 @@
         <v/>
       </c>
       <c r="Z51" s="7">
-        <f>IF(OR(Y51="",'多次统计数据'!$B$8=""),"",Y51-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE51="",'多次统计数据'!$B$8=""),"",AE51-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA51" s="10">
@@ -4225,6 +4433,10 @@
         <v/>
       </c>
       <c r="AD51" s="2" t="n"/>
+      <c r="AE51" s="7">
+        <f>IF(OR(X51="",C51="",C51&lt;=0),"",X51/C51)</f>
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n"/>
@@ -4277,7 +4489,7 @@
         <v/>
       </c>
       <c r="Z52" s="7">
-        <f>IF(OR(Y52="",'多次统计数据'!$B$8=""),"",Y52-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE52="",'多次统计数据'!$B$8=""),"",AE52-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA52" s="10">
@@ -4293,6 +4505,10 @@
         <v/>
       </c>
       <c r="AD52" s="2" t="n"/>
+      <c r="AE52" s="7">
+        <f>IF(OR(X52="",C52="",C52&lt;=0),"",X52/C52)</f>
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n"/>
@@ -4345,7 +4561,7 @@
         <v/>
       </c>
       <c r="Z53" s="7">
-        <f>IF(OR(Y53="",'多次统计数据'!$B$8=""),"",Y53-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE53="",'多次统计数据'!$B$8=""),"",AE53-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA53" s="10">
@@ -4361,6 +4577,10 @@
         <v/>
       </c>
       <c r="AD53" s="2" t="n"/>
+      <c r="AE53" s="7">
+        <f>IF(OR(X53="",C53="",C53&lt;=0),"",X53/C53)</f>
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n"/>
@@ -4413,7 +4633,7 @@
         <v/>
       </c>
       <c r="Z54" s="7">
-        <f>IF(OR(Y54="",'多次统计数据'!$B$8=""),"",Y54-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE54="",'多次统计数据'!$B$8=""),"",AE54-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA54" s="10">
@@ -4429,6 +4649,10 @@
         <v/>
       </c>
       <c r="AD54" s="2" t="n"/>
+      <c r="AE54" s="7">
+        <f>IF(OR(X54="",C54="",C54&lt;=0),"",X54/C54)</f>
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n"/>
@@ -4481,7 +4705,7 @@
         <v/>
       </c>
       <c r="Z55" s="7">
-        <f>IF(OR(Y55="",'多次统计数据'!$B$8=""),"",Y55-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE55="",'多次统计数据'!$B$8=""),"",AE55-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA55" s="10">
@@ -4497,6 +4721,10 @@
         <v/>
       </c>
       <c r="AD55" s="2" t="n"/>
+      <c r="AE55" s="7">
+        <f>IF(OR(X55="",C55="",C55&lt;=0),"",X55/C55)</f>
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n"/>
@@ -4549,7 +4777,7 @@
         <v/>
       </c>
       <c r="Z56" s="7">
-        <f>IF(OR(Y56="",'多次统计数据'!$B$8=""),"",Y56-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE56="",'多次统计数据'!$B$8=""),"",AE56-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA56" s="10">
@@ -4565,6 +4793,10 @@
         <v/>
       </c>
       <c r="AD56" s="2" t="n"/>
+      <c r="AE56" s="7">
+        <f>IF(OR(X56="",C56="",C56&lt;=0),"",X56/C56)</f>
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n"/>
@@ -4617,7 +4849,7 @@
         <v/>
       </c>
       <c r="Z57" s="7">
-        <f>IF(OR(Y57="",'多次统计数据'!$B$8=""),"",Y57-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE57="",'多次统计数据'!$B$8=""),"",AE57-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA57" s="10">
@@ -4633,6 +4865,10 @@
         <v/>
       </c>
       <c r="AD57" s="2" t="n"/>
+      <c r="AE57" s="7">
+        <f>IF(OR(X57="",C57="",C57&lt;=0),"",X57/C57)</f>
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n"/>
@@ -4685,7 +4921,7 @@
         <v/>
       </c>
       <c r="Z58" s="7">
-        <f>IF(OR(Y58="",'多次统计数据'!$B$8=""),"",Y58-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE58="",'多次统计数据'!$B$8=""),"",AE58-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA58" s="10">
@@ -4701,6 +4937,10 @@
         <v/>
       </c>
       <c r="AD58" s="2" t="n"/>
+      <c r="AE58" s="7">
+        <f>IF(OR(X58="",C58="",C58&lt;=0),"",X58/C58)</f>
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n"/>
@@ -4753,7 +4993,7 @@
         <v/>
       </c>
       <c r="Z59" s="7">
-        <f>IF(OR(Y59="",'多次统计数据'!$B$8=""),"",Y59-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE59="",'多次统计数据'!$B$8=""),"",AE59-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA59" s="10">
@@ -4769,6 +5009,10 @@
         <v/>
       </c>
       <c r="AD59" s="2" t="n"/>
+      <c r="AE59" s="7">
+        <f>IF(OR(X59="",C59="",C59&lt;=0),"",X59/C59)</f>
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n"/>
@@ -4821,7 +5065,7 @@
         <v/>
       </c>
       <c r="Z60" s="7">
-        <f>IF(OR(Y60="",'多次统计数据'!$B$8=""),"",Y60-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE60="",'多次统计数据'!$B$8=""),"",AE60-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA60" s="10">
@@ -4837,6 +5081,10 @@
         <v/>
       </c>
       <c r="AD60" s="2" t="n"/>
+      <c r="AE60" s="7">
+        <f>IF(OR(X60="",C60="",C60&lt;=0),"",X60/C60)</f>
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n"/>
@@ -4889,7 +5137,7 @@
         <v/>
       </c>
       <c r="Z61" s="7">
-        <f>IF(OR(Y61="",'多次统计数据'!$B$8=""),"",Y61-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE61="",'多次统计数据'!$B$8=""),"",AE61-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA61" s="10">
@@ -4905,6 +5153,10 @@
         <v/>
       </c>
       <c r="AD61" s="2" t="n"/>
+      <c r="AE61" s="7">
+        <f>IF(OR(X61="",C61="",C61&lt;=0),"",X61/C61)</f>
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n"/>
@@ -4957,7 +5209,7 @@
         <v/>
       </c>
       <c r="Z62" s="7">
-        <f>IF(OR(Y62="",'多次统计数据'!$B$8=""),"",Y62-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE62="",'多次统计数据'!$B$8=""),"",AE62-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA62" s="10">
@@ -4973,6 +5225,10 @@
         <v/>
       </c>
       <c r="AD62" s="2" t="n"/>
+      <c r="AE62" s="7">
+        <f>IF(OR(X62="",C62="",C62&lt;=0),"",X62/C62)</f>
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n"/>
@@ -5025,7 +5281,7 @@
         <v/>
       </c>
       <c r="Z63" s="7">
-        <f>IF(OR(Y63="",'多次统计数据'!$B$8=""),"",Y63-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE63="",'多次统计数据'!$B$8=""),"",AE63-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA63" s="10">
@@ -5041,6 +5297,10 @@
         <v/>
       </c>
       <c r="AD63" s="2" t="n"/>
+      <c r="AE63" s="7">
+        <f>IF(OR(X63="",C63="",C63&lt;=0),"",X63/C63)</f>
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n"/>
@@ -5093,7 +5353,7 @@
         <v/>
       </c>
       <c r="Z64" s="7">
-        <f>IF(OR(Y64="",'多次统计数据'!$B$8=""),"",Y64-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE64="",'多次统计数据'!$B$8=""),"",AE64-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA64" s="10">
@@ -5109,6 +5369,10 @@
         <v/>
       </c>
       <c r="AD64" s="2" t="n"/>
+      <c r="AE64" s="7">
+        <f>IF(OR(X64="",C64="",C64&lt;=0),"",X64/C64)</f>
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n"/>
@@ -5161,7 +5425,7 @@
         <v/>
       </c>
       <c r="Z65" s="7">
-        <f>IF(OR(Y65="",'多次统计数据'!$B$8=""),"",Y65-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE65="",'多次统计数据'!$B$8=""),"",AE65-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA65" s="10">
@@ -5177,6 +5441,10 @@
         <v/>
       </c>
       <c r="AD65" s="2" t="n"/>
+      <c r="AE65" s="7">
+        <f>IF(OR(X65="",C65="",C65&lt;=0),"",X65/C65)</f>
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n"/>
@@ -5229,7 +5497,7 @@
         <v/>
       </c>
       <c r="Z66" s="7">
-        <f>IF(OR(Y66="",'多次统计数据'!$B$8=""),"",Y66-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE66="",'多次统计数据'!$B$8=""),"",AE66-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA66" s="10">
@@ -5245,6 +5513,10 @@
         <v/>
       </c>
       <c r="AD66" s="2" t="n"/>
+      <c r="AE66" s="7">
+        <f>IF(OR(X66="",C66="",C66&lt;=0),"",X66/C66)</f>
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n"/>
@@ -5297,7 +5569,7 @@
         <v/>
       </c>
       <c r="Z67" s="7">
-        <f>IF(OR(Y67="",'多次统计数据'!$B$8=""),"",Y67-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE67="",'多次统计数据'!$B$8=""),"",AE67-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA67" s="10">
@@ -5313,6 +5585,10 @@
         <v/>
       </c>
       <c r="AD67" s="2" t="n"/>
+      <c r="AE67" s="7">
+        <f>IF(OR(X67="",C67="",C67&lt;=0),"",X67/C67)</f>
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n"/>
@@ -5365,7 +5641,7 @@
         <v/>
       </c>
       <c r="Z68" s="7">
-        <f>IF(OR(Y68="",'多次统计数据'!$B$8=""),"",Y68-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE68="",'多次统计数据'!$B$8=""),"",AE68-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA68" s="10">
@@ -5381,6 +5657,10 @@
         <v/>
       </c>
       <c r="AD68" s="2" t="n"/>
+      <c r="AE68" s="7">
+        <f>IF(OR(X68="",C68="",C68&lt;=0),"",X68/C68)</f>
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n"/>
@@ -5433,7 +5713,7 @@
         <v/>
       </c>
       <c r="Z69" s="7">
-        <f>IF(OR(Y69="",'多次统计数据'!$B$8=""),"",Y69-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE69="",'多次统计数据'!$B$8=""),"",AE69-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA69" s="10">
@@ -5449,6 +5729,10 @@
         <v/>
       </c>
       <c r="AD69" s="2" t="n"/>
+      <c r="AE69" s="7">
+        <f>IF(OR(X69="",C69="",C69&lt;=0),"",X69/C69)</f>
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n"/>
@@ -5501,7 +5785,7 @@
         <v/>
       </c>
       <c r="Z70" s="7">
-        <f>IF(OR(Y70="",'多次统计数据'!$B$8=""),"",Y70-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE70="",'多次统计数据'!$B$8=""),"",AE70-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA70" s="10">
@@ -5517,6 +5801,10 @@
         <v/>
       </c>
       <c r="AD70" s="2" t="n"/>
+      <c r="AE70" s="7">
+        <f>IF(OR(X70="",C70="",C70&lt;=0),"",X70/C70)</f>
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n"/>
@@ -5569,7 +5857,7 @@
         <v/>
       </c>
       <c r="Z71" s="7">
-        <f>IF(OR(Y71="",'多次统计数据'!$B$8=""),"",Y71-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE71="",'多次统计数据'!$B$8=""),"",AE71-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA71" s="10">
@@ -5585,6 +5873,10 @@
         <v/>
       </c>
       <c r="AD71" s="2" t="n"/>
+      <c r="AE71" s="7">
+        <f>IF(OR(X71="",C71="",C71&lt;=0),"",X71/C71)</f>
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n"/>
@@ -5637,7 +5929,7 @@
         <v/>
       </c>
       <c r="Z72" s="7">
-        <f>IF(OR(Y72="",'多次统计数据'!$B$8=""),"",Y72-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE72="",'多次统计数据'!$B$8=""),"",AE72-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA72" s="10">
@@ -5653,6 +5945,10 @@
         <v/>
       </c>
       <c r="AD72" s="2" t="n"/>
+      <c r="AE72" s="7">
+        <f>IF(OR(X72="",C72="",C72&lt;=0),"",X72/C72)</f>
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n"/>
@@ -5705,7 +6001,7 @@
         <v/>
       </c>
       <c r="Z73" s="7">
-        <f>IF(OR(Y73="",'多次统计数据'!$B$8=""),"",Y73-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE73="",'多次统计数据'!$B$8=""),"",AE73-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA73" s="10">
@@ -5721,6 +6017,10 @@
         <v/>
       </c>
       <c r="AD73" s="2" t="n"/>
+      <c r="AE73" s="7">
+        <f>IF(OR(X73="",C73="",C73&lt;=0),"",X73/C73)</f>
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n"/>
@@ -5773,7 +6073,7 @@
         <v/>
       </c>
       <c r="Z74" s="7">
-        <f>IF(OR(Y74="",'多次统计数据'!$B$8=""),"",Y74-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE74="",'多次统计数据'!$B$8=""),"",AE74-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA74" s="10">
@@ -5789,6 +6089,10 @@
         <v/>
       </c>
       <c r="AD74" s="2" t="n"/>
+      <c r="AE74" s="7">
+        <f>IF(OR(X74="",C74="",C74&lt;=0),"",X74/C74)</f>
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n"/>
@@ -5841,7 +6145,7 @@
         <v/>
       </c>
       <c r="Z75" s="7">
-        <f>IF(OR(Y75="",'多次统计数据'!$B$8=""),"",Y75-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE75="",'多次统计数据'!$B$8=""),"",AE75-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA75" s="10">
@@ -5857,6 +6161,10 @@
         <v/>
       </c>
       <c r="AD75" s="2" t="n"/>
+      <c r="AE75" s="7">
+        <f>IF(OR(X75="",C75="",C75&lt;=0),"",X75/C75)</f>
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n"/>
@@ -5909,7 +6217,7 @@
         <v/>
       </c>
       <c r="Z76" s="7">
-        <f>IF(OR(Y76="",'多次统计数据'!$B$8=""),"",Y76-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE76="",'多次统计数据'!$B$8=""),"",AE76-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA76" s="10">
@@ -5925,6 +6233,10 @@
         <v/>
       </c>
       <c r="AD76" s="2" t="n"/>
+      <c r="AE76" s="7">
+        <f>IF(OR(X76="",C76="",C76&lt;=0),"",X76/C76)</f>
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n"/>
@@ -5977,7 +6289,7 @@
         <v/>
       </c>
       <c r="Z77" s="7">
-        <f>IF(OR(Y77="",'多次统计数据'!$B$8=""),"",Y77-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE77="",'多次统计数据'!$B$8=""),"",AE77-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA77" s="10">
@@ -5993,6 +6305,10 @@
         <v/>
       </c>
       <c r="AD77" s="2" t="n"/>
+      <c r="AE77" s="7">
+        <f>IF(OR(X77="",C77="",C77&lt;=0),"",X77/C77)</f>
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n"/>
@@ -6045,7 +6361,7 @@
         <v/>
       </c>
       <c r="Z78" s="7">
-        <f>IF(OR(Y78="",'多次统计数据'!$B$8=""),"",Y78-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE78="",'多次统计数据'!$B$8=""),"",AE78-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA78" s="10">
@@ -6061,6 +6377,10 @@
         <v/>
       </c>
       <c r="AD78" s="2" t="n"/>
+      <c r="AE78" s="7">
+        <f>IF(OR(X78="",C78="",C78&lt;=0),"",X78/C78)</f>
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n"/>
@@ -6113,7 +6433,7 @@
         <v/>
       </c>
       <c r="Z79" s="7">
-        <f>IF(OR(Y79="",'多次统计数据'!$B$8=""),"",Y79-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE79="",'多次统计数据'!$B$8=""),"",AE79-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA79" s="10">
@@ -6129,6 +6449,10 @@
         <v/>
       </c>
       <c r="AD79" s="2" t="n"/>
+      <c r="AE79" s="7">
+        <f>IF(OR(X79="",C79="",C79&lt;=0),"",X79/C79)</f>
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n"/>
@@ -6181,7 +6505,7 @@
         <v/>
       </c>
       <c r="Z80" s="7">
-        <f>IF(OR(Y80="",'多次统计数据'!$B$8=""),"",Y80-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE80="",'多次统计数据'!$B$8=""),"",AE80-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA80" s="10">
@@ -6197,6 +6521,10 @@
         <v/>
       </c>
       <c r="AD80" s="2" t="n"/>
+      <c r="AE80" s="7">
+        <f>IF(OR(X80="",C80="",C80&lt;=0),"",X80/C80)</f>
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n"/>
@@ -6249,7 +6577,7 @@
         <v/>
       </c>
       <c r="Z81" s="7">
-        <f>IF(OR(Y81="",'多次统计数据'!$B$8=""),"",Y81-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE81="",'多次统计数据'!$B$8=""),"",AE81-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA81" s="10">
@@ -6265,6 +6593,10 @@
         <v/>
       </c>
       <c r="AD81" s="2" t="n"/>
+      <c r="AE81" s="7">
+        <f>IF(OR(X81="",C81="",C81&lt;=0),"",X81/C81)</f>
+        <v/>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n"/>
@@ -6317,7 +6649,7 @@
         <v/>
       </c>
       <c r="Z82" s="7">
-        <f>IF(OR(Y82="",'多次统计数据'!$B$8=""),"",Y82-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE82="",'多次统计数据'!$B$8=""),"",AE82-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA82" s="10">
@@ -6333,6 +6665,10 @@
         <v/>
       </c>
       <c r="AD82" s="2" t="n"/>
+      <c r="AE82" s="7">
+        <f>IF(OR(X82="",C82="",C82&lt;=0),"",X82/C82)</f>
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n"/>
@@ -6385,7 +6721,7 @@
         <v/>
       </c>
       <c r="Z83" s="7">
-        <f>IF(OR(Y83="",'多次统计数据'!$B$8=""),"",Y83-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE83="",'多次统计数据'!$B$8=""),"",AE83-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA83" s="10">
@@ -6401,6 +6737,10 @@
         <v/>
       </c>
       <c r="AD83" s="2" t="n"/>
+      <c r="AE83" s="7">
+        <f>IF(OR(X83="",C83="",C83&lt;=0),"",X83/C83)</f>
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n"/>
@@ -6453,7 +6793,7 @@
         <v/>
       </c>
       <c r="Z84" s="7">
-        <f>IF(OR(Y84="",'多次统计数据'!$B$8=""),"",Y84-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE84="",'多次统计数据'!$B$8=""),"",AE84-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA84" s="10">
@@ -6469,6 +6809,10 @@
         <v/>
       </c>
       <c r="AD84" s="2" t="n"/>
+      <c r="AE84" s="7">
+        <f>IF(OR(X84="",C84="",C84&lt;=0),"",X84/C84)</f>
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n"/>
@@ -6521,7 +6865,7 @@
         <v/>
       </c>
       <c r="Z85" s="7">
-        <f>IF(OR(Y85="",'多次统计数据'!$B$8=""),"",Y85-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE85="",'多次统计数据'!$B$8=""),"",AE85-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA85" s="10">
@@ -6537,6 +6881,10 @@
         <v/>
       </c>
       <c r="AD85" s="2" t="n"/>
+      <c r="AE85" s="7">
+        <f>IF(OR(X85="",C85="",C85&lt;=0),"",X85/C85)</f>
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n"/>
@@ -6589,7 +6937,7 @@
         <v/>
       </c>
       <c r="Z86" s="7">
-        <f>IF(OR(Y86="",'多次统计数据'!$B$8=""),"",Y86-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE86="",'多次统计数据'!$B$8=""),"",AE86-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA86" s="10">
@@ -6605,6 +6953,10 @@
         <v/>
       </c>
       <c r="AD86" s="2" t="n"/>
+      <c r="AE86" s="7">
+        <f>IF(OR(X86="",C86="",C86&lt;=0),"",X86/C86)</f>
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n"/>
@@ -6657,7 +7009,7 @@
         <v/>
       </c>
       <c r="Z87" s="7">
-        <f>IF(OR(Y87="",'多次统计数据'!$B$8=""),"",Y87-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE87="",'多次统计数据'!$B$8=""),"",AE87-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA87" s="10">
@@ -6673,6 +7025,10 @@
         <v/>
       </c>
       <c r="AD87" s="2" t="n"/>
+      <c r="AE87" s="7">
+        <f>IF(OR(X87="",C87="",C87&lt;=0),"",X87/C87)</f>
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n"/>
@@ -6725,7 +7081,7 @@
         <v/>
       </c>
       <c r="Z88" s="7">
-        <f>IF(OR(Y88="",'多次统计数据'!$B$8=""),"",Y88-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE88="",'多次统计数据'!$B$8=""),"",AE88-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA88" s="10">
@@ -6741,6 +7097,10 @@
         <v/>
       </c>
       <c r="AD88" s="2" t="n"/>
+      <c r="AE88" s="7">
+        <f>IF(OR(X88="",C88="",C88&lt;=0),"",X88/C88)</f>
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n"/>
@@ -6793,7 +7153,7 @@
         <v/>
       </c>
       <c r="Z89" s="7">
-        <f>IF(OR(Y89="",'多次统计数据'!$B$8=""),"",Y89-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE89="",'多次统计数据'!$B$8=""),"",AE89-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA89" s="10">
@@ -6809,6 +7169,10 @@
         <v/>
       </c>
       <c r="AD89" s="2" t="n"/>
+      <c r="AE89" s="7">
+        <f>IF(OR(X89="",C89="",C89&lt;=0),"",X89/C89)</f>
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n"/>
@@ -6861,7 +7225,7 @@
         <v/>
       </c>
       <c r="Z90" s="7">
-        <f>IF(OR(Y90="",'多次统计数据'!$B$8=""),"",Y90-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE90="",'多次统计数据'!$B$8=""),"",AE90-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA90" s="10">
@@ -6877,6 +7241,10 @@
         <v/>
       </c>
       <c r="AD90" s="2" t="n"/>
+      <c r="AE90" s="7">
+        <f>IF(OR(X90="",C90="",C90&lt;=0),"",X90/C90)</f>
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n"/>
@@ -6929,7 +7297,7 @@
         <v/>
       </c>
       <c r="Z91" s="7">
-        <f>IF(OR(Y91="",'多次统计数据'!$B$8=""),"",Y91-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE91="",'多次统计数据'!$B$8=""),"",AE91-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA91" s="10">
@@ -6945,6 +7313,10 @@
         <v/>
       </c>
       <c r="AD91" s="2" t="n"/>
+      <c r="AE91" s="7">
+        <f>IF(OR(X91="",C91="",C91&lt;=0),"",X91/C91)</f>
+        <v/>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n"/>
@@ -6997,7 +7369,7 @@
         <v/>
       </c>
       <c r="Z92" s="7">
-        <f>IF(OR(Y92="",'多次统计数据'!$B$8=""),"",Y92-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE92="",'多次统计数据'!$B$8=""),"",AE92-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA92" s="10">
@@ -7013,6 +7385,10 @@
         <v/>
       </c>
       <c r="AD92" s="2" t="n"/>
+      <c r="AE92" s="7">
+        <f>IF(OR(X92="",C92="",C92&lt;=0),"",X92/C92)</f>
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n"/>
@@ -7065,7 +7441,7 @@
         <v/>
       </c>
       <c r="Z93" s="7">
-        <f>IF(OR(Y93="",'多次统计数据'!$B$8=""),"",Y93-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE93="",'多次统计数据'!$B$8=""),"",AE93-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA93" s="10">
@@ -7081,6 +7457,10 @@
         <v/>
       </c>
       <c r="AD93" s="2" t="n"/>
+      <c r="AE93" s="7">
+        <f>IF(OR(X93="",C93="",C93&lt;=0),"",X93/C93)</f>
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n"/>
@@ -7133,7 +7513,7 @@
         <v/>
       </c>
       <c r="Z94" s="7">
-        <f>IF(OR(Y94="",'多次统计数据'!$B$8=""),"",Y94-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE94="",'多次统计数据'!$B$8=""),"",AE94-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA94" s="10">
@@ -7149,6 +7529,10 @@
         <v/>
       </c>
       <c r="AD94" s="2" t="n"/>
+      <c r="AE94" s="7">
+        <f>IF(OR(X94="",C94="",C94&lt;=0),"",X94/C94)</f>
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n"/>
@@ -7201,7 +7585,7 @@
         <v/>
       </c>
       <c r="Z95" s="7">
-        <f>IF(OR(Y95="",'多次统计数据'!$B$8=""),"",Y95-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE95="",'多次统计数据'!$B$8=""),"",AE95-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA95" s="10">
@@ -7217,6 +7601,10 @@
         <v/>
       </c>
       <c r="AD95" s="2" t="n"/>
+      <c r="AE95" s="7">
+        <f>IF(OR(X95="",C95="",C95&lt;=0),"",X95/C95)</f>
+        <v/>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n"/>
@@ -7269,7 +7657,7 @@
         <v/>
       </c>
       <c r="Z96" s="7">
-        <f>IF(OR(Y96="",'多次统计数据'!$B$8=""),"",Y96-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE96="",'多次统计数据'!$B$8=""),"",AE96-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA96" s="10">
@@ -7285,6 +7673,10 @@
         <v/>
       </c>
       <c r="AD96" s="2" t="n"/>
+      <c r="AE96" s="7">
+        <f>IF(OR(X96="",C96="",C96&lt;=0),"",X96/C96)</f>
+        <v/>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n"/>
@@ -7337,7 +7729,7 @@
         <v/>
       </c>
       <c r="Z97" s="7">
-        <f>IF(OR(Y97="",'多次统计数据'!$B$8=""),"",Y97-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE97="",'多次统计数据'!$B$8=""),"",AE97-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA97" s="10">
@@ -7353,6 +7745,10 @@
         <v/>
       </c>
       <c r="AD97" s="2" t="n"/>
+      <c r="AE97" s="7">
+        <f>IF(OR(X97="",C97="",C97&lt;=0),"",X97/C97)</f>
+        <v/>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n"/>
@@ -7405,7 +7801,7 @@
         <v/>
       </c>
       <c r="Z98" s="7">
-        <f>IF(OR(Y98="",'多次统计数据'!$B$8=""),"",Y98-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE98="",'多次统计数据'!$B$8=""),"",AE98-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA98" s="10">
@@ -7421,6 +7817,10 @@
         <v/>
       </c>
       <c r="AD98" s="2" t="n"/>
+      <c r="AE98" s="7">
+        <f>IF(OR(X98="",C98="",C98&lt;=0),"",X98/C98)</f>
+        <v/>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n"/>
@@ -7473,7 +7873,7 @@
         <v/>
       </c>
       <c r="Z99" s="7">
-        <f>IF(OR(Y99="",'多次统计数据'!$B$8=""),"",Y99-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE99="",'多次统计数据'!$B$8=""),"",AE99-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA99" s="10">
@@ -7489,6 +7889,10 @@
         <v/>
       </c>
       <c r="AD99" s="2" t="n"/>
+      <c r="AE99" s="7">
+        <f>IF(OR(X99="",C99="",C99&lt;=0),"",X99/C99)</f>
+        <v/>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n"/>
@@ -7541,7 +7945,7 @@
         <v/>
       </c>
       <c r="Z100" s="7">
-        <f>IF(OR(Y100="",'多次统计数据'!$B$8=""),"",Y100-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE100="",'多次统计数据'!$B$8=""),"",AE100-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA100" s="10">
@@ -7557,6 +7961,10 @@
         <v/>
       </c>
       <c r="AD100" s="2" t="n"/>
+      <c r="AE100" s="7">
+        <f>IF(OR(X100="",C100="",C100&lt;=0),"",X100/C100)</f>
+        <v/>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n"/>
@@ -7609,7 +8017,7 @@
         <v/>
       </c>
       <c r="Z101" s="7">
-        <f>IF(OR(Y101="",'多次统计数据'!$B$8=""),"",Y101-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE101="",'多次统计数据'!$B$8=""),"",AE101-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA101" s="10">
@@ -7625,6 +8033,10 @@
         <v/>
       </c>
       <c r="AD101" s="2" t="n"/>
+      <c r="AE101" s="7">
+        <f>IF(OR(X101="",C101="",C101&lt;=0),"",X101/C101)</f>
+        <v/>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n"/>
@@ -7677,7 +8089,7 @@
         <v/>
       </c>
       <c r="Z102" s="7">
-        <f>IF(OR(Y102="",'多次统计数据'!$B$8=""),"",Y102-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE102="",'多次统计数据'!$B$8=""),"",AE102-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA102" s="10">
@@ -7693,6 +8105,10 @@
         <v/>
       </c>
       <c r="AD102" s="2" t="n"/>
+      <c r="AE102" s="7">
+        <f>IF(OR(X102="",C102="",C102&lt;=0),"",X102/C102)</f>
+        <v/>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n"/>
@@ -7745,7 +8161,7 @@
         <v/>
       </c>
       <c r="Z103" s="7">
-        <f>IF(OR(Y103="",'多次统计数据'!$B$8=""),"",Y103-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE103="",'多次统计数据'!$B$8=""),"",AE103-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA103" s="10">
@@ -7761,6 +8177,10 @@
         <v/>
       </c>
       <c r="AD103" s="2" t="n"/>
+      <c r="AE103" s="7">
+        <f>IF(OR(X103="",C103="",C103&lt;=0),"",X103/C103)</f>
+        <v/>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n"/>
@@ -7813,7 +8233,7 @@
         <v/>
       </c>
       <c r="Z104" s="7">
-        <f>IF(OR(Y104="",'多次统计数据'!$B$8=""),"",Y104-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE104="",'多次统计数据'!$B$8=""),"",AE104-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA104" s="10">
@@ -7829,6 +8249,10 @@
         <v/>
       </c>
       <c r="AD104" s="2" t="n"/>
+      <c r="AE104" s="7">
+        <f>IF(OR(X104="",C104="",C104&lt;=0),"",X104/C104)</f>
+        <v/>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n"/>
@@ -7881,7 +8305,7 @@
         <v/>
       </c>
       <c r="Z105" s="7">
-        <f>IF(OR(Y105="",'多次统计数据'!$B$8=""),"",Y105-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE105="",'多次统计数据'!$B$8=""),"",AE105-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA105" s="10">
@@ -7897,6 +8321,10 @@
         <v/>
       </c>
       <c r="AD105" s="2" t="n"/>
+      <c r="AE105" s="7">
+        <f>IF(OR(X105="",C105="",C105&lt;=0),"",X105/C105)</f>
+        <v/>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n"/>
@@ -7949,7 +8377,7 @@
         <v/>
       </c>
       <c r="Z106" s="7">
-        <f>IF(OR(Y106="",'多次统计数据'!$B$8=""),"",Y106-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE106="",'多次统计数据'!$B$8=""),"",AE106-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA106" s="10">
@@ -7965,6 +8393,10 @@
         <v/>
       </c>
       <c r="AD106" s="2" t="n"/>
+      <c r="AE106" s="7">
+        <f>IF(OR(X106="",C106="",C106&lt;=0),"",X106/C106)</f>
+        <v/>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n"/>
@@ -8017,7 +8449,7 @@
         <v/>
       </c>
       <c r="Z107" s="7">
-        <f>IF(OR(Y107="",'多次统计数据'!$B$8=""),"",Y107-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE107="",'多次统计数据'!$B$8=""),"",AE107-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA107" s="10">
@@ -8033,6 +8465,10 @@
         <v/>
       </c>
       <c r="AD107" s="2" t="n"/>
+      <c r="AE107" s="7">
+        <f>IF(OR(X107="",C107="",C107&lt;=0),"",X107/C107)</f>
+        <v/>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n"/>
@@ -8085,7 +8521,7 @@
         <v/>
       </c>
       <c r="Z108" s="7">
-        <f>IF(OR(Y108="",'多次统计数据'!$B$8=""),"",Y108-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE108="",'多次统计数据'!$B$8=""),"",AE108-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA108" s="10">
@@ -8101,6 +8537,10 @@
         <v/>
       </c>
       <c r="AD108" s="2" t="n"/>
+      <c r="AE108" s="7">
+        <f>IF(OR(X108="",C108="",C108&lt;=0),"",X108/C108)</f>
+        <v/>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n"/>
@@ -8153,7 +8593,7 @@
         <v/>
       </c>
       <c r="Z109" s="7">
-        <f>IF(OR(Y109="",'多次统计数据'!$B$8=""),"",Y109-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE109="",'多次统计数据'!$B$8=""),"",AE109-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA109" s="10">
@@ -8169,6 +8609,10 @@
         <v/>
       </c>
       <c r="AD109" s="2" t="n"/>
+      <c r="AE109" s="7">
+        <f>IF(OR(X109="",C109="",C109&lt;=0),"",X109/C109)</f>
+        <v/>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n"/>
@@ -8221,7 +8665,7 @@
         <v/>
       </c>
       <c r="Z110" s="7">
-        <f>IF(OR(Y110="",'多次统计数据'!$B$8=""),"",Y110-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE110="",'多次统计数据'!$B$8=""),"",AE110-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA110" s="10">
@@ -8237,6 +8681,10 @@
         <v/>
       </c>
       <c r="AD110" s="2" t="n"/>
+      <c r="AE110" s="7">
+        <f>IF(OR(X110="",C110="",C110&lt;=0),"",X110/C110)</f>
+        <v/>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n"/>
@@ -8289,7 +8737,7 @@
         <v/>
       </c>
       <c r="Z111" s="7">
-        <f>IF(OR(Y111="",'多次统计数据'!$B$8=""),"",Y111-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE111="",'多次统计数据'!$B$8=""),"",AE111-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA111" s="10">
@@ -8305,6 +8753,10 @@
         <v/>
       </c>
       <c r="AD111" s="2" t="n"/>
+      <c r="AE111" s="7">
+        <f>IF(OR(X111="",C111="",C111&lt;=0),"",X111/C111)</f>
+        <v/>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n"/>
@@ -8357,7 +8809,7 @@
         <v/>
       </c>
       <c r="Z112" s="7">
-        <f>IF(OR(Y112="",'多次统计数据'!$B$8=""),"",Y112-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE112="",'多次统计数据'!$B$8=""),"",AE112-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA112" s="10">
@@ -8373,6 +8825,10 @@
         <v/>
       </c>
       <c r="AD112" s="2" t="n"/>
+      <c r="AE112" s="7">
+        <f>IF(OR(X112="",C112="",C112&lt;=0),"",X112/C112)</f>
+        <v/>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n"/>
@@ -8425,7 +8881,7 @@
         <v/>
       </c>
       <c r="Z113" s="7">
-        <f>IF(OR(Y113="",'多次统计数据'!$B$8=""),"",Y113-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE113="",'多次统计数据'!$B$8=""),"",AE113-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA113" s="10">
@@ -8441,6 +8897,10 @@
         <v/>
       </c>
       <c r="AD113" s="2" t="n"/>
+      <c r="AE113" s="7">
+        <f>IF(OR(X113="",C113="",C113&lt;=0),"",X113/C113)</f>
+        <v/>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n"/>
@@ -8493,7 +8953,7 @@
         <v/>
       </c>
       <c r="Z114" s="7">
-        <f>IF(OR(Y114="",'多次统计数据'!$B$8=""),"",Y114-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE114="",'多次统计数据'!$B$8=""),"",AE114-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA114" s="10">
@@ -8509,6 +8969,10 @@
         <v/>
       </c>
       <c r="AD114" s="2" t="n"/>
+      <c r="AE114" s="7">
+        <f>IF(OR(X114="",C114="",C114&lt;=0),"",X114/C114)</f>
+        <v/>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n"/>
@@ -8561,7 +9025,7 @@
         <v/>
       </c>
       <c r="Z115" s="7">
-        <f>IF(OR(Y115="",'多次统计数据'!$B$8=""),"",Y115-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE115="",'多次统计数据'!$B$8=""),"",AE115-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA115" s="10">
@@ -8577,6 +9041,10 @@
         <v/>
       </c>
       <c r="AD115" s="2" t="n"/>
+      <c r="AE115" s="7">
+        <f>IF(OR(X115="",C115="",C115&lt;=0),"",X115/C115)</f>
+        <v/>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n"/>
@@ -8629,7 +9097,7 @@
         <v/>
       </c>
       <c r="Z116" s="7">
-        <f>IF(OR(Y116="",'多次统计数据'!$B$8=""),"",Y116-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE116="",'多次统计数据'!$B$8=""),"",AE116-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA116" s="10">
@@ -8645,6 +9113,10 @@
         <v/>
       </c>
       <c r="AD116" s="2" t="n"/>
+      <c r="AE116" s="7">
+        <f>IF(OR(X116="",C116="",C116&lt;=0),"",X116/C116)</f>
+        <v/>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n"/>
@@ -8697,7 +9169,7 @@
         <v/>
       </c>
       <c r="Z117" s="7">
-        <f>IF(OR(Y117="",'多次统计数据'!$B$8=""),"",Y117-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE117="",'多次统计数据'!$B$8=""),"",AE117-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA117" s="10">
@@ -8713,6 +9185,10 @@
         <v/>
       </c>
       <c r="AD117" s="2" t="n"/>
+      <c r="AE117" s="7">
+        <f>IF(OR(X117="",C117="",C117&lt;=0),"",X117/C117)</f>
+        <v/>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n"/>
@@ -8765,7 +9241,7 @@
         <v/>
       </c>
       <c r="Z118" s="7">
-        <f>IF(OR(Y118="",'多次统计数据'!$B$8=""),"",Y118-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE118="",'多次统计数据'!$B$8=""),"",AE118-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA118" s="10">
@@ -8781,6 +9257,10 @@
         <v/>
       </c>
       <c r="AD118" s="2" t="n"/>
+      <c r="AE118" s="7">
+        <f>IF(OR(X118="",C118="",C118&lt;=0),"",X118/C118)</f>
+        <v/>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n"/>
@@ -8833,7 +9313,7 @@
         <v/>
       </c>
       <c r="Z119" s="7">
-        <f>IF(OR(Y119="",'多次统计数据'!$B$8=""),"",Y119-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE119="",'多次统计数据'!$B$8=""),"",AE119-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA119" s="10">
@@ -8849,6 +9329,10 @@
         <v/>
       </c>
       <c r="AD119" s="2" t="n"/>
+      <c r="AE119" s="7">
+        <f>IF(OR(X119="",C119="",C119&lt;=0),"",X119/C119)</f>
+        <v/>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n"/>
@@ -8901,7 +9385,7 @@
         <v/>
       </c>
       <c r="Z120" s="7">
-        <f>IF(OR(Y120="",'多次统计数据'!$B$8=""),"",Y120-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE120="",'多次统计数据'!$B$8=""),"",AE120-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA120" s="10">
@@ -8917,6 +9401,10 @@
         <v/>
       </c>
       <c r="AD120" s="2" t="n"/>
+      <c r="AE120" s="7">
+        <f>IF(OR(X120="",C120="",C120&lt;=0),"",X120/C120)</f>
+        <v/>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n"/>
@@ -8969,7 +9457,7 @@
         <v/>
       </c>
       <c r="Z121" s="7">
-        <f>IF(OR(Y121="",'多次统计数据'!$B$8=""),"",Y121-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE121="",'多次统计数据'!$B$8=""),"",AE121-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA121" s="10">
@@ -8985,6 +9473,10 @@
         <v/>
       </c>
       <c r="AD121" s="2" t="n"/>
+      <c r="AE121" s="7">
+        <f>IF(OR(X121="",C121="",C121&lt;=0),"",X121/C121)</f>
+        <v/>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n"/>
@@ -9037,7 +9529,7 @@
         <v/>
       </c>
       <c r="Z122" s="7">
-        <f>IF(OR(Y122="",'多次统计数据'!$B$8=""),"",Y122-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE122="",'多次统计数据'!$B$8=""),"",AE122-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA122" s="10">
@@ -9053,6 +9545,10 @@
         <v/>
       </c>
       <c r="AD122" s="2" t="n"/>
+      <c r="AE122" s="7">
+        <f>IF(OR(X122="",C122="",C122&lt;=0),"",X122/C122)</f>
+        <v/>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n"/>
@@ -9105,7 +9601,7 @@
         <v/>
       </c>
       <c r="Z123" s="7">
-        <f>IF(OR(Y123="",'多次统计数据'!$B$8=""),"",Y123-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE123="",'多次统计数据'!$B$8=""),"",AE123-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA123" s="10">
@@ -9121,6 +9617,10 @@
         <v/>
       </c>
       <c r="AD123" s="2" t="n"/>
+      <c r="AE123" s="7">
+        <f>IF(OR(X123="",C123="",C123&lt;=0),"",X123/C123)</f>
+        <v/>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n"/>
@@ -9173,7 +9673,7 @@
         <v/>
       </c>
       <c r="Z124" s="7">
-        <f>IF(OR(Y124="",'多次统计数据'!$B$8=""),"",Y124-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE124="",'多次统计数据'!$B$8=""),"",AE124-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA124" s="10">
@@ -9189,6 +9689,10 @@
         <v/>
       </c>
       <c r="AD124" s="2" t="n"/>
+      <c r="AE124" s="7">
+        <f>IF(OR(X124="",C124="",C124&lt;=0),"",X124/C124)</f>
+        <v/>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n"/>
@@ -9241,7 +9745,7 @@
         <v/>
       </c>
       <c r="Z125" s="7">
-        <f>IF(OR(Y125="",'多次统计数据'!$B$8=""),"",Y125-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE125="",'多次统计数据'!$B$8=""),"",AE125-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA125" s="10">
@@ -9257,6 +9761,10 @@
         <v/>
       </c>
       <c r="AD125" s="2" t="n"/>
+      <c r="AE125" s="7">
+        <f>IF(OR(X125="",C125="",C125&lt;=0),"",X125/C125)</f>
+        <v/>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n"/>
@@ -9309,7 +9817,7 @@
         <v/>
       </c>
       <c r="Z126" s="7">
-        <f>IF(OR(Y126="",'多次统计数据'!$B$8=""),"",Y126-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE126="",'多次统计数据'!$B$8=""),"",AE126-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA126" s="10">
@@ -9325,6 +9833,10 @@
         <v/>
       </c>
       <c r="AD126" s="2" t="n"/>
+      <c r="AE126" s="7">
+        <f>IF(OR(X126="",C126="",C126&lt;=0),"",X126/C126)</f>
+        <v/>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n"/>
@@ -9377,7 +9889,7 @@
         <v/>
       </c>
       <c r="Z127" s="7">
-        <f>IF(OR(Y127="",'多次统计数据'!$B$8=""),"",Y127-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE127="",'多次统计数据'!$B$8=""),"",AE127-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA127" s="10">
@@ -9393,6 +9905,10 @@
         <v/>
       </c>
       <c r="AD127" s="2" t="n"/>
+      <c r="AE127" s="7">
+        <f>IF(OR(X127="",C127="",C127&lt;=0),"",X127/C127)</f>
+        <v/>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n"/>
@@ -9445,7 +9961,7 @@
         <v/>
       </c>
       <c r="Z128" s="7">
-        <f>IF(OR(Y128="",'多次统计数据'!$B$8=""),"",Y128-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE128="",'多次统计数据'!$B$8=""),"",AE128-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA128" s="10">
@@ -9461,6 +9977,10 @@
         <v/>
       </c>
       <c r="AD128" s="2" t="n"/>
+      <c r="AE128" s="7">
+        <f>IF(OR(X128="",C128="",C128&lt;=0),"",X128/C128)</f>
+        <v/>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n"/>
@@ -9513,7 +10033,7 @@
         <v/>
       </c>
       <c r="Z129" s="7">
-        <f>IF(OR(Y129="",'多次统计数据'!$B$8=""),"",Y129-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE129="",'多次统计数据'!$B$8=""),"",AE129-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA129" s="10">
@@ -9529,6 +10049,10 @@
         <v/>
       </c>
       <c r="AD129" s="2" t="n"/>
+      <c r="AE129" s="7">
+        <f>IF(OR(X129="",C129="",C129&lt;=0),"",X129/C129)</f>
+        <v/>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n"/>
@@ -9581,7 +10105,7 @@
         <v/>
       </c>
       <c r="Z130" s="7">
-        <f>IF(OR(Y130="",'多次统计数据'!$B$8=""),"",Y130-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE130="",'多次统计数据'!$B$8=""),"",AE130-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA130" s="10">
@@ -9597,6 +10121,10 @@
         <v/>
       </c>
       <c r="AD130" s="2" t="n"/>
+      <c r="AE130" s="7">
+        <f>IF(OR(X130="",C130="",C130&lt;=0),"",X130/C130)</f>
+        <v/>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n"/>
@@ -9649,7 +10177,7 @@
         <v/>
       </c>
       <c r="Z131" s="7">
-        <f>IF(OR(Y131="",'多次统计数据'!$B$8=""),"",Y131-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE131="",'多次统计数据'!$B$8=""),"",AE131-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA131" s="10">
@@ -9665,6 +10193,10 @@
         <v/>
       </c>
       <c r="AD131" s="2" t="n"/>
+      <c r="AE131" s="7">
+        <f>IF(OR(X131="",C131="",C131&lt;=0),"",X131/C131)</f>
+        <v/>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n"/>
@@ -9717,7 +10249,7 @@
         <v/>
       </c>
       <c r="Z132" s="7">
-        <f>IF(OR(Y132="",'多次统计数据'!$B$8=""),"",Y132-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE132="",'多次统计数据'!$B$8=""),"",AE132-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA132" s="10">
@@ -9733,6 +10265,10 @@
         <v/>
       </c>
       <c r="AD132" s="2" t="n"/>
+      <c r="AE132" s="7">
+        <f>IF(OR(X132="",C132="",C132&lt;=0),"",X132/C132)</f>
+        <v/>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n"/>
@@ -9785,7 +10321,7 @@
         <v/>
       </c>
       <c r="Z133" s="7">
-        <f>IF(OR(Y133="",'多次统计数据'!$B$8=""),"",Y133-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE133="",'多次统计数据'!$B$8=""),"",AE133-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA133" s="10">
@@ -9801,6 +10337,10 @@
         <v/>
       </c>
       <c r="AD133" s="2" t="n"/>
+      <c r="AE133" s="7">
+        <f>IF(OR(X133="",C133="",C133&lt;=0),"",X133/C133)</f>
+        <v/>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n"/>
@@ -9853,7 +10393,7 @@
         <v/>
       </c>
       <c r="Z134" s="7">
-        <f>IF(OR(Y134="",'多次统计数据'!$B$8=""),"",Y134-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE134="",'多次统计数据'!$B$8=""),"",AE134-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA134" s="10">
@@ -9869,6 +10409,10 @@
         <v/>
       </c>
       <c r="AD134" s="2" t="n"/>
+      <c r="AE134" s="7">
+        <f>IF(OR(X134="",C134="",C134&lt;=0),"",X134/C134)</f>
+        <v/>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n"/>
@@ -9921,7 +10465,7 @@
         <v/>
       </c>
       <c r="Z135" s="7">
-        <f>IF(OR(Y135="",'多次统计数据'!$B$8=""),"",Y135-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE135="",'多次统计数据'!$B$8=""),"",AE135-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA135" s="10">
@@ -9937,6 +10481,10 @@
         <v/>
       </c>
       <c r="AD135" s="2" t="n"/>
+      <c r="AE135" s="7">
+        <f>IF(OR(X135="",C135="",C135&lt;=0),"",X135/C135)</f>
+        <v/>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n"/>
@@ -9989,7 +10537,7 @@
         <v/>
       </c>
       <c r="Z136" s="7">
-        <f>IF(OR(Y136="",'多次统计数据'!$B$8=""),"",Y136-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE136="",'多次统计数据'!$B$8=""),"",AE136-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA136" s="10">
@@ -10005,6 +10553,10 @@
         <v/>
       </c>
       <c r="AD136" s="2" t="n"/>
+      <c r="AE136" s="7">
+        <f>IF(OR(X136="",C136="",C136&lt;=0),"",X136/C136)</f>
+        <v/>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n"/>
@@ -10057,7 +10609,7 @@
         <v/>
       </c>
       <c r="Z137" s="7">
-        <f>IF(OR(Y137="",'多次统计数据'!$B$8=""),"",Y137-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE137="",'多次统计数据'!$B$8=""),"",AE137-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA137" s="10">
@@ -10073,6 +10625,10 @@
         <v/>
       </c>
       <c r="AD137" s="2" t="n"/>
+      <c r="AE137" s="7">
+        <f>IF(OR(X137="",C137="",C137&lt;=0),"",X137/C137)</f>
+        <v/>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n"/>
@@ -10125,7 +10681,7 @@
         <v/>
       </c>
       <c r="Z138" s="7">
-        <f>IF(OR(Y138="",'多次统计数据'!$B$8=""),"",Y138-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE138="",'多次统计数据'!$B$8=""),"",AE138-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA138" s="10">
@@ -10141,6 +10697,10 @@
         <v/>
       </c>
       <c r="AD138" s="2" t="n"/>
+      <c r="AE138" s="7">
+        <f>IF(OR(X138="",C138="",C138&lt;=0),"",X138/C138)</f>
+        <v/>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n"/>
@@ -10193,7 +10753,7 @@
         <v/>
       </c>
       <c r="Z139" s="7">
-        <f>IF(OR(Y139="",'多次统计数据'!$B$8=""),"",Y139-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE139="",'多次统计数据'!$B$8=""),"",AE139-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA139" s="10">
@@ -10209,6 +10769,10 @@
         <v/>
       </c>
       <c r="AD139" s="2" t="n"/>
+      <c r="AE139" s="7">
+        <f>IF(OR(X139="",C139="",C139&lt;=0),"",X139/C139)</f>
+        <v/>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n"/>
@@ -10261,7 +10825,7 @@
         <v/>
       </c>
       <c r="Z140" s="7">
-        <f>IF(OR(Y140="",'多次统计数据'!$B$8=""),"",Y140-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE140="",'多次统计数据'!$B$8=""),"",AE140-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA140" s="10">
@@ -10277,6 +10841,10 @@
         <v/>
       </c>
       <c r="AD140" s="2" t="n"/>
+      <c r="AE140" s="7">
+        <f>IF(OR(X140="",C140="",C140&lt;=0),"",X140/C140)</f>
+        <v/>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n"/>
@@ -10329,7 +10897,7 @@
         <v/>
       </c>
       <c r="Z141" s="7">
-        <f>IF(OR(Y141="",'多次统计数据'!$B$8=""),"",Y141-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE141="",'多次统计数据'!$B$8=""),"",AE141-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA141" s="10">
@@ -10345,6 +10913,10 @@
         <v/>
       </c>
       <c r="AD141" s="2" t="n"/>
+      <c r="AE141" s="7">
+        <f>IF(OR(X141="",C141="",C141&lt;=0),"",X141/C141)</f>
+        <v/>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n"/>
@@ -10397,7 +10969,7 @@
         <v/>
       </c>
       <c r="Z142" s="7">
-        <f>IF(OR(Y142="",'多次统计数据'!$B$8=""),"",Y142-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE142="",'多次统计数据'!$B$8=""),"",AE142-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA142" s="10">
@@ -10413,6 +10985,10 @@
         <v/>
       </c>
       <c r="AD142" s="2" t="n"/>
+      <c r="AE142" s="7">
+        <f>IF(OR(X142="",C142="",C142&lt;=0),"",X142/C142)</f>
+        <v/>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n"/>
@@ -10465,7 +11041,7 @@
         <v/>
       </c>
       <c r="Z143" s="7">
-        <f>IF(OR(Y143="",'多次统计数据'!$B$8=""),"",Y143-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE143="",'多次统计数据'!$B$8=""),"",AE143-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA143" s="10">
@@ -10481,6 +11057,10 @@
         <v/>
       </c>
       <c r="AD143" s="2" t="n"/>
+      <c r="AE143" s="7">
+        <f>IF(OR(X143="",C143="",C143&lt;=0),"",X143/C143)</f>
+        <v/>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n"/>
@@ -10533,7 +11113,7 @@
         <v/>
       </c>
       <c r="Z144" s="7">
-        <f>IF(OR(Y144="",'多次统计数据'!$B$8=""),"",Y144-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE144="",'多次统计数据'!$B$8=""),"",AE144-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA144" s="10">
@@ -10549,6 +11129,10 @@
         <v/>
       </c>
       <c r="AD144" s="2" t="n"/>
+      <c r="AE144" s="7">
+        <f>IF(OR(X144="",C144="",C144&lt;=0),"",X144/C144)</f>
+        <v/>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n"/>
@@ -10601,7 +11185,7 @@
         <v/>
       </c>
       <c r="Z145" s="7">
-        <f>IF(OR(Y145="",'多次统计数据'!$B$8=""),"",Y145-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE145="",'多次统计数据'!$B$8=""),"",AE145-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA145" s="10">
@@ -10617,6 +11201,10 @@
         <v/>
       </c>
       <c r="AD145" s="2" t="n"/>
+      <c r="AE145" s="7">
+        <f>IF(OR(X145="",C145="",C145&lt;=0),"",X145/C145)</f>
+        <v/>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n"/>
@@ -10669,7 +11257,7 @@
         <v/>
       </c>
       <c r="Z146" s="7">
-        <f>IF(OR(Y146="",'多次统计数据'!$B$8=""),"",Y146-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE146="",'多次统计数据'!$B$8=""),"",AE146-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA146" s="10">
@@ -10685,6 +11273,10 @@
         <v/>
       </c>
       <c r="AD146" s="2" t="n"/>
+      <c r="AE146" s="7">
+        <f>IF(OR(X146="",C146="",C146&lt;=0),"",X146/C146)</f>
+        <v/>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n"/>
@@ -10737,7 +11329,7 @@
         <v/>
       </c>
       <c r="Z147" s="7">
-        <f>IF(OR(Y147="",'多次统计数据'!$B$8=""),"",Y147-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE147="",'多次统计数据'!$B$8=""),"",AE147-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA147" s="10">
@@ -10753,6 +11345,10 @@
         <v/>
       </c>
       <c r="AD147" s="2" t="n"/>
+      <c r="AE147" s="7">
+        <f>IF(OR(X147="",C147="",C147&lt;=0),"",X147/C147)</f>
+        <v/>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n"/>
@@ -10805,7 +11401,7 @@
         <v/>
       </c>
       <c r="Z148" s="7">
-        <f>IF(OR(Y148="",'多次统计数据'!$B$8=""),"",Y148-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE148="",'多次统计数据'!$B$8=""),"",AE148-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA148" s="10">
@@ -10821,6 +11417,10 @@
         <v/>
       </c>
       <c r="AD148" s="2" t="n"/>
+      <c r="AE148" s="7">
+        <f>IF(OR(X148="",C148="",C148&lt;=0),"",X148/C148)</f>
+        <v/>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n"/>
@@ -10873,7 +11473,7 @@
         <v/>
       </c>
       <c r="Z149" s="7">
-        <f>IF(OR(Y149="",'多次统计数据'!$B$8=""),"",Y149-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE149="",'多次统计数据'!$B$8=""),"",AE149-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA149" s="10">
@@ -10889,6 +11489,10 @@
         <v/>
       </c>
       <c r="AD149" s="2" t="n"/>
+      <c r="AE149" s="7">
+        <f>IF(OR(X149="",C149="",C149&lt;=0),"",X149/C149)</f>
+        <v/>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n"/>
@@ -10941,7 +11545,7 @@
         <v/>
       </c>
       <c r="Z150" s="7">
-        <f>IF(OR(Y150="",'多次统计数据'!$B$8=""),"",Y150-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE150="",'多次统计数据'!$B$8=""),"",AE150-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA150" s="10">
@@ -10957,6 +11561,10 @@
         <v/>
       </c>
       <c r="AD150" s="2" t="n"/>
+      <c r="AE150" s="7">
+        <f>IF(OR(X150="",C150="",C150&lt;=0),"",X150/C150)</f>
+        <v/>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n"/>
@@ -11009,7 +11617,7 @@
         <v/>
       </c>
       <c r="Z151" s="7">
-        <f>IF(OR(Y151="",'多次统计数据'!$B$8=""),"",Y151-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE151="",'多次统计数据'!$B$8=""),"",AE151-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA151" s="10">
@@ -11025,6 +11633,10 @@
         <v/>
       </c>
       <c r="AD151" s="2" t="n"/>
+      <c r="AE151" s="7">
+        <f>IF(OR(X151="",C151="",C151&lt;=0),"",X151/C151)</f>
+        <v/>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n"/>
@@ -11077,7 +11689,7 @@
         <v/>
       </c>
       <c r="Z152" s="7">
-        <f>IF(OR(Y152="",'多次统计数据'!$B$8=""),"",Y152-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE152="",'多次统计数据'!$B$8=""),"",AE152-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA152" s="10">
@@ -11093,6 +11705,10 @@
         <v/>
       </c>
       <c r="AD152" s="2" t="n"/>
+      <c r="AE152" s="7">
+        <f>IF(OR(X152="",C152="",C152&lt;=0),"",X152/C152)</f>
+        <v/>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n"/>
@@ -11145,7 +11761,7 @@
         <v/>
       </c>
       <c r="Z153" s="7">
-        <f>IF(OR(Y153="",'多次统计数据'!$B$8=""),"",Y153-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE153="",'多次统计数据'!$B$8=""),"",AE153-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA153" s="10">
@@ -11161,6 +11777,10 @@
         <v/>
       </c>
       <c r="AD153" s="2" t="n"/>
+      <c r="AE153" s="7">
+        <f>IF(OR(X153="",C153="",C153&lt;=0),"",X153/C153)</f>
+        <v/>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n"/>
@@ -11213,7 +11833,7 @@
         <v/>
       </c>
       <c r="Z154" s="7">
-        <f>IF(OR(Y154="",'多次统计数据'!$B$8=""),"",Y154-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE154="",'多次统计数据'!$B$8=""),"",AE154-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA154" s="10">
@@ -11229,6 +11849,10 @@
         <v/>
       </c>
       <c r="AD154" s="2" t="n"/>
+      <c r="AE154" s="7">
+        <f>IF(OR(X154="",C154="",C154&lt;=0),"",X154/C154)</f>
+        <v/>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n"/>
@@ -11281,7 +11905,7 @@
         <v/>
       </c>
       <c r="Z155" s="7">
-        <f>IF(OR(Y155="",'多次统计数据'!$B$8=""),"",Y155-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE155="",'多次统计数据'!$B$8=""),"",AE155-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA155" s="10">
@@ -11297,6 +11921,10 @@
         <v/>
       </c>
       <c r="AD155" s="2" t="n"/>
+      <c r="AE155" s="7">
+        <f>IF(OR(X155="",C155="",C155&lt;=0),"",X155/C155)</f>
+        <v/>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n"/>
@@ -11349,7 +11977,7 @@
         <v/>
       </c>
       <c r="Z156" s="7">
-        <f>IF(OR(Y156="",'多次统计数据'!$B$8=""),"",Y156-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE156="",'多次统计数据'!$B$8=""),"",AE156-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA156" s="10">
@@ -11365,6 +11993,10 @@
         <v/>
       </c>
       <c r="AD156" s="2" t="n"/>
+      <c r="AE156" s="7">
+        <f>IF(OR(X156="",C156="",C156&lt;=0),"",X156/C156)</f>
+        <v/>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n"/>
@@ -11417,7 +12049,7 @@
         <v/>
       </c>
       <c r="Z157" s="7">
-        <f>IF(OR(Y157="",'多次统计数据'!$B$8=""),"",Y157-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE157="",'多次统计数据'!$B$8=""),"",AE157-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA157" s="10">
@@ -11433,6 +12065,10 @@
         <v/>
       </c>
       <c r="AD157" s="2" t="n"/>
+      <c r="AE157" s="7">
+        <f>IF(OR(X157="",C157="",C157&lt;=0),"",X157/C157)</f>
+        <v/>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n"/>
@@ -11485,7 +12121,7 @@
         <v/>
       </c>
       <c r="Z158" s="7">
-        <f>IF(OR(Y158="",'多次统计数据'!$B$8=""),"",Y158-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE158="",'多次统计数据'!$B$8=""),"",AE158-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA158" s="10">
@@ -11501,6 +12137,10 @@
         <v/>
       </c>
       <c r="AD158" s="2" t="n"/>
+      <c r="AE158" s="7">
+        <f>IF(OR(X158="",C158="",C158&lt;=0),"",X158/C158)</f>
+        <v/>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n"/>
@@ -11553,7 +12193,7 @@
         <v/>
       </c>
       <c r="Z159" s="7">
-        <f>IF(OR(Y159="",'多次统计数据'!$B$8=""),"",Y159-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE159="",'多次统计数据'!$B$8=""),"",AE159-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA159" s="10">
@@ -11569,6 +12209,10 @@
         <v/>
       </c>
       <c r="AD159" s="2" t="n"/>
+      <c r="AE159" s="7">
+        <f>IF(OR(X159="",C159="",C159&lt;=0),"",X159/C159)</f>
+        <v/>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n"/>
@@ -11621,7 +12265,7 @@
         <v/>
       </c>
       <c r="Z160" s="7">
-        <f>IF(OR(Y160="",'多次统计数据'!$B$8=""),"",Y160-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE160="",'多次统计数据'!$B$8=""),"",AE160-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA160" s="10">
@@ -11637,6 +12281,10 @@
         <v/>
       </c>
       <c r="AD160" s="2" t="n"/>
+      <c r="AE160" s="7">
+        <f>IF(OR(X160="",C160="",C160&lt;=0),"",X160/C160)</f>
+        <v/>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n"/>
@@ -11689,7 +12337,7 @@
         <v/>
       </c>
       <c r="Z161" s="7">
-        <f>IF(OR(Y161="",'多次统计数据'!$B$8=""),"",Y161-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE161="",'多次统计数据'!$B$8=""),"",AE161-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA161" s="10">
@@ -11705,6 +12353,10 @@
         <v/>
       </c>
       <c r="AD161" s="2" t="n"/>
+      <c r="AE161" s="7">
+        <f>IF(OR(X161="",C161="",C161&lt;=0),"",X161/C161)</f>
+        <v/>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n"/>
@@ -11757,7 +12409,7 @@
         <v/>
       </c>
       <c r="Z162" s="7">
-        <f>IF(OR(Y162="",'多次统计数据'!$B$8=""),"",Y162-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE162="",'多次统计数据'!$B$8=""),"",AE162-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA162" s="10">
@@ -11773,6 +12425,10 @@
         <v/>
       </c>
       <c r="AD162" s="2" t="n"/>
+      <c r="AE162" s="7">
+        <f>IF(OR(X162="",C162="",C162&lt;=0),"",X162/C162)</f>
+        <v/>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n"/>
@@ -11825,7 +12481,7 @@
         <v/>
       </c>
       <c r="Z163" s="7">
-        <f>IF(OR(Y163="",'多次统计数据'!$B$8=""),"",Y163-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE163="",'多次统计数据'!$B$8=""),"",AE163-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA163" s="10">
@@ -11841,6 +12497,10 @@
         <v/>
       </c>
       <c r="AD163" s="2" t="n"/>
+      <c r="AE163" s="7">
+        <f>IF(OR(X163="",C163="",C163&lt;=0),"",X163/C163)</f>
+        <v/>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n"/>
@@ -11893,7 +12553,7 @@
         <v/>
       </c>
       <c r="Z164" s="7">
-        <f>IF(OR(Y164="",'多次统计数据'!$B$8=""),"",Y164-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE164="",'多次统计数据'!$B$8=""),"",AE164-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA164" s="10">
@@ -11909,6 +12569,10 @@
         <v/>
       </c>
       <c r="AD164" s="2" t="n"/>
+      <c r="AE164" s="7">
+        <f>IF(OR(X164="",C164="",C164&lt;=0),"",X164/C164)</f>
+        <v/>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n"/>
@@ -11961,7 +12625,7 @@
         <v/>
       </c>
       <c r="Z165" s="7">
-        <f>IF(OR(Y165="",'多次统计数据'!$B$8=""),"",Y165-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE165="",'多次统计数据'!$B$8=""),"",AE165-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA165" s="10">
@@ -11977,6 +12641,10 @@
         <v/>
       </c>
       <c r="AD165" s="2" t="n"/>
+      <c r="AE165" s="7">
+        <f>IF(OR(X165="",C165="",C165&lt;=0),"",X165/C165)</f>
+        <v/>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n"/>
@@ -12029,7 +12697,7 @@
         <v/>
       </c>
       <c r="Z166" s="7">
-        <f>IF(OR(Y166="",'多次统计数据'!$B$8=""),"",Y166-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE166="",'多次统计数据'!$B$8=""),"",AE166-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA166" s="10">
@@ -12045,6 +12713,10 @@
         <v/>
       </c>
       <c r="AD166" s="2" t="n"/>
+      <c r="AE166" s="7">
+        <f>IF(OR(X166="",C166="",C166&lt;=0),"",X166/C166)</f>
+        <v/>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n"/>
@@ -12097,7 +12769,7 @@
         <v/>
       </c>
       <c r="Z167" s="7">
-        <f>IF(OR(Y167="",'多次统计数据'!$B$8=""),"",Y167-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE167="",'多次统计数据'!$B$8=""),"",AE167-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA167" s="10">
@@ -12113,6 +12785,10 @@
         <v/>
       </c>
       <c r="AD167" s="2" t="n"/>
+      <c r="AE167" s="7">
+        <f>IF(OR(X167="",C167="",C167&lt;=0),"",X167/C167)</f>
+        <v/>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n"/>
@@ -12165,7 +12841,7 @@
         <v/>
       </c>
       <c r="Z168" s="7">
-        <f>IF(OR(Y168="",'多次统计数据'!$B$8=""),"",Y168-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE168="",'多次统计数据'!$B$8=""),"",AE168-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA168" s="10">
@@ -12181,6 +12857,10 @@
         <v/>
       </c>
       <c r="AD168" s="2" t="n"/>
+      <c r="AE168" s="7">
+        <f>IF(OR(X168="",C168="",C168&lt;=0),"",X168/C168)</f>
+        <v/>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n"/>
@@ -12233,7 +12913,7 @@
         <v/>
       </c>
       <c r="Z169" s="7">
-        <f>IF(OR(Y169="",'多次统计数据'!$B$8=""),"",Y169-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE169="",'多次统计数据'!$B$8=""),"",AE169-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA169" s="10">
@@ -12249,6 +12929,10 @@
         <v/>
       </c>
       <c r="AD169" s="2" t="n"/>
+      <c r="AE169" s="7">
+        <f>IF(OR(X169="",C169="",C169&lt;=0),"",X169/C169)</f>
+        <v/>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n"/>
@@ -12301,7 +12985,7 @@
         <v/>
       </c>
       <c r="Z170" s="7">
-        <f>IF(OR(Y170="",'多次统计数据'!$B$8=""),"",Y170-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE170="",'多次统计数据'!$B$8=""),"",AE170-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA170" s="10">
@@ -12317,6 +13001,10 @@
         <v/>
       </c>
       <c r="AD170" s="2" t="n"/>
+      <c r="AE170" s="7">
+        <f>IF(OR(X170="",C170="",C170&lt;=0),"",X170/C170)</f>
+        <v/>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n"/>
@@ -12369,7 +13057,7 @@
         <v/>
       </c>
       <c r="Z171" s="7">
-        <f>IF(OR(Y171="",'多次统计数据'!$B$8=""),"",Y171-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE171="",'多次统计数据'!$B$8=""),"",AE171-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA171" s="10">
@@ -12385,6 +13073,10 @@
         <v/>
       </c>
       <c r="AD171" s="2" t="n"/>
+      <c r="AE171" s="7">
+        <f>IF(OR(X171="",C171="",C171&lt;=0),"",X171/C171)</f>
+        <v/>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n"/>
@@ -12437,7 +13129,7 @@
         <v/>
       </c>
       <c r="Z172" s="7">
-        <f>IF(OR(Y172="",'多次统计数据'!$B$8=""),"",Y172-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE172="",'多次统计数据'!$B$8=""),"",AE172-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA172" s="10">
@@ -12453,6 +13145,10 @@
         <v/>
       </c>
       <c r="AD172" s="2" t="n"/>
+      <c r="AE172" s="7">
+        <f>IF(OR(X172="",C172="",C172&lt;=0),"",X172/C172)</f>
+        <v/>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n"/>
@@ -12505,7 +13201,7 @@
         <v/>
       </c>
       <c r="Z173" s="7">
-        <f>IF(OR(Y173="",'多次统计数据'!$B$8=""),"",Y173-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE173="",'多次统计数据'!$B$8=""),"",AE173-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA173" s="10">
@@ -12521,6 +13217,10 @@
         <v/>
       </c>
       <c r="AD173" s="2" t="n"/>
+      <c r="AE173" s="7">
+        <f>IF(OR(X173="",C173="",C173&lt;=0),"",X173/C173)</f>
+        <v/>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n"/>
@@ -12573,7 +13273,7 @@
         <v/>
       </c>
       <c r="Z174" s="7">
-        <f>IF(OR(Y174="",'多次统计数据'!$B$8=""),"",Y174-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE174="",'多次统计数据'!$B$8=""),"",AE174-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA174" s="10">
@@ -12589,6 +13289,10 @@
         <v/>
       </c>
       <c r="AD174" s="2" t="n"/>
+      <c r="AE174" s="7">
+        <f>IF(OR(X174="",C174="",C174&lt;=0),"",X174/C174)</f>
+        <v/>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n"/>
@@ -12641,7 +13345,7 @@
         <v/>
       </c>
       <c r="Z175" s="7">
-        <f>IF(OR(Y175="",'多次统计数据'!$B$8=""),"",Y175-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE175="",'多次统计数据'!$B$8=""),"",AE175-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA175" s="10">
@@ -12657,6 +13361,10 @@
         <v/>
       </c>
       <c r="AD175" s="2" t="n"/>
+      <c r="AE175" s="7">
+        <f>IF(OR(X175="",C175="",C175&lt;=0),"",X175/C175)</f>
+        <v/>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n"/>
@@ -12709,7 +13417,7 @@
         <v/>
       </c>
       <c r="Z176" s="7">
-        <f>IF(OR(Y176="",'多次统计数据'!$B$8=""),"",Y176-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE176="",'多次统计数据'!$B$8=""),"",AE176-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA176" s="10">
@@ -12725,6 +13433,10 @@
         <v/>
       </c>
       <c r="AD176" s="2" t="n"/>
+      <c r="AE176" s="7">
+        <f>IF(OR(X176="",C176="",C176&lt;=0),"",X176/C176)</f>
+        <v/>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n"/>
@@ -12777,7 +13489,7 @@
         <v/>
       </c>
       <c r="Z177" s="7">
-        <f>IF(OR(Y177="",'多次统计数据'!$B$8=""),"",Y177-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE177="",'多次统计数据'!$B$8=""),"",AE177-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA177" s="10">
@@ -12793,6 +13505,10 @@
         <v/>
       </c>
       <c r="AD177" s="2" t="n"/>
+      <c r="AE177" s="7">
+        <f>IF(OR(X177="",C177="",C177&lt;=0),"",X177/C177)</f>
+        <v/>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n"/>
@@ -12845,7 +13561,7 @@
         <v/>
       </c>
       <c r="Z178" s="7">
-        <f>IF(OR(Y178="",'多次统计数据'!$B$8=""),"",Y178-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE178="",'多次统计数据'!$B$8=""),"",AE178-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA178" s="10">
@@ -12861,6 +13577,10 @@
         <v/>
       </c>
       <c r="AD178" s="2" t="n"/>
+      <c r="AE178" s="7">
+        <f>IF(OR(X178="",C178="",C178&lt;=0),"",X178/C178)</f>
+        <v/>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n"/>
@@ -12913,7 +13633,7 @@
         <v/>
       </c>
       <c r="Z179" s="7">
-        <f>IF(OR(Y179="",'多次统计数据'!$B$8=""),"",Y179-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE179="",'多次统计数据'!$B$8=""),"",AE179-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA179" s="10">
@@ -12929,6 +13649,10 @@
         <v/>
       </c>
       <c r="AD179" s="2" t="n"/>
+      <c r="AE179" s="7">
+        <f>IF(OR(X179="",C179="",C179&lt;=0),"",X179/C179)</f>
+        <v/>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n"/>
@@ -12981,7 +13705,7 @@
         <v/>
       </c>
       <c r="Z180" s="7">
-        <f>IF(OR(Y180="",'多次统计数据'!$B$8=""),"",Y180-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE180="",'多次统计数据'!$B$8=""),"",AE180-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA180" s="10">
@@ -12997,6 +13721,10 @@
         <v/>
       </c>
       <c r="AD180" s="2" t="n"/>
+      <c r="AE180" s="7">
+        <f>IF(OR(X180="",C180="",C180&lt;=0),"",X180/C180)</f>
+        <v/>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n"/>
@@ -13049,7 +13777,7 @@
         <v/>
       </c>
       <c r="Z181" s="7">
-        <f>IF(OR(Y181="",'多次统计数据'!$B$8=""),"",Y181-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE181="",'多次统计数据'!$B$8=""),"",AE181-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA181" s="10">
@@ -13065,6 +13793,10 @@
         <v/>
       </c>
       <c r="AD181" s="2" t="n"/>
+      <c r="AE181" s="7">
+        <f>IF(OR(X181="",C181="",C181&lt;=0),"",X181/C181)</f>
+        <v/>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n"/>
@@ -13117,7 +13849,7 @@
         <v/>
       </c>
       <c r="Z182" s="7">
-        <f>IF(OR(Y182="",'多次统计数据'!$B$8=""),"",Y182-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE182="",'多次统计数据'!$B$8=""),"",AE182-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA182" s="10">
@@ -13133,6 +13865,10 @@
         <v/>
       </c>
       <c r="AD182" s="2" t="n"/>
+      <c r="AE182" s="7">
+        <f>IF(OR(X182="",C182="",C182&lt;=0),"",X182/C182)</f>
+        <v/>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n"/>
@@ -13185,7 +13921,7 @@
         <v/>
       </c>
       <c r="Z183" s="7">
-        <f>IF(OR(Y183="",'多次统计数据'!$B$8=""),"",Y183-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE183="",'多次统计数据'!$B$8=""),"",AE183-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA183" s="10">
@@ -13201,6 +13937,10 @@
         <v/>
       </c>
       <c r="AD183" s="2" t="n"/>
+      <c r="AE183" s="7">
+        <f>IF(OR(X183="",C183="",C183&lt;=0),"",X183/C183)</f>
+        <v/>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n"/>
@@ -13253,7 +13993,7 @@
         <v/>
       </c>
       <c r="Z184" s="7">
-        <f>IF(OR(Y184="",'多次统计数据'!$B$8=""),"",Y184-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE184="",'多次统计数据'!$B$8=""),"",AE184-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA184" s="10">
@@ -13269,6 +14009,10 @@
         <v/>
       </c>
       <c r="AD184" s="2" t="n"/>
+      <c r="AE184" s="7">
+        <f>IF(OR(X184="",C184="",C184&lt;=0),"",X184/C184)</f>
+        <v/>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n"/>
@@ -13321,7 +14065,7 @@
         <v/>
       </c>
       <c r="Z185" s="7">
-        <f>IF(OR(Y185="",'多次统计数据'!$B$8=""),"",Y185-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE185="",'多次统计数据'!$B$8=""),"",AE185-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA185" s="10">
@@ -13337,6 +14081,10 @@
         <v/>
       </c>
       <c r="AD185" s="2" t="n"/>
+      <c r="AE185" s="7">
+        <f>IF(OR(X185="",C185="",C185&lt;=0),"",X185/C185)</f>
+        <v/>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n"/>
@@ -13389,7 +14137,7 @@
         <v/>
       </c>
       <c r="Z186" s="7">
-        <f>IF(OR(Y186="",'多次统计数据'!$B$8=""),"",Y186-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE186="",'多次统计数据'!$B$8=""),"",AE186-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA186" s="10">
@@ -13405,6 +14153,10 @@
         <v/>
       </c>
       <c r="AD186" s="2" t="n"/>
+      <c r="AE186" s="7">
+        <f>IF(OR(X186="",C186="",C186&lt;=0),"",X186/C186)</f>
+        <v/>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n"/>
@@ -13457,7 +14209,7 @@
         <v/>
       </c>
       <c r="Z187" s="7">
-        <f>IF(OR(Y187="",'多次统计数据'!$B$8=""),"",Y187-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE187="",'多次统计数据'!$B$8=""),"",AE187-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA187" s="10">
@@ -13473,6 +14225,10 @@
         <v/>
       </c>
       <c r="AD187" s="2" t="n"/>
+      <c r="AE187" s="7">
+        <f>IF(OR(X187="",C187="",C187&lt;=0),"",X187/C187)</f>
+        <v/>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n"/>
@@ -13525,7 +14281,7 @@
         <v/>
       </c>
       <c r="Z188" s="7">
-        <f>IF(OR(Y188="",'多次统计数据'!$B$8=""),"",Y188-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE188="",'多次统计数据'!$B$8=""),"",AE188-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA188" s="10">
@@ -13541,6 +14297,10 @@
         <v/>
       </c>
       <c r="AD188" s="2" t="n"/>
+      <c r="AE188" s="7">
+        <f>IF(OR(X188="",C188="",C188&lt;=0),"",X188/C188)</f>
+        <v/>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n"/>
@@ -13593,7 +14353,7 @@
         <v/>
       </c>
       <c r="Z189" s="7">
-        <f>IF(OR(Y189="",'多次统计数据'!$B$8=""),"",Y189-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE189="",'多次统计数据'!$B$8=""),"",AE189-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA189" s="10">
@@ -13609,6 +14369,10 @@
         <v/>
       </c>
       <c r="AD189" s="2" t="n"/>
+      <c r="AE189" s="7">
+        <f>IF(OR(X189="",C189="",C189&lt;=0),"",X189/C189)</f>
+        <v/>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n"/>
@@ -13661,7 +14425,7 @@
         <v/>
       </c>
       <c r="Z190" s="7">
-        <f>IF(OR(Y190="",'多次统计数据'!$B$8=""),"",Y190-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE190="",'多次统计数据'!$B$8=""),"",AE190-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA190" s="10">
@@ -13677,6 +14441,10 @@
         <v/>
       </c>
       <c r="AD190" s="2" t="n"/>
+      <c r="AE190" s="7">
+        <f>IF(OR(X190="",C190="",C190&lt;=0),"",X190/C190)</f>
+        <v/>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n"/>
@@ -13729,7 +14497,7 @@
         <v/>
       </c>
       <c r="Z191" s="7">
-        <f>IF(OR(Y191="",'多次统计数据'!$B$8=""),"",Y191-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE191="",'多次统计数据'!$B$8=""),"",AE191-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA191" s="10">
@@ -13745,6 +14513,10 @@
         <v/>
       </c>
       <c r="AD191" s="2" t="n"/>
+      <c r="AE191" s="7">
+        <f>IF(OR(X191="",C191="",C191&lt;=0),"",X191/C191)</f>
+        <v/>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n"/>
@@ -13797,7 +14569,7 @@
         <v/>
       </c>
       <c r="Z192" s="7">
-        <f>IF(OR(Y192="",'多次统计数据'!$B$8=""),"",Y192-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE192="",'多次统计数据'!$B$8=""),"",AE192-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA192" s="10">
@@ -13813,6 +14585,10 @@
         <v/>
       </c>
       <c r="AD192" s="2" t="n"/>
+      <c r="AE192" s="7">
+        <f>IF(OR(X192="",C192="",C192&lt;=0),"",X192/C192)</f>
+        <v/>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n"/>
@@ -13865,7 +14641,7 @@
         <v/>
       </c>
       <c r="Z193" s="7">
-        <f>IF(OR(Y193="",'多次统计数据'!$B$8=""),"",Y193-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE193="",'多次统计数据'!$B$8=""),"",AE193-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA193" s="10">
@@ -13881,6 +14657,10 @@
         <v/>
       </c>
       <c r="AD193" s="2" t="n"/>
+      <c r="AE193" s="7">
+        <f>IF(OR(X193="",C193="",C193&lt;=0),"",X193/C193)</f>
+        <v/>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n"/>
@@ -13933,7 +14713,7 @@
         <v/>
       </c>
       <c r="Z194" s="7">
-        <f>IF(OR(Y194="",'多次统计数据'!$B$8=""),"",Y194-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE194="",'多次统计数据'!$B$8=""),"",AE194-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA194" s="10">
@@ -13949,6 +14729,10 @@
         <v/>
       </c>
       <c r="AD194" s="2" t="n"/>
+      <c r="AE194" s="7">
+        <f>IF(OR(X194="",C194="",C194&lt;=0),"",X194/C194)</f>
+        <v/>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n"/>
@@ -14001,7 +14785,7 @@
         <v/>
       </c>
       <c r="Z195" s="7">
-        <f>IF(OR(Y195="",'多次统计数据'!$B$8=""),"",Y195-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE195="",'多次统计数据'!$B$8=""),"",AE195-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA195" s="10">
@@ -14017,6 +14801,10 @@
         <v/>
       </c>
       <c r="AD195" s="2" t="n"/>
+      <c r="AE195" s="7">
+        <f>IF(OR(X195="",C195="",C195&lt;=0),"",X195/C195)</f>
+        <v/>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n"/>
@@ -14069,7 +14857,7 @@
         <v/>
       </c>
       <c r="Z196" s="7">
-        <f>IF(OR(Y196="",'多次统计数据'!$B$8=""),"",Y196-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE196="",'多次统计数据'!$B$8=""),"",AE196-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA196" s="10">
@@ -14085,6 +14873,10 @@
         <v/>
       </c>
       <c r="AD196" s="2" t="n"/>
+      <c r="AE196" s="7">
+        <f>IF(OR(X196="",C196="",C196&lt;=0),"",X196/C196)</f>
+        <v/>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n"/>
@@ -14137,7 +14929,7 @@
         <v/>
       </c>
       <c r="Z197" s="7">
-        <f>IF(OR(Y197="",'多次统计数据'!$B$8=""),"",Y197-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE197="",'多次统计数据'!$B$8=""),"",AE197-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA197" s="10">
@@ -14153,6 +14945,10 @@
         <v/>
       </c>
       <c r="AD197" s="2" t="n"/>
+      <c r="AE197" s="7">
+        <f>IF(OR(X197="",C197="",C197&lt;=0),"",X197/C197)</f>
+        <v/>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n"/>
@@ -14205,7 +15001,7 @@
         <v/>
       </c>
       <c r="Z198" s="7">
-        <f>IF(OR(Y198="",'多次统计数据'!$B$8=""),"",Y198-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE198="",'多次统计数据'!$B$8=""),"",AE198-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA198" s="10">
@@ -14221,6 +15017,10 @@
         <v/>
       </c>
       <c r="AD198" s="2" t="n"/>
+      <c r="AE198" s="7">
+        <f>IF(OR(X198="",C198="",C198&lt;=0),"",X198/C198)</f>
+        <v/>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n"/>
@@ -14273,7 +15073,7 @@
         <v/>
       </c>
       <c r="Z199" s="7">
-        <f>IF(OR(Y199="",'多次统计数据'!$B$8=""),"",Y199-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE199="",'多次统计数据'!$B$8=""),"",AE199-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA199" s="10">
@@ -14289,6 +15089,10 @@
         <v/>
       </c>
       <c r="AD199" s="2" t="n"/>
+      <c r="AE199" s="7">
+        <f>IF(OR(X199="",C199="",C199&lt;=0),"",X199/C199)</f>
+        <v/>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n"/>
@@ -14341,7 +15145,7 @@
         <v/>
       </c>
       <c r="Z200" s="7">
-        <f>IF(OR(Y200="",'多次统计数据'!$B$8=""),"",Y200-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE200="",'多次统计数据'!$B$8=""),"",AE200-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA200" s="10">
@@ -14357,6 +15161,10 @@
         <v/>
       </c>
       <c r="AD200" s="2" t="n"/>
+      <c r="AE200" s="7">
+        <f>IF(OR(X200="",C200="",C200&lt;=0),"",X200/C200)</f>
+        <v/>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n"/>
@@ -14409,7 +15217,7 @@
         <v/>
       </c>
       <c r="Z201" s="7">
-        <f>IF(OR(Y201="",'多次统计数据'!$B$8=""),"",Y201-'多次统计数据'!$B$8)</f>
+        <f>IF(OR(AE201="",'多次统计数据'!$B$8=""),"",AE201-'多次统计数据'!$B$8)</f>
         <v/>
       </c>
       <c r="AA201" s="10">
@@ -14425,6 +15233,10 @@
         <v/>
       </c>
       <c r="AD201" s="2" t="n"/>
+      <c r="AE201" s="7">
+        <f>IF(OR(X201="",C201="",C201&lt;=0),"",X201/C201)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="X2:X201">
@@ -14456,11 +15268,19 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="AE2:AE201">
+    <cfRule type="cellIs" priority="8" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="9" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="G2:G201">
-    <cfRule type="expression" priority="8" dxfId="1">
+    <cfRule type="expression" priority="10" dxfId="1">
       <formula>$G2="禁止开仓"</formula>
     </cfRule>
-    <cfRule type="expression" priority="9" dxfId="0">
+    <cfRule type="expression" priority="11" dxfId="0">
       <formula>$G2="允许开仓"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20221,12 +21041,12 @@
         </is>
       </c>
       <c r="B8" s="7">
-        <f>IFERROR(AVERAGEIF('单次交易'!X2:X201,"&gt;0",'单次交易'!Y2:Y201),"")</f>
+        <f>IFERROR(AVERAGEIF('单次交易'!X2:X201,"&gt;0",'单次交易'!AE2:AE201),"")</f>
         <v/>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>盈利交易实际收益率的平均值</t>
+          <t>盈利交易实际账户收益率的平均值</t>
         </is>
       </c>
     </row>
@@ -20237,12 +21057,12 @@
         </is>
       </c>
       <c r="B9" s="7">
-        <f>IFERROR(-AVERAGEIF('单次交易'!X2:X201,"&lt;0",'单次交易'!Y2:Y201),"")</f>
+        <f>IFERROR(-AVERAGEIF('单次交易'!X2:X201,"&lt;0",'单次交易'!AE2:AE201),"")</f>
         <v/>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>以正数显示亏损幅度</t>
+          <t>亏损交易实际账户收益率绝对值的平均值</t>
         </is>
       </c>
     </row>
@@ -20317,12 +21137,12 @@
         </is>
       </c>
       <c r="B14" s="7">
-        <f>IF(OR(B3+B4=0,B8="",B9=""),"",POWER(1+B8,B3)*POWER(1-B9,B4)-1)</f>
+        <f>IF(COUNT('单次交易'!AE2:AE201)=0,"",EXP(SUMPRODUCT(IFERROR(LN(1+'单次交易'!AE2:AE201),0)))-1)</f>
         <v/>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>基于历史平均盈亏率的几何复利模拟</t>
+          <t>按每笔实际账户收益率逐笔连乘</t>
         </is>
       </c>
     </row>
@@ -20337,7 +21157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -20498,6 +21318,22 @@
       <c r="C10" s="12" t="inlineStr">
         <is>
           <t>当月允许最大亏损金额－当前未平仓理论亏损</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>账户实际累计收益率</t>
+        </is>
+      </c>
+      <c r="B11" s="7">
+        <f>IF(OR(B2="",B3="",B2&lt;=0),"",B3/B2-1)</f>
+        <v/>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>当前总金额÷初始总金额－1；无入金出金时为账户权威累计收益</t>
         </is>
       </c>
     </row>
@@ -20642,12 +21478,12 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>IF(OR(B4="",B5="",B6="",B5&lt;=0,B6&lt;=0),"暂不可计算",ROUNDUP(B4/(B5*B6),0))</f>
+        <f>IF(OR(B3="",B6="",B3&lt;=0,B6&lt;=0),"暂不可计算",ROUNDUP(LN(1+B3)/LN(1+B6),0))</f>
         <v/>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>向上取整；历史期望收益率不为正时不计算</t>
+          <t>按目标收益率与历史账户期望收益率复利计算并向上取整</t>
         </is>
       </c>
     </row>

--- a/交易管理系统.xlsx
+++ b/交易管理系统.xlsx
@@ -151,7 +151,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="158">
   <si>
     <t>交易编号</t>
   </si>
@@ -255,6 +255,12 @@
     <t>之前的压力位</t>
   </si>
   <si>
+    <t>下方支撑位</t>
+  </si>
+  <si>
+    <t>前高</t>
+  </si>
+  <si>
     <t>所属板块</t>
   </si>
   <si>
@@ -280,6 +286,9 @@
   </si>
   <si>
     <t>1.跳空支撑的交易很大支撑强，一只没跌破，2，之前的高电形成支撑，3十字星显示空方出现颓势，没有跌破支撑位</t>
+  </si>
+  <si>
+    <t>1.十字星显示空方力量不强，组成看涨吞没，2，占到均线上方，3.MACD即将变红</t>
   </si>
   <si>
     <t>指标</t>
@@ -1950,21 +1959,21 @@
         <f t="shared" ref="Y2:Y65" si="6">IF(OR(X2="",E2="",H2=""),"",IF(E2*H2+IF(O2="",0,O2)&lt;=0,"",X2/(E2*H2+IF(O2="",0,O2))))</f>
         <v>-0.0429166666666667</v>
       </c>
-      <c r="Z2" s="7" t="str">
+      <c r="Z2" s="7">
         <f>IF(OR(AE2="",多次统计数据!$B$8=""),"",AE2-多次统计数据!$B$8)</f>
-        <v/>
+        <v>-0.102826765350049</v>
       </c>
       <c r="AA2" s="12">
         <f t="shared" ref="AA2:AA65" si="7">IF(OR(I2="",M2="",M2&lt;I2),"",M2-I2)</f>
         <v>4</v>
       </c>
-      <c r="AB2" s="7" t="str">
+      <c r="AB2" s="7">
         <f>IF(OR(A2="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0294585894566018</v>
       </c>
       <c r="AC2" s="8" t="str">
         <f>IF(OR(AB2="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB2,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>达到或超过上限</v>
       </c>
       <c r="AD2" s="2"/>
       <c r="AE2" s="7">
@@ -1981,7 +1990,7 @@
       </c>
       <c r="C3" s="5">
         <f>IF(C2="","",C2+SUM(单次交易!Y2:Y201))</f>
-        <v>99999.9259936865</v>
+        <v>99999.9984368683</v>
       </c>
       <c r="D3" s="6">
         <v>0.02</v>
@@ -2045,98 +2054,122 @@
         <f t="shared" si="6"/>
         <v>-0.0310896468457593</v>
       </c>
-      <c r="Z3" s="7" t="str">
+      <c r="Z3" s="7">
         <f>IF(OR(AE3="",多次统计数据!$B$8=""),"",AE3-多次统计数据!$B$8)</f>
-        <v/>
+        <v>-0.0935567658491572</v>
       </c>
       <c r="AA3" s="12">
         <f t="shared" si="7"/>
         <v>12</v>
       </c>
-      <c r="AB3" s="7" t="str">
+      <c r="AB3" s="7">
         <f>IF(OR(A3="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0294585894566018</v>
       </c>
       <c r="AC3" s="8" t="str">
         <f>IF(OR(AB3="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB3,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>达到或超过上限</v>
       </c>
       <c r="AD3" s="2"/>
       <c r="AE3" s="7">
         <f t="shared" si="8"/>
-        <v>-0.0319300236302335</v>
+        <v>-0.0319300004991081</v>
       </c>
     </row>
     <row r="4" ht="17" spans="1:31">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="8" t="str">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="9">
+        <v>92687</v>
+      </c>
+      <c r="D4" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E4" s="9">
+        <v>28.16</v>
+      </c>
+      <c r="F4" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>2800</v>
       </c>
       <c r="G4" s="8" t="str">
         <f>IF(OR(A4="",F4="",E4="",N4="",E4&lt;=N4,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H4="",F4*(E4-N4),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H4" s="2"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H4" s="2">
+        <v>2800</v>
+      </c>
+      <c r="I4" s="10">
+        <v>45226</v>
+      </c>
+      <c r="J4" s="9">
+        <v>30</v>
+      </c>
+      <c r="K4" s="9">
+        <v>30.2</v>
+      </c>
+      <c r="L4" s="8">
         <f t="shared" si="1"/>
-        <v/>
+        <v>2800</v>
       </c>
       <c r="M4" s="10"/>
-      <c r="N4" s="9"/>
+      <c r="N4" s="9">
+        <v>27.5</v>
+      </c>
       <c r="O4" s="9"/>
       <c r="P4" s="9"/>
       <c r="Q4" s="2"/>
-      <c r="R4" s="2"/>
-      <c r="S4" s="2"/>
+      <c r="R4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="T4" s="2"/>
-      <c r="U4" s="7" t="str">
+      <c r="U4" s="7">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="V4" s="7" t="str">
+        <v>0.0653409090909091</v>
+      </c>
+      <c r="V4" s="7">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="W4" s="11" t="str">
+        <v>0.0234375</v>
+      </c>
+      <c r="W4" s="11">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="X4" s="5" t="str">
+        <v>2.78787878787879</v>
+      </c>
+      <c r="X4" s="5">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Y4" s="7" t="str">
+        <v>5712</v>
+      </c>
+      <c r="Y4" s="7">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="Z4" s="7" t="str">
+        <v>0.0724431818181818</v>
+      </c>
+      <c r="Z4" s="7">
         <f>IF(OR(AE4="",多次统计数据!$B$8=""),"",AE4-多次统计数据!$B$8)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AA4" s="12" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AB4" s="7" t="str">
+      <c r="AB4" s="7">
         <f>IF(OR(A4="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0294585894566018</v>
       </c>
       <c r="AC4" s="8" t="str">
         <f>IF(OR(AB4="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB4,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>达到或超过上限</v>
       </c>
       <c r="AD4" s="2"/>
-      <c r="AE4" s="7" t="str">
+      <c r="AE4" s="7">
         <f t="shared" si="8"/>
-        <v/>
+        <v>0.0616267653500491</v>
       </c>
     </row>
     <row r="5" ht="17" spans="1:31">
@@ -16428,25 +16461,25 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" ht="34" spans="1:9">
@@ -16461,7 +16494,7 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" ht="51" spans="1:9">
@@ -16474,10 +16507,10 @@
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" ht="34" spans="1:9">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -16486,7 +16519,9 @@
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
+      <c r="I4" s="2" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="2"/>
@@ -21989,169 +22024,169 @@
   <sheetData>
     <row r="1" ht="17" spans="1:3">
       <c r="A1" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" ht="17" spans="1:3">
       <c r="A2" s="4" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B2" s="8">
         <f>COUNT(单次交易!M2:M201)</f>
         <v>2</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" ht="17" spans="1:3">
       <c r="A3" s="4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B3" s="8">
         <f>COUNTIF(单次交易!X2:X201,"&gt;0")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" ht="17" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B4" s="8">
         <f>COUNTIF(单次交易!X2:X201,"&lt;0")</f>
         <v>2</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" ht="17" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B5" s="8">
         <f>COUNTIFS(单次交易!M2:M201,"&lt;&gt;",单次交易!X2:X201,"=0")</f>
         <v>0</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" ht="17" spans="1:3">
       <c r="A6" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B6" s="7">
         <f>IFERROR(B3/(B3+B4),"")</f>
-        <v>0</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" ht="17" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B7" s="7">
         <f>IFERROR(B4/(B3+B4),"")</f>
-        <v>1</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" ht="17" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B8" s="7" t="str">
+        <v>61</v>
+      </c>
+      <c r="B8" s="7">
         <f>IFERROR(AVERAGEIF(单次交易!X2:X201,"&gt;0",单次交易!AE2:AE201),"")</f>
-        <v/>
+        <v>0.0616267653500491</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" ht="17" spans="1:3">
       <c r="A9" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B9" s="7">
         <f>IFERROR(-AVERAGEIF(单次交易!X2:X201,"&lt;0",单次交易!AE2:AE201),"")</f>
-        <v>0.0365650118151168</v>
+        <v>0.0365650002495541</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" ht="17" spans="1:3">
       <c r="A10" s="4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B10" s="8">
         <f>SUMIF(单次交易!X2:X201,"&gt;0",单次交易!AA2:AA201)</f>
         <v>0</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" ht="17" spans="1:3">
       <c r="A11" s="4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B11" s="8">
         <f>SUMIF(单次交易!X2:X201,"&lt;0",单次交易!AA2:AA201)</f>
         <v>16</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" ht="17" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B12" s="5">
         <f>IFERROR(SUMPRODUCT(单次交易!E2:E201,单次交易!H2:H201)/COUNT(单次交易!H2:H201),"")</f>
-        <v>99351.5</v>
+        <v>92517</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" ht="17" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B13" s="7" t="str">
+        <v>70</v>
+      </c>
+      <c r="B13" s="7">
         <f>IF(OR(B6="",B7="",B8="",B9=""),"",B6*B8-B7*B9)</f>
-        <v/>
+        <v>-0.00383441171635301</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14" ht="17" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B14" s="7">
         <f>IF(COUNT(单次交易!AE2:AE201)=0,"",EXP(SUMPRODUCT(IFERROR(LN(1+单次交易!AE2:AE201),0)))-1)</f>
-        <v>-0.071814506656668</v>
+        <v>-0.0146134135121898</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -22173,130 +22208,130 @@
   <sheetData>
     <row r="1" ht="17" spans="1:3">
       <c r="A1" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" ht="17" spans="1:3">
       <c r="A2" s="4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B2" s="9">
         <v>100000</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" ht="17" spans="1:3">
       <c r="A3" s="4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B3" s="5">
         <f>IF(B2="","",B2+SUM(单次交易!X2:X201))</f>
-        <v>92687</v>
+        <v>98399</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" ht="17" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B4" s="6">
         <v>0.02</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" ht="17" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B5" s="5">
         <f>IF(B3="","",B3*B4)</f>
-        <v>1853.74</v>
+        <v>1967.98</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" ht="17" spans="1:3">
       <c r="A6" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B6" s="6">
         <v>0.06</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" ht="17" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B7" s="5">
         <f>IF(B3="","",B3*B6)</f>
-        <v>5561.22</v>
+        <v>5903.94</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" ht="17" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B8" s="5">
         <f ca="1">SUMIFS(单次交易!X2:X201,单次交易!X2:X201,"&lt;0",单次交易!M2:M201,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,单次交易!M2:M201,"&lt;="&amp;EOMONTH(TODAY(),0))</f>
         <v>0</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" ht="17" spans="1:3">
       <c r="A9" s="4" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B9" s="5">
         <f>IFERROR(SUMPRODUCT((单次交易!M2:M201="")*(单次交易!H2:H201&gt;0)*(单次交易!E2:E201&gt;单次交易!N2:N201)*单次交易!H2:H201*(单次交易!E2:E201-单次交易!N2:N201)),0)</f>
-        <v>0</v>
+        <v>1848</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" ht="17" spans="1:3">
       <c r="A10" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B10" s="5">
         <f>IF(OR(B7="",B9=""),"",B7-B9)</f>
-        <v>5561.22</v>
+        <v>4055.94</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" ht="17" spans="1:3">
       <c r="A11" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B11" s="7">
         <f>IF(OR(B2="",B3="",B2&lt;=0),"",B3/B2-1)</f>
-        <v>-0.0731300000000001</v>
+        <v>-0.0160100000000002</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -22337,84 +22372,84 @@
   <sheetData>
     <row r="1" ht="17" spans="1:3">
       <c r="A1" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" ht="17" spans="1:3">
       <c r="A2" s="4" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B2" s="5">
         <f>账户数据!B3</f>
-        <v>92687</v>
+        <v>98399</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" ht="17" spans="1:3">
       <c r="A3" s="4" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B3" s="6">
         <v>0.1</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" ht="17" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B4" s="5">
         <f>IF(OR(B2="",B3=""),"",B2*B3)</f>
-        <v>9268.7</v>
+        <v>9839.9</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" ht="17" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B5" s="5">
         <f>多次统计数据!B12</f>
-        <v>99351.5</v>
+        <v>92517</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" ht="17" spans="1:3">
       <c r="A6" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="B6" s="7" t="str">
+        <v>103</v>
+      </c>
+      <c r="B6" s="7">
         <f>多次统计数据!B13</f>
-        <v/>
+        <v>-0.00383441171635301</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" ht="17" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B7" s="8" t="str">
         <f>IF(OR(B3="",B6="",B3&lt;=0,B6&lt;=0),"暂不可计算",ROUNDUP(LN(1+B3)/LN(1+B6),0))</f>
         <v>暂不可计算</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -22441,233 +22476,233 @@
   <sheetData>
     <row r="1" ht="42" customHeight="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" ht="17" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" ht="17" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" ht="17" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" ht="17" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" ht="17" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" ht="17" spans="1:3">
       <c r="A7" s="2" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" ht="17" spans="1:3">
       <c r="A8" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9" ht="17" spans="1:3">
       <c r="A9" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10" ht="17" spans="1:3">
       <c r="A10" s="2" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11" ht="17" spans="1:3">
       <c r="A11" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12" ht="17" spans="1:3">
       <c r="A12" s="2" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13" ht="17" spans="1:3">
       <c r="A13" s="2" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14" ht="17" spans="1:3">
       <c r="A14" s="2" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15" ht="17" spans="1:3">
       <c r="A15" s="2" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="16" ht="17" spans="1:3">
       <c r="A16" s="2" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="17" ht="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="18" ht="17" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="19" ht="17" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="20" ht="17" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="21" ht="17" spans="1:3">
       <c r="A21" s="2" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="22" spans="1:3">

--- a/交易管理系统.xlsx
+++ b/交易管理系统.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\个人相关\学习\股票\learn_socks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31E02C3F-45D2-4A0A-B112-B30D5CDCB1BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9582626-613B-4F53-9C9D-21EDAADDF39F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="8460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="8460" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="单次交易" sheetId="1" r:id="rId1"/>
@@ -144,7 +144,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="170">
   <si>
     <t>交易编号</t>
   </si>
@@ -668,14 +668,26 @@
     <t>1.突破箱体 2.回踩支撑不破 3.跳空支撑4.均线支撑</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <t>北方稀土</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>前方高点，整数位，凑一下啊盈亏比</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.差一点的启明星 2突破前期压力位，3之前下跌量不大，最近放量上涨，说明空方卖的意愿不大</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="178" formatCode="\¥#,##0.00;[Red]\-\¥#,##0.00"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="\¥#,##0.00;[Red]\-\¥#,##0.00"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -780,7 +792,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -792,10 +804,10 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1490,7 +1502,7 @@
       </c>
       <c r="Z2" s="7">
         <f>IF(OR(AE2="",多次统计数据!$B$8=""),"",AE2-多次统计数据!$B$8)</f>
-        <v>-0.10282676535004909</v>
+        <v>-0.13936409756148377</v>
       </c>
       <c r="AA2" s="12">
         <f t="shared" ref="AA2:AA65" si="7">IF(OR(I2="",M2="",M2&lt;I2),"",M2-I2)</f>
@@ -1498,7 +1510,7 @@
       </c>
       <c r="AB2" s="7">
         <f>IF(OR(A2="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>1.1889240932741907E-2</v>
+        <v>3.0731156291036399E-2</v>
       </c>
       <c r="AC2" s="8" t="str">
         <f>IF(OR(AB2="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB2,"低于上限","达到或超过上限"))</f>
@@ -1519,7 +1531,7 @@
       </c>
       <c r="C3" s="5">
         <f>IF(C2="","",C2+SUM(单次交易!Y2:Y201))</f>
-        <v>99999.847613672624</v>
+        <v>99999.967165869137</v>
       </c>
       <c r="D3" s="6">
         <v>0.02</v>
@@ -1585,7 +1597,7 @@
       </c>
       <c r="Z3" s="7">
         <f>IF(OR(AE3="",多次统计数据!$B$8=""),"",AE3-多次统计数据!$B$8)</f>
-        <v>-9.3556814007077715E-2</v>
+        <v>-0.13009410804542532</v>
       </c>
       <c r="AA3" s="12">
         <f t="shared" si="7"/>
@@ -1593,7 +1605,7 @@
       </c>
       <c r="AB3" s="7">
         <f>IF(OR(A3="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>1.1889240932741907E-2</v>
+        <v>3.0731156291036399E-2</v>
       </c>
       <c r="AC3" s="8" t="str">
         <f>IF(OR(AB3="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB3,"低于上限","达到或超过上限"))</f>
@@ -1602,7 +1614,7 @@
       <c r="AD3" s="2"/>
       <c r="AE3" s="7">
         <f t="shared" si="8"/>
-        <v>-3.1930048657028622E-2</v>
+        <v>-3.1930010483941569E-2</v>
       </c>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.15">
@@ -1683,7 +1695,7 @@
       </c>
       <c r="Z4" s="7">
         <f>IF(OR(AE4="",多次统计数据!$B$8=""),"",AE4-多次统计数据!$B$8)</f>
-        <v>0</v>
+        <v>-3.6537332211434667E-2</v>
       </c>
       <c r="AA4" s="12">
         <f t="shared" si="7"/>
@@ -1691,7 +1703,7 @@
       </c>
       <c r="AB4" s="7">
         <f>IF(OR(A4="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>1.1889240932741907E-2</v>
+        <v>3.0731156291036399E-2</v>
       </c>
       <c r="AC4" s="8" t="str">
         <f>IF(OR(AB4="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB4,"低于上限","达到或超过上限"))</f>
@@ -1781,7 +1793,7 @@
       </c>
       <c r="Z5" s="7">
         <f>IF(OR(AE5="",多次统计数据!$B$8=""),"",AE5-多次统计数据!$B$8)</f>
-        <v>-8.9574203840277644E-2</v>
+        <v>-0.12611153605171233</v>
       </c>
       <c r="AA5" s="12">
         <f t="shared" si="7"/>
@@ -1789,7 +1801,7 @@
       </c>
       <c r="AB5" s="7">
         <f>IF(OR(A5="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>1.1889240932741907E-2</v>
+        <v>3.0731156291036399E-2</v>
       </c>
       <c r="AC5" s="8" t="str">
         <f>IF(OR(AB5="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB5,"低于上限","达到或超过上限"))</f>
@@ -1879,7 +1891,7 @@
       </c>
       <c r="Z6" s="7">
         <f>IF(OR(AE6="",多次统计数据!$B$8=""),"",AE6-多次统计数据!$B$8)</f>
-        <v>-9.1360479241464579E-2</v>
+        <v>-0.12789781145289925</v>
       </c>
       <c r="AA6" s="12">
         <f t="shared" si="7"/>
@@ -1887,7 +1899,7 @@
       </c>
       <c r="AB6" s="7">
         <f>IF(OR(A6="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>1.1889240932741907E-2</v>
+        <v>3.0731156291036399E-2</v>
       </c>
       <c r="AC6" s="8" t="str">
         <f>IF(OR(AB6="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB6,"低于上限","达到或超过上限"))</f>
@@ -1973,7 +1985,7 @@
       </c>
       <c r="Z7" s="7">
         <f>IF(OR(AE7="",多次统计数据!$B$8=""),"",AE7-多次统计数据!$B$8)</f>
-        <v>-0.10074103721040144</v>
+        <v>-0.13727836942183611</v>
       </c>
       <c r="AA7" s="12">
         <f t="shared" si="7"/>
@@ -1981,7 +1993,7 @@
       </c>
       <c r="AB7" s="7">
         <f>IF(OR(A7="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>1.1889240932741907E-2</v>
+        <v>3.0731156291036399E-2</v>
       </c>
       <c r="AC7" s="8" t="str">
         <f>IF(OR(AB7="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB7,"低于上限","达到或超过上限"))</f>
@@ -2137,148 +2149,196 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="8" t="str">
+    <row r="10" spans="1:31" ht="27" x14ac:dyDescent="0.15">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="C10" s="9">
+        <v>89175</v>
+      </c>
+      <c r="D10" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E10" s="9">
+        <v>16.87</v>
+      </c>
+      <c r="F10" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>4200</v>
       </c>
       <c r="G10" s="8" t="str">
         <f>IF(OR(A10="",F10="",E10="",N10="",E10&lt;=N10,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H10="",F10*(E10-N10),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H10" s="2"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H10" s="2">
+        <v>4200</v>
+      </c>
+      <c r="I10" s="10">
+        <v>45559</v>
+      </c>
+      <c r="J10" s="9">
+        <v>18</v>
+      </c>
+      <c r="K10" s="9">
+        <v>19.73</v>
+      </c>
+      <c r="L10" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M10" s="10"/>
-      <c r="N10" s="9"/>
+        <v>4200</v>
+      </c>
+      <c r="M10" s="10">
+        <v>45576</v>
+      </c>
+      <c r="N10" s="9">
+        <v>16.45</v>
+      </c>
       <c r="O10" s="9"/>
       <c r="P10" s="9"/>
       <c r="Q10" s="2"/>
-      <c r="R10" s="2"/>
-      <c r="S10" s="2"/>
+      <c r="R10" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="S10" s="13" t="s">
+        <v>168</v>
+      </c>
       <c r="T10" s="2"/>
-      <c r="U10" s="7" t="str">
+      <c r="U10" s="7">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="V10" s="7" t="str">
+        <v>6.6982809721398875E-2</v>
+      </c>
+      <c r="V10" s="7">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="W10" s="11" t="str">
+        <v>2.4896265560166074E-2</v>
+      </c>
+      <c r="W10" s="11">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="X10" s="5" t="str">
+        <v>2.6904761904761774</v>
+      </c>
+      <c r="X10" s="5">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Y10" s="7" t="str">
+        <v>12012</v>
+      </c>
+      <c r="Y10" s="7">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="Z10" s="7" t="str">
+        <v>0.16953171310017784</v>
+      </c>
+      <c r="Z10" s="7">
         <f>IF(OR(AE10="",多次统计数据!$B$8=""),"",AE10-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA10" s="12" t="str">
+        <v>3.6537332211434653E-2</v>
+      </c>
+      <c r="AA10" s="12">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB10" s="7" t="str">
+        <v>17</v>
+      </c>
+      <c r="AB10" s="7">
         <f>IF(OR(A10="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>3.0731156291036399E-2</v>
       </c>
       <c r="AC10" s="8" t="str">
         <f>IF(OR(AB10="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB10,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>达到或超过上限</v>
       </c>
       <c r="AD10" s="2"/>
-      <c r="AE10" s="7" t="str">
+      <c r="AE10" s="7">
         <f t="shared" si="8"/>
-        <v/>
+        <v>0.13470142977291841</v>
       </c>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="8" t="str">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="C11" s="9">
+        <v>101187</v>
+      </c>
+      <c r="D11" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E11" s="9">
+        <v>24.41</v>
+      </c>
+      <c r="F11" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>1800</v>
       </c>
       <c r="G11" s="8" t="str">
         <f>IF(OR(A11="",F11="",E11="",N11="",E11&lt;=N11,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H11="",F11*(E11-N11),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H11" s="2"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H11" s="2">
+        <v>1800</v>
+      </c>
+      <c r="I11" s="10">
+        <v>45783</v>
+      </c>
+      <c r="J11" s="9">
+        <v>26.8</v>
+      </c>
+      <c r="K11" s="9">
+        <v>23.19</v>
+      </c>
+      <c r="L11" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M11" s="10"/>
-      <c r="N11" s="9"/>
+        <v>1800</v>
+      </c>
+      <c r="M11" s="10">
+        <v>45799</v>
+      </c>
+      <c r="N11" s="9">
+        <v>23.3</v>
+      </c>
       <c r="O11" s="9"/>
       <c r="P11" s="9"/>
       <c r="Q11" s="2"/>
       <c r="R11" s="2"/>
       <c r="S11" s="2"/>
       <c r="T11" s="2"/>
-      <c r="U11" s="7" t="str">
+      <c r="U11" s="7">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="V11" s="7" t="str">
+        <v>9.7910692339205269E-2</v>
+      </c>
+      <c r="V11" s="7">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="W11" s="11" t="str">
+        <v>4.547316673494467E-2</v>
+      </c>
+      <c r="W11" s="11">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="X11" s="5" t="str">
+        <v>2.1531531531531547</v>
+      </c>
+      <c r="X11" s="5">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Y11" s="7" t="str">
+        <v>-2196</v>
+      </c>
+      <c r="Y11" s="7">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="Z11" s="7" t="str">
+        <v>-4.9979516591560837E-2</v>
+      </c>
+      <c r="Z11" s="7">
         <f>IF(OR(AE11="",多次统计数据!$B$8=""),"",AE11-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA11" s="12" t="str">
+        <v>-0.11986649016132365</v>
+      </c>
+      <c r="AA11" s="12">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB11" s="7" t="str">
+        <v>16</v>
+      </c>
+      <c r="AB11" s="7">
         <f>IF(OR(A11="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>3.0731156291036399E-2</v>
       </c>
       <c r="AC11" s="8" t="str">
         <f>IF(OR(AB11="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB11,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>达到或超过上限</v>
       </c>
       <c r="AD11" s="2"/>
-      <c r="AE11" s="7" t="str">
+      <c r="AE11" s="7">
         <f t="shared" si="8"/>
-        <v/>
+        <v>-2.1702392599839901E-2</v>
       </c>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.15">
@@ -16195,8 +16255,10 @@
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A10" s="2"/>
+    <row r="10" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -16204,7 +16266,9 @@
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
+      <c r="I10" s="13" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A11" s="2"/>
@@ -21655,7 +21719,7 @@
       </c>
       <c r="B2" s="8">
         <f>COUNT(单次交易!M2:M201)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>50</v>
@@ -21667,7 +21731,7 @@
       </c>
       <c r="B3" s="8">
         <f>COUNTIF(单次交易!X2:X201,"&gt;0")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>52</v>
@@ -21679,7 +21743,7 @@
       </c>
       <c r="B4" s="8">
         <f>COUNTIF(单次交易!X2:X201,"&lt;0")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>54</v>
@@ -21703,7 +21767,7 @@
       </c>
       <c r="B6" s="7">
         <f>IFERROR(B3/(B3+B4),"")</f>
-        <v>0.16666666666666666</v>
+        <v>0.25</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>58</v>
@@ -21715,7 +21779,7 @@
       </c>
       <c r="B7" s="7">
         <f>IFERROR(B4/(B3+B4),"")</f>
-        <v>0.83333333333333337</v>
+        <v>0.75</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>60</v>
@@ -21727,7 +21791,7 @@
       </c>
       <c r="B8" s="7">
         <f>IFERROR(AVERAGEIF(单次交易!X2:X201,"&gt;0",单次交易!AE2:AE201),"")</f>
-        <v>6.1626765350049087E-2</v>
+        <v>9.8164097561483754E-2</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>62</v>
@@ -21739,7 +21803,7 @@
       </c>
       <c r="B9" s="7">
         <f>IFERROR(-AVERAGEIF(单次交易!X2:X201,"&lt;0",单次交易!AE2:AE201),"")</f>
-        <v>3.3985094579805003E-2</v>
+        <v>3.193797122096298E-2</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>64</v>
@@ -21751,7 +21815,7 @@
       </c>
       <c r="B10" s="8">
         <f>SUMIF(单次交易!X2:X201,"&gt;0",单次交易!AA2:AA201)</f>
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>66</v>
@@ -21763,7 +21827,7 @@
       </c>
       <c r="B11" s="8">
         <f>SUMIF(单次交易!X2:X201,"&lt;0",单次交易!AA2:AA201)</f>
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>66</v>
@@ -21775,7 +21839,7 @@
       </c>
       <c r="B12" s="5">
         <f>IFERROR(SUMPRODUCT(单次交易!E2:E201,单次交易!H2:H201)/COUNT(单次交易!H2:H201),"")</f>
-        <v>96108.166666666672</v>
+        <v>86430.125</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>69</v>
@@ -21787,7 +21851,7 @@
       </c>
       <c r="B13" s="7">
         <f>IF(OR(B6="",B7="",B8="",B9=""),"",B6*B8-B7*B9)</f>
-        <v>-1.804978459149599E-2</v>
+        <v>5.8754597464870384E-4</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>71</v>
@@ -21849,7 +21913,7 @@
       </c>
       <c r="B3" s="5">
         <f>IF(B2="","",B2+SUM(单次交易!X2:X201))</f>
-        <v>89174.999999999985</v>
+        <v>98990.999999999985</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>79</v>
@@ -21872,7 +21936,7 @@
       </c>
       <c r="B5" s="5">
         <f>IF(B3="","",B3*B4)</f>
-        <v>1783.4999999999998</v>
+        <v>1979.8199999999997</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>83</v>
@@ -21895,7 +21959,7 @@
       </c>
       <c r="B7" s="5">
         <f>IF(B3="","",B3*B6)</f>
-        <v>5350.4999999999991</v>
+        <v>5939.4599999999991</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>87</v>
@@ -21931,7 +21995,7 @@
       </c>
       <c r="B10" s="5">
         <f>IF(OR(B7="",B9=""),"",B7-B9)</f>
-        <v>5350.4999999999991</v>
+        <v>5939.4599999999991</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>93</v>
@@ -21943,7 +22007,7 @@
       </c>
       <c r="B11" s="7">
         <f>IF(OR(B2="",B3="",B2&lt;=0),"",B3/B2-1)</f>
-        <v>-0.10825000000000018</v>
+        <v>-1.0090000000000154E-2</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>95</v>
@@ -22001,7 +22065,7 @@
       </c>
       <c r="B2" s="5">
         <f>账户数据!B3</f>
-        <v>89174.999999999985</v>
+        <v>98990.999999999985</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>97</v>
@@ -22024,7 +22088,7 @@
       </c>
       <c r="B4" s="5">
         <f>IF(OR(B2="",B3=""),"",B2*B3)</f>
-        <v>8917.4999999999982</v>
+        <v>9899.0999999999985</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>101</v>
@@ -22036,7 +22100,7 @@
       </c>
       <c r="B5" s="5">
         <f>多次统计数据!B12</f>
-        <v>96108.166666666672</v>
+        <v>86430.125</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>102</v>
@@ -22048,7 +22112,7 @@
       </c>
       <c r="B6" s="7">
         <f>多次统计数据!B13</f>
-        <v>-1.804978459149599E-2</v>
+        <v>5.8754597464870384E-4</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>104</v>
@@ -22058,9 +22122,9 @@
       <c r="A7" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B7" s="8" t="str">
+      <c r="B7" s="8">
         <f>IF(OR(B3="",B6="",B3&lt;=0,B6&lt;=0),"暂不可计算",ROUNDUP(LN(1+B3)/LN(1+B6),0))</f>
-        <v>暂不可计算</v>
+        <v>163</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>106</v>

--- a/交易管理系统.xlsx
+++ b/交易管理系统.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\个人相关\学习\股票\learn_socks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9582626-613B-4F53-9C9D-21EDAADDF39F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A49ECF7A-366B-4E2F-B779-7C09EBF71366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="8460" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="8460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="单次交易" sheetId="1" r:id="rId1"/>
@@ -39,6 +39,7 @@
           <rPr>
             <sz val="10"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>开仓时从“账户数据”的当前总金额复制，并粘贴为数值；不要保留公式。</t>
@@ -51,6 +52,7 @@
           <rPr>
             <sz val="10"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>开仓时从“账户数据”的单次交易允许亏损比例复制，并粘贴为数值。</t>
@@ -63,6 +65,7 @@
           <rPr>
             <sz val="10"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>按账户快照、本次风险比例和止损距离计算；仅作仓位建议。</t>
@@ -75,6 +78,7 @@
           <rPr>
             <sz val="10"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>比较全部未平仓理论亏损（含本行拟开仓风险）与当月允许最大亏损金额。</t>
@@ -87,6 +91,7 @@
           <rPr>
             <sz val="10"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>手动填写实际成交股数；后续盈亏、收益率和统计均引用此列。</t>
@@ -99,6 +104,7 @@
           <rPr>
             <sz val="10"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>默认等于实际买入股数；本系统按一次卖出处理。</t>
@@ -111,6 +117,7 @@
           <rPr>
             <sz val="10"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>实际盈亏金额÷买入时账户金额快照；用于账户口径统计与逐笔复利。</t>
@@ -133,6 +140,7 @@
           <rPr>
             <sz val="10"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>可在本列继续添加或修改指标；买入理由页的三个下拉框会引用A2:A201。</t>
@@ -144,7 +152,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="175">
   <si>
     <t>交易编号</t>
   </si>
@@ -680,6 +688,26 @@
     <t>1.差一点的启明星 2突破前期压力位，3之前下跌量不大，最近放量上涨，说明空方卖的意愿不大</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <t>前方支撑位</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>前方高点</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>赛轮轮胎</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.低点反弹，放量上涨，2突破前期支撑区域 3.MACD转正，4，均线开始支撑</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>前方支撑区域</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -702,17 +730,20 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1502,7 +1533,7 @@
       </c>
       <c r="Z2" s="7">
         <f>IF(OR(AE2="",多次统计数据!$B$8=""),"",AE2-多次统计数据!$B$8)</f>
-        <v>-0.13936409756148377</v>
+        <v>-9.439591633570403E-2</v>
       </c>
       <c r="AA2" s="12">
         <f t="shared" ref="AA2:AA65" si="7">IF(OR(I2="",M2="",M2&lt;I2),"",M2-I2)</f>
@@ -1510,7 +1541,7 @@
       </c>
       <c r="AB2" s="7">
         <f>IF(OR(A2="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>3.0731156291036399E-2</v>
+        <v>2.9182449035646263E-2</v>
       </c>
       <c r="AC2" s="8" t="str">
         <f>IF(OR(AB2="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB2,"低于上限","达到或超过上限"))</f>
@@ -1531,7 +1562,7 @@
       </c>
       <c r="C3" s="5">
         <f>IF(C2="","",C2+SUM(单次交易!Y2:Y201))</f>
-        <v>99999.967165869137</v>
+        <v>99999.936847327364</v>
       </c>
       <c r="D3" s="6">
         <v>0.02</v>
@@ -1597,7 +1628,7 @@
       </c>
       <c r="Z3" s="7">
         <f>IF(OR(AE3="",多次统计数据!$B$8=""),"",AE3-多次统计数据!$B$8)</f>
-        <v>-0.13009410804542532</v>
+        <v>-8.512593650036529E-2</v>
       </c>
       <c r="AA3" s="12">
         <f t="shared" si="7"/>
@@ -1605,7 +1636,7 @@
       </c>
       <c r="AB3" s="7">
         <f>IF(OR(A3="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>3.0731156291036399E-2</v>
+        <v>2.9182449035646263E-2</v>
       </c>
       <c r="AC3" s="8" t="str">
         <f>IF(OR(AB3="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB3,"低于上限","达到或超过上限"))</f>
@@ -1614,7 +1645,7 @@
       <c r="AD3" s="2"/>
       <c r="AE3" s="7">
         <f t="shared" si="8"/>
-        <v>-3.1930010483941569E-2</v>
+        <v>-3.1930020164661253E-2</v>
       </c>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.15">
@@ -1695,7 +1726,7 @@
       </c>
       <c r="Z4" s="7">
         <f>IF(OR(AE4="",多次统计数据!$B$8=""),"",AE4-多次统计数据!$B$8)</f>
-        <v>-3.6537332211434667E-2</v>
+        <v>8.4308490143450571E-3</v>
       </c>
       <c r="AA4" s="12">
         <f t="shared" si="7"/>
@@ -1703,7 +1734,7 @@
       </c>
       <c r="AB4" s="7">
         <f>IF(OR(A4="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>3.0731156291036399E-2</v>
+        <v>2.9182449035646263E-2</v>
       </c>
       <c r="AC4" s="8" t="str">
         <f>IF(OR(AB4="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB4,"低于上限","达到或超过上限"))</f>
@@ -1793,7 +1824,7 @@
       </c>
       <c r="Z5" s="7">
         <f>IF(OR(AE5="",多次统计数据!$B$8=""),"",AE5-多次统计数据!$B$8)</f>
-        <v>-0.12611153605171233</v>
+        <v>-8.1143354825932587E-2</v>
       </c>
       <c r="AA5" s="12">
         <f t="shared" si="7"/>
@@ -1801,7 +1832,7 @@
       </c>
       <c r="AB5" s="7">
         <f>IF(OR(A5="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>3.0731156291036399E-2</v>
+        <v>2.9182449035646263E-2</v>
       </c>
       <c r="AC5" s="8" t="str">
         <f>IF(OR(AB5="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB5,"低于上限","达到或超过上限"))</f>
@@ -1891,7 +1922,7 @@
       </c>
       <c r="Z6" s="7">
         <f>IF(OR(AE6="",多次统计数据!$B$8=""),"",AE6-多次统计数据!$B$8)</f>
-        <v>-0.12789781145289925</v>
+        <v>-8.2929630227119522E-2</v>
       </c>
       <c r="AA6" s="12">
         <f t="shared" si="7"/>
@@ -1899,7 +1930,7 @@
       </c>
       <c r="AB6" s="7">
         <f>IF(OR(A6="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>3.0731156291036399E-2</v>
+        <v>2.9182449035646263E-2</v>
       </c>
       <c r="AC6" s="8" t="str">
         <f>IF(OR(AB6="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB6,"低于上限","达到或超过上限"))</f>
@@ -1985,7 +2016,7 @@
       </c>
       <c r="Z7" s="7">
         <f>IF(OR(AE7="",多次统计数据!$B$8=""),"",AE7-多次统计数据!$B$8)</f>
-        <v>-0.13727836942183611</v>
+        <v>-9.2310188196056381E-2</v>
       </c>
       <c r="AA7" s="12">
         <f t="shared" si="7"/>
@@ -1993,7 +2024,7 @@
       </c>
       <c r="AB7" s="7">
         <f>IF(OR(A7="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>3.0731156291036399E-2</v>
+        <v>2.9182449035646263E-2</v>
       </c>
       <c r="AC7" s="8" t="str">
         <f>IF(OR(AB7="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB7,"低于上限","达到或超过上限"))</f>
@@ -2227,7 +2258,7 @@
       </c>
       <c r="Z10" s="7">
         <f>IF(OR(AE10="",多次统计数据!$B$8=""),"",AE10-多次统计数据!$B$8)</f>
-        <v>3.6537332211434653E-2</v>
+        <v>8.1505513437214377E-2</v>
       </c>
       <c r="AA10" s="12">
         <f t="shared" si="7"/>
@@ -2235,7 +2266,7 @@
       </c>
       <c r="AB10" s="7">
         <f>IF(OR(A10="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>3.0731156291036399E-2</v>
+        <v>2.9182449035646263E-2</v>
       </c>
       <c r="AC10" s="8" t="str">
         <f>IF(OR(AB10="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB10,"低于上限","达到或超过上限"))</f>
@@ -2321,7 +2352,7 @@
       </c>
       <c r="Z11" s="7">
         <f>IF(OR(AE11="",多次统计数据!$B$8=""),"",AE11-多次统计数据!$B$8)</f>
-        <v>-0.11986649016132365</v>
+        <v>-7.4898308935543931E-2</v>
       </c>
       <c r="AA11" s="12">
         <f t="shared" si="7"/>
@@ -2329,7 +2360,7 @@
       </c>
       <c r="AB11" s="7">
         <f>IF(OR(A11="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>3.0731156291036399E-2</v>
+        <v>2.9182449035646263E-2</v>
       </c>
       <c r="AC11" s="8" t="str">
         <f>IF(OR(AB11="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB11,"低于上限","达到或超过上限"))</f>
@@ -2342,226 +2373,308 @@
       </c>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="8" t="str">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="C12" s="9">
+        <v>98991</v>
+      </c>
+      <c r="D12" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E12" s="9">
+        <v>8.2200000000000006</v>
+      </c>
+      <c r="F12" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3100</v>
       </c>
       <c r="G12" s="8" t="str">
         <f>IF(OR(A12="",F12="",E12="",N12="",E12&lt;=N12,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H12="",F12*(E12-N12),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H12" s="2"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H12" s="2">
+        <v>3100</v>
+      </c>
+      <c r="I12" s="10">
+        <v>44867</v>
+      </c>
+      <c r="J12" s="9">
+        <v>9.5</v>
+      </c>
+      <c r="K12" s="9">
+        <v>8.44</v>
+      </c>
+      <c r="L12" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M12" s="10"/>
-      <c r="N12" s="9"/>
+        <v>3100</v>
+      </c>
+      <c r="M12" s="10">
+        <v>44923</v>
+      </c>
+      <c r="N12" s="9">
+        <v>7.6</v>
+      </c>
       <c r="O12" s="9"/>
       <c r="P12" s="9"/>
       <c r="Q12" s="2"/>
-      <c r="R12" s="2"/>
-      <c r="S12" s="2"/>
+      <c r="R12" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="S12" s="13" t="s">
+        <v>171</v>
+      </c>
       <c r="T12" s="2"/>
-      <c r="U12" s="7" t="str">
+      <c r="U12" s="7">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="V12" s="7" t="str">
+        <v>0.15571776155717754</v>
+      </c>
+      <c r="V12" s="7">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="W12" s="11" t="str">
+        <v>7.5425790754258024E-2</v>
+      </c>
+      <c r="W12" s="11">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="X12" s="5" t="str">
+        <v>2.064516129032254</v>
+      </c>
+      <c r="X12" s="5">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Y12" s="7" t="str">
+        <v>681.99999999999636</v>
+      </c>
+      <c r="Y12" s="7">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="Z12" s="7" t="str">
+        <v>2.6763990267639755E-2</v>
+      </c>
+      <c r="Z12" s="7">
         <f>IF(OR(AE12="",多次统计数据!$B$8=""),"",AE12-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA12" s="12" t="str">
+        <v>-4.6306401127250776E-2</v>
+      </c>
+      <c r="AA12" s="12">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB12" s="7" t="str">
+        <v>56</v>
+      </c>
+      <c r="AB12" s="7">
         <f>IF(OR(A12="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>2.9182449035646263E-2</v>
       </c>
       <c r="AC12" s="8" t="str">
         <f>IF(OR(AB12="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB12,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>达到或超过上限</v>
       </c>
       <c r="AD12" s="2"/>
-      <c r="AE12" s="7" t="str">
+      <c r="AE12" s="7">
         <f t="shared" si="8"/>
-        <v/>
+        <v>6.889515208453257E-3</v>
       </c>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="8" t="str">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="C13" s="9">
+        <v>99673</v>
+      </c>
+      <c r="D13" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E13" s="9">
+        <v>10.38</v>
+      </c>
+      <c r="F13" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>2200</v>
       </c>
       <c r="G13" s="8" t="str">
         <f>IF(OR(A13="",F13="",E13="",N13="",E13&lt;=N13,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H13="",F13*(E13-N13),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H13" s="2"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="9"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H13" s="2">
+        <v>2200</v>
+      </c>
+      <c r="I13" s="10">
+        <v>44979</v>
+      </c>
+      <c r="J13" s="9">
+        <v>12.17</v>
+      </c>
+      <c r="K13" s="9">
+        <v>9.5500000000000007</v>
+      </c>
+      <c r="L13" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M13" s="10"/>
-      <c r="N13" s="9"/>
+        <v>2200</v>
+      </c>
+      <c r="M13" s="10">
+        <v>44995</v>
+      </c>
+      <c r="N13" s="9">
+        <v>9.5</v>
+      </c>
       <c r="O13" s="9"/>
       <c r="P13" s="9"/>
       <c r="Q13" s="2"/>
-      <c r="R13" s="2"/>
-      <c r="S13" s="2"/>
+      <c r="R13" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="S13" s="13" t="s">
+        <v>171</v>
+      </c>
       <c r="T13" s="2"/>
-      <c r="U13" s="7" t="str">
+      <c r="U13" s="7">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="V13" s="7" t="str">
+        <v>0.17244701348747582</v>
+      </c>
+      <c r="V13" s="7">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="W13" s="11" t="str">
+        <v>8.477842003853571E-2</v>
+      </c>
+      <c r="W13" s="11">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="X13" s="5" t="str">
+        <v>2.0340909090909065</v>
+      </c>
+      <c r="X13" s="5">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Y13" s="7" t="str">
+        <v>-1826</v>
+      </c>
+      <c r="Y13" s="7">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="Z13" s="7" t="str">
+        <v>-7.9961464354527945E-2</v>
+      </c>
+      <c r="Z13" s="7">
         <f>IF(OR(AE13="",多次统计数据!$B$8=""),"",AE13-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA13" s="12" t="str">
+        <v>-7.151582242862789E-2</v>
+      </c>
+      <c r="AA13" s="12">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB13" s="7" t="str">
+        <v>16</v>
+      </c>
+      <c r="AB13" s="7">
         <f>IF(OR(A13="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>2.9182449035646263E-2</v>
       </c>
       <c r="AC13" s="8" t="str">
         <f>IF(OR(AB13="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB13,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>达到或超过上限</v>
       </c>
       <c r="AD13" s="2"/>
-      <c r="AE13" s="7" t="str">
+      <c r="AE13" s="7">
         <f t="shared" si="8"/>
-        <v/>
+        <v>-1.831990609292386E-2</v>
       </c>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="8" t="str">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="C14" s="9">
+        <v>97847</v>
+      </c>
+      <c r="D14" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E14" s="9">
+        <v>10.49</v>
+      </c>
+      <c r="F14" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3900</v>
       </c>
       <c r="G14" s="8" t="str">
         <f>IF(OR(A14="",F14="",E14="",N14="",E14&lt;=N14,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H14="",F14*(E14-N14),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H14" s="2"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H14" s="2">
+        <v>3900</v>
+      </c>
+      <c r="I14" s="10">
+        <v>45106</v>
+      </c>
+      <c r="J14" s="9">
+        <v>12</v>
+      </c>
+      <c r="K14" s="9">
+        <v>10.73</v>
+      </c>
+      <c r="L14" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M14" s="10"/>
-      <c r="N14" s="9"/>
+        <v>3900</v>
+      </c>
+      <c r="M14" s="10">
+        <v>45119</v>
+      </c>
+      <c r="N14" s="9">
+        <v>10</v>
+      </c>
       <c r="O14" s="9"/>
       <c r="P14" s="9"/>
       <c r="Q14" s="2"/>
       <c r="R14" s="2"/>
       <c r="S14" s="2"/>
       <c r="T14" s="2"/>
-      <c r="U14" s="7" t="str">
+      <c r="U14" s="7">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="V14" s="7" t="str">
+        <v>0.14394661582459484</v>
+      </c>
+      <c r="V14" s="7">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="W14" s="11" t="str">
+        <v>4.671115347950431E-2</v>
+      </c>
+      <c r="W14" s="11">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="X14" s="5" t="str">
+        <v>3.0816326530612228</v>
+      </c>
+      <c r="X14" s="5">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Y14" s="7" t="str">
+        <v>936</v>
+      </c>
+      <c r="Y14" s="7">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="Z14" s="7" t="str">
+        <v>2.2878932316491896E-2</v>
+      </c>
+      <c r="Z14" s="7">
         <f>IF(OR(AE14="",多次统计数据!$B$8=""),"",AE14-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA14" s="12" t="str">
+        <v>-4.3629961324308686E-2</v>
+      </c>
+      <c r="AA14" s="12">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB14" s="7" t="str">
+        <v>13</v>
+      </c>
+      <c r="AB14" s="7">
         <f>IF(OR(A14="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>2.9182449035646263E-2</v>
       </c>
       <c r="AC14" s="8" t="str">
         <f>IF(OR(AB14="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB14,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>达到或超过上限</v>
       </c>
       <c r="AD14" s="2"/>
-      <c r="AE14" s="7" t="str">
+      <c r="AE14" s="7">
         <f t="shared" si="8"/>
-        <v/>
+        <v>9.5659550113953423E-3</v>
       </c>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.15">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="6"/>
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="C15" s="9">
+        <v>98783</v>
+      </c>
+      <c r="D15" s="6">
+        <v>0.02</v>
+      </c>
       <c r="E15" s="9"/>
       <c r="F15" s="8" t="str">
         <f t="shared" si="0"/>
@@ -2615,13 +2728,13 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AB15" s="7" t="str">
+      <c r="AB15" s="7">
         <f>IF(OR(A15="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>2.9182449035646263E-2</v>
       </c>
       <c r="AC15" s="8" t="str">
         <f>IF(OR(AB15="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB15,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>达到或超过上限</v>
       </c>
       <c r="AD15" s="2"/>
       <c r="AE15" s="7" t="str">
@@ -16270,8 +16383,10 @@
         <v>169</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A11" s="2"/>
+    <row r="11" spans="1:10" ht="27" x14ac:dyDescent="0.15">
+      <c r="A11" s="2">
+        <v>11</v>
+      </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -16279,7 +16394,9 @@
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
+      <c r="I11" s="13" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A12" s="2"/>
@@ -21719,7 +21836,7 @@
       </c>
       <c r="B2" s="8">
         <f>COUNT(单次交易!M2:M201)</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>50</v>
@@ -21731,7 +21848,7 @@
       </c>
       <c r="B3" s="8">
         <f>COUNTIF(单次交易!X2:X201,"&gt;0")</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>52</v>
@@ -21743,7 +21860,7 @@
       </c>
       <c r="B4" s="8">
         <f>COUNTIF(单次交易!X2:X201,"&lt;0")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>54</v>
@@ -21767,7 +21884,7 @@
       </c>
       <c r="B6" s="7">
         <f>IFERROR(B3/(B3+B4),"")</f>
-        <v>0.25</v>
+        <v>0.36363636363636365</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>58</v>
@@ -21779,7 +21896,7 @@
       </c>
       <c r="B7" s="7">
         <f>IFERROR(B4/(B3+B4),"")</f>
-        <v>0.75</v>
+        <v>0.63636363636363635</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>60</v>
@@ -21791,7 +21908,7 @@
       </c>
       <c r="B8" s="7">
         <f>IFERROR(AVERAGEIF(单次交易!X2:X201,"&gt;0",单次交易!AE2:AE201),"")</f>
-        <v>9.8164097561483754E-2</v>
+        <v>5.319591633570403E-2</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>62</v>
@@ -21803,7 +21920,7 @@
       </c>
       <c r="B9" s="7">
         <f>IFERROR(-AVERAGEIF(单次交易!X2:X201,"&lt;0",单次交易!AE2:AE201),"")</f>
-        <v>3.193797122096298E-2</v>
+        <v>2.9992534728488774E-2</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>64</v>
@@ -21815,7 +21932,7 @@
       </c>
       <c r="B10" s="8">
         <f>SUMIF(单次交易!X2:X201,"&gt;0",单次交易!AA2:AA201)</f>
-        <v>22</v>
+        <v>91</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>66</v>
@@ -21827,7 +21944,7 @@
       </c>
       <c r="B11" s="8">
         <f>SUMIF(单次交易!X2:X201,"&lt;0",单次交易!AA2:AA201)</f>
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>66</v>
@@ -21839,7 +21956,7 @@
       </c>
       <c r="B12" s="5">
         <f>IFERROR(SUMPRODUCT(单次交易!E2:E201,单次交易!H2:H201)/COUNT(单次交易!H2:H201),"")</f>
-        <v>86430.125</v>
+        <v>70970</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>69</v>
@@ -21851,7 +21968,7 @@
       </c>
       <c r="B13" s="7">
         <f>IF(OR(B6="",B7="",B8="",B9=""),"",B6*B8-B7*B9)</f>
-        <v>5.8754597464870384E-4</v>
+        <v>2.5781111303588289E-4</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>71</v>
@@ -21863,7 +21980,7 @@
       </c>
       <c r="B14" s="7">
         <f>IF(COUNT(单次交易!AE2:AE201)=0,"",EXP(SUMPRODUCT(IFERROR(LN(1+单次交易!AE2:AE201),0)))-1)</f>
-        <v>0</v>
+        <v>9.565955011395344E-3</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>73</v>
@@ -21913,7 +22030,7 @@
       </c>
       <c r="B3" s="5">
         <f>IF(B2="","",B2+SUM(单次交易!X2:X201))</f>
-        <v>98990.999999999985</v>
+        <v>98782.999999999985</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>79</v>
@@ -21936,7 +22053,7 @@
       </c>
       <c r="B5" s="5">
         <f>IF(B3="","",B3*B4)</f>
-        <v>1979.8199999999997</v>
+        <v>1975.6599999999999</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>83</v>
@@ -21959,7 +22076,7 @@
       </c>
       <c r="B7" s="5">
         <f>IF(B3="","",B3*B6)</f>
-        <v>5939.4599999999991</v>
+        <v>5926.9799999999987</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>87</v>
@@ -21995,7 +22112,7 @@
       </c>
       <c r="B10" s="5">
         <f>IF(OR(B7="",B9=""),"",B7-B9)</f>
-        <v>5939.4599999999991</v>
+        <v>5926.9799999999987</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>93</v>
@@ -22007,7 +22124,7 @@
       </c>
       <c r="B11" s="7">
         <f>IF(OR(B2="",B3="",B2&lt;=0),"",B3/B2-1)</f>
-        <v>-1.0090000000000154E-2</v>
+        <v>-1.2170000000000125E-2</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>95</v>
@@ -22065,7 +22182,7 @@
       </c>
       <c r="B2" s="5">
         <f>账户数据!B3</f>
-        <v>98990.999999999985</v>
+        <v>98782.999999999985</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>97</v>
@@ -22088,7 +22205,7 @@
       </c>
       <c r="B4" s="5">
         <f>IF(OR(B2="",B3=""),"",B2*B3)</f>
-        <v>9899.0999999999985</v>
+        <v>9878.2999999999993</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>101</v>
@@ -22100,7 +22217,7 @@
       </c>
       <c r="B5" s="5">
         <f>多次统计数据!B12</f>
-        <v>86430.125</v>
+        <v>70970</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>102</v>
@@ -22112,7 +22229,7 @@
       </c>
       <c r="B6" s="7">
         <f>多次统计数据!B13</f>
-        <v>5.8754597464870384E-4</v>
+        <v>2.5781111303588289E-4</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>104</v>
@@ -22124,7 +22241,7 @@
       </c>
       <c r="B7" s="8">
         <f>IF(OR(B3="",B6="",B3&lt;=0,B6&lt;=0),"暂不可计算",ROUNDUP(LN(1+B3)/LN(1+B6),0))</f>
-        <v>163</v>
+        <v>370</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>106</v>

--- a/交易管理系统.xlsx
+++ b/交易管理系统.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="14060"/>
+    <workbookView windowWidth="29400" windowHeight="14060" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="单次交易" sheetId="1" r:id="rId1"/>
@@ -151,7 +151,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="187">
   <si>
     <t>交易编号</t>
   </si>
@@ -288,6 +288,9 @@
     <t>新高</t>
   </si>
   <si>
+    <t>通富微电</t>
+  </si>
+  <si>
     <t>所属板块</t>
   </si>
   <si>
@@ -368,6 +371,30 @@
   </si>
   <si>
     <t>1.突然放量，锤子线，2.上升交易量大，下跌交易量小，供己较少</t>
+  </si>
+  <si>
+    <t>1.交易平稳，已经没有多少卖方之前出现过大量交易，需求方逐渐占据上风 2. 前方出现启明星，3支撑比较给力靠近都反弹</t>
+  </si>
+  <si>
+    <t>1.交易量在稳步放大，2.锤子线没有出现大交易量，下方没有太多抛盘了，</t>
+  </si>
+  <si>
+    <t>1.之前下跌，交易量逐渐变小，下方没有卖出，供应减少，2交易放量且增长3.站上均线</t>
+  </si>
+  <si>
+    <t>1.交易量放大，同样的交易量，涨幅变大，供应减少，2.出现跳空突破前压力位</t>
+  </si>
+  <si>
+    <t>1.交易量放大，下方支撑位买入量比较大，可能开始吸筹2.之前有刺透与跳空，那个是第一波</t>
+  </si>
+  <si>
+    <t>1.需求增强，供应减弱，下方的供应被吸收完毕2.两个吞没形态</t>
+  </si>
+  <si>
+    <t>1.交易量放大，之前有看涨 2.支撑比较强力2。看涨吞没3.但是没有之前强。上方还是有不少套牢盘</t>
+  </si>
+  <si>
+    <t>1.下跌的交易量逐步减少，前方锤子与十字星那边可以看出来，供应几乎没有了，2放量上涨站上均线3.可能刚开始吸筹</t>
   </si>
   <si>
     <t>指标</t>
@@ -2071,7 +2098,7 @@
       </c>
       <c r="Z2" s="7">
         <f>IF(OR(AE2="",多次统计数据!$B$8=""),"",AE2-多次统计数据!$B$8)</f>
-        <v>-0.0939134900620892</v>
+        <v>-0.109017318636015</v>
       </c>
       <c r="AA2" s="14">
         <f t="shared" ref="AA2:AA65" si="7">IF(OR(I2="",M2="",M2&lt;I2),"",M2-I2)</f>
@@ -2079,7 +2106,7 @@
       </c>
       <c r="AB2" s="7">
         <f>IF(OR(A2="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0439544480228042</v>
+        <v>0.0583754206956539</v>
       </c>
       <c r="AC2" s="8" t="str">
         <f>IF(OR(AB2="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB2,"低于上限","达到或超过上限"))</f>
@@ -2100,7 +2127,7 @@
       </c>
       <c r="C3" s="5">
         <f>IF(C2="","",C2+SUM(单次交易!Y2:Y201))</f>
-        <v>100000.147487448</v>
+        <v>100000.521735843</v>
       </c>
       <c r="D3" s="6">
         <v>0.02</v>
@@ -2166,7 +2193,7 @@
       </c>
       <c r="Z3" s="7">
         <f>IF(OR(AE3="",多次统计数据!$B$8=""),"",AE3-多次统计数据!$B$8)</f>
-        <v>-0.0846434429694167</v>
+        <v>-0.0997471520466298</v>
       </c>
       <c r="AA3" s="14">
         <f t="shared" si="7"/>
@@ -2174,7 +2201,7 @@
       </c>
       <c r="AB3" s="7">
         <f>IF(OR(A3="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0439544480228042</v>
+        <v>0.0583754206956539</v>
       </c>
       <c r="AC3" s="8" t="str">
         <f>IF(OR(AB3="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB3,"低于上限","达到或超过上限"))</f>
@@ -2183,7 +2210,7 @@
       <c r="AD3" s="2"/>
       <c r="AE3" s="7">
         <f t="shared" si="8"/>
-        <v>-0.0319299529073275</v>
+        <v>-0.0319298334106147</v>
       </c>
     </row>
     <row r="4" ht="17" spans="1:31">
@@ -2264,7 +2291,7 @@
       </c>
       <c r="Z4" s="7">
         <f>IF(OR(AE4="",多次统计数据!$B$8=""),"",AE4-多次统计数据!$B$8)</f>
-        <v>0.00891327528795987</v>
+        <v>-0.00619055328596603</v>
       </c>
       <c r="AA4" s="14">
         <f t="shared" si="7"/>
@@ -2272,7 +2299,7 @@
       </c>
       <c r="AB4" s="7">
         <f>IF(OR(A4="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0439544480228042</v>
+        <v>0.0583754206956539</v>
       </c>
       <c r="AC4" s="8" t="str">
         <f>IF(OR(AB4="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB4,"低于上限","达到或超过上限"))</f>
@@ -2362,7 +2389,7 @@
       </c>
       <c r="Z5" s="7">
         <f>IF(OR(AE5="",多次统计数据!$B$8=""),"",AE5-多次统计数据!$B$8)</f>
-        <v>-0.0806609285523178</v>
+        <v>-0.0957647571262437</v>
       </c>
       <c r="AA5" s="14">
         <f t="shared" si="7"/>
@@ -2370,7 +2397,7 @@
       </c>
       <c r="AB5" s="7">
         <f>IF(OR(A5="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0439544480228042</v>
+        <v>0.0583754206956539</v>
       </c>
       <c r="AC5" s="8" t="str">
         <f>IF(OR(AB5="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB5,"低于上限","达到或超过上限"))</f>
@@ -2460,7 +2487,7 @@
       </c>
       <c r="Z6" s="7">
         <f>IF(OR(AE6="",多次统计数据!$B$8=""),"",AE6-多次统计数据!$B$8)</f>
-        <v>-0.0824472039535047</v>
+        <v>-0.0975510325274306</v>
       </c>
       <c r="AA6" s="14">
         <f t="shared" si="7"/>
@@ -2468,7 +2495,7 @@
       </c>
       <c r="AB6" s="7">
         <f>IF(OR(A6="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0439544480228042</v>
+        <v>0.0583754206956539</v>
       </c>
       <c r="AC6" s="8" t="str">
         <f>IF(OR(AB6="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB6,"低于上限","达到或超过上限"))</f>
@@ -2554,7 +2581,7 @@
       </c>
       <c r="Z7" s="7">
         <f>IF(OR(AE7="",多次统计数据!$B$8=""),"",AE7-多次统计数据!$B$8)</f>
-        <v>-0.0918277619224416</v>
+        <v>-0.106931590496367</v>
       </c>
       <c r="AA7" s="14">
         <f t="shared" si="7"/>
@@ -2562,7 +2589,7 @@
       </c>
       <c r="AB7" s="7">
         <f>IF(OR(A7="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0439544480228042</v>
+        <v>0.0583754206956539</v>
       </c>
       <c r="AC7" s="8" t="str">
         <f>IF(OR(AB7="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB7,"低于上限","达到或超过上限"))</f>
@@ -2796,7 +2823,7 @@
       </c>
       <c r="Z10" s="7">
         <f>IF(OR(AE10="",多次统计数据!$B$8=""),"",AE10-多次统计数据!$B$8)</f>
-        <v>0.0819879397108292</v>
+        <v>0.0668841111369033</v>
       </c>
       <c r="AA10" s="14">
         <f t="shared" si="7"/>
@@ -2804,7 +2831,7 @@
       </c>
       <c r="AB10" s="7">
         <f>IF(OR(A10="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0439544480228042</v>
+        <v>0.0583754206956539</v>
       </c>
       <c r="AC10" s="8" t="str">
         <f>IF(OR(AB10="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB10,"低于上限","达到或超过上限"))</f>
@@ -2890,7 +2917,7 @@
       </c>
       <c r="Z11" s="7">
         <f>IF(OR(AE11="",多次统计数据!$B$8=""),"",AE11-多次统计数据!$B$8)</f>
-        <v>-0.0744158826619291</v>
+        <v>-0.089519711235855</v>
       </c>
       <c r="AA11" s="14">
         <f t="shared" si="7"/>
@@ -2898,7 +2925,7 @@
       </c>
       <c r="AB11" s="7">
         <f>IF(OR(A11="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0439544480228042</v>
+        <v>0.0583754206956539</v>
       </c>
       <c r="AC11" s="8" t="str">
         <f>IF(OR(AB11="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB11,"低于上限","达到或超过上限"))</f>
@@ -2988,7 +3015,7 @@
       </c>
       <c r="Z12" s="7">
         <f>IF(OR(AE12="",多次统计数据!$B$8=""),"",AE12-多次统计数据!$B$8)</f>
-        <v>-0.045823974853636</v>
+        <v>-0.0609278034275619</v>
       </c>
       <c r="AA12" s="14">
         <f t="shared" si="7"/>
@@ -2996,7 +3023,7 @@
       </c>
       <c r="AB12" s="7">
         <f>IF(OR(A12="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0439544480228042</v>
+        <v>0.0583754206956539</v>
       </c>
       <c r="AC12" s="8" t="str">
         <f>IF(OR(AB12="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB12,"低于上限","达到或超过上限"))</f>
@@ -3086,7 +3113,7 @@
       </c>
       <c r="Z13" s="7">
         <f>IF(OR(AE13="",多次统计数据!$B$8=""),"",AE13-多次统计数据!$B$8)</f>
-        <v>-0.0710333961550131</v>
+        <v>-0.086137224728939</v>
       </c>
       <c r="AA13" s="14">
         <f t="shared" si="7"/>
@@ -3094,7 +3121,7 @@
       </c>
       <c r="AB13" s="7">
         <f>IF(OR(A13="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0439544480228042</v>
+        <v>0.0583754206956539</v>
       </c>
       <c r="AC13" s="8" t="str">
         <f>IF(OR(AB13="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB13,"低于上限","达到或超过上限"))</f>
@@ -3184,7 +3211,7 @@
       </c>
       <c r="Z14" s="7">
         <f>IF(OR(AE14="",多次统计数据!$B$8=""),"",AE14-多次统计数据!$B$8)</f>
-        <v>-0.0431475350506939</v>
+        <v>-0.0582513636246198</v>
       </c>
       <c r="AA14" s="14">
         <f t="shared" si="7"/>
@@ -3192,7 +3219,7 @@
       </c>
       <c r="AB14" s="7">
         <f>IF(OR(A14="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0439544480228042</v>
+        <v>0.0583754206956539</v>
       </c>
       <c r="AC14" s="8" t="str">
         <f>IF(OR(AB14="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB14,"低于上限","达到或超过上限"))</f>
@@ -3278,7 +3305,7 @@
       </c>
       <c r="Z15" s="7">
         <f>IF(OR(AE15="",多次统计数据!$B$8=""),"",AE15-多次统计数据!$B$8)</f>
-        <v>0.0125811456545827</v>
+        <v>-0.00252268291934322</v>
       </c>
       <c r="AA15" s="14">
         <f t="shared" si="7"/>
@@ -3286,7 +3313,7 @@
       </c>
       <c r="AB15" s="7">
         <f>IF(OR(A15="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0439544480228042</v>
+        <v>0.0583754206956539</v>
       </c>
       <c r="AC15" s="8" t="str">
         <f>IF(OR(AB15="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB15,"低于上限","达到或超过上限"))</f>
@@ -3372,7 +3399,7 @@
       </c>
       <c r="Z16" s="7">
         <f>IF(OR(AE16="",多次统计数据!$B$8=""),"",AE16-多次统计数据!$B$8)</f>
-        <v>-0.0698183906160979</v>
+        <v>-0.0849222191900238</v>
       </c>
       <c r="AA16" s="14">
         <f t="shared" si="7"/>
@@ -3380,7 +3407,7 @@
       </c>
       <c r="AB16" s="7">
         <f>IF(OR(A16="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0439544480228042</v>
+        <v>0.0583754206956539</v>
       </c>
       <c r="AC16" s="8" t="str">
         <f>IF(OR(AB16="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB16,"低于上限","达到或超过上限"))</f>
@@ -3466,7 +3493,7 @@
       </c>
       <c r="Z17" s="7">
         <f>IF(OR(AE17="",多次统计数据!$B$8=""),"",AE17-多次统计数据!$B$8)</f>
-        <v>-0.043722162342696</v>
+        <v>-0.0588259909166219</v>
       </c>
       <c r="AA17" s="14">
         <f t="shared" si="7"/>
@@ -3474,7 +3501,7 @@
       </c>
       <c r="AB17" s="7">
         <f>IF(OR(A17="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0439544480228042</v>
+        <v>0.0583754206956539</v>
       </c>
       <c r="AC17" s="8" t="str">
         <f>IF(OR(AB17="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB17,"低于上限","达到或超过上限"))</f>
@@ -3560,7 +3587,7 @@
       </c>
       <c r="Z18" s="7">
         <f>IF(OR(AE18="",多次统计数据!$B$8=""),"",AE18-多次统计数据!$B$8)</f>
-        <v>0.0292113115936541</v>
+        <v>0.0141074830197282</v>
       </c>
       <c r="AA18" s="14">
         <f t="shared" si="7"/>
@@ -3568,7 +3595,7 @@
       </c>
       <c r="AB18" s="7">
         <f>IF(OR(A18="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0439544480228042</v>
+        <v>0.0583754206956539</v>
       </c>
       <c r="AC18" s="8" t="str">
         <f>IF(OR(AB18="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB18,"低于上限","达到或超过上限"))</f>
@@ -3581,579 +3608,755 @@
       </c>
     </row>
     <row r="19" ht="17" spans="1:31">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="8" t="str">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" s="9">
+        <v>112913</v>
+      </c>
+      <c r="D19" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E19" s="9">
+        <v>20.1</v>
+      </c>
+      <c r="F19" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>2000</v>
       </c>
       <c r="G19" s="8" t="str">
         <f>IF(OR(A19="",F19="",E19="",N19="",E19&lt;=N19,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H19="",F19*(E19-N19),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H19" s="2"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="9"/>
-      <c r="K19" s="9"/>
-      <c r="L19" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H19" s="2">
+        <v>2000</v>
+      </c>
+      <c r="I19" s="10">
+        <v>44540</v>
+      </c>
+      <c r="J19" s="9">
+        <v>23</v>
+      </c>
+      <c r="K19" s="9">
+        <v>18.9</v>
+      </c>
+      <c r="L19" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M19" s="10"/>
-      <c r="N19" s="9"/>
+        <v>2000</v>
+      </c>
+      <c r="M19" s="10">
+        <v>44550</v>
+      </c>
+      <c r="N19" s="9">
+        <v>19</v>
+      </c>
       <c r="O19" s="9"/>
       <c r="P19" s="9"/>
       <c r="Q19" s="2"/>
       <c r="R19" s="2"/>
       <c r="S19" s="2"/>
       <c r="T19" s="2"/>
-      <c r="U19" s="7" t="str">
+      <c r="U19" s="7">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="V19" s="7" t="str">
+        <v>0.144278606965174</v>
+      </c>
+      <c r="V19" s="7">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="W19" s="13" t="str">
+        <v>0.0547263681592041</v>
+      </c>
+      <c r="W19" s="13">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="X19" s="5" t="str">
+        <v>2.63636363636363</v>
+      </c>
+      <c r="X19" s="5">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Y19" s="7" t="str">
+        <v>-2400</v>
+      </c>
+      <c r="Y19" s="7">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="Z19" s="7" t="str">
+        <v>-0.0597014925373134</v>
+      </c>
+      <c r="Z19" s="7">
         <f>IF(OR(AE19="",多次统计数据!$B$8=""),"",AE19-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA19" s="14" t="str">
+        <v>-0.0890726213912337</v>
+      </c>
+      <c r="AA19" s="14">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB19" s="7" t="str">
+        <v>10</v>
+      </c>
+      <c r="AB19" s="7">
         <f>IF(OR(A19="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0583754206956539</v>
       </c>
       <c r="AC19" s="8" t="str">
         <f>IF(OR(AB19="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB19,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>低于上限</v>
       </c>
       <c r="AD19" s="2"/>
-      <c r="AE19" s="7" t="str">
+      <c r="AE19" s="7">
         <f t="shared" si="8"/>
-        <v/>
+        <v>-0.0212553027552186</v>
       </c>
     </row>
     <row r="20" ht="17" spans="1:31">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="8" t="str">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" s="9">
+        <v>110513</v>
+      </c>
+      <c r="D20" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E20" s="9">
+        <v>14.23</v>
+      </c>
+      <c r="F20" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="G20" s="8" t="str">
         <f>IF(OR(A20="",F20="",E20="",N20="",E20&lt;=N20,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H20="",F20*(E20-N20),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H20" s="2"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="9"/>
-      <c r="K20" s="9"/>
-      <c r="L20" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H20" s="2">
+        <v>3000</v>
+      </c>
+      <c r="I20" s="10">
+        <v>44727</v>
+      </c>
+      <c r="J20" s="9">
+        <v>16</v>
+      </c>
+      <c r="K20" s="9">
+        <v>14.86</v>
+      </c>
+      <c r="L20" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M20" s="10"/>
-      <c r="N20" s="9"/>
+        <v>3000</v>
+      </c>
+      <c r="M20" s="10">
+        <v>44741</v>
+      </c>
+      <c r="N20" s="9">
+        <v>13.5</v>
+      </c>
       <c r="O20" s="9"/>
       <c r="P20" s="9"/>
       <c r="Q20" s="2"/>
       <c r="R20" s="2"/>
       <c r="S20" s="2"/>
       <c r="T20" s="2"/>
-      <c r="U20" s="7" t="str">
+      <c r="U20" s="7">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="V20" s="7" t="str">
+        <v>0.1243851018974</v>
+      </c>
+      <c r="V20" s="7">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="W20" s="13" t="str">
+        <v>0.0513000702740689</v>
+      </c>
+      <c r="W20" s="13">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="X20" s="5" t="str">
+        <v>2.42465753424657</v>
+      </c>
+      <c r="X20" s="5">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Y20" s="7" t="str">
+        <v>1890</v>
+      </c>
+      <c r="Y20" s="7">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="Z20" s="7" t="str">
+        <v>0.0442726633872101</v>
+      </c>
+      <c r="Z20" s="7">
         <f>IF(OR(AE20="",多次统计数据!$B$8=""),"",AE20-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA20" s="14" t="str">
+        <v>-0.0507152582449299</v>
+      </c>
+      <c r="AA20" s="14">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB20" s="7" t="str">
+        <v>14</v>
+      </c>
+      <c r="AB20" s="7">
         <f>IF(OR(A20="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0583754206956539</v>
       </c>
       <c r="AC20" s="8" t="str">
         <f>IF(OR(AB20="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB20,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>低于上限</v>
       </c>
       <c r="AD20" s="2"/>
-      <c r="AE20" s="7" t="str">
+      <c r="AE20" s="7">
         <f t="shared" si="8"/>
-        <v/>
+        <v>0.0171020603910852</v>
       </c>
     </row>
     <row r="21" ht="17" spans="1:31">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="8" t="str">
+      <c r="A21" s="2">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" s="9">
+        <v>112403</v>
+      </c>
+      <c r="D21" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E21" s="9">
+        <v>20.05</v>
+      </c>
+      <c r="F21" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>4000</v>
       </c>
       <c r="G21" s="8" t="str">
         <f>IF(OR(A21="",F21="",E21="",N21="",E21&lt;=N21,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H21="",F21*(E21-N21),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H21" s="2"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="9"/>
-      <c r="K21" s="9"/>
-      <c r="L21" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H21" s="2">
+        <v>4000</v>
+      </c>
+      <c r="I21" s="10">
+        <v>45068</v>
+      </c>
+      <c r="J21" s="9">
+        <v>22.5</v>
+      </c>
+      <c r="K21" s="9">
+        <v>25.16</v>
+      </c>
+      <c r="L21" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M21" s="10"/>
-      <c r="N21" s="9"/>
+        <v>4000</v>
+      </c>
+      <c r="M21" s="10">
+        <v>45091</v>
+      </c>
+      <c r="N21" s="9">
+        <v>19.5</v>
+      </c>
       <c r="O21" s="9"/>
       <c r="P21" s="9"/>
       <c r="Q21" s="2"/>
       <c r="R21" s="2"/>
       <c r="S21" s="2"/>
       <c r="T21" s="2"/>
-      <c r="U21" s="7" t="str">
+      <c r="U21" s="7">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="V21" s="7" t="str">
+        <v>0.122194513715711</v>
+      </c>
+      <c r="V21" s="7">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="W21" s="13" t="str">
+        <v>0.0274314214463841</v>
+      </c>
+      <c r="W21" s="13">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="X21" s="5" t="str">
+        <v>4.45454545454545</v>
+      </c>
+      <c r="X21" s="5">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Y21" s="7" t="str">
+        <v>20440</v>
+      </c>
+      <c r="Y21" s="7">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="Z21" s="7" t="str">
+        <v>0.254862842892768</v>
+      </c>
+      <c r="Z21" s="7">
         <f>IF(OR(AE21="",多次统计数据!$B$8=""),"",AE21-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA21" s="14" t="str">
+        <v>0.114028361639422</v>
+      </c>
+      <c r="AA21" s="14">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB21" s="7" t="str">
+        <v>23</v>
+      </c>
+      <c r="AB21" s="7">
         <f>IF(OR(A21="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0583754206956539</v>
       </c>
       <c r="AC21" s="8" t="str">
         <f>IF(OR(AB21="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB21,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>低于上限</v>
       </c>
       <c r="AD21" s="2"/>
-      <c r="AE21" s="7" t="str">
+      <c r="AE21" s="7">
         <f t="shared" si="8"/>
-        <v/>
+        <v>0.181845680275437</v>
       </c>
     </row>
     <row r="22" ht="17" spans="1:31">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="8" t="str">
+      <c r="A22" s="2">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22" s="9">
+        <v>132843</v>
+      </c>
+      <c r="D22" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E22" s="9">
+        <v>24.36</v>
+      </c>
+      <c r="F22" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>1900</v>
       </c>
       <c r="G22" s="8" t="str">
         <f>IF(OR(A22="",F22="",E22="",N22="",E22&lt;=N22,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H22="",F22*(E22-N22),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H22" s="2"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="9"/>
-      <c r="K22" s="9"/>
-      <c r="L22" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H22" s="2">
+        <v>1900</v>
+      </c>
+      <c r="I22" s="10">
+        <v>45128</v>
+      </c>
+      <c r="J22" s="9">
+        <v>28</v>
+      </c>
+      <c r="K22" s="9">
+        <v>22.11</v>
+      </c>
+      <c r="L22" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M22" s="10"/>
-      <c r="N22" s="9"/>
+        <v>1900</v>
+      </c>
+      <c r="M22" s="10">
+        <v>45134</v>
+      </c>
+      <c r="N22" s="9">
+        <v>23</v>
+      </c>
       <c r="O22" s="9"/>
       <c r="P22" s="9"/>
       <c r="Q22" s="2"/>
       <c r="R22" s="2"/>
       <c r="S22" s="2"/>
       <c r="T22" s="2"/>
-      <c r="U22" s="7" t="str">
+      <c r="U22" s="7">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="V22" s="7" t="str">
+        <v>0.149425287356322</v>
+      </c>
+      <c r="V22" s="7">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="W22" s="13" t="str">
+        <v>0.0558292282430213</v>
+      </c>
+      <c r="W22" s="13">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="X22" s="5" t="str">
+        <v>2.6764705882353</v>
+      </c>
+      <c r="X22" s="5">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Y22" s="7" t="str">
+        <v>-4275</v>
+      </c>
+      <c r="Y22" s="7">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="Z22" s="7" t="str">
+        <v>-0.0923645320197044</v>
+      </c>
+      <c r="Z22" s="7">
         <f>IF(OR(AE22="",多次统计数据!$B$8=""),"",AE22-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA22" s="14" t="str">
+        <v>-0.0999981636937148</v>
+      </c>
+      <c r="AA22" s="14">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB22" s="7" t="str">
+        <v>6</v>
+      </c>
+      <c r="AB22" s="7">
         <f>IF(OR(A22="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0583754206956539</v>
       </c>
       <c r="AC22" s="8" t="str">
         <f>IF(OR(AB22="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB22,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>低于上限</v>
       </c>
       <c r="AD22" s="2"/>
-      <c r="AE22" s="7" t="str">
+      <c r="AE22" s="7">
         <f t="shared" si="8"/>
-        <v/>
+        <v>-0.0321808450576997</v>
       </c>
     </row>
     <row r="23" ht="17" spans="1:31">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="8" t="str">
+      <c r="A23" s="2">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" s="9">
+        <v>128568</v>
+      </c>
+      <c r="D23" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E23" s="9">
+        <v>19.84</v>
+      </c>
+      <c r="F23" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>1300</v>
       </c>
       <c r="G23" s="8" t="str">
         <f>IF(OR(A23="",F23="",E23="",N23="",E23&lt;=N23,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H23="",F23*(E23-N23),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H23" s="2"/>
-      <c r="I23" s="10"/>
-      <c r="J23" s="9"/>
-      <c r="K23" s="9"/>
-      <c r="L23" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H23" s="2">
+        <v>1300</v>
+      </c>
+      <c r="I23" s="10">
+        <v>45218</v>
+      </c>
+      <c r="J23" s="9">
+        <v>24</v>
+      </c>
+      <c r="K23" s="9">
+        <v>17.84</v>
+      </c>
+      <c r="L23" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M23" s="10"/>
-      <c r="N23" s="9"/>
+        <v>1300</v>
+      </c>
+      <c r="M23" s="10">
+        <v>45222</v>
+      </c>
+      <c r="N23" s="9">
+        <v>18</v>
+      </c>
       <c r="O23" s="9"/>
       <c r="P23" s="9"/>
       <c r="Q23" s="2"/>
       <c r="R23" s="2"/>
       <c r="S23" s="2"/>
       <c r="T23" s="2"/>
-      <c r="U23" s="7" t="str">
+      <c r="U23" s="7">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="V23" s="7" t="str">
+        <v>0.209677419354839</v>
+      </c>
+      <c r="V23" s="7">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="W23" s="13" t="str">
+        <v>0.092741935483871</v>
+      </c>
+      <c r="W23" s="13">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="X23" s="5" t="str">
+        <v>2.26086956521739</v>
+      </c>
+      <c r="X23" s="5">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Y23" s="7" t="str">
+        <v>-2600</v>
+      </c>
+      <c r="Y23" s="7">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="Z23" s="7" t="str">
+        <v>-0.100806451612903</v>
+      </c>
+      <c r="Z23" s="7">
         <f>IF(OR(AE23="",多次统计数据!$B$8=""),"",AE23-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA23" s="14" t="str">
+        <v>-0.0880400801318772</v>
+      </c>
+      <c r="AA23" s="14">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB23" s="7" t="str">
+        <v>4</v>
+      </c>
+      <c r="AB23" s="7">
         <f>IF(OR(A23="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0583754206956539</v>
       </c>
       <c r="AC23" s="8" t="str">
         <f>IF(OR(AB23="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB23,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>低于上限</v>
       </c>
       <c r="AD23" s="2"/>
-      <c r="AE23" s="7" t="str">
+      <c r="AE23" s="7">
         <f t="shared" si="8"/>
-        <v/>
+        <v>-0.0202227614958621</v>
       </c>
     </row>
     <row r="24" ht="17" spans="1:31">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="8" t="str">
+      <c r="A24" s="2">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="9">
+        <v>125968</v>
+      </c>
+      <c r="D24" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E24" s="9">
+        <v>21.54</v>
+      </c>
+      <c r="F24" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3400</v>
       </c>
       <c r="G24" s="8" t="str">
         <f>IF(OR(A24="",F24="",E24="",N24="",E24&lt;=N24,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H24="",F24*(E24-N24),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H24" s="2"/>
-      <c r="I24" s="10"/>
-      <c r="J24" s="9"/>
-      <c r="K24" s="9"/>
-      <c r="L24" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H24" s="2">
+        <v>3400</v>
+      </c>
+      <c r="I24" s="10">
+        <v>45439</v>
+      </c>
+      <c r="J24" s="9">
+        <v>27</v>
+      </c>
+      <c r="K24" s="9">
+        <v>23.44</v>
+      </c>
+      <c r="L24" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M24" s="10"/>
-      <c r="N24" s="9"/>
+        <v>3400</v>
+      </c>
+      <c r="M24" s="10">
+        <v>45449</v>
+      </c>
+      <c r="N24" s="9">
+        <v>20.8</v>
+      </c>
       <c r="O24" s="9"/>
       <c r="P24" s="9"/>
       <c r="Q24" s="2"/>
       <c r="R24" s="2"/>
       <c r="S24" s="2"/>
       <c r="T24" s="2"/>
-      <c r="U24" s="7" t="str">
+      <c r="U24" s="7">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="V24" s="7" t="str">
+        <v>0.253481894150418</v>
+      </c>
+      <c r="V24" s="7">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="W24" s="13" t="str">
+        <v>0.0343546889507892</v>
+      </c>
+      <c r="W24" s="13">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="X24" s="5" t="str">
+        <v>7.3783783783784</v>
+      </c>
+      <c r="X24" s="5">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Y24" s="7" t="str">
+        <v>6460</v>
+      </c>
+      <c r="Y24" s="7">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="Z24" s="7" t="str">
+        <v>0.0882079851439183</v>
+      </c>
+      <c r="Z24" s="7">
         <f>IF(OR(AE24="",多次统计数据!$B$8=""),"",AE24-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA24" s="14" t="str">
+        <v>-0.016534453146367</v>
+      </c>
+      <c r="AA24" s="14">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB24" s="7" t="str">
+        <v>10</v>
+      </c>
+      <c r="AB24" s="7">
         <f>IF(OR(A24="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0583754206956539</v>
       </c>
       <c r="AC24" s="8" t="str">
         <f>IF(OR(AB24="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB24,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>低于上限</v>
       </c>
       <c r="AD24" s="2"/>
-      <c r="AE24" s="7" t="str">
+      <c r="AE24" s="7">
         <f t="shared" si="8"/>
-        <v/>
+        <v>0.0512828654896482</v>
       </c>
     </row>
     <row r="25" ht="17" spans="1:31">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="8" t="str">
+      <c r="A25" s="2">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C25" s="9">
+        <v>132428</v>
+      </c>
+      <c r="D25" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E25" s="9">
+        <v>22.04</v>
+      </c>
+      <c r="F25" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>2100</v>
       </c>
       <c r="G25" s="8" t="str">
         <f>IF(OR(A25="",F25="",E25="",N25="",E25&lt;=N25,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H25="",F25*(E25-N25),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H25" s="2"/>
-      <c r="I25" s="10"/>
-      <c r="J25" s="9"/>
-      <c r="K25" s="9"/>
-      <c r="L25" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H25" s="2">
+        <v>2100</v>
+      </c>
+      <c r="I25" s="10">
+        <v>45503</v>
+      </c>
+      <c r="J25" s="9">
+        <v>24.5</v>
+      </c>
+      <c r="K25" s="9">
+        <v>20.51</v>
+      </c>
+      <c r="L25" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M25" s="10"/>
-      <c r="N25" s="9"/>
+        <v>2100</v>
+      </c>
+      <c r="M25" s="10">
+        <v>45509</v>
+      </c>
+      <c r="N25" s="9">
+        <v>20.8</v>
+      </c>
       <c r="O25" s="9"/>
       <c r="P25" s="9"/>
       <c r="Q25" s="2"/>
       <c r="R25" s="2"/>
       <c r="S25" s="2"/>
       <c r="T25" s="2"/>
-      <c r="U25" s="7" t="str">
+      <c r="U25" s="7">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="V25" s="7" t="str">
+        <v>0.111615245009074</v>
+      </c>
+      <c r="V25" s="7">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="W25" s="13" t="str">
+        <v>0.0562613430127041</v>
+      </c>
+      <c r="W25" s="13">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="X25" s="5" t="str">
+        <v>1.98387096774194</v>
+      </c>
+      <c r="X25" s="5">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Y25" s="7" t="str">
+        <v>-3213</v>
+      </c>
+      <c r="Y25" s="7">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="Z25" s="7" t="str">
+        <v>-0.0694192377495463</v>
+      </c>
+      <c r="Z25" s="7">
         <f>IF(OR(AE25="",多次统计数据!$B$8=""),"",AE25-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA25" s="14" t="str">
+        <v>-0.0920795592497826</v>
+      </c>
+      <c r="AA25" s="14">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB25" s="7" t="str">
+        <v>6</v>
+      </c>
+      <c r="AB25" s="7">
         <f>IF(OR(A25="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0583754206956539</v>
       </c>
       <c r="AC25" s="8" t="str">
         <f>IF(OR(AB25="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB25,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>低于上限</v>
       </c>
       <c r="AD25" s="2"/>
-      <c r="AE25" s="7" t="str">
+      <c r="AE25" s="7">
         <f t="shared" si="8"/>
-        <v/>
+        <v>-0.0242622406137675</v>
       </c>
     </row>
     <row r="26" ht="17" spans="1:31">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="8" t="str">
+      <c r="A26" s="2">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C26" s="9">
+        <v>129215</v>
+      </c>
+      <c r="D26" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E26" s="9">
+        <v>18.92</v>
+      </c>
+      <c r="F26" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>2800</v>
       </c>
       <c r="G26" s="8" t="str">
         <f>IF(OR(A26="",F26="",E26="",N26="",E26&lt;=N26,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H26="",F26*(E26-N26),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H26" s="2"/>
-      <c r="I26" s="10"/>
-      <c r="J26" s="9"/>
-      <c r="K26" s="9"/>
-      <c r="L26" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H26" s="2">
+        <v>2800</v>
+      </c>
+      <c r="I26" s="10">
+        <v>45559</v>
+      </c>
+      <c r="J26" s="9">
+        <v>21</v>
+      </c>
+      <c r="K26" s="9">
+        <v>24.77</v>
+      </c>
+      <c r="L26" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M26" s="10"/>
-      <c r="N26" s="9"/>
+        <v>2800</v>
+      </c>
+      <c r="M26" s="10">
+        <v>45574</v>
+      </c>
+      <c r="N26" s="9">
+        <v>18</v>
+      </c>
       <c r="O26" s="9"/>
       <c r="P26" s="9"/>
       <c r="Q26" s="2"/>
       <c r="R26" s="2"/>
       <c r="S26" s="2"/>
       <c r="T26" s="2"/>
-      <c r="U26" s="7" t="str">
+      <c r="U26" s="7">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="V26" s="7" t="str">
+        <v>0.109936575052854</v>
+      </c>
+      <c r="V26" s="7">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="W26" s="13" t="str">
+        <v>0.0486257928118394</v>
+      </c>
+      <c r="W26" s="13">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="X26" s="5" t="str">
+        <v>2.26086956521739</v>
+      </c>
+      <c r="X26" s="5">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Y26" s="7" t="str">
+        <v>16380</v>
+      </c>
+      <c r="Y26" s="7">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="Z26" s="7" t="str">
+        <v>0.309196617336152</v>
+      </c>
+      <c r="Z26" s="7">
         <f>IF(OR(AE26="",多次统计数据!$B$8=""),"",AE26-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA26" s="14" t="str">
+        <v>0.0589481497693557</v>
+      </c>
+      <c r="AA26" s="14">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB26" s="7" t="str">
+        <v>15</v>
+      </c>
+      <c r="AB26" s="7">
         <f>IF(OR(A26="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0583754206956539</v>
       </c>
       <c r="AC26" s="8" t="str">
         <f>IF(OR(AB26="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB26,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>低于上限</v>
       </c>
       <c r="AD26" s="2"/>
-      <c r="AE26" s="7" t="str">
+      <c r="AE26" s="7">
         <f t="shared" si="8"/>
-        <v/>
+        <v>0.126765468405371</v>
       </c>
     </row>
     <row r="27" ht="17" spans="1:31">
@@ -16862,28 +17065,28 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" ht="34" spans="1:10">
@@ -16898,7 +17101,7 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" ht="51" spans="1:10">
@@ -16911,7 +17114,7 @@
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" ht="34" spans="1:10">
@@ -16924,7 +17127,7 @@
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" ht="34" spans="1:10">
@@ -16937,7 +17140,7 @@
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" ht="34" spans="1:10">
@@ -16950,10 +17153,10 @@
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" ht="17" spans="1:10">
@@ -16966,7 +17169,7 @@
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -17003,7 +17206,7 @@
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" ht="34" spans="1:10">
@@ -17018,7 +17221,7 @@
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" ht="51" spans="1:10">
@@ -17033,7 +17236,7 @@
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" ht="34" spans="1:10">
@@ -17048,7 +17251,7 @@
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" ht="34" spans="1:10">
@@ -17063,7 +17266,7 @@
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" ht="34" spans="1:10">
@@ -17078,11 +17281,13 @@
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="2"/>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" ht="51" spans="1:10">
+      <c r="A16" s="2">
+        <v>18</v>
+      </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
@@ -17090,10 +17295,14 @@
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17" s="2"/>
+      <c r="I16" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" ht="34" spans="1:9">
+      <c r="A17" s="2">
+        <v>19</v>
+      </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
@@ -17101,10 +17310,14 @@
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="A18" s="2"/>
+      <c r="I17" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="18" ht="34" spans="1:9">
+      <c r="A18" s="2">
+        <v>20</v>
+      </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
@@ -17112,10 +17325,14 @@
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="A19" s="2"/>
+      <c r="I18" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="19" ht="34" spans="1:9">
+      <c r="A19" s="2">
+        <v>21</v>
+      </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
@@ -17123,10 +17340,14 @@
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-    </row>
-    <row r="20" spans="1:9">
-      <c r="A20" s="2"/>
+      <c r="I19" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" ht="34" spans="1:9">
+      <c r="A20" s="2">
+        <v>22</v>
+      </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
@@ -17134,10 +17355,14 @@
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-    </row>
-    <row r="21" spans="1:9">
-      <c r="A21" s="2"/>
+      <c r="I20" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21" ht="34" spans="1:9">
+      <c r="A21" s="2">
+        <v>23</v>
+      </c>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
@@ -17145,10 +17370,14 @@
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-    </row>
-    <row r="22" spans="1:9">
-      <c r="A22" s="2"/>
+      <c r="I21" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="22" ht="34" spans="1:9">
+      <c r="A22" s="2">
+        <v>24</v>
+      </c>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
@@ -17156,10 +17385,14 @@
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-    </row>
-    <row r="23" spans="1:9">
-      <c r="A23" s="2"/>
+      <c r="I22" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23" ht="51" spans="1:9">
+      <c r="A23" s="2">
+        <v>25</v>
+      </c>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
@@ -17167,7 +17400,9 @@
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
+      <c r="I23" s="2" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="2"/>
@@ -22461,169 +22696,169 @@
   <sheetData>
     <row r="1" ht="17" spans="1:3">
       <c r="A1" s="3" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" ht="17" spans="1:3">
       <c r="A2" s="4" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="B2" s="8">
         <f>COUNT(单次交易!M2:M201)</f>
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" ht="17" spans="1:3">
       <c r="A3" s="4" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="B3" s="8">
         <f>COUNTIF(单次交易!X2:X201,"&gt;0")</f>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" ht="17" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="B4" s="8">
         <f>COUNTIF(单次交易!X2:X201,"&lt;0")</f>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" ht="17" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="B5" s="8">
         <f>COUNTIFS(单次交易!M2:M201,"&lt;&gt;",单次交易!X2:X201,"=0")</f>
         <v>0</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" ht="17" spans="1:3">
       <c r="A6" s="4" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="B6" s="7">
         <f>IFERROR(B3/(B3+B4),"")</f>
-        <v>0.466666666666667</v>
+        <v>0.478260869565217</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" ht="17" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="B7" s="7">
         <f>IFERROR(B4/(B3+B4),"")</f>
-        <v>0.533333333333333</v>
+        <v>0.521739130434783</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" ht="17" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="B8" s="7">
         <f>IFERROR(AVERAGEIF(单次交易!X2:X201,"&gt;0",单次交易!AE2:AE201),"")</f>
-        <v>0.0527134900620892</v>
+        <v>0.0678173186360151</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" ht="17" spans="1:3">
       <c r="A9" s="4" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="B9" s="7">
         <f>IFERROR(-AVERAGEIF(单次交易!X2:X201,"&lt;0",单次交易!AE2:AE201),"")</f>
-        <v>0.028381572049512</v>
+        <v>0.0270811339018276</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" ht="17" spans="1:3">
       <c r="A10" s="4" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="B10" s="8">
         <f>SUMIF(单次交易!X2:X201,"&gt;0",单次交易!AA2:AA201)</f>
-        <v>269</v>
+        <v>331</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" ht="17" spans="1:3">
       <c r="A11" s="4" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="B11" s="8">
         <f>SUMIF(单次交易!X2:X201,"&lt;0",单次交易!AA2:AA201)</f>
-        <v>91</v>
+        <v>117</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" ht="17" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="B12" s="5">
         <f>IFERROR(SUMPRODUCT(单次交易!E2:E201,单次交易!H2:H201)/COUNT(单次交易!H2:H201),"")</f>
-        <v>69330</v>
+        <v>62939.652173913</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13" ht="17" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="B13" s="7">
         <f>IF(OR(B6="",B7="",B8="",B9=""),"",B6*B8-B7*B9)</f>
-        <v>0.00946279026923521</v>
+        <v>0.0183050825293146</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" ht="17" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="B14" s="7">
         <f>IF(COUNT(单次交易!AE2:AE201)=0,"",EXP(SUMPRODUCT(IFERROR(LN(1+单次交易!AE2:AE201),0)))-1)</f>
-        <v>0.130731820265939</v>
+        <v>0.458015637642215</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -22645,130 +22880,130 @@
   <sheetData>
     <row r="1" ht="17" spans="1:3">
       <c r="A1" s="3" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" ht="17" spans="1:3">
       <c r="A2" s="4" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="B2" s="9">
         <v>100000</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" ht="17" spans="1:3">
       <c r="A3" s="4" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="B3" s="5">
         <f>IF(B2="","",B2+SUM(单次交易!X2:X201))</f>
-        <v>112913</v>
+        <v>145595</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" ht="17" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="B4" s="6">
         <v>0.02</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" ht="17" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="B5" s="5">
         <f>IF(B3="","",B3*B4)</f>
-        <v>2258.26</v>
+        <v>2911.9</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" ht="17" spans="1:3">
       <c r="A6" s="4" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="B6" s="6">
         <v>0.06</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" ht="17" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="B7" s="5">
         <f>IF(B3="","",B3*B6)</f>
-        <v>6774.78</v>
+        <v>8735.7</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" ht="17" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="B8" s="5">
         <f ca="1">SUMIFS(单次交易!X2:X201,单次交易!X2:X201,"&lt;0",单次交易!M2:M201,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,单次交易!M2:M201,"&lt;="&amp;EOMONTH(TODAY(),0))</f>
         <v>0</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" ht="17" spans="1:3">
       <c r="A9" s="4" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="B9" s="5">
         <f>IFERROR(SUMPRODUCT((单次交易!M2:M201="")*(单次交易!H2:H201&gt;0)*(单次交易!E2:E201&gt;单次交易!N2:N201)*单次交易!H2:H201*(单次交易!E2:E201-单次交易!N2:N201)),0)</f>
         <v>0</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" ht="17" spans="1:3">
       <c r="A10" s="4" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B10" s="5">
         <f>IF(OR(B7="",B9=""),"",B7-B9)</f>
-        <v>6774.78</v>
+        <v>8735.7</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" ht="17" spans="1:3">
       <c r="A11" s="4" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="B11" s="7">
         <f>IF(OR(B2="",B3="",B2&lt;=0),"",B3/B2-1)</f>
-        <v>0.12913</v>
+        <v>0.45595</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -22809,84 +23044,84 @@
   <sheetData>
     <row r="1" ht="17" spans="1:3">
       <c r="A1" s="3" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" ht="17" spans="1:3">
       <c r="A2" s="4" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="B2" s="5">
         <f>账户数据!B3</f>
-        <v>112913</v>
+        <v>145595</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3" ht="17" spans="1:3">
       <c r="A3" s="4" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="B3" s="6">
         <v>0.1</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" ht="17" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="B4" s="5">
         <f>IF(OR(B2="",B3=""),"",B2*B3)</f>
-        <v>11291.3</v>
+        <v>14559.5</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" ht="17" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="B5" s="5">
         <f>多次统计数据!B12</f>
-        <v>69330</v>
+        <v>62939.652173913</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" ht="17" spans="1:3">
       <c r="A6" s="4" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="B6" s="7">
         <f>多次统计数据!B13</f>
-        <v>0.00946279026923521</v>
+        <v>0.0183050825293146</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" ht="17" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="B7" s="8">
         <f>IF(OR(B3="",B6="",B3&lt;=0,B6&lt;=0),"暂不可计算",ROUNDUP(LN(1+B3)/LN(1+B6),0))</f>
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -22913,233 +23148,233 @@
   <sheetData>
     <row r="1" ht="42" customHeight="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
     </row>
     <row r="2" ht="17" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" ht="17" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" ht="17" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" ht="17" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6" ht="17" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
     </row>
     <row r="7" ht="17" spans="1:3">
       <c r="A7" s="2" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
     </row>
     <row r="8" ht="17" spans="1:3">
       <c r="A8" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>137</v>
-      </c>
       <c r="C8" s="2" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
     </row>
     <row r="9" ht="17" spans="1:3">
       <c r="A9" s="2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
     </row>
     <row r="10" ht="17" spans="1:3">
       <c r="A10" s="2" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11" ht="17" spans="1:3">
       <c r="A11" s="2" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12" ht="17" spans="1:3">
       <c r="A12" s="2" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13" ht="17" spans="1:3">
       <c r="A13" s="2" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
     </row>
     <row r="14" ht="17" spans="1:3">
       <c r="A14" s="2" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
     </row>
     <row r="15" ht="17" spans="1:3">
       <c r="A15" s="2" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16" ht="17" spans="1:3">
       <c r="A16" s="2" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="17" ht="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
     </row>
     <row r="18" ht="17" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
     </row>
     <row r="19" ht="17" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
     </row>
     <row r="20" ht="17" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
     </row>
     <row r="21" ht="17" spans="1:3">
       <c r="A21" s="2" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
     </row>
     <row r="22" spans="1:3">

--- a/交易管理系统.xlsx
+++ b/交易管理系统.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="14060" activeTab="3"/>
+    <workbookView windowWidth="29400" windowHeight="14060"/>
   </bookViews>
   <sheets>
     <sheet name="单次交易" sheetId="1" r:id="rId1"/>
@@ -151,7 +151,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="245">
   <si>
     <t>交易编号</t>
   </si>
@@ -246,6 +246,9 @@
     <t>实际账户收益率</t>
   </si>
   <si>
+    <t>列1</t>
+  </si>
+  <si>
     <t>长电科技</t>
   </si>
   <si>
@@ -291,6 +294,42 @@
     <t>通富微电</t>
   </si>
   <si>
+    <t>比亚迪</t>
+  </si>
+  <si>
+    <t>特别注意，放大了风险</t>
+  </si>
+  <si>
+    <t>沪电股份</t>
+  </si>
+  <si>
+    <t>不遵守纪律</t>
+  </si>
+  <si>
+    <t>深南电路</t>
+  </si>
+  <si>
+    <t>不准守纪律，想上涨</t>
+  </si>
+  <si>
+    <t>盈利比不好，强行买入了</t>
+  </si>
+  <si>
+    <t>不要强跑等确认上升</t>
+  </si>
+  <si>
+    <t>双汇发展</t>
+  </si>
+  <si>
+    <t>航发动力</t>
+  </si>
+  <si>
+    <t>别贪，这是低点反弹</t>
+  </si>
+  <si>
+    <t>东方电气</t>
+  </si>
+  <si>
     <t>所属板块</t>
   </si>
   <si>
@@ -310,9 +349,6 @@
   </si>
   <si>
     <t>综述</t>
-  </si>
-  <si>
-    <t>列1</t>
   </si>
   <si>
     <t>1.超越跳空支撑2.下方海域支撑，3突破之前的压力位，4.交易量放大</t>
@@ -395,6 +431,144 @@
   </si>
   <si>
     <t>1.下跌的交易量逐步减少，前方锤子与十字星那边可以看出来，供应几乎没有了，2放量上涨站上均线3.可能刚开始吸筹</t>
+  </si>
+  <si>
+    <t>1.下跌中都是小实体，说明都被吸收了，开始放量2.出现启明星</t>
+  </si>
+  <si>
+    <t>1.没什么交易量，突然拉升，2，没有破前低，之前感觉想吸筹3，上升空间不是很大，小试一下</t>
+  </si>
+  <si>
+    <t>1.之前十字星大交易没有下跌，努力没有用，说明下方需求旺盛，后面也验证了支撑点2.放量突破80，之前的跳空窗口也被突破了</t>
+  </si>
+  <si>
+    <t>1.交易量与振幅相对之前都扩大了，下跌也比较无力，一直收窄，供应不足，2.80压力位被突破已经站上了</t>
+  </si>
+  <si>
+    <t>1.试一下长线交易，支撑位从80到了85，稳步抬升2.适合长期不适合短期，主力再一点点的吸筹</t>
+  </si>
+  <si>
+    <t>1.突破了70压力位，成交量扩大，顶部供应不足，成交量减少，涨幅变大，缩量上涨</t>
+  </si>
+  <si>
+    <t>1.下跌交易量越来越少，说明供应开始减少，上涨交易量开始增加，量增加，2.本身也是低点，突破了12压力位</t>
+  </si>
+  <si>
+    <t>1.开始吸筹拉高，但是不停的再震荡 波段明显，没有破前低，卖出的但是之前的高位的买入的</t>
+  </si>
+  <si>
+    <t>1.超级大量，第二天低处被吸收，2，低点放量都被吸收了，前方供应不足了，一直在吸收</t>
+  </si>
+  <si>
+    <t>1。供应减少2刺头形态，3前低没破</t>
+  </si>
+  <si>
+    <t>1.成交量大涨。需求旺盛，下跌都是小实体2.突破前期压力点位，新高</t>
+  </si>
+  <si>
+    <t>1.努力没有回报，锤子线，交易量大但是没有下跌，2.小启明星</t>
+  </si>
+  <si>
+    <t>1.前一天大涨，之前同样的交易量小实体说明供应被吸收了，2，当天交易量大但是没有大下跌3，但是收在了尾端，可能不好</t>
+  </si>
+  <si>
+    <t>1.最大量交易量但是没有收跌，13.5有强支撑</t>
+  </si>
+  <si>
+    <t>1.开始上升柱，交易量同步扩大，下跌都是小实体，底部有跳空支撑</t>
+  </si>
+  <si>
+    <t>1.反弹的力度开始变大，买盘小</t>
+  </si>
+  <si>
+    <t>准备走长线交易，做波段，高抛低吸2.下跌没有成功</t>
+  </si>
+  <si>
+    <t>1.上方有压力，不需要大赚2.没破前低，吸收放量</t>
+  </si>
+  <si>
+    <t>1.没有破上升的的位置，低点量很大但是没下跌，2.上方压力大，3位置舒服</t>
+  </si>
+  <si>
+    <t>1.交易放量，下方吸收的差不多了，启明星2.交易量逐步放大了</t>
+  </si>
+  <si>
+    <t>1.交易量逐渐缩小，2.50是比较明显的支撑位置，会有人买入</t>
+  </si>
+  <si>
+    <t>1.跌幅在缩小，2出现10字星，3.50支撑明显</t>
+  </si>
+  <si>
+    <t>1.底部交易量放大，被吸收了，2。十字形</t>
+  </si>
+  <si>
+    <t>1.下跌无力没有跌破大阳线，前期触碰 100</t>
+  </si>
+  <si>
+    <t>同上，130是强支撑</t>
+  </si>
+  <si>
+    <t>1.大交易量之后回调，下跌都是小实体2.回调不破前低</t>
+  </si>
+  <si>
+    <t>1.j红色柱体开始增多，下跌都是小实体 2.两个看涨吞没状态</t>
+  </si>
+  <si>
+    <t>1.前方跳空，红柱站优势，2交易量不是很大，没有显著突破</t>
+  </si>
+  <si>
+    <t>1.交易量扩大，下跌中的交易量都被吸收了，开始反弹 2，没有明显的反弹信号，绿柱更站优势</t>
+  </si>
+  <si>
+    <t>1.上涨趋势，下跌都是小实体被吸收了，开始继续上涨，但是柱体不是太强</t>
+  </si>
+  <si>
+    <t>1.大红柱，交易量上升，2.看涨吞没 + 跳空没有被击穿，在支撑下方购买 3.交易量不大，可能没经</t>
+  </si>
+  <si>
+    <t>1.上涨趋势中，回调买入，没有破之前的支撑，下跌交易量变小，但是柱体不是很小，回谈没什么力气</t>
+  </si>
+  <si>
+    <t>1.需求方强势，供应不足，红柱不破买入，就是红柱柱体太小了，交易量不大</t>
+  </si>
+  <si>
+    <t>1.出现大红柱，等等回调没有破后买入，交易量不大，没有明显反转型号</t>
+  </si>
+  <si>
+    <t>1.刺透加十字星，放量但是没有下跌</t>
+  </si>
+  <si>
+    <t>1.需求占优势，然后下跌没有破大红柱，下跌都是小实体，但是前方有上影线+ 成交量，有压力</t>
+  </si>
+  <si>
+    <t>1.跳空，放量，之前有恐慌抛盘，下跌没到低点，需求方站优势</t>
+  </si>
+  <si>
+    <t>1.目前处于右端2，锤子筑底，红柱没有被突破2.但是交易量没那么大，总体再变大</t>
+  </si>
+  <si>
+    <t>1.右侧交易，没有跌破红柱，但是交易量减少了2.下方支撑比较强硬</t>
+  </si>
+  <si>
+    <t>1.右侧交易，没有跌破红柱，交易量开放大，可能已经完成吸筹，</t>
+  </si>
+  <si>
+    <t>1.右侧交易，回撤没破前面的红柱，总体交易量降低，上冲没什么力气，遇到危险信号就跑</t>
+  </si>
+  <si>
+    <t>1.右侧交易  需求站优势，小柱体没破前面的红柱2.交易量不大，之前两个看涨大吞没</t>
+  </si>
+  <si>
+    <t>与上一次完全一样的剧情</t>
+  </si>
+  <si>
+    <t>又是一样的剧情，不知道是商贩</t>
+  </si>
+  <si>
+    <t>上升右侧，交易放量，没有跌破前低 2上方有影线，是一个看涨吞没</t>
+  </si>
+  <si>
+    <t>上升平台交易，显著高于之前的红柱</t>
   </si>
   <si>
     <t>指标</t>
@@ -1526,9 +1700,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TradeRecords" displayName="TradeRecords" ref="A1:AE201">
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AE201" etc:filterBottomFollowUsedRange="0"/>
-  <tableColumns count="31">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TradeRecords" displayName="TradeRecords" ref="A1:AF201">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AF201" etc:filterBottomFollowUsedRange="0"/>
+  <tableColumns count="32">
     <tableColumn id="1" name="交易编号"/>
     <tableColumn id="2" name="股票代码"/>
     <tableColumn id="3" name="买入时账户金额"/>
@@ -1586,6 +1760,7 @@
     <tableColumn id="31" name="实际账户收益率">
       <calculatedColumnFormula>IF(OR(X2="",C2="",C2&lt;=0),"",X2/C2)</calculatedColumnFormula>
     </tableColumn>
+    <tableColumn id="32" name="列1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1907,7 +2082,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AE201"/>
+  <dimension ref="A1:AF201"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="2" width="14" customWidth="1"/>
@@ -1916,7 +2091,9 @@
     <col min="5" max="5" width="14" customWidth="1"/>
     <col min="6" max="8" width="16" customWidth="1"/>
     <col min="9" max="9" width="13" customWidth="1"/>
-    <col min="10" max="12" width="14" customWidth="1"/>
+    <col min="10" max="10" width="14.4230769230769" customWidth="1"/>
+    <col min="11" max="11" width="15.0576923076923" customWidth="1"/>
+    <col min="12" max="12" width="14" customWidth="1"/>
     <col min="13" max="13" width="13" customWidth="1"/>
     <col min="14" max="16" width="14" customWidth="1"/>
     <col min="17" max="20" width="24" customWidth="1"/>
@@ -1925,7 +2102,7 @@
     <col min="29" max="31" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="42" customHeight="1" spans="1:31">
+    <row r="1" ht="42" customHeight="1" spans="1:32">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2019,13 +2196,16 @@
       <c r="AE1" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="2" ht="17" spans="1:31">
+      <c r="AF1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" ht="17" spans="1:32">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2" s="9">
         <v>100000</v>
@@ -2070,10 +2250,10 @@
       <c r="P2" s="9"/>
       <c r="Q2" s="2"/>
       <c r="R2" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="T2" s="2"/>
       <c r="U2" s="7">
@@ -2098,7 +2278,7 @@
       </c>
       <c r="Z2" s="7">
         <f>IF(OR(AE2="",多次统计数据!$B$8=""),"",AE2-多次统计数据!$B$8)</f>
-        <v>-0.109017318636015</v>
+        <v>-0.100433514464113</v>
       </c>
       <c r="AA2" s="14">
         <f t="shared" ref="AA2:AA65" si="7">IF(OR(I2="",M2="",M2&lt;I2),"",M2-I2)</f>
@@ -2106,7 +2286,7 @@
       </c>
       <c r="AB2" s="7">
         <f>IF(OR(A2="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0583754206956539</v>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC2" s="8" t="str">
         <f>IF(OR(AB2="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB2,"低于上限","达到或超过上限"))</f>
@@ -2118,16 +2298,16 @@
         <v>-0.0412</v>
       </c>
     </row>
-    <row r="3" ht="17" spans="1:31">
+    <row r="3" ht="17" spans="1:32">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C3" s="5">
         <f>IF(C2="","",C2+SUM(单次交易!Y2:Y201))</f>
-        <v>100000.521735843</v>
+        <v>100001.051939774</v>
       </c>
       <c r="D3" s="6">
         <v>0.02</v>
@@ -2193,7 +2373,7 @@
       </c>
       <c r="Z3" s="7">
         <f>IF(OR(AE3="",多次统计数据!$B$8=""),"",AE3-多次统计数据!$B$8)</f>
-        <v>-0.0997471520466298</v>
+        <v>-0.0911631785832771</v>
       </c>
       <c r="AA3" s="14">
         <f t="shared" si="7"/>
@@ -2201,7 +2381,7 @@
       </c>
       <c r="AB3" s="7">
         <f>IF(OR(A3="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0583754206956539</v>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC3" s="8" t="str">
         <f>IF(OR(AB3="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB3,"低于上限","达到或超过上限"))</f>
@@ -2210,15 +2390,15 @@
       <c r="AD3" s="2"/>
       <c r="AE3" s="7">
         <f t="shared" si="8"/>
-        <v>-0.0319298334106147</v>
-      </c>
-    </row>
-    <row r="4" ht="17" spans="1:31">
+        <v>-0.0319296641191637</v>
+      </c>
+    </row>
+    <row r="4" ht="17" spans="1:32">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C4" s="9">
         <v>92687</v>
@@ -2263,10 +2443,10 @@
       <c r="P4" s="9"/>
       <c r="Q4" s="2"/>
       <c r="R4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T4" s="2"/>
       <c r="U4" s="7">
@@ -2291,7 +2471,7 @@
       </c>
       <c r="Z4" s="7">
         <f>IF(OR(AE4="",多次统计数据!$B$8=""),"",AE4-多次统计数据!$B$8)</f>
-        <v>-0.00619055328596603</v>
+        <v>0.00239325088593565</v>
       </c>
       <c r="AA4" s="14">
         <f t="shared" si="7"/>
@@ -2299,7 +2479,7 @@
       </c>
       <c r="AB4" s="7">
         <f>IF(OR(A4="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0583754206956539</v>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC4" s="8" t="str">
         <f>IF(OR(AB4="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB4,"低于上限","达到或超过上限"))</f>
@@ -2311,12 +2491,12 @@
         <v>0.0616267653500491</v>
       </c>
     </row>
-    <row r="5" ht="17" spans="1:31">
+    <row r="5" ht="17" spans="1:32">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C5" s="9">
         <v>98399</v>
@@ -2361,10 +2541,10 @@
       <c r="P5" s="9"/>
       <c r="Q5" s="2"/>
       <c r="R5" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S5" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T5" s="2"/>
       <c r="U5" s="7">
@@ -2389,7 +2569,7 @@
       </c>
       <c r="Z5" s="7">
         <f>IF(OR(AE5="",多次统计数据!$B$8=""),"",AE5-多次统计数据!$B$8)</f>
-        <v>-0.0957647571262437</v>
+        <v>-0.087180952954342</v>
       </c>
       <c r="AA5" s="14">
         <f t="shared" si="7"/>
@@ -2397,7 +2577,7 @@
       </c>
       <c r="AB5" s="7">
         <f>IF(OR(A5="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0583754206956539</v>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC5" s="8" t="str">
         <f>IF(OR(AB5="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB5,"低于上限","达到或超过上限"))</f>
@@ -2409,12 +2589,12 @@
         <v>-0.0279474384902286</v>
       </c>
     </row>
-    <row r="6" ht="17" spans="1:31">
+    <row r="6" ht="17" spans="1:32">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C6" s="9">
         <v>95649</v>
@@ -2459,10 +2639,10 @@
       <c r="P6" s="9"/>
       <c r="Q6" s="2"/>
       <c r="R6" s="11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S6" s="11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="T6" s="2"/>
       <c r="U6" s="7">
@@ -2487,7 +2667,7 @@
       </c>
       <c r="Z6" s="7">
         <f>IF(OR(AE6="",多次统计数据!$B$8=""),"",AE6-多次统计数据!$B$8)</f>
-        <v>-0.0975510325274306</v>
+        <v>-0.0889672283555289</v>
       </c>
       <c r="AA6" s="14">
         <f t="shared" si="7"/>
@@ -2495,7 +2675,7 @@
       </c>
       <c r="AB6" s="7">
         <f>IF(OR(A6="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0583754206956539</v>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC6" s="8" t="str">
         <f>IF(OR(AB6="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB6,"低于上限","达到或超过上限"))</f>
@@ -2507,12 +2687,12 @@
         <v>-0.0297337138914155</v>
       </c>
     </row>
-    <row r="7" ht="17" spans="1:31">
+    <row r="7" ht="17" spans="1:32">
       <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C7" s="9">
         <v>92805</v>
@@ -2581,7 +2761,7 @@
       </c>
       <c r="Z7" s="7">
         <f>IF(OR(AE7="",多次统计数据!$B$8=""),"",AE7-多次统计数据!$B$8)</f>
-        <v>-0.106931590496367</v>
+        <v>-0.0983477863244658</v>
       </c>
       <c r="AA7" s="14">
         <f t="shared" si="7"/>
@@ -2589,7 +2769,7 @@
       </c>
       <c r="AB7" s="7">
         <f>IF(OR(A7="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0583754206956539</v>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC7" s="8" t="str">
         <f>IF(OR(AB7="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB7,"低于上限","达到或超过上限"))</f>
@@ -2601,7 +2781,7 @@
         <v>-0.0391142718603524</v>
       </c>
     </row>
-    <row r="8" ht="17" spans="1:31">
+    <row r="8" ht="17" spans="1:32">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="9"/>
@@ -2673,7 +2853,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="17" spans="1:31">
+    <row r="9" ht="17" spans="1:32">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="9"/>
@@ -2745,12 +2925,12 @@
         <v/>
       </c>
     </row>
-    <row r="10" ht="34" spans="1:31">
+    <row r="10" ht="34" spans="1:32">
       <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C10" s="9">
         <v>89175</v>
@@ -2795,10 +2975,10 @@
       <c r="P10" s="9"/>
       <c r="Q10" s="2"/>
       <c r="R10" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="S10" s="11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="T10" s="2"/>
       <c r="U10" s="7">
@@ -2823,7 +3003,7 @@
       </c>
       <c r="Z10" s="7">
         <f>IF(OR(AE10="",多次统计数据!$B$8=""),"",AE10-多次统计数据!$B$8)</f>
-        <v>0.0668841111369033</v>
+        <v>0.075467915308805</v>
       </c>
       <c r="AA10" s="14">
         <f t="shared" si="7"/>
@@ -2831,7 +3011,7 @@
       </c>
       <c r="AB10" s="7">
         <f>IF(OR(A10="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0583754206956539</v>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC10" s="8" t="str">
         <f>IF(OR(AB10="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB10,"低于上限","达到或超过上限"))</f>
@@ -2843,12 +3023,12 @@
         <v>0.134701429772918</v>
       </c>
     </row>
-    <row r="11" ht="17" spans="1:31">
+    <row r="11" ht="17" spans="1:32">
       <c r="A11" s="2">
         <v>10</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C11" s="9">
         <v>101187</v>
@@ -2917,7 +3097,7 @@
       </c>
       <c r="Z11" s="7">
         <f>IF(OR(AE11="",多次统计数据!$B$8=""),"",AE11-多次统计数据!$B$8)</f>
-        <v>-0.089519711235855</v>
+        <v>-0.0809359070639533</v>
       </c>
       <c r="AA11" s="14">
         <f t="shared" si="7"/>
@@ -2925,7 +3105,7 @@
       </c>
       <c r="AB11" s="7">
         <f>IF(OR(A11="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0583754206956539</v>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC11" s="8" t="str">
         <f>IF(OR(AB11="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB11,"低于上限","达到或超过上限"))</f>
@@ -2937,12 +3117,12 @@
         <v>-0.0217023925998399</v>
       </c>
     </row>
-    <row r="12" ht="17" spans="1:31">
+    <row r="12" ht="17" spans="1:32">
       <c r="A12" s="2">
         <v>11</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C12" s="9">
         <v>98991</v>
@@ -2987,10 +3167,10 @@
       <c r="P12" s="9"/>
       <c r="Q12" s="2"/>
       <c r="R12" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="S12" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="T12" s="2"/>
       <c r="U12" s="7">
@@ -3015,7 +3195,7 @@
       </c>
       <c r="Z12" s="7">
         <f>IF(OR(AE12="",多次统计数据!$B$8=""),"",AE12-多次统计数据!$B$8)</f>
-        <v>-0.0609278034275619</v>
+        <v>-0.0523439992556602</v>
       </c>
       <c r="AA12" s="14">
         <f t="shared" si="7"/>
@@ -3023,7 +3203,7 @@
       </c>
       <c r="AB12" s="7">
         <f>IF(OR(A12="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0583754206956539</v>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC12" s="8" t="str">
         <f>IF(OR(AB12="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB12,"低于上限","达到或超过上限"))</f>
@@ -3035,12 +3215,12 @@
         <v>0.00688951520845326</v>
       </c>
     </row>
-    <row r="13" ht="17" spans="1:31">
+    <row r="13" ht="17" spans="1:32">
       <c r="A13" s="2">
         <v>12</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C13" s="9">
         <v>99673</v>
@@ -3085,10 +3265,10 @@
       <c r="P13" s="9"/>
       <c r="Q13" s="2"/>
       <c r="R13" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="S13" s="11" t="s">
         <v>43</v>
-      </c>
-      <c r="S13" s="11" t="s">
-        <v>42</v>
       </c>
       <c r="T13" s="2"/>
       <c r="U13" s="7">
@@ -3113,7 +3293,7 @@
       </c>
       <c r="Z13" s="7">
         <f>IF(OR(AE13="",多次统计数据!$B$8=""),"",AE13-多次统计数据!$B$8)</f>
-        <v>-0.086137224728939</v>
+        <v>-0.0775534205570373</v>
       </c>
       <c r="AA13" s="14">
         <f t="shared" si="7"/>
@@ -3121,7 +3301,7 @@
       </c>
       <c r="AB13" s="7">
         <f>IF(OR(A13="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0583754206956539</v>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC13" s="8" t="str">
         <f>IF(OR(AB13="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB13,"低于上限","达到或超过上限"))</f>
@@ -3133,12 +3313,12 @@
         <v>-0.0183199060929239</v>
       </c>
     </row>
-    <row r="14" ht="17" spans="1:31">
+    <row r="14" ht="17" spans="1:32">
       <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C14" s="9">
         <v>97847</v>
@@ -3183,10 +3363,10 @@
       <c r="P14" s="9"/>
       <c r="Q14" s="2"/>
       <c r="R14" s="11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="T14" s="2"/>
       <c r="U14" s="7">
@@ -3211,7 +3391,7 @@
       </c>
       <c r="Z14" s="7">
         <f>IF(OR(AE14="",多次统计数据!$B$8=""),"",AE14-多次统计数据!$B$8)</f>
-        <v>-0.0582513636246198</v>
+        <v>-0.0496675594527181</v>
       </c>
       <c r="AA14" s="14">
         <f t="shared" si="7"/>
@@ -3219,7 +3399,7 @@
       </c>
       <c r="AB14" s="7">
         <f>IF(OR(A14="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0583754206956539</v>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC14" s="8" t="str">
         <f>IF(OR(AB14="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB14,"低于上限","达到或超过上限"))</f>
@@ -3231,12 +3411,12 @@
         <v>0.00956595501139534</v>
       </c>
     </row>
-    <row r="15" ht="17" spans="1:31">
+    <row r="15" ht="17" spans="1:32">
       <c r="A15" s="2">
         <v>14</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C15" s="9">
         <v>98783</v>
@@ -3259,7 +3439,7 @@
         <v>7500</v>
       </c>
       <c r="I15" s="10">
-        <v>45216</v>
+        <v>45320</v>
       </c>
       <c r="J15" s="9">
         <v>11</v>
@@ -3305,15 +3485,15 @@
       </c>
       <c r="Z15" s="7">
         <f>IF(OR(AE15="",多次统计数据!$B$8=""),"",AE15-多次统计数据!$B$8)</f>
-        <v>-0.00252268291934322</v>
+        <v>0.00606112125255846</v>
       </c>
       <c r="AA15" s="14">
         <f t="shared" si="7"/>
-        <v>107</v>
+        <v>3</v>
       </c>
       <c r="AB15" s="7">
         <f>IF(OR(A15="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0583754206956539</v>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC15" s="8" t="str">
         <f>IF(OR(AB15="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB15,"低于上限","达到或超过上限"))</f>
@@ -3325,12 +3505,12 @@
         <v>0.0652946357166719</v>
       </c>
     </row>
-    <row r="16" ht="17" spans="1:31">
+    <row r="16" ht="17" spans="1:32">
       <c r="A16" s="2">
         <v>15</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C16" s="9">
         <v>105233</v>
@@ -3399,7 +3579,7 @@
       </c>
       <c r="Z16" s="7">
         <f>IF(OR(AE16="",多次统计数据!$B$8=""),"",AE16-多次统计数据!$B$8)</f>
-        <v>-0.0849222191900238</v>
+        <v>-0.0763384150181222</v>
       </c>
       <c r="AA16" s="14">
         <f t="shared" si="7"/>
@@ -3407,7 +3587,7 @@
       </c>
       <c r="AB16" s="7">
         <f>IF(OR(A16="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0583754206956539</v>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC16" s="8" t="str">
         <f>IF(OR(AB16="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB16,"低于上限","达到或超过上限"))</f>
@@ -3419,12 +3599,12 @@
         <v>-0.0171049005540087</v>
       </c>
     </row>
-    <row r="17" ht="17" spans="1:31">
+    <row r="17" ht="17" spans="1:32">
       <c r="A17" s="2">
         <v>16</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C17" s="9">
         <v>103433</v>
@@ -3493,7 +3673,7 @@
       </c>
       <c r="Z17" s="7">
         <f>IF(OR(AE17="",多次统计数据!$B$8=""),"",AE17-多次统计数据!$B$8)</f>
-        <v>-0.0588259909166219</v>
+        <v>-0.0502421867447202</v>
       </c>
       <c r="AA17" s="14">
         <f t="shared" si="7"/>
@@ -3501,7 +3681,7 @@
       </c>
       <c r="AB17" s="7">
         <f>IF(OR(A17="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0583754206956539</v>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC17" s="8" t="str">
         <f>IF(OR(AB17="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB17,"低于上限","达到或超过上限"))</f>
@@ -3513,12 +3693,12 @@
         <v>0.00899132771939323</v>
       </c>
     </row>
-    <row r="18" ht="17" spans="1:31">
+    <row r="18" ht="17" spans="1:32">
       <c r="A18" s="2">
         <v>17</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C18" s="9">
         <v>104364</v>
@@ -3587,7 +3767,7 @@
       </c>
       <c r="Z18" s="7">
         <f>IF(OR(AE18="",多次统计数据!$B$8=""),"",AE18-多次统计数据!$B$8)</f>
-        <v>0.0141074830197282</v>
+        <v>0.0226912871916299</v>
       </c>
       <c r="AA18" s="14">
         <f t="shared" si="7"/>
@@ -3595,7 +3775,7 @@
       </c>
       <c r="AB18" s="7">
         <f>IF(OR(A18="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0583754206956539</v>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC18" s="8" t="str">
         <f>IF(OR(AB18="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB18,"低于上限","达到或超过上限"))</f>
@@ -3607,12 +3787,12 @@
         <v>0.0819248016557434</v>
       </c>
     </row>
-    <row r="19" ht="17" spans="1:31">
+    <row r="19" ht="17" spans="1:32">
       <c r="A19" s="2">
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C19" s="9">
         <v>112913</v>
@@ -3681,7 +3861,7 @@
       </c>
       <c r="Z19" s="7">
         <f>IF(OR(AE19="",多次统计数据!$B$8=""),"",AE19-多次统计数据!$B$8)</f>
-        <v>-0.0890726213912337</v>
+        <v>-0.0804888172193321</v>
       </c>
       <c r="AA19" s="14">
         <f t="shared" si="7"/>
@@ -3689,7 +3869,7 @@
       </c>
       <c r="AB19" s="7">
         <f>IF(OR(A19="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0583754206956539</v>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC19" s="8" t="str">
         <f>IF(OR(AB19="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB19,"低于上限","达到或超过上限"))</f>
@@ -3701,12 +3881,12 @@
         <v>-0.0212553027552186</v>
       </c>
     </row>
-    <row r="20" ht="17" spans="1:31">
+    <row r="20" ht="17" spans="1:32">
       <c r="A20" s="2">
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C20" s="9">
         <v>110513</v>
@@ -3775,7 +3955,7 @@
       </c>
       <c r="Z20" s="7">
         <f>IF(OR(AE20="",多次统计数据!$B$8=""),"",AE20-多次统计数据!$B$8)</f>
-        <v>-0.0507152582449299</v>
+        <v>-0.0421314540730282</v>
       </c>
       <c r="AA20" s="14">
         <f t="shared" si="7"/>
@@ -3783,7 +3963,7 @@
       </c>
       <c r="AB20" s="7">
         <f>IF(OR(A20="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0583754206956539</v>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC20" s="8" t="str">
         <f>IF(OR(AB20="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB20,"低于上限","达到或超过上限"))</f>
@@ -3795,12 +3975,12 @@
         <v>0.0171020603910852</v>
       </c>
     </row>
-    <row r="21" ht="17" spans="1:31">
+    <row r="21" ht="17" spans="1:32">
       <c r="A21" s="2">
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C21" s="9">
         <v>112403</v>
@@ -3869,7 +4049,7 @@
       </c>
       <c r="Z21" s="7">
         <f>IF(OR(AE21="",多次统计数据!$B$8=""),"",AE21-多次统计数据!$B$8)</f>
-        <v>0.114028361639422</v>
+        <v>0.122612165811324</v>
       </c>
       <c r="AA21" s="14">
         <f t="shared" si="7"/>
@@ -3877,7 +4057,7 @@
       </c>
       <c r="AB21" s="7">
         <f>IF(OR(A21="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0583754206956539</v>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC21" s="8" t="str">
         <f>IF(OR(AB21="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB21,"低于上限","达到或超过上限"))</f>
@@ -3889,12 +4069,12 @@
         <v>0.181845680275437</v>
       </c>
     </row>
-    <row r="22" ht="17" spans="1:31">
+    <row r="22" ht="17" spans="1:32">
       <c r="A22" s="2">
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C22" s="9">
         <v>132843</v>
@@ -3963,7 +4143,7 @@
       </c>
       <c r="Z22" s="7">
         <f>IF(OR(AE22="",多次统计数据!$B$8=""),"",AE22-多次统计数据!$B$8)</f>
-        <v>-0.0999981636937148</v>
+        <v>-0.0914143595218131</v>
       </c>
       <c r="AA22" s="14">
         <f t="shared" si="7"/>
@@ -3971,7 +4151,7 @@
       </c>
       <c r="AB22" s="7">
         <f>IF(OR(A22="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0583754206956539</v>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC22" s="8" t="str">
         <f>IF(OR(AB22="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB22,"低于上限","达到或超过上限"))</f>
@@ -3983,12 +4163,12 @@
         <v>-0.0321808450576997</v>
       </c>
     </row>
-    <row r="23" ht="17" spans="1:31">
+    <row r="23" ht="17" spans="1:32">
       <c r="A23" s="2">
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C23" s="9">
         <v>128568</v>
@@ -4057,7 +4237,7 @@
       </c>
       <c r="Z23" s="7">
         <f>IF(OR(AE23="",多次统计数据!$B$8=""),"",AE23-多次统计数据!$B$8)</f>
-        <v>-0.0880400801318772</v>
+        <v>-0.0794562759599755</v>
       </c>
       <c r="AA23" s="14">
         <f t="shared" si="7"/>
@@ -4065,7 +4245,7 @@
       </c>
       <c r="AB23" s="7">
         <f>IF(OR(A23="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0583754206956539</v>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC23" s="8" t="str">
         <f>IF(OR(AB23="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB23,"低于上限","达到或超过上限"))</f>
@@ -4077,12 +4257,12 @@
         <v>-0.0202227614958621</v>
       </c>
     </row>
-    <row r="24" ht="17" spans="1:31">
+    <row r="24" ht="17" spans="1:32">
       <c r="A24" s="2">
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C24" s="9">
         <v>125968</v>
@@ -4151,7 +4331,7 @@
       </c>
       <c r="Z24" s="7">
         <f>IF(OR(AE24="",多次统计数据!$B$8=""),"",AE24-多次统计数据!$B$8)</f>
-        <v>-0.016534453146367</v>
+        <v>-0.00795064897446527</v>
       </c>
       <c r="AA24" s="14">
         <f t="shared" si="7"/>
@@ -4159,7 +4339,7 @@
       </c>
       <c r="AB24" s="7">
         <f>IF(OR(A24="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0583754206956539</v>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC24" s="8" t="str">
         <f>IF(OR(AB24="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB24,"低于上限","达到或超过上限"))</f>
@@ -4171,12 +4351,12 @@
         <v>0.0512828654896482</v>
       </c>
     </row>
-    <row r="25" ht="17" spans="1:31">
+    <row r="25" ht="17" spans="1:32">
       <c r="A25" s="2">
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C25" s="9">
         <v>132428</v>
@@ -4245,7 +4425,7 @@
       </c>
       <c r="Z25" s="7">
         <f>IF(OR(AE25="",多次统计数据!$B$8=""),"",AE25-多次统计数据!$B$8)</f>
-        <v>-0.0920795592497826</v>
+        <v>-0.0834957550778809</v>
       </c>
       <c r="AA25" s="14">
         <f t="shared" si="7"/>
@@ -4253,7 +4433,7 @@
       </c>
       <c r="AB25" s="7">
         <f>IF(OR(A25="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0583754206956539</v>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC25" s="8" t="str">
         <f>IF(OR(AB25="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB25,"低于上限","达到或超过上限"))</f>
@@ -4265,12 +4445,12 @@
         <v>-0.0242622406137675</v>
       </c>
     </row>
-    <row r="26" ht="17" spans="1:31">
+    <row r="26" ht="17" spans="1:32">
       <c r="A26" s="2">
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C26" s="9">
         <v>129215</v>
@@ -4339,7 +4519,7 @@
       </c>
       <c r="Z26" s="7">
         <f>IF(OR(AE26="",多次统计数据!$B$8=""),"",AE26-多次统计数据!$B$8)</f>
-        <v>0.0589481497693557</v>
+        <v>0.0675319539412574</v>
       </c>
       <c r="AA26" s="14">
         <f t="shared" si="7"/>
@@ -4347,7 +4527,7 @@
       </c>
       <c r="AB26" s="7">
         <f>IF(OR(A26="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0583754206956539</v>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC26" s="8" t="str">
         <f>IF(OR(AB26="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB26,"低于上限","达到或超过上限"))</f>
@@ -4359,3460 +4539,4534 @@
         <v>0.126765468405371</v>
       </c>
     </row>
-    <row r="27" ht="17" spans="1:31">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="8" t="str">
+    <row r="27" ht="17" spans="1:32">
+      <c r="A27" s="2">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C27" s="9">
+        <v>145595</v>
+      </c>
+      <c r="D27" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E27" s="9">
+        <v>73.35</v>
+      </c>
+      <c r="F27" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>500</v>
       </c>
       <c r="G27" s="8" t="str">
         <f>IF(OR(A27="",F27="",E27="",N27="",E27&lt;=N27,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H27="",F27*(E27-N27),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H27" s="2"/>
-      <c r="I27" s="10"/>
-      <c r="J27" s="9"/>
-      <c r="K27" s="9"/>
-      <c r="L27" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H27" s="2">
+        <v>500</v>
+      </c>
+      <c r="I27" s="10">
+        <v>44636</v>
+      </c>
+      <c r="J27" s="9">
+        <v>85</v>
+      </c>
+      <c r="K27" s="9">
+        <v>92.9</v>
+      </c>
+      <c r="L27" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M27" s="10"/>
-      <c r="N27" s="9"/>
+        <v>500</v>
+      </c>
+      <c r="M27" s="10">
+        <v>44804</v>
+      </c>
+      <c r="N27" s="9">
+        <v>68</v>
+      </c>
       <c r="O27" s="9"/>
       <c r="P27" s="9"/>
       <c r="Q27" s="2"/>
       <c r="R27" s="2"/>
       <c r="S27" s="2"/>
       <c r="T27" s="2"/>
-      <c r="U27" s="7" t="str">
+      <c r="U27" s="7">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="V27" s="7" t="str">
+        <v>0.158827539195637</v>
+      </c>
+      <c r="V27" s="7">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="W27" s="13" t="str">
+        <v>0.07293796864349</v>
+      </c>
+      <c r="W27" s="13">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="X27" s="5" t="str">
+        <v>2.17757009345795</v>
+      </c>
+      <c r="X27" s="5">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Y27" s="7" t="str">
+        <v>9775</v>
+      </c>
+      <c r="Y27" s="7">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="Z27" s="7" t="str">
+        <v>0.266530334014997</v>
+      </c>
+      <c r="Z27" s="7">
         <f>IF(OR(AE27="",多次统计数据!$B$8=""),"",AE27-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA27" s="14" t="str">
+        <v>0.00790478012017861</v>
+      </c>
+      <c r="AA27" s="14">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB27" s="7" t="str">
+        <v>168</v>
+      </c>
+      <c r="AB27" s="7">
         <f>IF(OR(A27="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC27" s="8" t="str">
         <f>IF(OR(AB27="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB27,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>低于上限</v>
       </c>
       <c r="AD27" s="2"/>
-      <c r="AE27" s="7" t="str">
+      <c r="AE27" s="7">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="17" spans="1:31">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="8" t="str">
+        <v>0.067138294584292</v>
+      </c>
+    </row>
+    <row r="28" ht="17" spans="1:32">
+      <c r="A28" s="2">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C28" s="9">
+        <v>155370</v>
+      </c>
+      <c r="D28" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E28" s="9">
+        <v>83.41</v>
+      </c>
+      <c r="F28" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>900</v>
       </c>
       <c r="G28" s="8" t="str">
         <f>IF(OR(A28="",F28="",E28="",N28="",E28&lt;=N28,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H28="",F28*(E28-N28),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H28" s="2"/>
-      <c r="I28" s="10"/>
-      <c r="J28" s="9"/>
-      <c r="K28" s="9"/>
-      <c r="L28" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H28" s="2">
+        <v>900</v>
+      </c>
+      <c r="I28" s="10">
+        <v>44895</v>
+      </c>
+      <c r="J28" s="9">
+        <v>90</v>
+      </c>
+      <c r="K28" s="9">
+        <v>84.9</v>
+      </c>
+      <c r="L28" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M28" s="10"/>
-      <c r="N28" s="9"/>
+        <v>900</v>
+      </c>
+      <c r="M28" s="10">
+        <v>44935</v>
+      </c>
+      <c r="N28" s="9">
+        <v>80</v>
+      </c>
       <c r="O28" s="9"/>
       <c r="P28" s="9"/>
       <c r="Q28" s="2"/>
       <c r="R28" s="2"/>
       <c r="S28" s="2"/>
       <c r="T28" s="2"/>
-      <c r="U28" s="7" t="str">
+      <c r="U28" s="7">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="V28" s="7" t="str">
+        <v>0.07900731327179</v>
+      </c>
+      <c r="V28" s="7">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="W28" s="13" t="str">
+        <v>0.0408823882028533</v>
+      </c>
+      <c r="W28" s="13">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="X28" s="5" t="str">
+        <v>1.9325513196481</v>
+      </c>
+      <c r="X28" s="5">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Y28" s="7" t="str">
+        <v>1341</v>
+      </c>
+      <c r="Y28" s="7">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="Z28" s="7" t="str">
+        <v>0.0178635655197219</v>
+      </c>
+      <c r="Z28" s="7">
         <f>IF(OR(AE28="",多次统计数据!$B$8=""),"",AE28-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA28" s="14" t="str">
+        <v>-0.0506025046166525</v>
+      </c>
+      <c r="AA28" s="14">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB28" s="7" t="str">
+        <v>40</v>
+      </c>
+      <c r="AB28" s="7">
         <f>IF(OR(A28="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC28" s="8" t="str">
         <f>IF(OR(AB28="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB28,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>低于上限</v>
       </c>
       <c r="AD28" s="2"/>
-      <c r="AE28" s="7" t="str">
+      <c r="AE28" s="7">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="17" spans="1:31">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="8" t="str">
+        <v>0.0086310098474609</v>
+      </c>
+    </row>
+    <row r="29" ht="17" spans="1:32">
+      <c r="A29" s="2">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C29" s="9">
+        <v>156711</v>
+      </c>
+      <c r="D29" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E29" s="9">
+        <v>82.64</v>
+      </c>
+      <c r="F29" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>1100</v>
       </c>
       <c r="G29" s="8" t="str">
         <f>IF(OR(A29="",F29="",E29="",N29="",E29&lt;=N29,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H29="",F29*(E29-N29),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H29" s="2"/>
-      <c r="I29" s="10"/>
-      <c r="J29" s="9"/>
-      <c r="K29" s="9"/>
-      <c r="L29" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H29" s="2">
+        <v>1100</v>
+      </c>
+      <c r="I29" s="10">
+        <v>45015</v>
+      </c>
+      <c r="J29" s="9">
+        <v>90</v>
+      </c>
+      <c r="K29" s="9">
+        <v>78.04</v>
+      </c>
+      <c r="L29" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M29" s="10"/>
-      <c r="N29" s="9"/>
+        <v>1100</v>
+      </c>
+      <c r="M29" s="10">
+        <v>45028</v>
+      </c>
+      <c r="N29" s="9">
+        <v>80</v>
+      </c>
       <c r="O29" s="9"/>
       <c r="P29" s="9"/>
       <c r="Q29" s="2"/>
       <c r="R29" s="2"/>
       <c r="S29" s="2"/>
       <c r="T29" s="2"/>
-      <c r="U29" s="7" t="str">
+      <c r="U29" s="7">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="V29" s="7" t="str">
+        <v>0.0890609874152953</v>
+      </c>
+      <c r="V29" s="7">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="W29" s="13" t="str">
+        <v>0.031945788964182</v>
+      </c>
+      <c r="W29" s="13">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="X29" s="5" t="str">
+        <v>2.78787878787879</v>
+      </c>
+      <c r="X29" s="5">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Y29" s="7" t="str">
+        <v>-5060</v>
+      </c>
+      <c r="Y29" s="7">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="Z29" s="7" t="str">
+        <v>-0.0556631171345595</v>
+      </c>
+      <c r="Z29" s="7">
         <f>IF(OR(AE29="",多次统计数据!$B$8=""),"",AE29-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA29" s="14" t="str">
+        <v>-0.0915222497794391</v>
+      </c>
+      <c r="AA29" s="14">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB29" s="7" t="str">
+        <v>13</v>
+      </c>
+      <c r="AB29" s="7">
         <f>IF(OR(A29="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC29" s="8" t="str">
         <f>IF(OR(AB29="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB29,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>低于上限</v>
       </c>
       <c r="AD29" s="2"/>
-      <c r="AE29" s="7" t="str">
+      <c r="AE29" s="7">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="17" spans="1:31">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="8" t="str">
+        <v>-0.0322887353153257</v>
+      </c>
+    </row>
+    <row r="30" ht="17" spans="1:32">
+      <c r="A30" s="2">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C30" s="9">
+        <v>151651</v>
+      </c>
+      <c r="D30" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E30" s="9">
+        <v>83.5</v>
+      </c>
+      <c r="F30" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>800</v>
       </c>
       <c r="G30" s="8" t="str">
         <f>IF(OR(A30="",F30="",E30="",N30="",E30&lt;=N30,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H30="",F30*(E30-N30),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H30" s="2"/>
-      <c r="I30" s="10"/>
-      <c r="J30" s="9"/>
-      <c r="K30" s="9"/>
-      <c r="L30" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H30" s="2">
+        <v>800</v>
+      </c>
+      <c r="I30" s="10">
+        <v>45056</v>
+      </c>
+      <c r="J30" s="9">
+        <v>90</v>
+      </c>
+      <c r="K30" s="9">
+        <v>79.23</v>
+      </c>
+      <c r="L30" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M30" s="10"/>
-      <c r="N30" s="9"/>
+        <v>800</v>
+      </c>
+      <c r="M30" s="10">
+        <v>45072</v>
+      </c>
+      <c r="N30" s="9">
+        <v>80</v>
+      </c>
       <c r="O30" s="9"/>
       <c r="P30" s="9"/>
       <c r="Q30" s="2"/>
       <c r="R30" s="2"/>
       <c r="S30" s="2"/>
       <c r="T30" s="2"/>
-      <c r="U30" s="7" t="str">
+      <c r="U30" s="7">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="V30" s="7" t="str">
+        <v>0.0778443113772455</v>
+      </c>
+      <c r="V30" s="7">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="W30" s="13" t="str">
+        <v>0.0419161676646707</v>
+      </c>
+      <c r="W30" s="13">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="X30" s="5" t="str">
+        <v>1.85714285714286</v>
+      </c>
+      <c r="X30" s="5">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Y30" s="7" t="str">
+        <v>-3416</v>
+      </c>
+      <c r="Y30" s="7">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="Z30" s="7" t="str">
+        <v>-0.0511377245508982</v>
+      </c>
+      <c r="Z30" s="7">
         <f>IF(OR(AE30="",多次统计数据!$B$8=""),"",AE30-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA30" s="14" t="str">
+        <v>-0.0817589181871354</v>
+      </c>
+      <c r="AA30" s="14">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB30" s="7" t="str">
+        <v>16</v>
+      </c>
+      <c r="AB30" s="7">
         <f>IF(OR(A30="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC30" s="8" t="str">
         <f>IF(OR(AB30="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB30,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>低于上限</v>
       </c>
       <c r="AD30" s="2"/>
-      <c r="AE30" s="7" t="str">
+      <c r="AE30" s="7">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="17" spans="1:31">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="8" t="str">
+        <v>-0.0225254037230219</v>
+      </c>
+    </row>
+    <row r="31" ht="17" spans="1:32">
+      <c r="A31" s="2">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C31" s="9">
+        <v>148235</v>
+      </c>
+      <c r="D31" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E31" s="9">
+        <v>86.28</v>
+      </c>
+      <c r="F31" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>1300</v>
       </c>
       <c r="G31" s="8" t="str">
         <f>IF(OR(A31="",F31="",E31="",N31="",E31&lt;=N31,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H31="",F31*(E31-N31),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H31" s="2"/>
-      <c r="I31" s="10"/>
-      <c r="J31" s="9"/>
-      <c r="K31" s="9"/>
-      <c r="L31" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H31" s="2">
+        <v>1300</v>
+      </c>
+      <c r="I31" s="10">
+        <v>45135</v>
+      </c>
+      <c r="J31" s="9">
+        <v>95</v>
+      </c>
+      <c r="K31" s="9">
+        <v>79.22</v>
+      </c>
+      <c r="L31" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M31" s="10"/>
-      <c r="N31" s="9"/>
+        <v>1300</v>
+      </c>
+      <c r="M31" s="10">
+        <v>45152</v>
+      </c>
+      <c r="N31" s="9">
+        <v>84</v>
+      </c>
       <c r="O31" s="9"/>
       <c r="P31" s="9"/>
       <c r="Q31" s="2"/>
       <c r="R31" s="2"/>
       <c r="S31" s="2"/>
       <c r="T31" s="2"/>
-      <c r="U31" s="7" t="str">
+      <c r="U31" s="7">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="V31" s="7" t="str">
+        <v>0.101066295781178</v>
+      </c>
+      <c r="V31" s="7">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="W31" s="13" t="str">
+        <v>0.0264255910987483</v>
+      </c>
+      <c r="W31" s="13">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="X31" s="5" t="str">
+        <v>3.82456140350877</v>
+      </c>
+      <c r="X31" s="5">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Y31" s="7" t="str">
+        <v>-9178</v>
+      </c>
+      <c r="Y31" s="7">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="Z31" s="7" t="str">
+        <v>-0.0818266110338433</v>
+      </c>
+      <c r="Z31" s="7">
         <f>IF(OR(AE31="",多次统计数据!$B$8=""),"",AE31-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA31" s="14" t="str">
+        <v>-0.121148716676816</v>
+      </c>
+      <c r="AA31" s="14">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB31" s="7" t="str">
+        <v>17</v>
+      </c>
+      <c r="AB31" s="7">
         <f>IF(OR(A31="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC31" s="8" t="str">
         <f>IF(OR(AB31="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB31,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>低于上限</v>
       </c>
       <c r="AD31" s="2"/>
-      <c r="AE31" s="7" t="str">
+      <c r="AE31" s="7">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="17" spans="1:31">
-      <c r="A32" s="2"/>
-      <c r="B32" s="2"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="8" t="str">
+        <v>-0.0619152022127028</v>
+      </c>
+      <c r="AF31" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="32" ht="17" spans="1:32">
+      <c r="A32" s="2">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C32" s="9">
+        <v>139057</v>
+      </c>
+      <c r="D32" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E32" s="9">
+        <v>73.91</v>
+      </c>
+      <c r="F32" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>700</v>
       </c>
       <c r="G32" s="8" t="str">
         <f>IF(OR(A32="",F32="",E32="",N32="",E32&lt;=N32,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H32="",F32*(E32-N32),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H32" s="2"/>
-      <c r="I32" s="10"/>
-      <c r="J32" s="9"/>
-      <c r="K32" s="9"/>
-      <c r="L32" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H32" s="2">
+        <v>700</v>
+      </c>
+      <c r="I32" s="10">
+        <v>45419</v>
+      </c>
+      <c r="J32" s="9">
+        <v>75</v>
+      </c>
+      <c r="K32" s="9">
+        <v>69.59</v>
+      </c>
+      <c r="L32" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M32" s="10"/>
-      <c r="N32" s="9"/>
+        <v>700</v>
+      </c>
+      <c r="M32" s="10">
+        <v>45434</v>
+      </c>
+      <c r="N32" s="9">
+        <v>70</v>
+      </c>
       <c r="O32" s="9"/>
       <c r="P32" s="9"/>
       <c r="Q32" s="2"/>
       <c r="R32" s="2"/>
       <c r="S32" s="2"/>
       <c r="T32" s="2"/>
-      <c r="U32" s="7" t="str">
+      <c r="U32" s="7">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="V32" s="7" t="str">
+        <v>0.0147476660803681</v>
+      </c>
+      <c r="V32" s="7">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="W32" s="13" t="str">
+        <v>0.0529021783249898</v>
+      </c>
+      <c r="W32" s="13">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="X32" s="5" t="str">
+        <v>0.278772378516625</v>
+      </c>
+      <c r="X32" s="5">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Y32" s="7" t="str">
+        <v>-3024</v>
+      </c>
+      <c r="Y32" s="7">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="Z32" s="7" t="str">
+        <v>-0.0584494655662292</v>
+      </c>
+      <c r="Z32" s="7">
         <f>IF(OR(AE32="",多次统计数据!$B$8=""),"",AE32-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA32" s="14" t="str">
+        <v>-0.080979992527066</v>
+      </c>
+      <c r="AA32" s="14">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB32" s="7" t="str">
+        <v>15</v>
+      </c>
+      <c r="AB32" s="7">
         <f>IF(OR(A32="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC32" s="8" t="str">
         <f>IF(OR(AB32="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB32,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>低于上限</v>
       </c>
       <c r="AD32" s="2"/>
-      <c r="AE32" s="7" t="str">
+      <c r="AE32" s="7">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="17" spans="1:31">
-      <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="8" t="str">
+        <v>-0.0217464780629526</v>
+      </c>
+    </row>
+    <row r="33" ht="17" spans="1:32">
+      <c r="A33" s="2">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C33" s="9">
+        <v>136033</v>
+      </c>
+      <c r="D33" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E33" s="9">
+        <v>11.92</v>
+      </c>
+      <c r="F33" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>6400</v>
       </c>
       <c r="G33" s="8" t="str">
         <f>IF(OR(A33="",F33="",E33="",N33="",E33&lt;=N33,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H33="",F33*(E33-N33),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H33" s="2"/>
-      <c r="I33" s="10"/>
-      <c r="J33" s="9"/>
-      <c r="K33" s="9"/>
-      <c r="L33" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H33" s="2">
+        <v>6400</v>
+      </c>
+      <c r="I33" s="10">
+        <v>44344</v>
+      </c>
+      <c r="J33" s="9">
+        <v>12.75</v>
+      </c>
+      <c r="K33" s="9">
+        <v>11.24</v>
+      </c>
+      <c r="L33" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M33" s="10"/>
-      <c r="N33" s="9"/>
+        <v>6400</v>
+      </c>
+      <c r="M33" s="10">
+        <v>44362</v>
+      </c>
+      <c r="N33" s="9">
+        <v>11.5</v>
+      </c>
       <c r="O33" s="9"/>
       <c r="P33" s="9"/>
       <c r="Q33" s="2"/>
       <c r="R33" s="2"/>
       <c r="S33" s="2"/>
       <c r="T33" s="2"/>
-      <c r="U33" s="7" t="str">
+      <c r="U33" s="7">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="V33" s="7" t="str">
+        <v>0.0696308724832215</v>
+      </c>
+      <c r="V33" s="7">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="W33" s="13" t="str">
+        <v>0.0352348993288591</v>
+      </c>
+      <c r="W33" s="13">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="X33" s="5" t="str">
+        <v>1.97619047619048</v>
+      </c>
+      <c r="X33" s="5">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Y33" s="7" t="str">
+        <v>-4352</v>
+      </c>
+      <c r="Y33" s="7">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="Z33" s="7" t="str">
+        <v>-0.0570469798657718</v>
+      </c>
+      <c r="Z33" s="7">
         <f>IF(OR(AE33="",多次统计数据!$B$8=""),"",AE33-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA33" s="14" t="str">
+        <v>-0.0912257516418571</v>
+      </c>
+      <c r="AA33" s="14">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB33" s="7" t="str">
+        <v>18</v>
+      </c>
+      <c r="AB33" s="7">
         <f>IF(OR(A33="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC33" s="8" t="str">
         <f>IF(OR(AB33="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB33,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>低于上限</v>
       </c>
       <c r="AD33" s="2"/>
-      <c r="AE33" s="7" t="str">
+      <c r="AE33" s="7">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="17" spans="1:31">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="8" t="str">
+        <v>-0.0319922371777436</v>
+      </c>
+    </row>
+    <row r="34" ht="17" spans="1:32">
+      <c r="A34" s="2">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C34" s="9">
+        <v>131681</v>
+      </c>
+      <c r="D34" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E34" s="9">
+        <v>12.13</v>
+      </c>
+      <c r="F34" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>2800</v>
       </c>
       <c r="G34" s="8" t="str">
         <f>IF(OR(A34="",F34="",E34="",N34="",E34&lt;=N34,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H34="",F34*(E34-N34),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H34" s="2"/>
-      <c r="I34" s="10"/>
-      <c r="J34" s="9"/>
-      <c r="K34" s="9"/>
-      <c r="L34" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H34" s="2">
+        <v>2800</v>
+      </c>
+      <c r="I34" s="10">
+        <v>44385</v>
+      </c>
+      <c r="J34" s="9">
+        <v>13</v>
+      </c>
+      <c r="K34" s="9">
+        <v>11.09</v>
+      </c>
+      <c r="L34" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M34" s="10"/>
-      <c r="N34" s="9"/>
+        <v>2800</v>
+      </c>
+      <c r="M34" s="10">
+        <v>44396</v>
+      </c>
+      <c r="N34" s="9">
+        <v>11.2</v>
+      </c>
       <c r="O34" s="9"/>
       <c r="P34" s="9"/>
       <c r="Q34" s="2"/>
       <c r="R34" s="2"/>
       <c r="S34" s="2"/>
       <c r="T34" s="2"/>
-      <c r="U34" s="7" t="str">
+      <c r="U34" s="7">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="V34" s="7" t="str">
+        <v>0.0717230008244022</v>
+      </c>
+      <c r="V34" s="7">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="W34" s="13" t="str">
+        <v>0.0766694146743612</v>
+      </c>
+      <c r="W34" s="13">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="X34" s="5" t="str">
+        <v>0.93548387096774</v>
+      </c>
+      <c r="X34" s="5">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Y34" s="7" t="str">
+        <v>-2912</v>
+      </c>
+      <c r="Y34" s="7">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="Z34" s="7" t="str">
+        <v>-0.0857378400659522</v>
+      </c>
+      <c r="Z34" s="7">
         <f>IF(OR(AE34="",多次统计数据!$B$8=""),"",AE34-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA34" s="14" t="str">
+        <v>-0.0813475628082178</v>
+      </c>
+      <c r="AA34" s="14">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB34" s="7" t="str">
+        <v>11</v>
+      </c>
+      <c r="AB34" s="7">
         <f>IF(OR(A34="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC34" s="8" t="str">
         <f>IF(OR(AB34="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB34,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>低于上限</v>
       </c>
       <c r="AD34" s="2"/>
-      <c r="AE34" s="7" t="str">
+      <c r="AE34" s="7">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="17" spans="1:31">
-      <c r="A35" s="2"/>
-      <c r="B35" s="2"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="8" t="str">
+        <v>-0.0221140483441043</v>
+      </c>
+    </row>
+    <row r="35" ht="17" spans="1:32">
+      <c r="A35" s="2">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C35" s="9">
+        <v>128769</v>
+      </c>
+      <c r="D35" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E35" s="9">
+        <v>11.08</v>
+      </c>
+      <c r="F35" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>4400</v>
       </c>
       <c r="G35" s="8" t="str">
         <f>IF(OR(A35="",F35="",E35="",N35="",E35&lt;=N35,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H35="",F35*(E35-N35),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H35" s="2"/>
-      <c r="I35" s="10"/>
-      <c r="J35" s="9"/>
-      <c r="K35" s="9"/>
-      <c r="L35" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H35" s="2">
+        <v>4400</v>
+      </c>
+      <c r="I35" s="10">
+        <v>44405</v>
+      </c>
+      <c r="J35" s="9">
+        <v>12.36</v>
+      </c>
+      <c r="K35" s="9">
+        <v>11.36</v>
+      </c>
+      <c r="L35" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M35" s="10"/>
-      <c r="N35" s="9"/>
+        <v>4400</v>
+      </c>
+      <c r="M35" s="10">
+        <v>44406</v>
+      </c>
+      <c r="N35" s="9">
+        <v>10.5</v>
+      </c>
       <c r="O35" s="9"/>
       <c r="P35" s="9"/>
       <c r="Q35" s="2"/>
       <c r="R35" s="2"/>
       <c r="S35" s="2"/>
       <c r="T35" s="2"/>
-      <c r="U35" s="7" t="str">
+      <c r="U35" s="7">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="V35" s="7" t="str">
+        <v>0.115523465703971</v>
+      </c>
+      <c r="V35" s="7">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="W35" s="13" t="str">
+        <v>0.0523465703971119</v>
+      </c>
+      <c r="W35" s="13">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="X35" s="5" t="str">
+        <v>2.20689655172414</v>
+      </c>
+      <c r="X35" s="5">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Y35" s="7" t="str">
+        <v>1232</v>
+      </c>
+      <c r="Y35" s="7">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="Z35" s="7" t="str">
+        <v>0.0252707581227437</v>
+      </c>
+      <c r="Z35" s="7">
         <f>IF(OR(AE35="",多次统计数据!$B$8=""),"",AE35-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA35" s="14" t="str">
+        <v>-0.0496659943311622</v>
+      </c>
+      <c r="AA35" s="14">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB35" s="7" t="str">
+        <v>1</v>
+      </c>
+      <c r="AB35" s="7">
         <f>IF(OR(A35="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC35" s="8" t="str">
         <f>IF(OR(AB35="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB35,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>低于上限</v>
       </c>
       <c r="AD35" s="2"/>
-      <c r="AE35" s="7" t="str">
+      <c r="AE35" s="7">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="17" spans="1:31">
-      <c r="A36" s="2"/>
-      <c r="B36" s="2"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="8" t="str">
+        <v>0.00956752013295125</v>
+      </c>
+    </row>
+    <row r="36" ht="17" spans="1:32">
+      <c r="A36" s="2">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C36" s="9">
+        <v>130001</v>
+      </c>
+      <c r="D36" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E36" s="9">
+        <v>8.38</v>
+      </c>
+      <c r="F36" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>6800</v>
       </c>
       <c r="G36" s="8" t="str">
         <f>IF(OR(A36="",F36="",E36="",N36="",E36&lt;=N36,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H36="",F36*(E36-N36),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H36" s="2"/>
-      <c r="I36" s="10"/>
-      <c r="J36" s="9"/>
-      <c r="K36" s="9"/>
-      <c r="L36" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H36" s="2">
+        <v>6800</v>
+      </c>
+      <c r="I36" s="10">
+        <v>44496</v>
+      </c>
+      <c r="J36" s="9">
+        <v>9.45</v>
+      </c>
+      <c r="K36" s="9">
+        <v>9.8</v>
+      </c>
+      <c r="L36" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M36" s="10"/>
-      <c r="N36" s="9"/>
+        <v>6800</v>
+      </c>
+      <c r="M36" s="10">
+        <v>44508</v>
+      </c>
+      <c r="N36" s="9">
+        <v>8</v>
+      </c>
       <c r="O36" s="9"/>
       <c r="P36" s="9"/>
       <c r="Q36" s="2"/>
       <c r="R36" s="2"/>
       <c r="S36" s="2"/>
       <c r="T36" s="2"/>
-      <c r="U36" s="7" t="str">
+      <c r="U36" s="7">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="V36" s="7" t="str">
+        <v>0.127684964200477</v>
+      </c>
+      <c r="V36" s="7">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="W36" s="13" t="str">
+        <v>0.0453460620525061</v>
+      </c>
+      <c r="W36" s="13">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="X36" s="5" t="str">
+        <v>2.8157894736842</v>
+      </c>
+      <c r="X36" s="5">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Y36" s="7" t="str">
+        <v>9655.99999999999</v>
+      </c>
+      <c r="Y36" s="7">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="Z36" s="7" t="str">
+        <v>0.16945107398568</v>
+      </c>
+      <c r="Z36" s="7">
         <f>IF(OR(AE36="",多次统计数据!$B$8=""),"",AE36-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA36" s="14" t="str">
+        <v>0.0150428372562579</v>
+      </c>
+      <c r="AA36" s="14">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB36" s="7" t="str">
+        <v>12</v>
+      </c>
+      <c r="AB36" s="7">
         <f>IF(OR(A36="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC36" s="8" t="str">
         <f>IF(OR(AB36="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB36,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>低于上限</v>
       </c>
       <c r="AD36" s="2"/>
-      <c r="AE36" s="7" t="str">
+      <c r="AE36" s="7">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="37" ht="17" spans="1:31">
-      <c r="A37" s="2"/>
-      <c r="B37" s="2"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="8" t="str">
+        <v>0.0742763517203713</v>
+      </c>
+    </row>
+    <row r="37" ht="17" spans="1:32">
+      <c r="A37" s="2">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C37" s="9">
+        <v>139657</v>
+      </c>
+      <c r="D37" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E37" s="9">
+        <v>15.16</v>
+      </c>
+      <c r="F37" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>2400</v>
       </c>
       <c r="G37" s="8" t="str">
         <f>IF(OR(A37="",F37="",E37="",N37="",E37&lt;=N37,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H37="",F37*(E37-N37),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H37" s="2"/>
-      <c r="I37" s="10"/>
-      <c r="J37" s="9"/>
-      <c r="K37" s="9"/>
-      <c r="L37" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H37" s="2">
+        <v>2400</v>
+      </c>
+      <c r="I37" s="10">
+        <v>44553</v>
+      </c>
+      <c r="J37" s="9">
+        <v>18</v>
+      </c>
+      <c r="K37" s="9">
+        <v>13.4</v>
+      </c>
+      <c r="L37" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M37" s="10"/>
-      <c r="N37" s="9"/>
+        <v>2400</v>
+      </c>
+      <c r="M37" s="10">
+        <v>44568</v>
+      </c>
+      <c r="N37" s="9">
+        <v>14</v>
+      </c>
       <c r="O37" s="9"/>
       <c r="P37" s="9"/>
       <c r="Q37" s="2"/>
       <c r="R37" s="2"/>
       <c r="S37" s="2"/>
       <c r="T37" s="2"/>
-      <c r="U37" s="7" t="str">
+      <c r="U37" s="7">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="V37" s="7" t="str">
+        <v>0.187335092348285</v>
+      </c>
+      <c r="V37" s="7">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="W37" s="13" t="str">
+        <v>0.0765171503957784</v>
+      </c>
+      <c r="W37" s="13">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="X37" s="5" t="str">
+        <v>2.44827586206896</v>
+      </c>
+      <c r="X37" s="5">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Y37" s="7" t="str">
+        <v>-4224</v>
+      </c>
+      <c r="Y37" s="7">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="Z37" s="7" t="str">
+        <v>-0.116094986807388</v>
+      </c>
+      <c r="Z37" s="7">
         <f>IF(OR(AE37="",多次统计数据!$B$8=""),"",AE37-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA37" s="14" t="str">
+        <v>-0.0894790445843366</v>
+      </c>
+      <c r="AA37" s="14">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB37" s="7" t="str">
+        <v>15</v>
+      </c>
+      <c r="AB37" s="7">
         <f>IF(OR(A37="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC37" s="8" t="str">
         <f>IF(OR(AB37="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB37,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>低于上限</v>
       </c>
       <c r="AD37" s="2"/>
-      <c r="AE37" s="7" t="str">
+      <c r="AE37" s="7">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="38" ht="17" spans="1:31">
-      <c r="A38" s="2"/>
-      <c r="B38" s="2"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="8" t="str">
+        <v>-0.0302455301202231</v>
+      </c>
+    </row>
+    <row r="38" ht="17" spans="1:32">
+      <c r="A38" s="2">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C38" s="9">
+        <v>135433</v>
+      </c>
+      <c r="D38" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E38" s="9">
+        <v>12.17</v>
+      </c>
+      <c r="F38" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>2700</v>
       </c>
       <c r="G38" s="8" t="str">
         <f>IF(OR(A38="",F38="",E38="",N38="",E38&lt;=N38,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H38="",F38*(E38-N38),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H38" s="2"/>
-      <c r="I38" s="10"/>
-      <c r="J38" s="9"/>
-      <c r="K38" s="9"/>
-      <c r="L38" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H38" s="2">
+        <v>2700</v>
+      </c>
+      <c r="I38" s="10">
+        <v>44641</v>
+      </c>
+      <c r="J38" s="9">
+        <v>14</v>
+      </c>
+      <c r="K38" s="9">
+        <v>9.49</v>
+      </c>
+      <c r="L38" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M38" s="10"/>
-      <c r="N38" s="9"/>
+        <v>2700</v>
+      </c>
+      <c r="M38" s="10">
+        <v>44662</v>
+      </c>
+      <c r="N38" s="9">
+        <v>11.2</v>
+      </c>
       <c r="O38" s="9"/>
       <c r="P38" s="9"/>
       <c r="Q38" s="2"/>
       <c r="R38" s="2"/>
       <c r="S38" s="2"/>
       <c r="T38" s="2"/>
-      <c r="U38" s="7" t="str">
+      <c r="U38" s="7">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="V38" s="7" t="str">
+        <v>0.150369761709121</v>
+      </c>
+      <c r="V38" s="7">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="W38" s="13" t="str">
+        <v>0.0797041906327034</v>
+      </c>
+      <c r="W38" s="13">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="X38" s="5" t="str">
+        <v>1.88659793814433</v>
+      </c>
+      <c r="X38" s="5">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Y38" s="7" t="str">
+        <v>-7236</v>
+      </c>
+      <c r="Y38" s="7">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="Z38" s="7" t="str">
+        <v>-0.220213640098603</v>
+      </c>
+      <c r="Z38" s="7">
         <f>IF(OR(AE38="",多次统计数据!$B$8=""),"",AE38-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA38" s="14" t="str">
+        <v>-0.112662147072119</v>
+      </c>
+      <c r="AA38" s="14">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB38" s="7" t="str">
+        <v>21</v>
+      </c>
+      <c r="AB38" s="7">
         <f>IF(OR(A38="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC38" s="8" t="str">
         <f>IF(OR(AB38="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB38,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>低于上限</v>
       </c>
       <c r="AD38" s="2"/>
-      <c r="AE38" s="7" t="str">
+      <c r="AE38" s="7">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="39" ht="17" spans="1:31">
-      <c r="A39" s="2"/>
-      <c r="B39" s="2"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="6"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="8" t="str">
+        <v>-0.0534286326080054</v>
+      </c>
+      <c r="AF38" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="39" ht="17" spans="1:32">
+      <c r="A39" s="2">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C39" s="9">
+        <v>128197</v>
+      </c>
+      <c r="D39" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E39" s="9">
+        <v>10.45</v>
+      </c>
+      <c r="F39" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>5600</v>
       </c>
       <c r="G39" s="8" t="str">
         <f>IF(OR(A39="",F39="",E39="",N39="",E39&lt;=N39,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H39="",F39*(E39-N39),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H39" s="2"/>
-      <c r="I39" s="10"/>
-      <c r="J39" s="9"/>
-      <c r="K39" s="9"/>
-      <c r="L39" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H39" s="2">
+        <v>5600</v>
+      </c>
+      <c r="I39" s="10">
+        <v>44670</v>
+      </c>
+      <c r="J39" s="9">
+        <v>12</v>
+      </c>
+      <c r="K39" s="9">
+        <v>9.28</v>
+      </c>
+      <c r="L39" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M39" s="10"/>
-      <c r="N39" s="9"/>
+        <v>5600</v>
+      </c>
+      <c r="M39" s="10">
+        <v>44676</v>
+      </c>
+      <c r="N39" s="9">
+        <v>10</v>
+      </c>
       <c r="O39" s="9"/>
       <c r="P39" s="9"/>
       <c r="Q39" s="2"/>
       <c r="R39" s="2"/>
       <c r="S39" s="2"/>
       <c r="T39" s="2"/>
-      <c r="U39" s="7" t="str">
+      <c r="U39" s="7">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="V39" s="7" t="str">
+        <v>0.148325358851675</v>
+      </c>
+      <c r="V39" s="7">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="W39" s="13" t="str">
+        <v>0.0430622009569377</v>
+      </c>
+      <c r="W39" s="13">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="X39" s="5" t="str">
+        <v>3.44444444444445</v>
+      </c>
+      <c r="X39" s="5">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Y39" s="7" t="str">
+        <v>-6551.99999999999</v>
+      </c>
+      <c r="Y39" s="7">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="Z39" s="7" t="str">
+        <v>-0.111961722488038</v>
+      </c>
+      <c r="Z39" s="7">
         <f>IF(OR(AE39="",多次统计数据!$B$8=""),"",AE39-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA39" s="14" t="str">
+        <v>-0.110342354764588</v>
+      </c>
+      <c r="AA39" s="14">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB39" s="7" t="str">
+        <v>6</v>
+      </c>
+      <c r="AB39" s="7">
         <f>IF(OR(A39="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC39" s="8" t="str">
         <f>IF(OR(AB39="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB39,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>低于上限</v>
       </c>
       <c r="AD39" s="2"/>
-      <c r="AE39" s="7" t="str">
+      <c r="AE39" s="7">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="40" ht="17" spans="1:31">
-      <c r="A40" s="2"/>
-      <c r="B40" s="2"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="6"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="8" t="str">
+        <v>-0.051108840300475</v>
+      </c>
+    </row>
+    <row r="40" ht="17" spans="1:32">
+      <c r="A40" s="2">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C40" s="9">
+        <v>121645</v>
+      </c>
+      <c r="D40" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E40" s="9">
+        <v>13.54</v>
+      </c>
+      <c r="F40" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>4500</v>
       </c>
       <c r="G40" s="8" t="str">
         <f>IF(OR(A40="",F40="",E40="",N40="",E40&lt;=N40,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H40="",F40*(E40-N40),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H40" s="2"/>
-      <c r="I40" s="10"/>
-      <c r="J40" s="9"/>
-      <c r="K40" s="9"/>
-      <c r="L40" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H40" s="2">
+        <v>4500</v>
+      </c>
+      <c r="I40" s="10">
+        <v>44740</v>
+      </c>
+      <c r="J40" s="9">
+        <v>15</v>
+      </c>
+      <c r="K40" s="9">
+        <v>12.66</v>
+      </c>
+      <c r="L40" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M40" s="10"/>
-      <c r="N40" s="9"/>
+        <v>4500</v>
+      </c>
+      <c r="M40" s="10">
+        <v>44743</v>
+      </c>
+      <c r="N40" s="9">
+        <v>13</v>
+      </c>
       <c r="O40" s="9"/>
       <c r="P40" s="9"/>
       <c r="Q40" s="2"/>
       <c r="R40" s="2"/>
       <c r="S40" s="2"/>
       <c r="T40" s="2"/>
-      <c r="U40" s="7" t="str">
+      <c r="U40" s="7">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="V40" s="7" t="str">
+        <v>0.107828655834564</v>
+      </c>
+      <c r="V40" s="7">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="W40" s="13" t="str">
+        <v>0.0398818316100443</v>
+      </c>
+      <c r="W40" s="13">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="X40" s="5" t="str">
+        <v>2.70370370370371</v>
+      </c>
+      <c r="X40" s="5">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Y40" s="7" t="str">
+        <v>-3959.99999999999</v>
+      </c>
+      <c r="Y40" s="7">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="Z40" s="7" t="str">
+        <v>-0.0649926144756277</v>
+      </c>
+      <c r="Z40" s="7">
         <f>IF(OR(AE40="",多次统计数据!$B$8=""),"",AE40-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA40" s="14" t="str">
+        <v>-0.0917872569113985</v>
+      </c>
+      <c r="AA40" s="14">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB40" s="7" t="str">
+        <v>3</v>
+      </c>
+      <c r="AB40" s="7">
         <f>IF(OR(A40="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC40" s="8" t="str">
         <f>IF(OR(AB40="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB40,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>低于上限</v>
       </c>
       <c r="AD40" s="2"/>
-      <c r="AE40" s="7" t="str">
+      <c r="AE40" s="7">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="41" ht="17" spans="1:31">
-      <c r="A41" s="2"/>
-      <c r="B41" s="2"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="6"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="8" t="str">
+        <v>-0.0325537424472851</v>
+      </c>
+    </row>
+    <row r="41" ht="17" spans="1:32">
+      <c r="A41" s="2">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C41" s="9">
+        <v>117685</v>
+      </c>
+      <c r="D41" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E41" s="9">
+        <v>11.67</v>
+      </c>
+      <c r="F41" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>2000</v>
       </c>
       <c r="G41" s="8" t="str">
         <f>IF(OR(A41="",F41="",E41="",N41="",E41&lt;=N41,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H41="",F41*(E41-N41),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H41" s="2"/>
-      <c r="I41" s="10"/>
-      <c r="J41" s="9"/>
-      <c r="K41" s="9"/>
-      <c r="L41" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H41" s="2">
+        <v>2000</v>
+      </c>
+      <c r="I41" s="10">
+        <v>44883</v>
+      </c>
+      <c r="J41" s="9">
+        <v>15</v>
+      </c>
+      <c r="K41" s="9">
+        <v>10.23</v>
+      </c>
+      <c r="L41" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M41" s="10"/>
-      <c r="N41" s="9"/>
+        <v>2000</v>
+      </c>
+      <c r="M41" s="10">
+        <v>44914</v>
+      </c>
+      <c r="N41" s="9">
+        <v>10.52</v>
+      </c>
       <c r="O41" s="9"/>
       <c r="P41" s="9"/>
       <c r="Q41" s="2"/>
       <c r="R41" s="2"/>
       <c r="S41" s="2"/>
       <c r="T41" s="2"/>
-      <c r="U41" s="7" t="str">
+      <c r="U41" s="7">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="V41" s="7" t="str">
+        <v>0.285347043701799</v>
+      </c>
+      <c r="V41" s="7">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="W41" s="13" t="str">
+        <v>0.0985432733504713</v>
+      </c>
+      <c r="W41" s="13">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="X41" s="5" t="str">
+        <v>2.89565217391304</v>
+      </c>
+      <c r="X41" s="5">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Y41" s="7" t="str">
+        <v>-2880</v>
+      </c>
+      <c r="Y41" s="7">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="Z41" s="7" t="str">
+        <v>-0.123393316195373</v>
+      </c>
+      <c r="Z41" s="7">
         <f>IF(OR(AE41="",多次统计数据!$B$8=""),"",AE41-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA41" s="14" t="str">
+        <v>-0.0837056222093656</v>
+      </c>
+      <c r="AA41" s="14">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB41" s="7" t="str">
+        <v>31</v>
+      </c>
+      <c r="AB41" s="7">
         <f>IF(OR(A41="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC41" s="8" t="str">
         <f>IF(OR(AB41="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB41,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>低于上限</v>
       </c>
       <c r="AD41" s="2"/>
-      <c r="AE41" s="7" t="str">
+      <c r="AE41" s="7">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="42" ht="17" spans="1:31">
-      <c r="A42" s="2"/>
-      <c r="B42" s="2"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="6"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="8" t="str">
+        <v>-0.0244721077452522</v>
+      </c>
+    </row>
+    <row r="42" ht="17" spans="1:32">
+      <c r="A42" s="2">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C42" s="9">
+        <v>114805</v>
+      </c>
+      <c r="D42" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E42" s="9">
+        <v>18.24</v>
+      </c>
+      <c r="F42" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>1800</v>
       </c>
       <c r="G42" s="8" t="str">
         <f>IF(OR(A42="",F42="",E42="",N42="",E42&lt;=N42,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H42="",F42*(E42-N42),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H42" s="2"/>
-      <c r="I42" s="10"/>
-      <c r="J42" s="9"/>
-      <c r="K42" s="9"/>
-      <c r="L42" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H42" s="2">
+        <v>1800</v>
+      </c>
+      <c r="I42" s="10">
+        <v>45064</v>
+      </c>
+      <c r="J42" s="9">
+        <v>20</v>
+      </c>
+      <c r="K42" s="9">
+        <v>16.44</v>
+      </c>
+      <c r="L42" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M42" s="10"/>
-      <c r="N42" s="9"/>
+        <v>1800</v>
+      </c>
+      <c r="M42" s="10">
+        <v>45069</v>
+      </c>
+      <c r="N42" s="9">
+        <v>17</v>
+      </c>
       <c r="O42" s="9"/>
       <c r="P42" s="9"/>
       <c r="Q42" s="2"/>
       <c r="R42" s="2"/>
       <c r="S42" s="2"/>
       <c r="T42" s="2"/>
-      <c r="U42" s="7" t="str">
+      <c r="U42" s="7">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="V42" s="7" t="str">
+        <v>0.0964912280701755</v>
+      </c>
+      <c r="V42" s="7">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="W42" s="13" t="str">
+        <v>0.0679824561403508</v>
+      </c>
+      <c r="W42" s="13">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="X42" s="5" t="str">
+        <v>1.41935483870968</v>
+      </c>
+      <c r="X42" s="5">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Y42" s="7" t="str">
+        <v>-3240</v>
+      </c>
+      <c r="Y42" s="7">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="Z42" s="7" t="str">
+        <v>-0.0986842105263157</v>
+      </c>
+      <c r="Z42" s="7">
         <f>IF(OR(AE42="",多次统计数据!$B$8=""),"",AE42-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA42" s="14" t="str">
+        <v>-0.0874552818087413</v>
+      </c>
+      <c r="AA42" s="14">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB42" s="7" t="str">
+        <v>5</v>
+      </c>
+      <c r="AB42" s="7">
         <f>IF(OR(A42="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC42" s="8" t="str">
         <f>IF(OR(AB42="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB42,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>低于上限</v>
       </c>
       <c r="AD42" s="2"/>
-      <c r="AE42" s="7" t="str">
+      <c r="AE42" s="7">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="43" ht="17" spans="1:31">
-      <c r="A43" s="2"/>
-      <c r="B43" s="2"/>
-      <c r="C43" s="9"/>
-      <c r="D43" s="6"/>
-      <c r="E43" s="9"/>
-      <c r="F43" s="8" t="str">
+        <v>-0.0282217673446278</v>
+      </c>
+    </row>
+    <row r="43" ht="17" spans="1:32">
+      <c r="A43" s="2">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C43" s="9">
+        <v>111565</v>
+      </c>
+      <c r="D43" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E43" s="9">
+        <v>20.31</v>
+      </c>
+      <c r="F43" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>1700</v>
       </c>
       <c r="G43" s="8" t="str">
         <f>IF(OR(A43="",F43="",E43="",N43="",E43&lt;=N43,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H43="",F43*(E43-N43),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H43" s="2"/>
-      <c r="I43" s="10"/>
-      <c r="J43" s="9"/>
-      <c r="K43" s="9"/>
-      <c r="L43" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H43" s="2">
+        <v>1700</v>
+      </c>
+      <c r="I43" s="10">
+        <v>45086</v>
+      </c>
+      <c r="J43" s="9">
+        <v>24</v>
+      </c>
+      <c r="K43" s="9">
+        <v>18</v>
+      </c>
+      <c r="L43" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M43" s="10"/>
-      <c r="N43" s="9"/>
+        <v>1700</v>
+      </c>
+      <c r="M43" s="10">
+        <v>45103</v>
+      </c>
+      <c r="N43" s="9">
+        <v>19</v>
+      </c>
       <c r="O43" s="9"/>
       <c r="P43" s="9"/>
       <c r="Q43" s="2"/>
       <c r="R43" s="2"/>
       <c r="S43" s="2"/>
       <c r="T43" s="2"/>
-      <c r="U43" s="7" t="str">
+      <c r="U43" s="7">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="V43" s="7" t="str">
+        <v>0.181683899556869</v>
+      </c>
+      <c r="V43" s="7">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="W43" s="13" t="str">
+        <v>0.0645002461841457</v>
+      </c>
+      <c r="W43" s="13">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="X43" s="5" t="str">
+        <v>2.81679389312977</v>
+      </c>
+      <c r="X43" s="5">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Y43" s="7" t="str">
+        <v>-3927</v>
+      </c>
+      <c r="Y43" s="7">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="Z43" s="7" t="str">
+        <v>-0.113737075332349</v>
+      </c>
+      <c r="Z43" s="7">
         <f>IF(OR(AE43="",多次统计数据!$B$8=""),"",AE43-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA43" s="14" t="str">
+        <v>-0.0944327256862709</v>
+      </c>
+      <c r="AA43" s="14">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB43" s="7" t="str">
+        <v>17</v>
+      </c>
+      <c r="AB43" s="7">
         <f>IF(OR(A43="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC43" s="8" t="str">
         <f>IF(OR(AB43="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB43,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>低于上限</v>
       </c>
       <c r="AD43" s="2"/>
-      <c r="AE43" s="7" t="str">
+      <c r="AE43" s="7">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="44" ht="17" spans="1:31">
-      <c r="A44" s="2"/>
-      <c r="B44" s="2"/>
-      <c r="C44" s="9"/>
-      <c r="D44" s="6"/>
-      <c r="E44" s="9"/>
-      <c r="F44" s="8" t="str">
+        <v>-0.0351992112221575</v>
+      </c>
+    </row>
+    <row r="44" ht="17" spans="1:32">
+      <c r="A44" s="2">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C44" s="9">
+        <v>107638</v>
+      </c>
+      <c r="D44" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E44" s="9">
+        <v>20.43</v>
+      </c>
+      <c r="F44" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>600</v>
       </c>
       <c r="G44" s="8" t="str">
         <f>IF(OR(A44="",F44="",E44="",N44="",E44&lt;=N44,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H44="",F44*(E44-N44),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H44" s="2"/>
-      <c r="I44" s="10"/>
-      <c r="J44" s="9"/>
-      <c r="K44" s="9"/>
-      <c r="L44" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H44" s="2">
+        <v>600</v>
+      </c>
+      <c r="I44" s="10">
+        <v>45138</v>
+      </c>
+      <c r="J44" s="9">
+        <v>24</v>
+      </c>
+      <c r="K44" s="9">
+        <v>30.34</v>
+      </c>
+      <c r="L44" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M44" s="10"/>
-      <c r="N44" s="9"/>
+        <v>600</v>
+      </c>
+      <c r="M44" s="10">
+        <v>45366</v>
+      </c>
+      <c r="N44" s="9">
+        <v>17</v>
+      </c>
       <c r="O44" s="9"/>
       <c r="P44" s="9"/>
       <c r="Q44" s="2"/>
       <c r="R44" s="2"/>
       <c r="S44" s="2"/>
       <c r="T44" s="2"/>
-      <c r="U44" s="7" t="str">
+      <c r="U44" s="7">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="V44" s="7" t="str">
+        <v>0.174743024963289</v>
+      </c>
+      <c r="V44" s="7">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="W44" s="13" t="str">
+        <v>0.16789035731767</v>
+      </c>
+      <c r="W44" s="13">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="X44" s="5" t="str">
+        <v>1.04081632653061</v>
+      </c>
+      <c r="X44" s="5">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Y44" s="7" t="str">
+        <v>5946</v>
+      </c>
+      <c r="Y44" s="7">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="Z44" s="7" t="str">
+        <v>0.485070974057758</v>
+      </c>
+      <c r="Z44" s="7">
         <f>IF(OR(AE44="",多次统计数据!$B$8=""),"",AE44-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA44" s="14" t="str">
+        <v>-0.00399280021821515</v>
+      </c>
+      <c r="AA44" s="14">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB44" s="7" t="str">
+        <v>228</v>
+      </c>
+      <c r="AB44" s="7">
         <f>IF(OR(A44="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC44" s="8" t="str">
         <f>IF(OR(AB44="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB44,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>低于上限</v>
       </c>
       <c r="AD44" s="2"/>
-      <c r="AE44" s="7" t="str">
+      <c r="AE44" s="7">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="45" ht="17" spans="1:31">
-      <c r="A45" s="2"/>
-      <c r="B45" s="2"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="6"/>
-      <c r="E45" s="9"/>
-      <c r="F45" s="8" t="str">
+        <v>0.0552407142458983</v>
+      </c>
+    </row>
+    <row r="45" ht="17" spans="1:32">
+      <c r="A45" s="2">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C45" s="9">
+        <v>113584</v>
+      </c>
+      <c r="D45" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E45" s="9">
+        <v>64.98</v>
+      </c>
+      <c r="F45" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>1100</v>
       </c>
       <c r="G45" s="8" t="str">
         <f>IF(OR(A45="",F45="",E45="",N45="",E45&lt;=N45,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H45="",F45*(E45-N45),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H45" s="2"/>
-      <c r="I45" s="10"/>
-      <c r="J45" s="9"/>
-      <c r="K45" s="9"/>
-      <c r="L45" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H45" s="2">
+        <v>1100</v>
+      </c>
+      <c r="I45" s="10">
+        <v>44613</v>
+      </c>
+      <c r="J45" s="9">
+        <v>69</v>
+      </c>
+      <c r="K45" s="9">
+        <v>69.19</v>
+      </c>
+      <c r="L45" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M45" s="10"/>
-      <c r="N45" s="9"/>
+        <v>1100</v>
+      </c>
+      <c r="M45" s="10">
+        <v>44719</v>
+      </c>
+      <c r="N45" s="9">
+        <v>63</v>
+      </c>
       <c r="O45" s="9"/>
       <c r="P45" s="9"/>
       <c r="Q45" s="2"/>
       <c r="R45" s="2"/>
       <c r="S45" s="2"/>
       <c r="T45" s="2"/>
-      <c r="U45" s="7" t="str">
+      <c r="U45" s="7">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="V45" s="7" t="str">
+        <v>0.0618651892890119</v>
+      </c>
+      <c r="V45" s="7">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="W45" s="13" t="str">
+        <v>0.0304709141274239</v>
+      </c>
+      <c r="W45" s="13">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="X45" s="5" t="str">
+        <v>2.03030303030302</v>
+      </c>
+      <c r="X45" s="5">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Y45" s="7" t="str">
+        <v>4631</v>
+      </c>
+      <c r="Y45" s="7">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="Z45" s="7" t="str">
+        <v>0.0647891658971991</v>
+      </c>
+      <c r="Z45" s="7">
         <f>IF(OR(AE45="",多次统计数据!$B$8=""),"",AE45-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA45" s="14" t="str">
+        <v>-0.0184619269165715</v>
+      </c>
+      <c r="AA45" s="14">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB45" s="7" t="str">
+        <v>106</v>
+      </c>
+      <c r="AB45" s="7">
         <f>IF(OR(A45="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC45" s="8" t="str">
         <f>IF(OR(AB45="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB45,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>低于上限</v>
       </c>
       <c r="AD45" s="2"/>
-      <c r="AE45" s="7" t="str">
+      <c r="AE45" s="7">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="46" ht="17" spans="1:31">
-      <c r="A46" s="2"/>
-      <c r="B46" s="2"/>
-      <c r="C46" s="9"/>
-      <c r="D46" s="6"/>
-      <c r="E46" s="9"/>
-      <c r="F46" s="8" t="str">
+        <v>0.0407715875475419</v>
+      </c>
+    </row>
+    <row r="46" ht="17" spans="1:32">
+      <c r="A46" s="2">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C46" s="9">
+        <v>118215</v>
+      </c>
+      <c r="D46" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E46" s="9">
+        <v>66.85</v>
+      </c>
+      <c r="F46" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>6700</v>
       </c>
       <c r="G46" s="8" t="str">
         <f>IF(OR(A46="",F46="",E46="",N46="",E46&lt;=N46,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H46="",F46*(E46-N46),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H46" s="2"/>
-      <c r="I46" s="10"/>
-      <c r="J46" s="9"/>
-      <c r="K46" s="9"/>
-      <c r="L46" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H46" s="2">
+        <v>6700</v>
+      </c>
+      <c r="I46" s="10">
+        <v>44722</v>
+      </c>
+      <c r="J46" s="9">
+        <v>69</v>
+      </c>
+      <c r="K46" s="9">
+        <v>66.07</v>
+      </c>
+      <c r="L46" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M46" s="10"/>
-      <c r="N46" s="9"/>
+        <v>6700</v>
+      </c>
+      <c r="M46" s="10">
+        <v>44725</v>
+      </c>
+      <c r="N46" s="9">
+        <v>66.5</v>
+      </c>
       <c r="O46" s="9"/>
       <c r="P46" s="9"/>
       <c r="Q46" s="2"/>
       <c r="R46" s="2"/>
       <c r="S46" s="2"/>
       <c r="T46" s="2"/>
-      <c r="U46" s="7" t="str">
+      <c r="U46" s="7">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="V46" s="7" t="str">
+        <v>0.0321615557217652</v>
+      </c>
+      <c r="V46" s="7">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="W46" s="13" t="str">
+        <v>0.00523560209424075</v>
+      </c>
+      <c r="W46" s="13">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="X46" s="5" t="str">
+        <v>6.14285714285726</v>
+      </c>
+      <c r="X46" s="5">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Y46" s="7" t="str">
+        <v>-5226</v>
+      </c>
+      <c r="Y46" s="7">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="Z46" s="7" t="str">
+        <v>-0.0116679132385939</v>
+      </c>
+      <c r="Z46" s="7">
         <f>IF(OR(AE46="",多次统计数据!$B$8=""),"",AE46-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA46" s="14" t="str">
+        <v>-0.103441102333673</v>
+      </c>
+      <c r="AA46" s="14">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB46" s="7" t="str">
+        <v>3</v>
+      </c>
+      <c r="AB46" s="7">
         <f>IF(OR(A46="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC46" s="8" t="str">
         <f>IF(OR(AB46="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB46,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>低于上限</v>
       </c>
       <c r="AD46" s="2"/>
-      <c r="AE46" s="7" t="str">
+      <c r="AE46" s="7">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="17" spans="1:31">
-      <c r="A47" s="2"/>
-      <c r="B47" s="2"/>
-      <c r="C47" s="9"/>
-      <c r="D47" s="6"/>
-      <c r="E47" s="9"/>
-      <c r="F47" s="8" t="str">
+        <v>-0.0442075878695597</v>
+      </c>
+    </row>
+    <row r="47" ht="17" spans="1:32">
+      <c r="A47" s="2">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C47" s="9">
+        <v>112989</v>
+      </c>
+      <c r="D47" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E47" s="9">
+        <v>66.45</v>
+      </c>
+      <c r="F47" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>1500</v>
       </c>
       <c r="G47" s="8" t="str">
         <f>IF(OR(A47="",F47="",E47="",N47="",E47&lt;=N47,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H47="",F47*(E47-N47),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H47" s="2"/>
-      <c r="I47" s="10"/>
-      <c r="J47" s="9"/>
-      <c r="K47" s="9"/>
-      <c r="L47" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H47" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I47" s="10">
+        <v>44732</v>
+      </c>
+      <c r="J47" s="9">
+        <v>69</v>
+      </c>
+      <c r="K47" s="9">
+        <v>63.21</v>
+      </c>
+      <c r="L47" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M47" s="10"/>
-      <c r="N47" s="9"/>
+        <v>1500</v>
+      </c>
+      <c r="M47" s="10">
+        <v>44764</v>
+      </c>
+      <c r="N47" s="9">
+        <v>65</v>
+      </c>
       <c r="O47" s="9"/>
       <c r="P47" s="9"/>
       <c r="Q47" s="2"/>
       <c r="R47" s="2"/>
       <c r="S47" s="2"/>
       <c r="T47" s="2"/>
-      <c r="U47" s="7" t="str">
+      <c r="U47" s="7">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="V47" s="7" t="str">
+        <v>0.0383747178329571</v>
+      </c>
+      <c r="V47" s="7">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="W47" s="13" t="str">
+        <v>0.0218209179834462</v>
+      </c>
+      <c r="W47" s="13">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="X47" s="5" t="str">
+        <v>1.75862068965517</v>
+      </c>
+      <c r="X47" s="5">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Y47" s="7" t="str">
+        <v>-4860</v>
+      </c>
+      <c r="Y47" s="7">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="Z47" s="7" t="str">
+        <v>-0.0487584650112867</v>
+      </c>
+      <c r="Z47" s="7">
         <f>IF(OR(AE47="",多次统计数据!$B$8=""),"",AE47-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA47" s="14" t="str">
+        <v>-0.1022465511314</v>
+      </c>
+      <c r="AA47" s="14">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB47" s="7" t="str">
+        <v>32</v>
+      </c>
+      <c r="AB47" s="7">
         <f>IF(OR(A47="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC47" s="8" t="str">
         <f>IF(OR(AB47="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB47,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>低于上限</v>
       </c>
       <c r="AD47" s="2"/>
-      <c r="AE47" s="7" t="str">
+      <c r="AE47" s="7">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="48" ht="17" spans="1:31">
-      <c r="A48" s="2"/>
-      <c r="B48" s="2"/>
-      <c r="C48" s="9"/>
-      <c r="D48" s="6"/>
-      <c r="E48" s="9"/>
-      <c r="F48" s="8" t="str">
+        <v>-0.0430130366672862</v>
+      </c>
+      <c r="AF47" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="48" ht="17" spans="1:32">
+      <c r="A48" s="2">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C48" s="9">
+        <v>108129</v>
+      </c>
+      <c r="D48" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E48" s="9">
+        <v>51.49</v>
+      </c>
+      <c r="F48" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>1400</v>
       </c>
       <c r="G48" s="8" t="str">
         <f>IF(OR(A48="",F48="",E48="",N48="",E48&lt;=N48,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H48="",F48*(E48-N48),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H48" s="2"/>
-      <c r="I48" s="10"/>
-      <c r="J48" s="9"/>
-      <c r="K48" s="9"/>
-      <c r="L48" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H48" s="2">
+        <v>1400</v>
+      </c>
+      <c r="I48" s="10">
+        <v>45070</v>
+      </c>
+      <c r="J48" s="9">
+        <v>55</v>
+      </c>
+      <c r="K48" s="9">
+        <v>56</v>
+      </c>
+      <c r="L48" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M48" s="10"/>
-      <c r="N48" s="9"/>
+        <v>1400</v>
+      </c>
+      <c r="M48" s="10">
+        <v>45077</v>
+      </c>
+      <c r="N48" s="9">
+        <v>50</v>
+      </c>
       <c r="O48" s="9"/>
       <c r="P48" s="9"/>
       <c r="Q48" s="2"/>
       <c r="R48" s="2"/>
       <c r="S48" s="2"/>
       <c r="T48" s="2"/>
-      <c r="U48" s="7" t="str">
+      <c r="U48" s="7">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="V48" s="7" t="str">
+        <v>0.0681685764226063</v>
+      </c>
+      <c r="V48" s="7">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="W48" s="13" t="str">
+        <v>0.0289376577976306</v>
+      </c>
+      <c r="W48" s="13">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="X48" s="5" t="str">
+        <v>2.35570469798657</v>
+      </c>
+      <c r="X48" s="5">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Y48" s="7" t="str">
+        <v>6314</v>
+      </c>
+      <c r="Y48" s="7">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="Z48" s="7" t="str">
+        <v>0.0875898232666537</v>
+      </c>
+      <c r="Z48" s="7">
         <f>IF(OR(AE48="",多次统计数据!$B$8=""),"",AE48-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA48" s="14" t="str">
+        <v>-0.000840298953010958</v>
+      </c>
+      <c r="AA48" s="14">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB48" s="7" t="str">
+        <v>7</v>
+      </c>
+      <c r="AB48" s="7">
         <f>IF(OR(A48="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC48" s="8" t="str">
         <f>IF(OR(AB48="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB48,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>低于上限</v>
       </c>
       <c r="AD48" s="2"/>
-      <c r="AE48" s="7" t="str">
+      <c r="AE48" s="7">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="49" ht="17" spans="1:31">
-      <c r="A49" s="2"/>
-      <c r="B49" s="2"/>
-      <c r="C49" s="9"/>
-      <c r="D49" s="6"/>
-      <c r="E49" s="9"/>
-      <c r="F49" s="8" t="str">
+        <v>0.0583932155111025</v>
+      </c>
+    </row>
+    <row r="49" ht="17" spans="1:32">
+      <c r="A49" s="2">
+        <v>48</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C49" s="9">
+        <v>111443</v>
+      </c>
+      <c r="D49" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E49" s="9">
+        <v>52.19</v>
+      </c>
+      <c r="F49" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>1000</v>
       </c>
       <c r="G49" s="8" t="str">
         <f>IF(OR(A49="",F49="",E49="",N49="",E49&lt;=N49,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H49="",F49*(E49-N49),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H49" s="2"/>
-      <c r="I49" s="10"/>
-      <c r="J49" s="9"/>
-      <c r="K49" s="9"/>
-      <c r="L49" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H49" s="2">
+        <v>1000</v>
+      </c>
+      <c r="I49" s="10">
+        <v>45153</v>
+      </c>
+      <c r="J49" s="9">
+        <v>55</v>
+      </c>
+      <c r="K49" s="9">
+        <v>46.45</v>
+      </c>
+      <c r="L49" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M49" s="10"/>
-      <c r="N49" s="9"/>
+        <v>1000</v>
+      </c>
+      <c r="M49" s="10">
+        <v>45159</v>
+      </c>
+      <c r="N49" s="9">
+        <v>50</v>
+      </c>
       <c r="O49" s="9"/>
       <c r="P49" s="9"/>
       <c r="Q49" s="2"/>
       <c r="R49" s="2"/>
       <c r="S49" s="2"/>
       <c r="T49" s="2"/>
-      <c r="U49" s="7" t="str">
+      <c r="U49" s="7">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="V49" s="7" t="str">
+        <v>0.0538417321325925</v>
+      </c>
+      <c r="V49" s="7">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="W49" s="13" t="str">
+        <v>0.0419620616976432</v>
+      </c>
+      <c r="W49" s="13">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="X49" s="5" t="str">
+        <v>1.28310502283105</v>
+      </c>
+      <c r="X49" s="5">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Y49" s="7" t="str">
+        <v>-5740</v>
+      </c>
+      <c r="Y49" s="7">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="Z49" s="7" t="str">
+        <v>-0.109982755317111</v>
+      </c>
+      <c r="Z49" s="7">
         <f>IF(OR(AE49="",多次统计数据!$B$8=""),"",AE49-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA49" s="14" t="str">
+        <v>-0.110739665590698</v>
+      </c>
+      <c r="AA49" s="14">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB49" s="7" t="str">
+        <v>6</v>
+      </c>
+      <c r="AB49" s="7">
         <f>IF(OR(A49="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC49" s="8" t="str">
         <f>IF(OR(AB49="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB49,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>低于上限</v>
       </c>
       <c r="AD49" s="2"/>
-      <c r="AE49" s="7" t="str">
+      <c r="AE49" s="7">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="50" ht="17" spans="1:31">
-      <c r="A50" s="2"/>
-      <c r="B50" s="2"/>
-      <c r="C50" s="9"/>
-      <c r="D50" s="6"/>
-      <c r="E50" s="9"/>
-      <c r="F50" s="8" t="str">
+        <v>-0.0515061511265849</v>
+      </c>
+      <c r="AF49" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="50" ht="17" spans="1:32">
+      <c r="A50" s="2">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C50" s="9">
+        <v>108793</v>
+      </c>
+      <c r="D50" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E50" s="9">
+        <v>41.88</v>
+      </c>
+      <c r="F50" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>1100</v>
       </c>
       <c r="G50" s="8" t="str">
         <f>IF(OR(A50="",F50="",E50="",N50="",E50&lt;=N50,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H50="",F50*(E50-N50),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H50" s="2"/>
-      <c r="I50" s="10"/>
-      <c r="J50" s="9"/>
-      <c r="K50" s="9"/>
-      <c r="L50" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H50" s="2">
+        <v>1100</v>
+      </c>
+      <c r="I50" s="10">
+        <v>45309</v>
+      </c>
+      <c r="J50" s="9">
+        <v>45.5</v>
+      </c>
+      <c r="K50" s="9">
+        <v>38.83</v>
+      </c>
+      <c r="L50" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M50" s="10"/>
-      <c r="N50" s="9"/>
+        <v>1100</v>
+      </c>
+      <c r="M50" s="10">
+        <v>45313</v>
+      </c>
+      <c r="N50" s="9">
+        <v>40</v>
+      </c>
       <c r="O50" s="9"/>
       <c r="P50" s="9"/>
       <c r="Q50" s="2"/>
       <c r="R50" s="2"/>
       <c r="S50" s="2"/>
       <c r="T50" s="2"/>
-      <c r="U50" s="7" t="str">
+      <c r="U50" s="7">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="V50" s="7" t="str">
+        <v>0.0864374403056351</v>
+      </c>
+      <c r="V50" s="7">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="W50" s="13" t="str">
+        <v>0.0448901623686725</v>
+      </c>
+      <c r="W50" s="13">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="X50" s="5" t="str">
+        <v>1.92553191489361</v>
+      </c>
+      <c r="X50" s="5">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Y50" s="7" t="str">
+        <v>-3355</v>
+      </c>
+      <c r="Y50" s="7">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="Z50" s="7" t="str">
+        <v>-0.0728271251193887</v>
+      </c>
+      <c r="Z50" s="7">
         <f>IF(OR(AE50="",多次统计数据!$B$8=""),"",AE50-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA50" s="14" t="str">
+        <v>-0.0900718956099592</v>
+      </c>
+      <c r="AA50" s="14">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB50" s="7" t="str">
+        <v>4</v>
+      </c>
+      <c r="AB50" s="7">
         <f>IF(OR(A50="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC50" s="8" t="str">
         <f>IF(OR(AB50="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB50,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>低于上限</v>
       </c>
       <c r="AD50" s="2"/>
-      <c r="AE50" s="7" t="str">
+      <c r="AE50" s="7">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="51" ht="17" spans="1:31">
-      <c r="A51" s="2"/>
-      <c r="B51" s="2"/>
-      <c r="C51" s="9"/>
-      <c r="D51" s="6"/>
-      <c r="E51" s="9"/>
-      <c r="F51" s="8" t="str">
+        <v>-0.0308383811458458</v>
+      </c>
+      <c r="AF50" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="51" ht="17" spans="1:32">
+      <c r="A51" s="2">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C51" s="9">
+        <v>105348</v>
+      </c>
+      <c r="D51" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E51" s="9">
+        <v>97.5</v>
+      </c>
+      <c r="F51" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>800</v>
       </c>
       <c r="G51" s="8" t="str">
         <f>IF(OR(A51="",F51="",E51="",N51="",E51&lt;=N51,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H51="",F51*(E51-N51),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H51" s="2"/>
-      <c r="I51" s="10"/>
-      <c r="J51" s="9"/>
-      <c r="K51" s="9"/>
-      <c r="L51" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H51" s="2">
+        <v>800</v>
+      </c>
+      <c r="I51" s="10">
+        <v>45833</v>
+      </c>
+      <c r="J51" s="9">
+        <v>100</v>
+      </c>
+      <c r="K51" s="9">
+        <v>129.8</v>
+      </c>
+      <c r="L51" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M51" s="10"/>
-      <c r="N51" s="9"/>
+        <v>800</v>
+      </c>
+      <c r="M51" s="10">
+        <v>45861</v>
+      </c>
+      <c r="N51" s="9">
+        <v>95</v>
+      </c>
       <c r="O51" s="9"/>
       <c r="P51" s="9"/>
       <c r="Q51" s="2"/>
       <c r="R51" s="2"/>
       <c r="S51" s="2"/>
       <c r="T51" s="2"/>
-      <c r="U51" s="7" t="str">
+      <c r="U51" s="7">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="V51" s="7" t="str">
+        <v>0.0256410256410256</v>
+      </c>
+      <c r="V51" s="7">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="W51" s="13" t="str">
+        <v>0.0256410256410256</v>
+      </c>
+      <c r="W51" s="13">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="X51" s="5" t="str">
+        <v>1</v>
+      </c>
+      <c r="X51" s="5">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Y51" s="7" t="str">
+        <v>25840</v>
+      </c>
+      <c r="Y51" s="7">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="Z51" s="7" t="str">
+        <v>0.331282051282051</v>
+      </c>
+      <c r="Z51" s="7">
         <f>IF(OR(AE51="",多次统计数据!$B$8=""),"",AE51-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA51" s="14" t="str">
+        <v>0.186048788000101</v>
+      </c>
+      <c r="AA51" s="14">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB51" s="7" t="str">
+        <v>28</v>
+      </c>
+      <c r="AB51" s="7">
         <f>IF(OR(A51="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC51" s="8" t="str">
         <f>IF(OR(AB51="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB51,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>低于上限</v>
       </c>
       <c r="AD51" s="2"/>
-      <c r="AE51" s="7" t="str">
+      <c r="AE51" s="7">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="52" ht="17" spans="1:31">
-      <c r="A52" s="2"/>
-      <c r="B52" s="2"/>
-      <c r="C52" s="9"/>
-      <c r="D52" s="6"/>
-      <c r="E52" s="9"/>
-      <c r="F52" s="8" t="str">
+        <v>0.245282302464214</v>
+      </c>
+    </row>
+    <row r="52" ht="17" spans="1:32">
+      <c r="A52" s="2">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C52" s="9">
+        <v>131188</v>
+      </c>
+      <c r="D52" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E52" s="9">
+        <v>139.18</v>
+      </c>
+      <c r="F52" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>600</v>
       </c>
       <c r="G52" s="8" t="str">
         <f>IF(OR(A52="",F52="",E52="",N52="",E52&lt;=N52,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H52="",F52*(E52-N52),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H52" s="2"/>
-      <c r="I52" s="10"/>
-      <c r="J52" s="9"/>
-      <c r="K52" s="9"/>
-      <c r="L52" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H52" s="2">
+        <v>600</v>
+      </c>
+      <c r="I52" s="10">
+        <v>45890</v>
+      </c>
+      <c r="J52" s="9">
+        <v>150</v>
+      </c>
+      <c r="K52" s="9">
+        <v>177.39</v>
+      </c>
+      <c r="L52" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M52" s="10"/>
-      <c r="N52" s="9"/>
+        <v>600</v>
+      </c>
+      <c r="M52" s="10">
+        <v>45902</v>
+      </c>
+      <c r="N52" s="9">
+        <v>135</v>
+      </c>
       <c r="O52" s="9"/>
       <c r="P52" s="9"/>
       <c r="Q52" s="2"/>
       <c r="R52" s="2"/>
       <c r="S52" s="2"/>
       <c r="T52" s="2"/>
-      <c r="U52" s="7" t="str">
+      <c r="U52" s="7">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="V52" s="7" t="str">
+        <v>0.0777410547492455</v>
+      </c>
+      <c r="V52" s="7">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="W52" s="13" t="str">
+        <v>0.030033050725679</v>
+      </c>
+      <c r="W52" s="13">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="X52" s="5" t="str">
+        <v>2.58851674641148</v>
+      </c>
+      <c r="X52" s="5">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Y52" s="7" t="str">
+        <v>22926</v>
+      </c>
+      <c r="Y52" s="7">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="Z52" s="7" t="str">
+        <v>0.274536571346458</v>
+      </c>
+      <c r="Z52" s="7">
         <f>IF(OR(AE52="",多次统计数据!$B$8=""),"",AE52-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA52" s="14" t="str">
+        <v>0.115523323051513</v>
+      </c>
+      <c r="AA52" s="14">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB52" s="7" t="str">
+        <v>12</v>
+      </c>
+      <c r="AB52" s="7">
         <f>IF(OR(A52="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC52" s="8" t="str">
         <f>IF(OR(AB52="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB52,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>低于上限</v>
       </c>
       <c r="AD52" s="2"/>
-      <c r="AE52" s="7" t="str">
+      <c r="AE52" s="7">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="53" ht="17" spans="1:31">
-      <c r="A53" s="2"/>
-      <c r="B53" s="2"/>
-      <c r="C53" s="9"/>
-      <c r="D53" s="6"/>
-      <c r="E53" s="9"/>
-      <c r="F53" s="8" t="str">
+        <v>0.174756837515626</v>
+      </c>
+    </row>
+    <row r="53" ht="17" spans="1:32">
+      <c r="A53" s="2">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C53" s="9">
+        <v>154114</v>
+      </c>
+      <c r="D53" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E53" s="9">
+        <v>41.46</v>
+      </c>
+      <c r="F53" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>1200</v>
       </c>
       <c r="G53" s="8" t="str">
         <f>IF(OR(A53="",F53="",E53="",N53="",E53&lt;=N53,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H53="",F53*(E53-N53),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H53" s="2"/>
-      <c r="I53" s="10"/>
-      <c r="J53" s="9"/>
-      <c r="K53" s="9"/>
-      <c r="L53" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H53" s="2">
+        <v>1200</v>
+      </c>
+      <c r="I53" s="10">
+        <v>44221</v>
+      </c>
+      <c r="J53" s="9">
+        <v>45</v>
+      </c>
+      <c r="K53" s="9">
+        <v>38.76</v>
+      </c>
+      <c r="L53" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M53" s="10"/>
-      <c r="N53" s="9"/>
+        <v>1200</v>
+      </c>
+      <c r="M53" s="10">
+        <v>44223</v>
+      </c>
+      <c r="N53" s="9">
+        <v>39</v>
+      </c>
       <c r="O53" s="9"/>
       <c r="P53" s="9"/>
       <c r="Q53" s="2"/>
       <c r="R53" s="2"/>
       <c r="S53" s="2"/>
       <c r="T53" s="2"/>
-      <c r="U53" s="7" t="str">
+      <c r="U53" s="7">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="V53" s="7" t="str">
+        <v>0.085383502170767</v>
+      </c>
+      <c r="V53" s="7">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="W53" s="13" t="str">
+        <v>0.0593342981186686</v>
+      </c>
+      <c r="W53" s="13">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="X53" s="5" t="str">
+        <v>1.4390243902439</v>
+      </c>
+      <c r="X53" s="5">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Y53" s="7" t="str">
+        <v>-3240</v>
+      </c>
+      <c r="Y53" s="7">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="Z53" s="7" t="str">
+        <v>-0.065123010130246</v>
+      </c>
+      <c r="Z53" s="7">
         <f>IF(OR(AE53="",多次统计数据!$B$8=""),"",AE53-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA53" s="14" t="str">
+        <v>-0.0802569127277365</v>
+      </c>
+      <c r="AA53" s="14">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB53" s="7" t="str">
+        <v>2</v>
+      </c>
+      <c r="AB53" s="7">
         <f>IF(OR(A53="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC53" s="8" t="str">
         <f>IF(OR(AB53="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB53,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>低于上限</v>
       </c>
       <c r="AD53" s="2"/>
-      <c r="AE53" s="7" t="str">
+      <c r="AE53" s="7">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="54" ht="17" spans="1:31">
-      <c r="A54" s="2"/>
-      <c r="B54" s="2"/>
-      <c r="C54" s="9"/>
-      <c r="D54" s="6"/>
-      <c r="E54" s="9"/>
-      <c r="F54" s="8" t="str">
+        <v>-0.021023398263623</v>
+      </c>
+    </row>
+    <row r="54" ht="17" spans="1:32">
+      <c r="A54" s="2">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C54" s="9">
+        <v>150874</v>
+      </c>
+      <c r="D54" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E54" s="9">
+        <v>20.64</v>
+      </c>
+      <c r="F54" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>1600</v>
       </c>
       <c r="G54" s="8" t="str">
         <f>IF(OR(A54="",F54="",E54="",N54="",E54&lt;=N54,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H54="",F54*(E54-N54),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H54" s="2"/>
-      <c r="I54" s="10"/>
-      <c r="J54" s="9"/>
-      <c r="K54" s="9"/>
-      <c r="L54" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H54" s="2">
+        <v>1600</v>
+      </c>
+      <c r="I54" s="10">
+        <v>44496</v>
+      </c>
+      <c r="J54" s="9">
+        <v>24</v>
+      </c>
+      <c r="K54" s="9">
+        <v>22.77</v>
+      </c>
+      <c r="L54" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M54" s="10"/>
-      <c r="N54" s="9"/>
+        <v>1600</v>
+      </c>
+      <c r="M54" s="10">
+        <v>44501</v>
+      </c>
+      <c r="N54" s="9">
+        <v>18.8</v>
+      </c>
       <c r="O54" s="9"/>
       <c r="P54" s="9"/>
       <c r="Q54" s="2"/>
       <c r="R54" s="2"/>
       <c r="S54" s="2"/>
       <c r="T54" s="2"/>
-      <c r="U54" s="7" t="str">
+      <c r="U54" s="7">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="V54" s="7" t="str">
+        <v>0.162790697674419</v>
+      </c>
+      <c r="V54" s="7">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="W54" s="13" t="str">
+        <v>0.0891472868217054</v>
+      </c>
+      <c r="W54" s="13">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="X54" s="5" t="str">
+        <v>1.82608695652174</v>
+      </c>
+      <c r="X54" s="5">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Y54" s="7" t="str">
+        <v>3408</v>
+      </c>
+      <c r="Y54" s="7">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="Z54" s="7" t="str">
+        <v>0.103197674418605</v>
+      </c>
+      <c r="Z54" s="7">
         <f>IF(OR(AE54="",多次统计数据!$B$8=""),"",AE54-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA54" s="14" t="str">
+        <v>-0.0366451294541051</v>
+      </c>
+      <c r="AA54" s="14">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB54" s="7" t="str">
+        <v>5</v>
+      </c>
+      <c r="AB54" s="7">
         <f>IF(OR(A54="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC54" s="8" t="str">
         <f>IF(OR(AB54="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB54,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>低于上限</v>
       </c>
       <c r="AD54" s="2"/>
-      <c r="AE54" s="7" t="str">
+      <c r="AE54" s="7">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="55" ht="17" spans="1:31">
-      <c r="A55" s="2"/>
-      <c r="B55" s="2"/>
-      <c r="C55" s="9"/>
-      <c r="D55" s="6"/>
-      <c r="E55" s="9"/>
-      <c r="F55" s="8" t="str">
+        <v>0.0225883850100084</v>
+      </c>
+    </row>
+    <row r="55" ht="17" spans="1:32">
+      <c r="A55" s="2">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C55" s="9">
+        <v>154282</v>
+      </c>
+      <c r="D55" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E55" s="9">
+        <v>21.57</v>
+      </c>
+      <c r="F55" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>1900</v>
       </c>
       <c r="G55" s="8" t="str">
         <f>IF(OR(A55="",F55="",E55="",N55="",E55&lt;=N55,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H55="",F55*(E55-N55),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H55" s="2"/>
-      <c r="I55" s="10"/>
-      <c r="J55" s="9"/>
-      <c r="K55" s="9"/>
-      <c r="L55" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H55" s="2">
+        <v>1900</v>
+      </c>
+      <c r="I55" s="10">
+        <v>44662</v>
+      </c>
+      <c r="J55" s="9">
+        <v>24</v>
+      </c>
+      <c r="K55" s="9">
+        <v>24.04</v>
+      </c>
+      <c r="L55" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M55" s="10"/>
-      <c r="N55" s="9"/>
+        <v>1900</v>
+      </c>
+      <c r="M55" s="10">
+        <v>44670</v>
+      </c>
+      <c r="N55" s="9">
+        <v>20</v>
+      </c>
       <c r="O55" s="9"/>
       <c r="P55" s="9"/>
       <c r="Q55" s="2"/>
       <c r="R55" s="2"/>
       <c r="S55" s="2"/>
       <c r="T55" s="2"/>
-      <c r="U55" s="7" t="str">
+      <c r="U55" s="7">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="V55" s="7" t="str">
+        <v>0.112656467315716</v>
+      </c>
+      <c r="V55" s="7">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="W55" s="13" t="str">
+        <v>0.0727862772369031</v>
+      </c>
+      <c r="W55" s="13">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="X55" s="5" t="str">
+        <v>1.54777070063694</v>
+      </c>
+      <c r="X55" s="5">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Y55" s="7" t="str">
+        <v>4693</v>
+      </c>
+      <c r="Y55" s="7">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="Z55" s="7" t="str">
+        <v>0.114510894761242</v>
+      </c>
+      <c r="Z55" s="7">
         <f>IF(OR(AE55="",多次统计数据!$B$8=""),"",AE55-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA55" s="14" t="str">
+        <v>-0.0288151895785143</v>
+      </c>
+      <c r="AA55" s="14">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB55" s="7" t="str">
+        <v>8</v>
+      </c>
+      <c r="AB55" s="7">
         <f>IF(OR(A55="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC55" s="8" t="str">
         <f>IF(OR(AB55="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB55,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>低于上限</v>
       </c>
       <c r="AD55" s="2"/>
-      <c r="AE55" s="7" t="str">
+      <c r="AE55" s="7">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="56" ht="17" spans="1:31">
-      <c r="A56" s="2"/>
-      <c r="B56" s="2"/>
-      <c r="C56" s="9"/>
-      <c r="D56" s="6"/>
-      <c r="E56" s="9"/>
-      <c r="F56" s="8" t="str">
+        <v>0.0304183248855991</v>
+      </c>
+    </row>
+    <row r="56" ht="17" spans="1:32">
+      <c r="A56" s="2">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C56" s="9">
+        <v>158975</v>
+      </c>
+      <c r="D56" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E56" s="9">
+        <v>21.3</v>
+      </c>
+      <c r="F56" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>2400</v>
       </c>
       <c r="G56" s="8" t="str">
         <f>IF(OR(A56="",F56="",E56="",N56="",E56&lt;=N56,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H56="",F56*(E56-N56),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H56" s="2"/>
-      <c r="I56" s="10"/>
-      <c r="J56" s="9"/>
-      <c r="K56" s="9"/>
-      <c r="L56" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H56" s="2">
+        <v>2000</v>
+      </c>
+      <c r="I56" s="10">
+        <v>44719</v>
+      </c>
+      <c r="J56" s="9">
+        <v>24</v>
+      </c>
+      <c r="K56" s="9">
+        <v>20.41</v>
+      </c>
+      <c r="L56" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M56" s="10"/>
-      <c r="N56" s="9"/>
+        <v>2000</v>
+      </c>
+      <c r="M56" s="10">
+        <v>44769</v>
+      </c>
+      <c r="N56" s="9">
+        <v>20</v>
+      </c>
       <c r="O56" s="9"/>
       <c r="P56" s="9"/>
       <c r="Q56" s="2"/>
       <c r="R56" s="2"/>
       <c r="S56" s="2"/>
       <c r="T56" s="2"/>
-      <c r="U56" s="7" t="str">
+      <c r="U56" s="7">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="V56" s="7" t="str">
+        <v>0.126760563380282</v>
+      </c>
+      <c r="V56" s="7">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="W56" s="13" t="str">
+        <v>0.0610328638497653</v>
+      </c>
+      <c r="W56" s="13">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="X56" s="5" t="str">
+        <v>2.07692307692308</v>
+      </c>
+      <c r="X56" s="5">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Y56" s="7" t="str">
+        <v>-1780</v>
+      </c>
+      <c r="Y56" s="7">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="Z56" s="7" t="str">
+        <v>-0.0417840375586854</v>
+      </c>
+      <c r="Z56" s="7">
         <f>IF(OR(AE56="",多次统计数据!$B$8=""),"",AE56-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA56" s="14" t="str">
+        <v>-0.0704302435095608</v>
+      </c>
+      <c r="AA56" s="14">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB56" s="7" t="str">
+        <v>50</v>
+      </c>
+      <c r="AB56" s="7">
         <f>IF(OR(A56="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC56" s="8" t="str">
         <f>IF(OR(AB56="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB56,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>低于上限</v>
       </c>
       <c r="AD56" s="2"/>
-      <c r="AE56" s="7" t="str">
+      <c r="AE56" s="7">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="57" ht="17" spans="1:31">
-      <c r="A57" s="2"/>
-      <c r="B57" s="2"/>
-      <c r="C57" s="9"/>
-      <c r="D57" s="6"/>
-      <c r="E57" s="9"/>
-      <c r="F57" s="8" t="str">
+        <v>-0.0111967290454474</v>
+      </c>
+    </row>
+    <row r="57" ht="17" spans="1:32">
+      <c r="A57" s="2">
+        <v>56</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C57" s="9">
+        <v>157195</v>
+      </c>
+      <c r="D57" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E57" s="9">
+        <v>50.39</v>
+      </c>
+      <c r="F57" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>1000</v>
       </c>
       <c r="G57" s="8" t="str">
         <f>IF(OR(A57="",F57="",E57="",N57="",E57&lt;=N57,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H57="",F57*(E57-N57),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H57" s="2"/>
-      <c r="I57" s="10"/>
-      <c r="J57" s="9"/>
-      <c r="K57" s="9"/>
-      <c r="L57" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H57" s="2">
+        <v>1000</v>
+      </c>
+      <c r="I57" s="10">
+        <v>44351</v>
+      </c>
+      <c r="J57" s="9">
+        <v>60</v>
+      </c>
+      <c r="K57" s="9">
+        <v>55</v>
+      </c>
+      <c r="L57" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M57" s="10"/>
-      <c r="N57" s="9"/>
+        <v>1000</v>
+      </c>
+      <c r="M57" s="10">
+        <v>44356</v>
+      </c>
+      <c r="N57" s="9">
+        <v>47.5</v>
+      </c>
       <c r="O57" s="9"/>
       <c r="P57" s="9"/>
       <c r="Q57" s="2"/>
       <c r="R57" s="2"/>
       <c r="S57" s="2"/>
       <c r="T57" s="2"/>
-      <c r="U57" s="7" t="str">
+      <c r="U57" s="7">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="V57" s="7" t="str">
+        <v>0.190712442945029</v>
+      </c>
+      <c r="V57" s="7">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="W57" s="13" t="str">
+        <v>0.0573526493351856</v>
+      </c>
+      <c r="W57" s="13">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="X57" s="5" t="str">
+        <v>3.32525951557093</v>
+      </c>
+      <c r="X57" s="5">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Y57" s="7" t="str">
+        <v>4610</v>
+      </c>
+      <c r="Y57" s="7">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="Z57" s="7" t="str">
+        <v>0.091486406032943</v>
+      </c>
+      <c r="Z57" s="7">
         <f>IF(OR(AE57="",多次统计数据!$B$8=""),"",AE57-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA57" s="14" t="str">
+        <v>-0.0299068819376336</v>
+      </c>
+      <c r="AA57" s="14">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB57" s="7" t="str">
+        <v>5</v>
+      </c>
+      <c r="AB57" s="7">
         <f>IF(OR(A57="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC57" s="8" t="str">
         <f>IF(OR(AB57="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB57,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>低于上限</v>
       </c>
       <c r="AD57" s="2"/>
-      <c r="AE57" s="7" t="str">
+      <c r="AE57" s="7">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="58" ht="17" spans="1:31">
-      <c r="A58" s="2"/>
-      <c r="B58" s="2"/>
-      <c r="C58" s="9"/>
-      <c r="D58" s="6"/>
-      <c r="E58" s="9"/>
-      <c r="F58" s="8" t="str">
+        <v>0.0293266325264799</v>
+      </c>
+    </row>
+    <row r="58" ht="17" spans="1:32">
+      <c r="A58" s="2">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C58" s="9">
+        <v>161805</v>
+      </c>
+      <c r="D58" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E58" s="9">
+        <v>45.04</v>
+      </c>
+      <c r="F58" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>1200</v>
       </c>
       <c r="G58" s="8" t="str">
         <f>IF(OR(A58="",F58="",E58="",N58="",E58&lt;=N58,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H58="",F58*(E58-N58),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H58" s="2"/>
-      <c r="I58" s="10"/>
-      <c r="J58" s="9"/>
-      <c r="K58" s="9"/>
-      <c r="L58" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H58" s="2">
+        <v>1200</v>
+      </c>
+      <c r="I58" s="10">
+        <v>44742</v>
+      </c>
+      <c r="J58" s="9">
+        <v>50</v>
+      </c>
+      <c r="K58" s="9">
+        <v>49.64</v>
+      </c>
+      <c r="L58" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M58" s="10"/>
-      <c r="N58" s="9"/>
+        <v>1200</v>
+      </c>
+      <c r="M58" s="10">
+        <v>44755</v>
+      </c>
+      <c r="N58" s="9">
+        <v>42.5</v>
+      </c>
       <c r="O58" s="9"/>
       <c r="P58" s="9"/>
       <c r="Q58" s="2"/>
       <c r="R58" s="2"/>
       <c r="S58" s="2"/>
       <c r="T58" s="2"/>
-      <c r="U58" s="7" t="str">
+      <c r="U58" s="7">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="V58" s="7" t="str">
+        <v>0.1101243339254</v>
+      </c>
+      <c r="V58" s="7">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="W58" s="13" t="str">
+        <v>0.0563943161634103</v>
+      </c>
+      <c r="W58" s="13">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="X58" s="5" t="str">
+        <v>1.95275590551181</v>
+      </c>
+      <c r="X58" s="5">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Y58" s="7" t="str">
+        <v>5520</v>
+      </c>
+      <c r="Y58" s="7">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="Z58" s="7" t="str">
+        <v>0.102131438721137</v>
+      </c>
+      <c r="Z58" s="7">
         <f>IF(OR(AE58="",多次统计数据!$B$8=""),"",AE58-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA58" s="14" t="str">
+        <v>-0.0251183758713629</v>
+      </c>
+      <c r="AA58" s="14">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB58" s="7" t="str">
+        <v>13</v>
+      </c>
+      <c r="AB58" s="7">
         <f>IF(OR(A58="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC58" s="8" t="str">
         <f>IF(OR(AB58="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB58,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>低于上限</v>
       </c>
       <c r="AD58" s="2"/>
-      <c r="AE58" s="7" t="str">
+      <c r="AE58" s="7">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="59" ht="17" spans="1:31">
-      <c r="A59" s="2"/>
-      <c r="B59" s="2"/>
-      <c r="C59" s="9"/>
-      <c r="D59" s="6"/>
-      <c r="E59" s="9"/>
-      <c r="F59" s="8" t="str">
+        <v>0.0341151385927505</v>
+      </c>
+    </row>
+    <row r="59" ht="17" spans="1:32">
+      <c r="A59" s="2">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C59" s="9">
+        <v>167325</v>
+      </c>
+      <c r="D59" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E59" s="9">
+        <v>44.84</v>
+      </c>
+      <c r="F59" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>2400</v>
       </c>
       <c r="G59" s="8" t="str">
         <f>IF(OR(A59="",F59="",E59="",N59="",E59&lt;=N59,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H59="",F59*(E59-N59),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H59" s="2"/>
-      <c r="I59" s="10"/>
-      <c r="J59" s="9"/>
-      <c r="K59" s="9"/>
-      <c r="L59" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H59" s="2">
+        <v>2400</v>
+      </c>
+      <c r="I59" s="10">
+        <v>44966</v>
+      </c>
+      <c r="J59" s="9">
+        <v>48.5</v>
+      </c>
+      <c r="K59" s="9">
+        <v>45.09</v>
+      </c>
+      <c r="L59" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M59" s="10"/>
-      <c r="N59" s="9"/>
+        <v>2400</v>
+      </c>
+      <c r="M59" s="10">
+        <v>44980</v>
+      </c>
+      <c r="N59" s="9">
+        <v>43.5</v>
+      </c>
       <c r="O59" s="9"/>
       <c r="P59" s="9"/>
       <c r="Q59" s="2"/>
       <c r="R59" s="2"/>
       <c r="S59" s="2"/>
       <c r="T59" s="2"/>
-      <c r="U59" s="7" t="str">
+      <c r="U59" s="7">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="V59" s="7" t="str">
+        <v>0.0816235504014272</v>
+      </c>
+      <c r="V59" s="7">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="W59" s="13" t="str">
+        <v>0.0298840321141838</v>
+      </c>
+      <c r="W59" s="13">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="X59" s="5" t="str">
+        <v>2.73134328358208</v>
+      </c>
+      <c r="X59" s="5">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Y59" s="7" t="str">
+        <v>600</v>
+      </c>
+      <c r="Y59" s="7">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="Z59" s="7" t="str">
+        <v>0.00557537912578055</v>
+      </c>
+      <c r="Z59" s="7">
         <f>IF(OR(AE59="",多次统计数据!$B$8=""),"",AE59-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA59" s="14" t="str">
+        <v>-0.0556476785161081</v>
+      </c>
+      <c r="AA59" s="14">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB59" s="7" t="str">
+        <v>14</v>
+      </c>
+      <c r="AB59" s="7">
         <f>IF(OR(A59="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC59" s="8" t="str">
         <f>IF(OR(AB59="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB59,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>低于上限</v>
       </c>
       <c r="AD59" s="2"/>
-      <c r="AE59" s="7" t="str">
+      <c r="AE59" s="7">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="60" ht="17" spans="1:31">
-      <c r="A60" s="2"/>
-      <c r="B60" s="2"/>
-      <c r="C60" s="9"/>
-      <c r="D60" s="6"/>
-      <c r="E60" s="9"/>
-      <c r="F60" s="8" t="str">
+        <v>0.00358583594800538</v>
+      </c>
+    </row>
+    <row r="60" ht="17" spans="1:32">
+      <c r="A60" s="2">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C60" s="9">
+        <v>167925</v>
+      </c>
+      <c r="D60" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E60" s="9">
+        <v>40.5</v>
+      </c>
+      <c r="F60" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>1600</v>
       </c>
       <c r="G60" s="8" t="str">
         <f>IF(OR(A60="",F60="",E60="",N60="",E60&lt;=N60,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H60="",F60*(E60-N60),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H60" s="2"/>
-      <c r="I60" s="10"/>
-      <c r="J60" s="9"/>
-      <c r="K60" s="9"/>
-      <c r="L60" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H60" s="2">
+        <v>1600</v>
+      </c>
+      <c r="I60" s="10">
+        <v>45104</v>
+      </c>
+      <c r="J60" s="9">
+        <v>42.5</v>
+      </c>
+      <c r="K60" s="9">
+        <v>42.23</v>
+      </c>
+      <c r="L60" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M60" s="10"/>
-      <c r="N60" s="9"/>
+        <v>1600</v>
+      </c>
+      <c r="M60" s="10">
+        <v>45112</v>
+      </c>
+      <c r="N60" s="9">
+        <v>38.5</v>
+      </c>
       <c r="O60" s="9"/>
       <c r="P60" s="9"/>
       <c r="Q60" s="2"/>
       <c r="R60" s="2"/>
       <c r="S60" s="2"/>
       <c r="T60" s="2"/>
-      <c r="U60" s="7" t="str">
+      <c r="U60" s="7">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="V60" s="7" t="str">
+        <v>0.0493827160493827</v>
+      </c>
+      <c r="V60" s="7">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="W60" s="13" t="str">
+        <v>0.0493827160493827</v>
+      </c>
+      <c r="W60" s="13">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="X60" s="5" t="str">
+        <v>1</v>
+      </c>
+      <c r="X60" s="5">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Y60" s="7" t="str">
+        <v>2768</v>
+      </c>
+      <c r="Y60" s="7">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="Z60" s="7" t="str">
+        <v>0.0427160493827161</v>
+      </c>
+      <c r="Z60" s="7">
         <f>IF(OR(AE60="",多次统计数据!$B$8=""),"",AE60-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA60" s="14" t="str">
+        <v>-0.0427499652606</v>
+      </c>
+      <c r="AA60" s="14">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB60" s="7" t="str">
+        <v>8</v>
+      </c>
+      <c r="AB60" s="7">
         <f>IF(OR(A60="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC60" s="8" t="str">
         <f>IF(OR(AB60="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB60,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>低于上限</v>
       </c>
       <c r="AD60" s="2"/>
-      <c r="AE60" s="7" t="str">
+      <c r="AE60" s="7">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="61" ht="17" spans="1:31">
-      <c r="A61" s="2"/>
-      <c r="B61" s="2"/>
-      <c r="C61" s="9"/>
-      <c r="D61" s="6"/>
-      <c r="E61" s="9"/>
-      <c r="F61" s="8" t="str">
+        <v>0.0164835492035135</v>
+      </c>
+    </row>
+    <row r="61" ht="17" spans="1:32">
+      <c r="A61" s="2">
+        <v>60</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C61" s="9">
+        <v>170693</v>
+      </c>
+      <c r="D61" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E61" s="9">
+        <v>38.09</v>
+      </c>
+      <c r="F61" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3100</v>
       </c>
       <c r="G61" s="8" t="str">
         <f>IF(OR(A61="",F61="",E61="",N61="",E61&lt;=N61,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H61="",F61*(E61-N61),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H61" s="2"/>
-      <c r="I61" s="10"/>
-      <c r="J61" s="9"/>
-      <c r="K61" s="9"/>
-      <c r="L61" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H61" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I61" s="10">
+        <v>45162</v>
+      </c>
+      <c r="J61" s="9">
+        <v>40</v>
+      </c>
+      <c r="K61" s="9">
+        <v>37.47</v>
+      </c>
+      <c r="L61" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M61" s="10"/>
-      <c r="N61" s="9"/>
+        <v>1500</v>
+      </c>
+      <c r="M61" s="10">
+        <v>45166</v>
+      </c>
+      <c r="N61" s="9">
+        <v>37</v>
+      </c>
       <c r="O61" s="9"/>
       <c r="P61" s="9"/>
       <c r="Q61" s="2"/>
       <c r="R61" s="2"/>
       <c r="S61" s="2"/>
       <c r="T61" s="2"/>
-      <c r="U61" s="7" t="str">
+      <c r="U61" s="7">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="V61" s="7" t="str">
+        <v>0.0501443948542924</v>
+      </c>
+      <c r="V61" s="7">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="W61" s="13" t="str">
+        <v>0.0286164347597796</v>
+      </c>
+      <c r="W61" s="13">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="X61" s="5" t="str">
+        <v>1.75229357798164</v>
+      </c>
+      <c r="X61" s="5">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Y61" s="7" t="str">
+        <v>-930.000000000007</v>
+      </c>
+      <c r="Y61" s="7">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="Z61" s="7" t="str">
+        <v>-0.0162772381202417</v>
+      </c>
+      <c r="Z61" s="7">
         <f>IF(OR(AE61="",多次统计数据!$B$8=""),"",AE61-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA61" s="14" t="str">
+        <v>-0.0646818925464016</v>
+      </c>
+      <c r="AA61" s="14">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB61" s="7" t="str">
+        <v>4</v>
+      </c>
+      <c r="AB61" s="7">
         <f>IF(OR(A61="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC61" s="8" t="str">
         <f>IF(OR(AB61="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB61,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>低于上限</v>
       </c>
       <c r="AD61" s="2"/>
-      <c r="AE61" s="7" t="str">
+      <c r="AE61" s="7">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="62" ht="17" spans="1:31">
-      <c r="A62" s="2"/>
-      <c r="B62" s="2"/>
-      <c r="C62" s="9"/>
-      <c r="D62" s="6"/>
-      <c r="E62" s="9"/>
-      <c r="F62" s="8" t="str">
+        <v>-0.00544837808228813</v>
+      </c>
+    </row>
+    <row r="62" ht="17" spans="1:32">
+      <c r="A62" s="2">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C62" s="9">
+        <v>169763</v>
+      </c>
+      <c r="D62" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E62" s="9">
+        <v>31.73</v>
+      </c>
+      <c r="F62" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>1900</v>
       </c>
       <c r="G62" s="8" t="str">
         <f>IF(OR(A62="",F62="",E62="",N62="",E62&lt;=N62,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H62="",F62*(E62-N62),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H62" s="2"/>
-      <c r="I62" s="10"/>
-      <c r="J62" s="9"/>
-      <c r="K62" s="9"/>
-      <c r="L62" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H62" s="2">
+        <v>1900</v>
+      </c>
+      <c r="I62" s="10">
+        <v>45313</v>
+      </c>
+      <c r="J62" s="9">
+        <v>35</v>
+      </c>
+      <c r="K62" s="9">
+        <v>29.67</v>
+      </c>
+      <c r="L62" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M62" s="10"/>
-      <c r="N62" s="9"/>
+        <v>1900</v>
+      </c>
+      <c r="M62" s="10">
+        <v>45324</v>
+      </c>
+      <c r="N62" s="9">
+        <v>30</v>
+      </c>
       <c r="O62" s="9"/>
       <c r="P62" s="9"/>
       <c r="Q62" s="2"/>
       <c r="R62" s="2"/>
       <c r="S62" s="2"/>
       <c r="T62" s="2"/>
-      <c r="U62" s="7" t="str">
+      <c r="U62" s="7">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="V62" s="7" t="str">
+        <v>0.103057043807123</v>
+      </c>
+      <c r="V62" s="7">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="W62" s="13" t="str">
+        <v>0.0545225338796092</v>
+      </c>
+      <c r="W62" s="13">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="X62" s="5" t="str">
+        <v>1.89017341040462</v>
+      </c>
+      <c r="X62" s="5">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Y62" s="7" t="str">
+        <v>-3914</v>
+      </c>
+      <c r="Y62" s="7">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="Z62" s="7" t="str">
+        <v>-0.0649227860069335</v>
+      </c>
+      <c r="Z62" s="7">
         <f>IF(OR(AE62="",多次统计数据!$B$8=""),"",AE62-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA62" s="14" t="str">
+        <v>-0.0822891861947025</v>
+      </c>
+      <c r="AA62" s="14">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB62" s="7" t="str">
+        <v>11</v>
+      </c>
+      <c r="AB62" s="7">
         <f>IF(OR(A62="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC62" s="8" t="str">
         <f>IF(OR(AB62="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB62,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>低于上限</v>
       </c>
       <c r="AD62" s="2"/>
-      <c r="AE62" s="7" t="str">
+      <c r="AE62" s="7">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="63" ht="17" spans="1:31">
-      <c r="A63" s="2"/>
-      <c r="B63" s="2"/>
-      <c r="C63" s="9"/>
-      <c r="D63" s="6"/>
-      <c r="E63" s="9"/>
-      <c r="F63" s="8" t="str">
+        <v>-0.0230556717305891</v>
+      </c>
+      <c r="AF62" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="63" ht="17" spans="1:32">
+      <c r="A63" s="2">
+        <v>62</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C63" s="9">
+        <v>165849</v>
+      </c>
+      <c r="D63" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E63" s="9">
+        <v>36.33</v>
+      </c>
+      <c r="F63" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>3900</v>
       </c>
       <c r="G63" s="8" t="str">
         <f>IF(OR(A63="",F63="",E63="",N63="",E63&lt;=N63,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H63="",F63*(E63-N63),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H63" s="2"/>
-      <c r="I63" s="10"/>
-      <c r="J63" s="9"/>
-      <c r="K63" s="9"/>
-      <c r="L63" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H63" s="2">
+        <v>1900</v>
+      </c>
+      <c r="I63" s="10">
+        <v>45429</v>
+      </c>
+      <c r="J63" s="9">
+        <v>38</v>
+      </c>
+      <c r="K63" s="9">
+        <v>35.05</v>
+      </c>
+      <c r="L63" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M63" s="10"/>
-      <c r="N63" s="9"/>
+        <v>1900</v>
+      </c>
+      <c r="M63" s="10">
+        <v>45435</v>
+      </c>
+      <c r="N63" s="9">
+        <v>35.5</v>
+      </c>
       <c r="O63" s="9"/>
       <c r="P63" s="9"/>
       <c r="Q63" s="2"/>
       <c r="R63" s="2"/>
       <c r="S63" s="2"/>
       <c r="T63" s="2"/>
-      <c r="U63" s="7" t="str">
+      <c r="U63" s="7">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="V63" s="7" t="str">
+        <v>0.0459675199559593</v>
+      </c>
+      <c r="V63" s="7">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="W63" s="13" t="str">
+        <v>0.0228461326727222</v>
+      </c>
+      <c r="W63" s="13">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="X63" s="5" t="str">
+        <v>2.01204819277109</v>
+      </c>
+      <c r="X63" s="5">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Y63" s="7" t="str">
+        <v>-2432</v>
+      </c>
+      <c r="Y63" s="7">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="Z63" s="7" t="str">
+        <v>-0.0352325901458849</v>
+      </c>
+      <c r="Z63" s="7">
         <f>IF(OR(AE63="",多次统计数据!$B$8=""),"",AE63-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA63" s="14" t="str">
+        <v>-0.0738974557601116</v>
+      </c>
+      <c r="AA63" s="14">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB63" s="7" t="str">
+        <v>6</v>
+      </c>
+      <c r="AB63" s="7">
         <f>IF(OR(A63="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC63" s="8" t="str">
         <f>IF(OR(AB63="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB63,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>低于上限</v>
       </c>
       <c r="AD63" s="2"/>
-      <c r="AE63" s="7" t="str">
+      <c r="AE63" s="7">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-    </row>
-    <row r="64" ht="17" spans="1:31">
-      <c r="A64" s="2"/>
-      <c r="B64" s="2"/>
-      <c r="C64" s="9"/>
-      <c r="D64" s="6"/>
-      <c r="E64" s="9"/>
-      <c r="F64" s="8" t="str">
+        <v>-0.0146639412959982</v>
+      </c>
+    </row>
+    <row r="64" ht="17" spans="1:32">
+      <c r="A64" s="2">
+        <v>63</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C64" s="9">
+        <v>163417</v>
+      </c>
+      <c r="D64" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E64" s="9">
+        <v>35</v>
+      </c>
+      <c r="F64" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>1600</v>
       </c>
       <c r="G64" s="8" t="str">
         <f>IF(OR(A64="",F64="",E64="",N64="",E64&lt;=N64,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H64="",F64*(E64-N64),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H64" s="2"/>
-      <c r="I64" s="10"/>
-      <c r="J64" s="9"/>
-      <c r="K64" s="9"/>
-      <c r="L64" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H64" s="2">
+        <v>1600</v>
+      </c>
+      <c r="I64" s="10">
+        <v>45785</v>
+      </c>
+      <c r="J64" s="9">
+        <v>37</v>
+      </c>
+      <c r="K64" s="9">
+        <v>41.19</v>
+      </c>
+      <c r="L64" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M64" s="10"/>
-      <c r="N64" s="9"/>
+        <v>1600</v>
+      </c>
+      <c r="M64" s="10">
+        <v>45870</v>
+      </c>
+      <c r="N64" s="9">
+        <v>33</v>
+      </c>
       <c r="O64" s="9"/>
       <c r="P64" s="9"/>
       <c r="Q64" s="2"/>
       <c r="R64" s="2"/>
       <c r="S64" s="2"/>
       <c r="T64" s="2"/>
-      <c r="U64" s="7" t="str">
+      <c r="U64" s="7">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="V64" s="7" t="str">
+        <v>0.0571428571428571</v>
+      </c>
+      <c r="V64" s="7">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="W64" s="13" t="str">
+        <v>0.0571428571428571</v>
+      </c>
+      <c r="W64" s="13">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="X64" s="5" t="str">
+        <v>1</v>
+      </c>
+      <c r="X64" s="5">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Y64" s="7" t="str">
+        <v>9904</v>
+      </c>
+      <c r="Y64" s="7">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="Z64" s="7" t="str">
+        <v>0.176857142857143</v>
+      </c>
+      <c r="Z64" s="7">
         <f>IF(OR(AE64="",多次统计数据!$B$8=""),"",AE64-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA64" s="14" t="str">
+        <v>0.00137217527440826</v>
+      </c>
+      <c r="AA64" s="14">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB64" s="7" t="str">
+        <v>85</v>
+      </c>
+      <c r="AB64" s="7">
         <f>IF(OR(A64="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC64" s="8" t="str">
         <f>IF(OR(AB64="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB64,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>低于上限</v>
       </c>
       <c r="AD64" s="2"/>
-      <c r="AE64" s="7" t="str">
+      <c r="AE64" s="7">
         <f t="shared" si="8"/>
-        <v/>
+        <v>0.0606056897385217</v>
       </c>
     </row>
     <row r="65" ht="17" spans="1:31">
-      <c r="A65" s="2"/>
-      <c r="B65" s="2"/>
-      <c r="C65" s="9"/>
-      <c r="D65" s="6"/>
-      <c r="E65" s="9"/>
-      <c r="F65" s="8" t="str">
+      <c r="A65" s="2">
+        <v>64</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C65" s="9">
+        <v>173321</v>
+      </c>
+      <c r="D65" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E65" s="9">
+        <v>9.64</v>
+      </c>
+      <c r="F65" s="8">
         <f t="shared" si="0"/>
-        <v/>
+        <v>10100</v>
       </c>
       <c r="G65" s="8" t="str">
         <f>IF(OR(A65="",F65="",E65="",N65="",E65&lt;=N65,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H65="",F65*(E65-N65),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H65" s="2"/>
-      <c r="I65" s="10"/>
-      <c r="J65" s="9"/>
-      <c r="K65" s="9"/>
-      <c r="L65" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H65" s="2">
+        <v>10100</v>
+      </c>
+      <c r="I65" s="10">
+        <v>44412</v>
+      </c>
+      <c r="J65" s="9">
+        <v>10.3</v>
+      </c>
+      <c r="K65" s="9">
+        <v>9.97</v>
+      </c>
+      <c r="L65" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="M65" s="10"/>
-      <c r="N65" s="9"/>
+        <v>10100</v>
+      </c>
+      <c r="M65" s="10">
+        <v>44414</v>
+      </c>
+      <c r="N65" s="9">
+        <v>9.3</v>
+      </c>
       <c r="O65" s="9"/>
       <c r="P65" s="9"/>
       <c r="Q65" s="2"/>
       <c r="R65" s="2"/>
       <c r="S65" s="2"/>
       <c r="T65" s="2"/>
-      <c r="U65" s="7" t="str">
+      <c r="U65" s="7">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="V65" s="7" t="str">
+        <v>0.0684647302904564</v>
+      </c>
+      <c r="V65" s="7">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="W65" s="13" t="str">
+        <v>0.0352697095435685</v>
+      </c>
+      <c r="W65" s="13">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="X65" s="5" t="str">
+        <v>1.94117647058824</v>
+      </c>
+      <c r="X65" s="5">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="Y65" s="7" t="str">
+        <v>3333</v>
+      </c>
+      <c r="Y65" s="7">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="Z65" s="7" t="str">
+        <v>0.0342323651452282</v>
+      </c>
+      <c r="Z65" s="7">
         <f>IF(OR(AE65="",多次统计数据!$B$8=""),"",AE65-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA65" s="14" t="str">
+        <v>-0.0400033000065463</v>
+      </c>
+      <c r="AA65" s="14">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AB65" s="7" t="str">
+        <v>2</v>
+      </c>
+      <c r="AB65" s="7">
         <f>IF(OR(A65="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC65" s="8" t="str">
         <f>IF(OR(AB65="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB65,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>低于上限</v>
       </c>
       <c r="AD65" s="2"/>
-      <c r="AE65" s="7" t="str">
+      <c r="AE65" s="7">
         <f t="shared" si="8"/>
-        <v/>
+        <v>0.0192302144575672</v>
       </c>
     </row>
     <row r="66" ht="17" spans="1:31">
-      <c r="A66" s="2"/>
-      <c r="B66" s="2"/>
-      <c r="C66" s="9"/>
-      <c r="D66" s="6"/>
-      <c r="E66" s="9"/>
-      <c r="F66" s="8" t="str">
+      <c r="A66" s="2">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C66" s="9">
+        <v>176654</v>
+      </c>
+      <c r="D66" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E66" s="9">
+        <v>14.13</v>
+      </c>
+      <c r="F66" s="8">
         <f t="shared" ref="F66:F129" si="9">IF(OR(C66="",D66="",E66="",N66="",C66&lt;=0,D66&lt;=0,E66&lt;=N66),"",ROUNDDOWN((C66*D66)/(E66-N66)/100,0)*100)</f>
-        <v/>
+        <v>3100</v>
       </c>
       <c r="G66" s="8" t="str">
         <f>IF(OR(A66="",F66="",E66="",N66="",E66&lt;=N66,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H66="",F66*(E66-N66),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H66" s="2"/>
-      <c r="I66" s="10"/>
-      <c r="J66" s="9"/>
-      <c r="K66" s="9"/>
-      <c r="L66" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H66" s="2">
+        <v>3100</v>
+      </c>
+      <c r="I66" s="10">
+        <v>44446</v>
+      </c>
+      <c r="J66" s="9">
+        <v>16</v>
+      </c>
+      <c r="K66" s="9">
+        <v>15.31</v>
+      </c>
+      <c r="L66" s="8">
         <f t="shared" ref="L66:L129" si="10">IF(K66="","",H66)</f>
-        <v/>
-      </c>
-      <c r="M66" s="10"/>
-      <c r="N66" s="9"/>
+        <v>3100</v>
+      </c>
+      <c r="M66" s="10">
+        <v>44449</v>
+      </c>
+      <c r="N66" s="9">
+        <v>13</v>
+      </c>
       <c r="O66" s="9"/>
       <c r="P66" s="9"/>
       <c r="Q66" s="2"/>
       <c r="R66" s="2"/>
       <c r="S66" s="2"/>
       <c r="T66" s="2"/>
-      <c r="U66" s="7" t="str">
+      <c r="U66" s="7">
         <f t="shared" ref="U66:U129" si="11">IF(OR(E66="",J66="",E66&lt;=0),"",(J66-E66)/E66)</f>
-        <v/>
-      </c>
-      <c r="V66" s="7" t="str">
+        <v>0.132342533616419</v>
+      </c>
+      <c r="V66" s="7">
         <f t="shared" ref="V66:V129" si="12">IF(OR(E66="",N66="",E66&lt;=0),"",(E66-N66)/E66)</f>
-        <v/>
-      </c>
-      <c r="W66" s="13" t="str">
+        <v>0.0799716914366596</v>
+      </c>
+      <c r="W66" s="13">
         <f t="shared" ref="W66:W129" si="13">IF(OR(U66="",V66="",V66&lt;=0),"",U66/V66)</f>
-        <v/>
-      </c>
-      <c r="X66" s="5" t="str">
+        <v>1.65486725663717</v>
+      </c>
+      <c r="X66" s="5">
         <f t="shared" ref="X66:X129" si="14">IF(OR(K66="",L66="",E66="",H66=""),"",K66*L66-E66*H66-IF(O66="",0,O66)-IF(P66="",0,P66))</f>
-        <v/>
-      </c>
-      <c r="Y66" s="7" t="str">
+        <v>3658</v>
+      </c>
+      <c r="Y66" s="7">
         <f t="shared" ref="Y66:Y129" si="15">IF(OR(X66="",E66="",H66=""),"",IF(E66*H66+IF(O66="",0,O66)&lt;=0,"",X66/(E66*H66+IF(O66="",0,O66))))</f>
-        <v/>
-      </c>
-      <c r="Z66" s="7" t="str">
+        <v>0.0835102618542109</v>
+      </c>
+      <c r="Z66" s="7">
         <f>IF(OR(AE66="",多次统计数据!$B$8=""),"",AE66-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA66" s="14" t="str">
+        <v>-0.0385263694235256</v>
+      </c>
+      <c r="AA66" s="14">
         <f t="shared" ref="AA66:AA129" si="16">IF(OR(I66="",M66="",M66&lt;I66),"",M66-I66)</f>
-        <v/>
-      </c>
-      <c r="AB66" s="7" t="str">
+        <v>3</v>
+      </c>
+      <c r="AB66" s="7">
         <f>IF(OR(A66="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC66" s="8" t="str">
         <f>IF(OR(AB66="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB66,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>低于上限</v>
       </c>
       <c r="AD66" s="2"/>
-      <c r="AE66" s="7" t="str">
+      <c r="AE66" s="7">
         <f t="shared" ref="AE66:AE129" si="17">IF(OR(X66="",C66="",C66&lt;=0),"",X66/C66)</f>
-        <v/>
+        <v>0.0207071450405878</v>
       </c>
     </row>
     <row r="67" ht="17" spans="1:31">
-      <c r="A67" s="2"/>
-      <c r="B67" s="2"/>
-      <c r="C67" s="9"/>
-      <c r="D67" s="6"/>
-      <c r="E67" s="9"/>
-      <c r="F67" s="8" t="str">
+      <c r="A67" s="2">
+        <v>66</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C67" s="9">
+        <v>180312</v>
+      </c>
+      <c r="D67" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E67" s="9">
+        <v>11.49</v>
+      </c>
+      <c r="F67" s="8">
         <f t="shared" si="9"/>
-        <v/>
+        <v>3600</v>
       </c>
       <c r="G67" s="8" t="str">
         <f>IF(OR(A67="",F67="",E67="",N67="",E67&lt;=N67,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H67="",F67*(E67-N67),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H67" s="2"/>
-      <c r="I67" s="10"/>
-      <c r="J67" s="9"/>
-      <c r="K67" s="9"/>
-      <c r="L67" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H67" s="2">
+        <v>3600</v>
+      </c>
+      <c r="I67" s="10">
+        <v>44706</v>
+      </c>
+      <c r="J67" s="9">
+        <v>13</v>
+      </c>
+      <c r="K67" s="9">
+        <v>14.49</v>
+      </c>
+      <c r="L67" s="8">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="M67" s="10"/>
-      <c r="N67" s="9"/>
+        <v>3600</v>
+      </c>
+      <c r="M67" s="10">
+        <v>44739</v>
+      </c>
+      <c r="N67" s="9">
+        <v>10.5</v>
+      </c>
       <c r="O67" s="9"/>
       <c r="P67" s="9"/>
       <c r="Q67" s="2"/>
       <c r="R67" s="2"/>
       <c r="S67" s="2"/>
       <c r="T67" s="2"/>
-      <c r="U67" s="7" t="str">
+      <c r="U67" s="7">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="V67" s="7" t="str">
+        <v>0.13141862489121</v>
+      </c>
+      <c r="V67" s="7">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="W67" s="13" t="str">
+        <v>0.0861618798955614</v>
+      </c>
+      <c r="W67" s="13">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="X67" s="5" t="str">
+        <v>1.52525252525252</v>
+      </c>
+      <c r="X67" s="5">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="Y67" s="7" t="str">
+        <v>10800</v>
+      </c>
+      <c r="Y67" s="7">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="Z67" s="7" t="str">
+        <v>0.261096605744125</v>
+      </c>
+      <c r="Z67" s="7">
         <f>IF(OR(AE67="",多次统计数据!$B$8=""),"",AE67-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA67" s="14" t="str">
+        <v>0.000662665490631674</v>
+      </c>
+      <c r="AA67" s="14">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="AB67" s="7" t="str">
+        <v>33</v>
+      </c>
+      <c r="AB67" s="7">
         <f>IF(OR(A67="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC67" s="8" t="str">
         <f>IF(OR(AB67="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB67,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>低于上限</v>
       </c>
       <c r="AD67" s="2"/>
-      <c r="AE67" s="7" t="str">
+      <c r="AE67" s="7">
         <f t="shared" si="17"/>
-        <v/>
+        <v>0.0598961799547451</v>
       </c>
     </row>
     <row r="68" ht="17" spans="1:31">
-      <c r="A68" s="2"/>
-      <c r="B68" s="2"/>
-      <c r="C68" s="9"/>
-      <c r="D68" s="6"/>
-      <c r="E68" s="9"/>
-      <c r="F68" s="8" t="str">
+      <c r="A68" s="2">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C68" s="9">
+        <v>191112</v>
+      </c>
+      <c r="D68" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E68" s="9">
+        <v>15.96</v>
+      </c>
+      <c r="F68" s="8">
         <f t="shared" si="9"/>
-        <v/>
+        <v>8300</v>
       </c>
       <c r="G68" s="8" t="str">
         <f>IF(OR(A68="",F68="",E68="",N68="",E68&lt;=N68,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H68="",F68*(E68-N68),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H68" s="2"/>
-      <c r="I68" s="10"/>
-      <c r="J68" s="9"/>
-      <c r="K68" s="9"/>
-      <c r="L68" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H68" s="2">
+        <v>8300</v>
+      </c>
+      <c r="I68" s="10">
+        <v>44764</v>
+      </c>
+      <c r="J68" s="9">
+        <v>17</v>
+      </c>
+      <c r="K68" s="9">
+        <v>14.83</v>
+      </c>
+      <c r="L68" s="8">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="M68" s="10"/>
-      <c r="N68" s="9"/>
+        <v>8300</v>
+      </c>
+      <c r="M68" s="10">
+        <v>44767</v>
+      </c>
+      <c r="N68" s="9">
+        <v>15.5</v>
+      </c>
       <c r="O68" s="9"/>
       <c r="P68" s="9"/>
       <c r="Q68" s="2"/>
       <c r="R68" s="2"/>
       <c r="S68" s="2"/>
       <c r="T68" s="2"/>
-      <c r="U68" s="7" t="str">
+      <c r="U68" s="7">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="V68" s="7" t="str">
+        <v>0.0651629072681704</v>
+      </c>
+      <c r="V68" s="7">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="W68" s="13" t="str">
+        <v>0.0288220551378447</v>
+      </c>
+      <c r="W68" s="13">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="X68" s="5" t="str">
+        <v>2.26086956521739</v>
+      </c>
+      <c r="X68" s="5">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="Y68" s="7" t="str">
+        <v>-9379</v>
+      </c>
+      <c r="Y68" s="7">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="Z68" s="7" t="str">
+        <v>-0.0708020050125313</v>
+      </c>
+      <c r="Z68" s="7">
         <f>IF(OR(AE68="",多次统计数据!$B$8=""),"",AE68-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA68" s="14" t="str">
+        <v>-0.108309448994651</v>
+      </c>
+      <c r="AA68" s="14">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="AB68" s="7" t="str">
+        <v>3</v>
+      </c>
+      <c r="AB68" s="7">
         <f>IF(OR(A68="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC68" s="8" t="str">
         <f>IF(OR(AB68="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB68,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>低于上限</v>
       </c>
       <c r="AD68" s="2"/>
-      <c r="AE68" s="7" t="str">
+      <c r="AE68" s="7">
         <f t="shared" si="17"/>
-        <v/>
+        <v>-0.0490759345305371</v>
       </c>
     </row>
     <row r="69" ht="17" spans="1:31">
-      <c r="A69" s="2"/>
-      <c r="B69" s="2"/>
-      <c r="C69" s="9"/>
-      <c r="D69" s="6"/>
-      <c r="E69" s="9"/>
-      <c r="F69" s="8" t="str">
+      <c r="A69" s="2">
+        <v>68</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C69" s="9">
+        <v>181733</v>
+      </c>
+      <c r="D69" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E69" s="9">
+        <v>20.37</v>
+      </c>
+      <c r="F69" s="8">
         <f t="shared" si="9"/>
-        <v/>
+        <v>3100</v>
       </c>
       <c r="G69" s="8" t="str">
         <f>IF(OR(A69="",F69="",E69="",N69="",E69&lt;=N69,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H69="",F69*(E69-N69),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H69" s="2"/>
-      <c r="I69" s="10"/>
-      <c r="J69" s="9"/>
-      <c r="K69" s="9"/>
-      <c r="L69" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H69" s="2">
+        <v>3100</v>
+      </c>
+      <c r="I69" s="10">
+        <v>44937</v>
+      </c>
+      <c r="J69" s="9">
+        <v>24</v>
+      </c>
+      <c r="K69" s="9">
+        <v>18.78</v>
+      </c>
+      <c r="L69" s="8">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="M69" s="10"/>
-      <c r="N69" s="9"/>
+        <v>3100</v>
+      </c>
+      <c r="M69" s="10">
+        <v>44980</v>
+      </c>
+      <c r="N69" s="9">
+        <v>19.2</v>
+      </c>
       <c r="O69" s="9"/>
       <c r="P69" s="9"/>
       <c r="Q69" s="2"/>
       <c r="R69" s="2"/>
       <c r="S69" s="2"/>
       <c r="T69" s="2"/>
-      <c r="U69" s="7" t="str">
+      <c r="U69" s="7">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="V69" s="7" t="str">
+        <v>0.17820324005891</v>
+      </c>
+      <c r="V69" s="7">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="W69" s="13" t="str">
+        <v>0.057437407952872</v>
+      </c>
+      <c r="W69" s="13">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="X69" s="5" t="str">
+        <v>3.1025641025641</v>
+      </c>
+      <c r="X69" s="5">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="Y69" s="7" t="str">
+        <v>-4929</v>
+      </c>
+      <c r="Y69" s="7">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="Z69" s="7" t="str">
+        <v>-0.0780559646539028</v>
+      </c>
+      <c r="Z69" s="7">
         <f>IF(OR(AE69="",多次统计数据!$B$8=""),"",AE69-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA69" s="14" t="str">
+        <v>-0.0863557212179776</v>
+      </c>
+      <c r="AA69" s="14">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="AB69" s="7" t="str">
+        <v>43</v>
+      </c>
+      <c r="AB69" s="7">
         <f>IF(OR(A69="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC69" s="8" t="str">
         <f>IF(OR(AB69="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB69,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>低于上限</v>
       </c>
       <c r="AD69" s="2"/>
-      <c r="AE69" s="7" t="str">
+      <c r="AE69" s="7">
         <f t="shared" si="17"/>
-        <v/>
+        <v>-0.0271222067538642</v>
       </c>
     </row>
     <row r="70" ht="17" spans="1:31">
-      <c r="A70" s="2"/>
-      <c r="B70" s="2"/>
-      <c r="C70" s="9"/>
-      <c r="D70" s="6"/>
-      <c r="E70" s="9"/>
-      <c r="F70" s="8" t="str">
+      <c r="A70" s="2">
+        <v>69</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C70" s="9">
+        <v>176804</v>
+      </c>
+      <c r="D70" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E70" s="9">
+        <v>19.13</v>
+      </c>
+      <c r="F70" s="8">
         <f t="shared" si="9"/>
-        <v/>
+        <v>3100</v>
       </c>
       <c r="G70" s="8" t="str">
         <f>IF(OR(A70="",F70="",E70="",N70="",E70&lt;=N70,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H70="",F70*(E70-N70),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H70" s="2"/>
-      <c r="I70" s="10"/>
-      <c r="J70" s="9"/>
-      <c r="K70" s="9"/>
-      <c r="L70" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H70" s="2">
+        <v>3100</v>
+      </c>
+      <c r="I70" s="10">
+        <v>44995</v>
+      </c>
+      <c r="J70" s="9">
+        <v>21.3</v>
+      </c>
+      <c r="K70" s="9">
+        <v>17.16</v>
+      </c>
+      <c r="L70" s="8">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="M70" s="10"/>
-      <c r="N70" s="9"/>
+        <v>3100</v>
+      </c>
+      <c r="M70" s="10">
+        <v>45002</v>
+      </c>
+      <c r="N70" s="9">
+        <v>18</v>
+      </c>
       <c r="O70" s="9"/>
       <c r="P70" s="9"/>
       <c r="Q70" s="2"/>
       <c r="R70" s="2"/>
       <c r="S70" s="2"/>
       <c r="T70" s="2"/>
-      <c r="U70" s="7" t="str">
+      <c r="U70" s="7">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="V70" s="7" t="str">
+        <v>0.113434396236278</v>
+      </c>
+      <c r="V70" s="7">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="W70" s="13" t="str">
+        <v>0.0590695243073706</v>
+      </c>
+      <c r="W70" s="13">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="X70" s="5" t="str">
+        <v>1.92035398230089</v>
+      </c>
+      <c r="X70" s="5">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="Y70" s="7" t="str">
+        <v>-6107</v>
+      </c>
+      <c r="Y70" s="7">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="Z70" s="7" t="str">
+        <v>-0.102979613173027</v>
+      </c>
+      <c r="Z70" s="7">
         <f>IF(OR(AE70="",多次统计数据!$B$8=""),"",AE70-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA70" s="14" t="str">
+        <v>-0.093774588195477</v>
+      </c>
+      <c r="AA70" s="14">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="AB70" s="7" t="str">
+        <v>7</v>
+      </c>
+      <c r="AB70" s="7">
         <f>IF(OR(A70="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC70" s="8" t="str">
         <f>IF(OR(AB70="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB70,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>低于上限</v>
       </c>
       <c r="AD70" s="2"/>
-      <c r="AE70" s="7" t="str">
+      <c r="AE70" s="7">
         <f t="shared" si="17"/>
-        <v/>
+        <v>-0.0345410737313635</v>
       </c>
     </row>
     <row r="71" ht="17" spans="1:31">
-      <c r="A71" s="2"/>
-      <c r="B71" s="2"/>
-      <c r="C71" s="9"/>
-      <c r="D71" s="6"/>
-      <c r="E71" s="9"/>
-      <c r="F71" s="8" t="str">
+      <c r="A71" s="2">
+        <v>70</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C71" s="9">
+        <v>170697</v>
+      </c>
+      <c r="D71" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E71" s="9">
+        <v>17.3</v>
+      </c>
+      <c r="F71" s="8">
         <f t="shared" si="9"/>
-        <v/>
+        <v>4200</v>
       </c>
       <c r="G71" s="8" t="str">
         <f>IF(OR(A71="",F71="",E71="",N71="",E71&lt;=N71,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H71="",F71*(E71-N71),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H71" s="2"/>
-      <c r="I71" s="10"/>
-      <c r="J71" s="9"/>
-      <c r="K71" s="9"/>
-      <c r="L71" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H71" s="2">
+        <v>4200</v>
+      </c>
+      <c r="I71" s="10">
+        <v>45068</v>
+      </c>
+      <c r="J71" s="9">
+        <v>20</v>
+      </c>
+      <c r="K71" s="9">
+        <v>16.47</v>
+      </c>
+      <c r="L71" s="8">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="M71" s="10"/>
-      <c r="N71" s="9"/>
+        <v>4200</v>
+      </c>
+      <c r="M71" s="10">
+        <v>45075</v>
+      </c>
+      <c r="N71" s="9">
+        <v>16.5</v>
+      </c>
       <c r="O71" s="9"/>
       <c r="P71" s="9"/>
       <c r="Q71" s="2"/>
       <c r="R71" s="2"/>
       <c r="S71" s="2"/>
       <c r="T71" s="2"/>
-      <c r="U71" s="7" t="str">
+      <c r="U71" s="7">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="V71" s="7" t="str">
+        <v>0.15606936416185</v>
+      </c>
+      <c r="V71" s="7">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="W71" s="13" t="str">
+        <v>0.046242774566474</v>
+      </c>
+      <c r="W71" s="13">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="X71" s="5" t="str">
+        <v>3.375</v>
+      </c>
+      <c r="X71" s="5">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="Y71" s="7" t="str">
+        <v>-3486</v>
+      </c>
+      <c r="Y71" s="7">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="Z71" s="7" t="str">
+        <v>-0.0479768786127168</v>
+      </c>
+      <c r="Z71" s="7">
         <f>IF(OR(AE71="",多次统计数据!$B$8=""),"",AE71-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA71" s="14" t="str">
+        <v>-0.0796556659957748</v>
+      </c>
+      <c r="AA71" s="14">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="AB71" s="7" t="str">
+        <v>7</v>
+      </c>
+      <c r="AB71" s="7">
         <f>IF(OR(A71="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC71" s="8" t="str">
         <f>IF(OR(AB71="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB71,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>低于上限</v>
       </c>
       <c r="AD71" s="2"/>
-      <c r="AE71" s="7" t="str">
+      <c r="AE71" s="7">
         <f t="shared" si="17"/>
-        <v/>
+        <v>-0.0204221515316614</v>
       </c>
     </row>
     <row r="72" ht="17" spans="1:31">
-      <c r="A72" s="2"/>
-      <c r="B72" s="2"/>
-      <c r="C72" s="9"/>
-      <c r="D72" s="6"/>
-      <c r="E72" s="9"/>
-      <c r="F72" s="8" t="str">
+      <c r="A72" s="2">
+        <v>71</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C72" s="9">
+        <v>167211</v>
+      </c>
+      <c r="D72" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E72" s="9">
+        <v>15</v>
+      </c>
+      <c r="F72" s="8">
         <f t="shared" si="9"/>
-        <v/>
+        <v>3300</v>
       </c>
       <c r="G72" s="8" t="str">
         <f>IF(OR(A72="",F72="",E72="",N72="",E72&lt;=N72,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H72="",F72*(E72-N72),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H72" s="2"/>
-      <c r="I72" s="10"/>
-      <c r="J72" s="9"/>
-      <c r="K72" s="9"/>
-      <c r="L72" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H72" s="2">
+        <v>3300</v>
+      </c>
+      <c r="I72" s="10">
+        <v>45357</v>
+      </c>
+      <c r="J72" s="9">
+        <v>16</v>
+      </c>
+      <c r="K72" s="9">
+        <v>13.75</v>
+      </c>
+      <c r="L72" s="8">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="M72" s="10"/>
-      <c r="N72" s="9"/>
+        <v>3300</v>
+      </c>
+      <c r="M72" s="10">
+        <v>45378</v>
+      </c>
+      <c r="N72" s="9">
+        <v>14</v>
+      </c>
       <c r="O72" s="9"/>
       <c r="P72" s="9"/>
       <c r="Q72" s="2"/>
       <c r="R72" s="2"/>
       <c r="S72" s="2"/>
       <c r="T72" s="2"/>
-      <c r="U72" s="7" t="str">
+      <c r="U72" s="7">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="V72" s="7" t="str">
+        <v>0.0666666666666667</v>
+      </c>
+      <c r="V72" s="7">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="W72" s="13" t="str">
+        <v>0.0666666666666667</v>
+      </c>
+      <c r="W72" s="13">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="X72" s="5" t="str">
+        <v>1</v>
+      </c>
+      <c r="X72" s="5">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="Y72" s="7" t="str">
+        <v>-4125</v>
+      </c>
+      <c r="Y72" s="7">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="Z72" s="7" t="str">
+        <v>-0.0833333333333333</v>
+      </c>
+      <c r="Z72" s="7">
         <f>IF(OR(AE72="",多次统计数据!$B$8=""),"",AE72-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA72" s="14" t="str">
+        <v>-0.0839029441069001</v>
+      </c>
+      <c r="AA72" s="14">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="AB72" s="7" t="str">
+        <v>21</v>
+      </c>
+      <c r="AB72" s="7">
         <f>IF(OR(A72="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC72" s="8" t="str">
         <f>IF(OR(AB72="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB72,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>低于上限</v>
       </c>
       <c r="AD72" s="2"/>
-      <c r="AE72" s="7" t="str">
+      <c r="AE72" s="7">
         <f t="shared" si="17"/>
-        <v/>
+        <v>-0.0246694296427867</v>
       </c>
     </row>
     <row r="73" ht="17" spans="1:31">
-      <c r="A73" s="2"/>
-      <c r="B73" s="2"/>
-      <c r="C73" s="9"/>
-      <c r="D73" s="6"/>
-      <c r="E73" s="9"/>
-      <c r="F73" s="8" t="str">
+      <c r="A73" s="2">
+        <v>72</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C73" s="9">
+        <v>163086</v>
+      </c>
+      <c r="D73" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E73" s="9">
+        <v>14.67</v>
+      </c>
+      <c r="F73" s="8">
         <f t="shared" si="9"/>
-        <v/>
+        <v>4800</v>
       </c>
       <c r="G73" s="8" t="str">
         <f>IF(OR(A73="",F73="",E73="",N73="",E73&lt;=N73,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H73="",F73*(E73-N73),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H73" s="2"/>
-      <c r="I73" s="10"/>
-      <c r="J73" s="9"/>
-      <c r="K73" s="9"/>
-      <c r="L73" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H73" s="2">
+        <v>4200</v>
+      </c>
+      <c r="I73" s="10">
+        <v>45750</v>
+      </c>
+      <c r="J73" s="9">
+        <v>16</v>
+      </c>
+      <c r="K73" s="9">
+        <v>13.15</v>
+      </c>
+      <c r="L73" s="8">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="M73" s="10"/>
-      <c r="N73" s="9"/>
+        <v>4200</v>
+      </c>
+      <c r="M73" s="10">
+        <v>45754</v>
+      </c>
+      <c r="N73" s="9">
+        <v>14</v>
+      </c>
       <c r="O73" s="9"/>
       <c r="P73" s="9"/>
       <c r="Q73" s="2"/>
       <c r="R73" s="2"/>
       <c r="S73" s="2"/>
       <c r="T73" s="2"/>
-      <c r="U73" s="7" t="str">
+      <c r="U73" s="7">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="V73" s="7" t="str">
+        <v>0.0906612133605999</v>
+      </c>
+      <c r="V73" s="7">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="W73" s="13" t="str">
+        <v>0.0456714383094751</v>
+      </c>
+      <c r="W73" s="13">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="X73" s="5" t="str">
+        <v>1.98507462686567</v>
+      </c>
+      <c r="X73" s="5">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="Y73" s="7" t="str">
+        <v>-6384</v>
+      </c>
+      <c r="Y73" s="7">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="Z73" s="7" t="str">
+        <v>-0.103612815269257</v>
+      </c>
+      <c r="Z73" s="7">
         <f>IF(OR(AE73="",多次统计数据!$B$8=""),"",AE73-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA73" s="14" t="str">
+        <v>-0.0983785054504642</v>
+      </c>
+      <c r="AA73" s="14">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="AB73" s="7" t="str">
+        <v>4</v>
+      </c>
+      <c r="AB73" s="7">
         <f>IF(OR(A73="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC73" s="8" t="str">
         <f>IF(OR(AB73="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB73,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>低于上限</v>
       </c>
       <c r="AD73" s="2"/>
-      <c r="AE73" s="7" t="str">
+      <c r="AE73" s="7">
         <f t="shared" si="17"/>
-        <v/>
+        <v>-0.0391449909863508</v>
       </c>
     </row>
     <row r="74" ht="17" spans="1:31">
-      <c r="A74" s="2"/>
-      <c r="B74" s="2"/>
-      <c r="C74" s="9"/>
-      <c r="D74" s="6"/>
-      <c r="E74" s="9"/>
-      <c r="F74" s="8" t="str">
+      <c r="A74" s="2">
+        <v>73</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C74" s="9">
+        <v>156702</v>
+      </c>
+      <c r="D74" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E74" s="9">
+        <v>15.77</v>
+      </c>
+      <c r="F74" s="8">
         <f t="shared" si="9"/>
-        <v/>
+        <v>4000</v>
       </c>
       <c r="G74" s="8" t="str">
         <f>IF(OR(A74="",F74="",E74="",N74="",E74&lt;=N74,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H74="",F74*(E74-N74),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H74" s="2"/>
-      <c r="I74" s="10"/>
-      <c r="J74" s="9"/>
-      <c r="K74" s="9"/>
-      <c r="L74" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H74" s="2">
+        <v>4000</v>
+      </c>
+      <c r="I74" s="10">
+        <v>45821</v>
+      </c>
+      <c r="J74" s="9">
+        <v>17</v>
+      </c>
+      <c r="K74" s="9">
+        <v>15.53</v>
+      </c>
+      <c r="L74" s="8">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="M74" s="10"/>
-      <c r="N74" s="9"/>
+        <v>4000</v>
+      </c>
+      <c r="M74" s="10">
+        <v>45827</v>
+      </c>
+      <c r="N74" s="9">
+        <v>15</v>
+      </c>
       <c r="O74" s="9"/>
       <c r="P74" s="9"/>
       <c r="Q74" s="2"/>
       <c r="R74" s="2"/>
       <c r="S74" s="2"/>
       <c r="T74" s="2"/>
-      <c r="U74" s="7" t="str">
+      <c r="U74" s="7">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="V74" s="7" t="str">
+        <v>0.077996195307546</v>
+      </c>
+      <c r="V74" s="7">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="W74" s="13" t="str">
+        <v>0.0488268864933418</v>
+      </c>
+      <c r="W74" s="13">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="X74" s="5" t="str">
+        <v>1.5974025974026</v>
+      </c>
+      <c r="X74" s="5">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="Y74" s="7" t="str">
+        <v>-960</v>
+      </c>
+      <c r="Y74" s="7">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="Z74" s="7" t="str">
+        <v>-0.0152187698161065</v>
+      </c>
+      <c r="Z74" s="7">
         <f>IF(OR(AE74="",多次统计数据!$B$8=""),"",AE74-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA74" s="14" t="str">
+        <v>-0.0653597923673948</v>
+      </c>
+      <c r="AA74" s="14">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="AB74" s="7" t="str">
+        <v>6</v>
+      </c>
+      <c r="AB74" s="7">
         <f>IF(OR(A74="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0412323315163184</v>
       </c>
       <c r="AC74" s="8" t="str">
         <f>IF(OR(AB74="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB74,"低于上限","达到或超过上限"))</f>
-        <v/>
+        <v>低于上限</v>
       </c>
       <c r="AD74" s="2"/>
-      <c r="AE74" s="7" t="str">
+      <c r="AE74" s="7">
         <f t="shared" si="17"/>
-        <v/>
+        <v>-0.00612627790328139</v>
       </c>
     </row>
     <row r="75" ht="17" spans="1:31">
@@ -17009,9 +18263,12 @@
     <dataValidation type="decimal" operator="greaterThan" allowBlank="1" sqref="C2 C4:C201 E2:E201 N2:N201 J2:K201">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" sqref="D17 D2:D16 D18:D201">
+    <dataValidation type="decimal" operator="between" allowBlank="1" sqref="D17 D44 D56 D2:D16 D18:D43 D45:D55 D57:D201">
       <formula1>0</formula1>
       <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" sqref="M38 M43 M2:M37 M39:M42 M44:M201">
+      <formula1>OR(M2="",AND(ISNUMBER(M2),M2&gt;=I2))</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="实际买入股数无效" error="实际买入股数必须是大于0的100股整数倍" sqref="H2:H201">
       <formula1>OR(H2="",AND(ISNUMBER(H2),H2&gt;0,MOD(H2,100)=0))</formula1>
@@ -17022,9 +18279,6 @@
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" sqref="L2:L201">
       <formula1>OR(L2="",L2=H2)</formula1>
-    </dataValidation>
-    <dataValidation type="custom" allowBlank="1" sqref="M2:M201">
-      <formula1>OR(M2="",AND(ISNUMBER(M2),M2&gt;=I2))</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="AD2:AD201">
       <formula1>"1-差,2-较差,3-一般,4-良好,5-优秀"</formula1>
@@ -17065,28 +18319,28 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="J1" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" ht="34" spans="1:10">
@@ -17101,7 +18355,7 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" ht="51" spans="1:10">
@@ -17114,7 +18368,7 @@
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" ht="34" spans="1:10">
@@ -17127,7 +18381,7 @@
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" ht="34" spans="1:10">
@@ -17140,7 +18394,7 @@
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="11" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" ht="34" spans="1:10">
@@ -17153,10 +18407,10 @@
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="11" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" ht="17" spans="1:10">
@@ -17169,7 +18423,7 @@
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="11" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -17206,7 +18460,7 @@
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="11" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11" ht="34" spans="1:10">
@@ -17221,7 +18475,7 @@
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="11" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" ht="51" spans="1:10">
@@ -17236,7 +18490,7 @@
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" ht="34" spans="1:10">
@@ -17251,7 +18505,7 @@
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" ht="34" spans="1:10">
@@ -17266,7 +18520,7 @@
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15" ht="34" spans="1:10">
@@ -17281,7 +18535,7 @@
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16" ht="51" spans="1:10">
@@ -17296,7 +18550,7 @@
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17" ht="34" spans="1:9">
@@ -17311,7 +18565,7 @@
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" ht="34" spans="1:9">
@@ -17326,7 +18580,7 @@
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" ht="34" spans="1:9">
@@ -17341,7 +18595,7 @@
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
     </row>
     <row r="20" ht="34" spans="1:9">
@@ -17356,7 +18610,7 @@
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21" ht="34" spans="1:9">
@@ -17371,7 +18625,7 @@
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
     </row>
     <row r="22" ht="34" spans="1:9">
@@ -17386,7 +18640,7 @@
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23" ht="51" spans="1:9">
@@ -17401,11 +18655,13 @@
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9">
-      <c r="A24" s="2"/>
+        <v>86</v>
+      </c>
+    </row>
+    <row r="24" ht="34" spans="1:9">
+      <c r="A24" s="2">
+        <v>26</v>
+      </c>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
@@ -17413,10 +18669,14 @@
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-    </row>
-    <row r="25" spans="1:9">
-      <c r="A25" s="2"/>
+      <c r="I24" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="25" ht="34" spans="1:9">
+      <c r="A25" s="2">
+        <v>27</v>
+      </c>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
@@ -17424,10 +18684,14 @@
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-    </row>
-    <row r="26" spans="1:9">
-      <c r="A26" s="2"/>
+      <c r="I25" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="26" ht="51" spans="1:9">
+      <c r="A26" s="2">
+        <v>28</v>
+      </c>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
@@ -17435,10 +18699,14 @@
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-    </row>
-    <row r="27" spans="1:9">
-      <c r="A27" s="2"/>
+      <c r="I26" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="27" ht="51" spans="1:9">
+      <c r="A27" s="2">
+        <v>29</v>
+      </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
@@ -17446,10 +18714,14 @@
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-    </row>
-    <row r="28" spans="1:9">
-      <c r="A28" s="2"/>
+      <c r="I27" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="28" ht="34" spans="1:9">
+      <c r="A28" s="2">
+        <v>30</v>
+      </c>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
@@ -17457,10 +18729,14 @@
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-    </row>
-    <row r="29" spans="1:9">
-      <c r="A29" s="2"/>
+      <c r="I28" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="29" ht="34" spans="1:9">
+      <c r="A29" s="2">
+        <v>31</v>
+      </c>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
@@ -17468,10 +18744,14 @@
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-    </row>
-    <row r="30" spans="1:9">
-      <c r="A30" s="2"/>
+      <c r="I29" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="30" ht="51" spans="1:9">
+      <c r="A30" s="2">
+        <v>32</v>
+      </c>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
@@ -17479,10 +18759,14 @@
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-    </row>
-    <row r="31" spans="1:9">
-      <c r="A31" s="2"/>
+      <c r="I30" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="31" ht="34" spans="1:9">
+      <c r="A31" s="2">
+        <v>33</v>
+      </c>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
@@ -17490,10 +18774,14 @@
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-    </row>
-    <row r="32" spans="1:9">
-      <c r="A32" s="2"/>
+      <c r="I31" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="32" ht="34" spans="1:9">
+      <c r="A32" s="2">
+        <v>34</v>
+      </c>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
@@ -17501,10 +18789,14 @@
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-    </row>
-    <row r="33" spans="1:9">
-      <c r="A33" s="2"/>
+      <c r="I32" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="33" ht="17" spans="1:9">
+      <c r="A33" s="2">
+        <v>35</v>
+      </c>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
@@ -17512,10 +18804,14 @@
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-    </row>
-    <row r="34" spans="1:9">
-      <c r="A34" s="2"/>
+      <c r="I33" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="34" ht="34" spans="1:9">
+      <c r="A34" s="2">
+        <v>36</v>
+      </c>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
@@ -17523,10 +18819,14 @@
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-    </row>
-    <row r="35" spans="1:9">
-      <c r="A35" s="2"/>
+      <c r="I34" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="35" ht="34" spans="1:9">
+      <c r="A35" s="2">
+        <v>37</v>
+      </c>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
@@ -17534,10 +18834,14 @@
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
-    </row>
-    <row r="36" spans="1:9">
-      <c r="A36" s="2"/>
+      <c r="I35" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="36" ht="51" spans="1:9">
+      <c r="A36" s="2">
+        <v>38</v>
+      </c>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
@@ -17545,10 +18849,14 @@
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
-    </row>
-    <row r="37" spans="1:9">
-      <c r="A37" s="2"/>
+      <c r="I36" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="37" ht="17" spans="1:9">
+      <c r="A37" s="2">
+        <v>39</v>
+      </c>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
@@ -17556,10 +18864,14 @@
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
-      <c r="I37" s="2"/>
-    </row>
-    <row r="38" spans="1:9">
-      <c r="A38" s="2"/>
+      <c r="I37" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" ht="34" spans="1:9">
+      <c r="A38" s="2">
+        <v>40</v>
+      </c>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
@@ -17567,10 +18879,14 @@
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
-    </row>
-    <row r="39" spans="1:9">
-      <c r="A39" s="2"/>
+      <c r="I38" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="39" ht="17" spans="1:9">
+      <c r="A39" s="2">
+        <v>41</v>
+      </c>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
@@ -17578,10 +18894,14 @@
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
-      <c r="I39" s="2"/>
-    </row>
-    <row r="40" spans="1:9">
-      <c r="A40" s="2"/>
+      <c r="I39" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="40" ht="34" spans="1:9">
+      <c r="A40" s="2">
+        <v>42</v>
+      </c>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
@@ -17589,10 +18909,14 @@
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
-    </row>
-    <row r="41" spans="1:9">
-      <c r="A41" s="2"/>
+      <c r="I40" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="41" ht="17" spans="1:9">
+      <c r="A41" s="2">
+        <v>43</v>
+      </c>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
@@ -17600,10 +18924,14 @@
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
-      <c r="I41" s="2"/>
-    </row>
-    <row r="42" spans="1:9">
-      <c r="A42" s="2"/>
+      <c r="I41" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="42" ht="34" spans="1:9">
+      <c r="A42" s="2">
+        <v>44</v>
+      </c>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
@@ -17611,10 +18939,14 @@
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
-      <c r="I42" s="2"/>
-    </row>
-    <row r="43" spans="1:9">
-      <c r="A43" s="2"/>
+      <c r="I42" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="43" ht="34" spans="1:9">
+      <c r="A43" s="2">
+        <v>45</v>
+      </c>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
@@ -17622,10 +18954,14 @@
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
-      <c r="I43" s="2"/>
-    </row>
-    <row r="44" spans="1:9">
-      <c r="A44" s="2"/>
+      <c r="I43" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="44" ht="34" spans="1:9">
+      <c r="A44" s="2">
+        <v>46</v>
+      </c>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
@@ -17633,10 +18969,14 @@
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
-      <c r="I44" s="2"/>
-    </row>
-    <row r="45" spans="1:9">
-      <c r="A45" s="2"/>
+      <c r="I44" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="45" ht="17" spans="1:9">
+      <c r="A45" s="2">
+        <v>47</v>
+      </c>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
@@ -17644,10 +18984,14 @@
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
-      <c r="I45" s="2"/>
-    </row>
-    <row r="46" spans="1:9">
-      <c r="A46" s="2"/>
+      <c r="I45" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="46" ht="17" spans="1:9">
+      <c r="A46" s="2">
+        <v>48</v>
+      </c>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
@@ -17655,10 +18999,14 @@
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
-    </row>
-    <row r="47" spans="1:9">
-      <c r="A47" s="2"/>
+      <c r="I46" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="47" ht="17" spans="1:9">
+      <c r="A47" s="2">
+        <v>49</v>
+      </c>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
@@ -17666,10 +19014,14 @@
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
-      <c r="I47" s="2"/>
-    </row>
-    <row r="48" spans="1:9">
-      <c r="A48" s="2"/>
+      <c r="I47" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="48" ht="17" spans="1:9">
+      <c r="A48" s="2">
+        <v>50</v>
+      </c>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
@@ -17677,10 +19029,14 @@
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
-      <c r="I48" s="2"/>
-    </row>
-    <row r="49" spans="1:9">
-      <c r="A49" s="2"/>
+      <c r="I48" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="49" ht="34" spans="1:9">
+      <c r="A49" s="2">
+        <v>51</v>
+      </c>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
       <c r="D49" s="2"/>
@@ -17688,10 +19044,14 @@
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
-      <c r="I49" s="2"/>
-    </row>
-    <row r="50" spans="1:9">
-      <c r="A50" s="2"/>
+      <c r="I49" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="50" ht="34" spans="1:9">
+      <c r="A50" s="2">
+        <v>52</v>
+      </c>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
@@ -17699,10 +19059,14 @@
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
-      <c r="I50" s="2"/>
-    </row>
-    <row r="51" spans="1:9">
-      <c r="A51" s="2"/>
+      <c r="I50" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="51" ht="34" spans="1:9">
+      <c r="A51" s="2">
+        <v>53</v>
+      </c>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
       <c r="D51" s="2"/>
@@ -17710,10 +19074,14 @@
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
-      <c r="I51" s="2"/>
-    </row>
-    <row r="52" spans="1:9">
-      <c r="A52" s="2"/>
+      <c r="I51" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="52" ht="34" spans="1:9">
+      <c r="A52" s="2">
+        <v>54</v>
+      </c>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
@@ -17721,10 +19089,14 @@
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
-      <c r="I52" s="2"/>
-    </row>
-    <row r="53" spans="1:9">
-      <c r="A53" s="2"/>
+      <c r="I52" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="53" ht="34" spans="1:9">
+      <c r="A53" s="2">
+        <v>55</v>
+      </c>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
       <c r="D53" s="2"/>
@@ -17732,10 +19104,14 @@
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
-      <c r="I53" s="2"/>
-    </row>
-    <row r="54" spans="1:9">
-      <c r="A54" s="2"/>
+      <c r="I53" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="54" ht="34" spans="1:9">
+      <c r="A54" s="2">
+        <v>56</v>
+      </c>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
@@ -17743,10 +19119,14 @@
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
-      <c r="I54" s="2"/>
-    </row>
-    <row r="55" spans="1:9">
-      <c r="A55" s="2"/>
+      <c r="I54" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="55" ht="51" spans="1:9">
+      <c r="A55" s="2">
+        <v>57</v>
+      </c>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
       <c r="D55" s="2"/>
@@ -17754,10 +19134,14 @@
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
-      <c r="I55" s="2"/>
-    </row>
-    <row r="56" spans="1:9">
-      <c r="A56" s="2"/>
+      <c r="I55" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="56" ht="34" spans="1:9">
+      <c r="A56" s="2">
+        <v>58</v>
+      </c>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
       <c r="D56" s="2"/>
@@ -17765,10 +19149,14 @@
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
-      <c r="I56" s="2"/>
-    </row>
-    <row r="57" spans="1:9">
-      <c r="A57" s="2"/>
+      <c r="I56" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="57" ht="34" spans="1:9">
+      <c r="A57" s="2">
+        <v>59</v>
+      </c>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
       <c r="D57" s="2"/>
@@ -17776,10 +19164,14 @@
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
-      <c r="I57" s="2"/>
-    </row>
-    <row r="58" spans="1:9">
-      <c r="A58" s="2"/>
+      <c r="I57" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="58" ht="17" spans="1:9">
+      <c r="A58" s="2">
+        <v>60</v>
+      </c>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
       <c r="D58" s="2"/>
@@ -17787,10 +19179,14 @@
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
       <c r="H58" s="2"/>
-      <c r="I58" s="2"/>
-    </row>
-    <row r="59" spans="1:9">
-      <c r="A59" s="2"/>
+      <c r="I58" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="59" ht="34" spans="1:9">
+      <c r="A59" s="2">
+        <v>61</v>
+      </c>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
       <c r="D59" s="2"/>
@@ -17798,10 +19194,14 @@
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
       <c r="H59" s="2"/>
-      <c r="I59" s="2"/>
-    </row>
-    <row r="60" spans="1:9">
-      <c r="A60" s="2"/>
+      <c r="I59" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="60" ht="34" spans="1:9">
+      <c r="A60" s="2">
+        <v>62</v>
+      </c>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
       <c r="D60" s="2"/>
@@ -17809,10 +19209,14 @@
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
-      <c r="I60" s="2"/>
-    </row>
-    <row r="61" spans="1:9">
-      <c r="A61" s="2"/>
+      <c r="I60" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="61" ht="34" spans="1:9">
+      <c r="A61" s="2">
+        <v>63</v>
+      </c>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
       <c r="D61" s="2"/>
@@ -17820,10 +19224,14 @@
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
-      <c r="I61" s="2"/>
-    </row>
-    <row r="62" spans="1:9">
-      <c r="A62" s="2"/>
+      <c r="I61" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="62" ht="34" spans="1:9">
+      <c r="A62" s="2">
+        <v>64</v>
+      </c>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
       <c r="D62" s="2"/>
@@ -17831,10 +19239,14 @@
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
       <c r="H62" s="2"/>
-      <c r="I62" s="2"/>
-    </row>
-    <row r="63" spans="1:9">
-      <c r="A63" s="2"/>
+      <c r="I62" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="63" ht="34" spans="1:9">
+      <c r="A63" s="2">
+        <v>65</v>
+      </c>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
       <c r="D63" s="2"/>
@@ -17842,10 +19254,14 @@
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
-      <c r="I63" s="2"/>
-    </row>
-    <row r="64" spans="1:9">
-      <c r="A64" s="2"/>
+      <c r="I63" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="64" ht="34" spans="1:9">
+      <c r="A64" s="2">
+        <v>66</v>
+      </c>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
       <c r="D64" s="2"/>
@@ -17853,10 +19269,14 @@
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
       <c r="H64" s="2"/>
-      <c r="I64" s="2"/>
-    </row>
-    <row r="65" spans="1:9">
-      <c r="A65" s="2"/>
+      <c r="I64" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="65" ht="34" spans="1:9">
+      <c r="A65" s="2">
+        <v>67</v>
+      </c>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
       <c r="D65" s="2"/>
@@ -17864,10 +19284,14 @@
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
       <c r="H65" s="2"/>
-      <c r="I65" s="2"/>
-    </row>
-    <row r="66" spans="1:9">
-      <c r="A66" s="2"/>
+      <c r="I65" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="66" ht="17" spans="1:9">
+      <c r="A66" s="2">
+        <v>68</v>
+      </c>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
       <c r="D66" s="2"/>
@@ -17875,10 +19299,14 @@
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
       <c r="H66" s="2"/>
-      <c r="I66" s="2"/>
-    </row>
-    <row r="67" spans="1:9">
-      <c r="A67" s="2"/>
+      <c r="I66" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="67" ht="17" spans="1:9">
+      <c r="A67" s="2">
+        <v>69</v>
+      </c>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
       <c r="D67" s="2"/>
@@ -17886,10 +19314,14 @@
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
       <c r="H67" s="2"/>
-      <c r="I67" s="2"/>
-    </row>
-    <row r="68" spans="1:9">
-      <c r="A68" s="2"/>
+      <c r="I67" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="68" ht="34" spans="1:9">
+      <c r="A68" s="2">
+        <v>70</v>
+      </c>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
       <c r="D68" s="2"/>
@@ -17897,10 +19329,14 @@
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
       <c r="H68" s="2"/>
-      <c r="I68" s="2"/>
-    </row>
-    <row r="69" spans="1:9">
-      <c r="A69" s="2"/>
+      <c r="I68" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="69" ht="17" spans="1:9">
+      <c r="A69" s="2">
+        <v>71</v>
+      </c>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
       <c r="D69" s="2"/>
@@ -17908,10 +19344,14 @@
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
-      <c r="I69" s="2"/>
+      <c r="I69" s="2" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="70" spans="1:9">
-      <c r="A70" s="2"/>
+      <c r="A70" s="2">
+        <v>72</v>
+      </c>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
       <c r="D70" s="2"/>
@@ -22696,169 +24136,169 @@
   <sheetData>
     <row r="1" ht="17" spans="1:3">
       <c r="A1" s="3" t="s">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>76</v>
+        <v>134</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" ht="17" spans="1:3">
       <c r="A2" s="4" t="s">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="B2" s="8">
         <f>COUNT(单次交易!M2:M201)</f>
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>79</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3" ht="17" spans="1:3">
       <c r="A3" s="4" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="B3" s="8">
         <f>COUNTIF(单次交易!X2:X201,"&gt;0")</f>
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>81</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" ht="17" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>82</v>
+        <v>140</v>
       </c>
       <c r="B4" s="8">
         <f>COUNTIF(单次交易!X2:X201,"&lt;0")</f>
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>83</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" ht="17" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="B5" s="8">
         <f>COUNTIFS(单次交易!M2:M201,"&lt;&gt;",单次交易!X2:X201,"=0")</f>
         <v>0</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>85</v>
+        <v>143</v>
       </c>
     </row>
     <row r="6" ht="17" spans="1:3">
       <c r="A6" s="4" t="s">
-        <v>86</v>
+        <v>144</v>
       </c>
       <c r="B6" s="7">
         <f>IFERROR(B3/(B3+B4),"")</f>
-        <v>0.478260869565217</v>
+        <v>0.422535211267606</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>87</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" ht="17" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>88</v>
+        <v>146</v>
       </c>
       <c r="B7" s="7">
         <f>IFERROR(B4/(B3+B4),"")</f>
-        <v>0.521739130434783</v>
+        <v>0.577464788732394</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>89</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" ht="17" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>90</v>
+        <v>148</v>
       </c>
       <c r="B8" s="7">
         <f>IFERROR(AVERAGEIF(单次交易!X2:X201,"&gt;0",单次交易!AE2:AE201),"")</f>
-        <v>0.0678173186360151</v>
+        <v>0.0592335144641134</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>91</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9" ht="17" spans="1:3">
       <c r="A9" s="4" t="s">
-        <v>92</v>
+        <v>150</v>
       </c>
       <c r="B9" s="7">
         <f>IFERROR(-AVERAGEIF(单次交易!X2:X201,"&lt;0",单次交易!AE2:AE201),"")</f>
-        <v>0.0270811339018276</v>
+        <v>0.0297278223039372</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>93</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10" ht="17" spans="1:3">
       <c r="A10" s="4" t="s">
-        <v>94</v>
+        <v>152</v>
       </c>
       <c r="B10" s="8">
         <f>SUMIF(单次交易!X2:X201,"&gt;0",单次交易!AA2:AA201)</f>
-        <v>331</v>
+        <v>1005</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>95</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11" ht="17" spans="1:3">
       <c r="A11" s="4" t="s">
-        <v>96</v>
+        <v>154</v>
       </c>
       <c r="B11" s="8">
         <f>SUMIF(单次交易!X2:X201,"&lt;0",单次交易!AA2:AA201)</f>
-        <v>117</v>
+        <v>514</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>95</v>
+        <v>153</v>
       </c>
     </row>
     <row r="12" ht="17" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>97</v>
+        <v>155</v>
       </c>
       <c r="B12" s="5">
         <f>IFERROR(SUMPRODUCT(单次交易!E2:E201,单次交易!H2:H201)/COUNT(单次交易!H2:H201),"")</f>
-        <v>62939.652173913</v>
+        <v>66330.4788732394</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>98</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13" ht="17" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>99</v>
+        <v>157</v>
       </c>
       <c r="B13" s="7">
         <f>IF(OR(B6="",B7="",B8="",B9=""),"",B6*B8-B7*B9)</f>
-        <v>0.0183050825293146</v>
+        <v>0.00786147492199969</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>100</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" ht="17" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>101</v>
+        <v>159</v>
       </c>
       <c r="B14" s="7">
         <f>IF(COUNT(单次交易!AE2:AE201)=0,"",EXP(SUMPRODUCT(IFERROR(LN(1+单次交易!AE2:AE201),0)))-1)</f>
-        <v>0.458015637642215</v>
+        <v>0.557453929679268</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>102</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -22880,130 +24320,130 @@
   <sheetData>
     <row r="1" ht="17" spans="1:3">
       <c r="A1" s="3" t="s">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>103</v>
+        <v>161</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>104</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2" ht="17" spans="1:3">
       <c r="A2" s="4" t="s">
-        <v>105</v>
+        <v>163</v>
       </c>
       <c r="B2" s="9">
         <v>100000</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>106</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" ht="17" spans="1:3">
       <c r="A3" s="4" t="s">
-        <v>107</v>
+        <v>165</v>
       </c>
       <c r="B3" s="5">
         <f>IF(B2="","",B2+SUM(单次交易!X2:X201))</f>
-        <v>145595</v>
+        <v>155742</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>108</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" ht="17" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>109</v>
+        <v>167</v>
       </c>
       <c r="B4" s="6">
         <v>0.02</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>110</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5" ht="17" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>111</v>
+        <v>169</v>
       </c>
       <c r="B5" s="5">
         <f>IF(B3="","",B3*B4)</f>
-        <v>2911.9</v>
+        <v>3114.84</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>112</v>
+        <v>170</v>
       </c>
     </row>
     <row r="6" ht="17" spans="1:3">
       <c r="A6" s="4" t="s">
-        <v>113</v>
+        <v>171</v>
       </c>
       <c r="B6" s="6">
         <v>0.06</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>114</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7" ht="17" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>115</v>
+        <v>173</v>
       </c>
       <c r="B7" s="5">
         <f>IF(B3="","",B3*B6)</f>
-        <v>8735.7</v>
+        <v>9344.52</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>116</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8" ht="17" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>117</v>
+        <v>175</v>
       </c>
       <c r="B8" s="5">
         <f ca="1">SUMIFS(单次交易!X2:X201,单次交易!X2:X201,"&lt;0",单次交易!M2:M201,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,单次交易!M2:M201,"&lt;="&amp;EOMONTH(TODAY(),0))</f>
         <v>0</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>118</v>
+        <v>176</v>
       </c>
     </row>
     <row r="9" ht="17" spans="1:3">
       <c r="A9" s="4" t="s">
-        <v>119</v>
+        <v>177</v>
       </c>
       <c r="B9" s="5">
         <f>IFERROR(SUMPRODUCT((单次交易!M2:M201="")*(单次交易!H2:H201&gt;0)*(单次交易!E2:E201&gt;单次交易!N2:N201)*单次交易!H2:H201*(单次交易!E2:E201-单次交易!N2:N201)),0)</f>
         <v>0</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>120</v>
+        <v>178</v>
       </c>
     </row>
     <row r="10" ht="17" spans="1:3">
       <c r="A10" s="4" t="s">
-        <v>121</v>
+        <v>179</v>
       </c>
       <c r="B10" s="5">
         <f>IF(OR(B7="",B9=""),"",B7-B9)</f>
-        <v>8735.7</v>
+        <v>9344.52</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>122</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11" ht="17" spans="1:3">
       <c r="A11" s="4" t="s">
-        <v>123</v>
+        <v>181</v>
       </c>
       <c r="B11" s="7">
         <f>IF(OR(B2="",B3="",B2&lt;=0),"",B3/B2-1)</f>
-        <v>0.45595</v>
+        <v>0.55742</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>124</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -23044,84 +24484,84 @@
   <sheetData>
     <row r="1" ht="17" spans="1:3">
       <c r="A1" s="3" t="s">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>103</v>
+        <v>161</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" ht="17" spans="1:3">
       <c r="A2" s="4" t="s">
-        <v>125</v>
+        <v>183</v>
       </c>
       <c r="B2" s="5">
         <f>账户数据!B3</f>
-        <v>145595</v>
+        <v>155742</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>126</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3" ht="17" spans="1:3">
       <c r="A3" s="4" t="s">
-        <v>127</v>
+        <v>185</v>
       </c>
       <c r="B3" s="6">
         <v>0.1</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>128</v>
+        <v>186</v>
       </c>
     </row>
     <row r="4" ht="17" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>129</v>
+        <v>187</v>
       </c>
       <c r="B4" s="5">
         <f>IF(OR(B2="",B3=""),"",B2*B3)</f>
-        <v>14559.5</v>
+        <v>15574.2</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>130</v>
+        <v>188</v>
       </c>
     </row>
     <row r="5" ht="17" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>97</v>
+        <v>155</v>
       </c>
       <c r="B5" s="5">
         <f>多次统计数据!B12</f>
-        <v>62939.652173913</v>
+        <v>66330.4788732394</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>131</v>
+        <v>189</v>
       </c>
     </row>
     <row r="6" ht="17" spans="1:3">
       <c r="A6" s="4" t="s">
-        <v>132</v>
+        <v>190</v>
       </c>
       <c r="B6" s="7">
         <f>多次统计数据!B13</f>
-        <v>0.0183050825293146</v>
+        <v>0.00786147492199969</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>133</v>
+        <v>191</v>
       </c>
     </row>
     <row r="7" ht="17" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>134</v>
+        <v>192</v>
       </c>
       <c r="B7" s="8">
         <f>IF(OR(B3="",B6="",B3&lt;=0,B6&lt;=0),"暂不可计算",ROUNDUP(LN(1+B3)/LN(1+B6),0))</f>
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>135</v>
+        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -23148,233 +24588,233 @@
   <sheetData>
     <row r="1" ht="42" customHeight="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>136</v>
+        <v>194</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>137</v>
+        <v>195</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>138</v>
+        <v>196</v>
       </c>
     </row>
     <row r="2" ht="17" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>139</v>
+        <v>197</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>140</v>
+        <v>198</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>141</v>
+        <v>199</v>
       </c>
     </row>
     <row r="3" ht="17" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>142</v>
+        <v>200</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>143</v>
+        <v>201</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>144</v>
+        <v>202</v>
       </c>
     </row>
     <row r="4" ht="17" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>145</v>
+        <v>203</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>146</v>
+        <v>204</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>147</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" ht="17" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>148</v>
+        <v>206</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>143</v>
+        <v>201</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>149</v>
+        <v>207</v>
       </c>
     </row>
     <row r="6" ht="17" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>150</v>
+        <v>208</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>151</v>
+        <v>209</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>152</v>
+        <v>210</v>
       </c>
     </row>
     <row r="7" ht="17" spans="1:3">
       <c r="A7" s="2" t="s">
-        <v>153</v>
+        <v>211</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>146</v>
+        <v>204</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>154</v>
+        <v>212</v>
       </c>
     </row>
     <row r="8" ht="17" spans="1:3">
       <c r="A8" s="2" t="s">
-        <v>155</v>
+        <v>213</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>146</v>
+        <v>204</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>156</v>
+        <v>214</v>
       </c>
     </row>
     <row r="9" ht="17" spans="1:3">
       <c r="A9" s="2" t="s">
-        <v>157</v>
+        <v>215</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>158</v>
+        <v>216</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>159</v>
+        <v>217</v>
       </c>
     </row>
     <row r="10" ht="17" spans="1:3">
       <c r="A10" s="2" t="s">
-        <v>160</v>
+        <v>218</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>161</v>
+        <v>219</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>162</v>
+        <v>220</v>
       </c>
     </row>
     <row r="11" ht="17" spans="1:3">
       <c r="A11" s="2" t="s">
-        <v>163</v>
+        <v>221</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>161</v>
+        <v>219</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>164</v>
+        <v>222</v>
       </c>
     </row>
     <row r="12" ht="17" spans="1:3">
       <c r="A12" s="2" t="s">
-        <v>165</v>
+        <v>223</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>140</v>
+        <v>198</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>166</v>
+        <v>224</v>
       </c>
     </row>
     <row r="13" ht="17" spans="1:3">
       <c r="A13" s="2" t="s">
-        <v>167</v>
+        <v>225</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>140</v>
+        <v>198</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>168</v>
+        <v>226</v>
       </c>
     </row>
     <row r="14" ht="17" spans="1:3">
       <c r="A14" s="2" t="s">
-        <v>169</v>
+        <v>227</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>143</v>
+        <v>201</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>170</v>
+        <v>228</v>
       </c>
     </row>
     <row r="15" ht="17" spans="1:3">
       <c r="A15" s="2" t="s">
-        <v>171</v>
+        <v>229</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>143</v>
+        <v>201</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
     </row>
     <row r="16" ht="17" spans="1:3">
       <c r="A16" s="2" t="s">
-        <v>173</v>
+        <v>231</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>151</v>
+        <v>209</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>174</v>
+        <v>232</v>
       </c>
     </row>
     <row r="17" ht="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>175</v>
+        <v>233</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>146</v>
+        <v>204</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>176</v>
+        <v>234</v>
       </c>
     </row>
     <row r="18" ht="17" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>177</v>
+        <v>235</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>158</v>
+        <v>216</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>178</v>
+        <v>236</v>
       </c>
     </row>
     <row r="19" ht="17" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>179</v>
+        <v>237</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>151</v>
+        <v>209</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>180</v>
+        <v>238</v>
       </c>
     </row>
     <row r="20" ht="17" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>181</v>
+        <v>239</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>182</v>
+        <v>240</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>183</v>
+        <v>241</v>
       </c>
     </row>
     <row r="21" ht="17" spans="1:3">
       <c r="A21" s="2" t="s">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>185</v>
+        <v>243</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>186</v>
+        <v>244</v>
       </c>
     </row>
     <row r="22" spans="1:3">

--- a/交易管理系统.xlsx
+++ b/交易管理系统.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\个人相关\学习\股票\learn_socks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BBF2660-9FF9-41B5-8A29-92C6B7BB30EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09C1764D-F9D6-4AE6-99E1-E8107DDC0AE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="8460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -144,7 +144,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="260">
   <si>
     <t>交易编号</t>
   </si>
@@ -926,14 +926,44 @@
     <t>完全按照预期来操作</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
+  <si>
+    <t>神马电力</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.供应住都是涨停住不太好，感觉就是吸引人注意，没有缓慢增长，2整体交易量已经放大，出现两波没有低于前低，支撑有效，钱交易量相对小脚，交易量比较大所以已经走过自然反弹，不是那么完美，相对安全，防止震仓</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>3-一般</t>
+  </si>
+  <si>
+    <t>现象不是那么完美</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>景旺电子</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.不是都是涨停，20附近买盘强势大交易量吸收了下跌，近期的供应线都被突破了，大量卖盘之后，后面还能上涨，，后面跌不动，说明供应不足，供应被吸收完毕了，前面是又震仓的，后面跨越小学出现了</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>1-差</t>
+  </si>
+  <si>
+    <t>1.期待超级上涨，判断正确的情况，后续动力不足没有发现，没有及时止盈</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="178" formatCode="\¥#,##0.00;[Red]\-\¥#,##0.00"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="\¥#,##0.00;[Red]\-\¥#,##0.00"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -1052,7 +1082,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1064,10 +1094,10 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1781,7 +1811,7 @@
       </c>
       <c r="AB2" s="7">
         <f>IF(OR(A2="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC2" s="8" t="str">
         <f>IF(OR(AB2="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB2,"低于上限","达到或超过上限"))</f>
@@ -1802,7 +1832,7 @@
       </c>
       <c r="C3" s="5">
         <f>IF(C2="","",C2+SUM(单次交易!Y2:Y201))</f>
-        <v>100001.29812713747</v>
+        <v>100001.09666635693</v>
       </c>
       <c r="D3" s="6">
         <v>0.02</v>
@@ -1868,7 +1898,7 @@
       </c>
       <c r="Z3" s="7">
         <f>IF(OR(AE3="",多次统计数据!$B$8=""),"",AE3-多次统计数据!$B$8)</f>
-        <v>-9.0469408050762173E-2</v>
+        <v>-9.0469472375648952E-2</v>
       </c>
       <c r="AA3" s="14">
         <f t="shared" si="7"/>
@@ -1876,7 +1906,7 @@
       </c>
       <c r="AB3" s="7">
         <f>IF(OR(A3="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC3" s="8" t="str">
         <f>IF(OR(AB3="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB3,"低于上限","达到或超过上限"))</f>
@@ -1885,7 +1915,7 @@
       <c r="AD3" s="2"/>
       <c r="AE3" s="7">
         <f t="shared" si="8"/>
-        <v>-3.1929585513385712E-2</v>
+        <v>-3.1929649838272484E-2</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.15">
@@ -1974,7 +2004,7 @@
       </c>
       <c r="AB4" s="7">
         <f>IF(OR(A4="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC4" s="8" t="str">
         <f>IF(OR(AB4="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB4,"低于上限","达到或超过上限"))</f>
@@ -2072,7 +2102,7 @@
       </c>
       <c r="AB5" s="7">
         <f>IF(OR(A5="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC5" s="8" t="str">
         <f>IF(OR(AB5="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB5,"低于上限","达到或超过上限"))</f>
@@ -2170,7 +2200,7 @@
       </c>
       <c r="AB6" s="7">
         <f>IF(OR(A6="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC6" s="8" t="str">
         <f>IF(OR(AB6="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB6,"低于上限","达到或超过上限"))</f>
@@ -2264,7 +2294,7 @@
       </c>
       <c r="AB7" s="7">
         <f>IF(OR(A7="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC7" s="8" t="str">
         <f>IF(OR(AB7="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB7,"低于上限","达到或超过上限"))</f>
@@ -2506,7 +2536,7 @@
       </c>
       <c r="AB10" s="7">
         <f>IF(OR(A10="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC10" s="8" t="str">
         <f>IF(OR(AB10="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB10,"低于上限","达到或超过上限"))</f>
@@ -2600,7 +2630,7 @@
       </c>
       <c r="AB11" s="7">
         <f>IF(OR(A11="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC11" s="8" t="str">
         <f>IF(OR(AB11="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB11,"低于上限","达到或超过上限"))</f>
@@ -2698,7 +2728,7 @@
       </c>
       <c r="AB12" s="7">
         <f>IF(OR(A12="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC12" s="8" t="str">
         <f>IF(OR(AB12="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB12,"低于上限","达到或超过上限"))</f>
@@ -2796,7 +2826,7 @@
       </c>
       <c r="AB13" s="7">
         <f>IF(OR(A13="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC13" s="8" t="str">
         <f>IF(OR(AB13="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB13,"低于上限","达到或超过上限"))</f>
@@ -2894,7 +2924,7 @@
       </c>
       <c r="AB14" s="7">
         <f>IF(OR(A14="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC14" s="8" t="str">
         <f>IF(OR(AB14="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB14,"低于上限","达到或超过上限"))</f>
@@ -2988,7 +3018,7 @@
       </c>
       <c r="AB15" s="7">
         <f>IF(OR(A15="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC15" s="8" t="str">
         <f>IF(OR(AB15="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB15,"低于上限","达到或超过上限"))</f>
@@ -3082,7 +3112,7 @@
       </c>
       <c r="AB16" s="7">
         <f>IF(OR(A16="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC16" s="8" t="str">
         <f>IF(OR(AB16="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB16,"低于上限","达到或超过上限"))</f>
@@ -3176,7 +3206,7 @@
       </c>
       <c r="AB17" s="7">
         <f>IF(OR(A17="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC17" s="8" t="str">
         <f>IF(OR(AB17="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB17,"低于上限","达到或超过上限"))</f>
@@ -3270,7 +3300,7 @@
       </c>
       <c r="AB18" s="7">
         <f>IF(OR(A18="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC18" s="8" t="str">
         <f>IF(OR(AB18="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB18,"低于上限","达到或超过上限"))</f>
@@ -3364,7 +3394,7 @@
       </c>
       <c r="AB19" s="7">
         <f>IF(OR(A19="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC19" s="8" t="str">
         <f>IF(OR(AB19="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB19,"低于上限","达到或超过上限"))</f>
@@ -3458,7 +3488,7 @@
       </c>
       <c r="AB20" s="7">
         <f>IF(OR(A20="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC20" s="8" t="str">
         <f>IF(OR(AB20="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB20,"低于上限","达到或超过上限"))</f>
@@ -3552,7 +3582,7 @@
       </c>
       <c r="AB21" s="7">
         <f>IF(OR(A21="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC21" s="8" t="str">
         <f>IF(OR(AB21="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB21,"低于上限","达到或超过上限"))</f>
@@ -3646,7 +3676,7 @@
       </c>
       <c r="AB22" s="7">
         <f>IF(OR(A22="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC22" s="8" t="str">
         <f>IF(OR(AB22="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB22,"低于上限","达到或超过上限"))</f>
@@ -3740,7 +3770,7 @@
       </c>
       <c r="AB23" s="7">
         <f>IF(OR(A23="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC23" s="8" t="str">
         <f>IF(OR(AB23="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB23,"低于上限","达到或超过上限"))</f>
@@ -3834,7 +3864,7 @@
       </c>
       <c r="AB24" s="7">
         <f>IF(OR(A24="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC24" s="8" t="str">
         <f>IF(OR(AB24="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB24,"低于上限","达到或超过上限"))</f>
@@ -3928,7 +3958,7 @@
       </c>
       <c r="AB25" s="7">
         <f>IF(OR(A25="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC25" s="8" t="str">
         <f>IF(OR(AB25="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB25,"低于上限","达到或超过上限"))</f>
@@ -4022,7 +4052,7 @@
       </c>
       <c r="AB26" s="7">
         <f>IF(OR(A26="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC26" s="8" t="str">
         <f>IF(OR(AB26="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB26,"低于上限","达到或超过上限"))</f>
@@ -4116,7 +4146,7 @@
       </c>
       <c r="AB27" s="7">
         <f>IF(OR(A27="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC27" s="8" t="str">
         <f>IF(OR(AB27="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB27,"低于上限","达到或超过上限"))</f>
@@ -4210,7 +4240,7 @@
       </c>
       <c r="AB28" s="7">
         <f>IF(OR(A28="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC28" s="8" t="str">
         <f>IF(OR(AB28="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB28,"低于上限","达到或超过上限"))</f>
@@ -4304,7 +4334,7 @@
       </c>
       <c r="AB29" s="7">
         <f>IF(OR(A29="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC29" s="8" t="str">
         <f>IF(OR(AB29="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB29,"低于上限","达到或超过上限"))</f>
@@ -4398,7 +4428,7 @@
       </c>
       <c r="AB30" s="7">
         <f>IF(OR(A30="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC30" s="8" t="str">
         <f>IF(OR(AB30="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB30,"低于上限","达到或超过上限"))</f>
@@ -4492,7 +4522,7 @@
       </c>
       <c r="AB31" s="7">
         <f>IF(OR(A31="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC31" s="8" t="str">
         <f>IF(OR(AB31="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB31,"低于上限","达到或超过上限"))</f>
@@ -4589,7 +4619,7 @@
       </c>
       <c r="AB32" s="7">
         <f>IF(OR(A32="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC32" s="8" t="str">
         <f>IF(OR(AB32="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB32,"低于上限","达到或超过上限"))</f>
@@ -4683,7 +4713,7 @@
       </c>
       <c r="AB33" s="7">
         <f>IF(OR(A33="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC33" s="8" t="str">
         <f>IF(OR(AB33="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB33,"低于上限","达到或超过上限"))</f>
@@ -4777,7 +4807,7 @@
       </c>
       <c r="AB34" s="7">
         <f>IF(OR(A34="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC34" s="8" t="str">
         <f>IF(OR(AB34="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB34,"低于上限","达到或超过上限"))</f>
@@ -4871,7 +4901,7 @@
       </c>
       <c r="AB35" s="7">
         <f>IF(OR(A35="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC35" s="8" t="str">
         <f>IF(OR(AB35="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB35,"低于上限","达到或超过上限"))</f>
@@ -4965,7 +4995,7 @@
       </c>
       <c r="AB36" s="7">
         <f>IF(OR(A36="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC36" s="8" t="str">
         <f>IF(OR(AB36="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB36,"低于上限","达到或超过上限"))</f>
@@ -5059,7 +5089,7 @@
       </c>
       <c r="AB37" s="7">
         <f>IF(OR(A37="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC37" s="8" t="str">
         <f>IF(OR(AB37="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB37,"低于上限","达到或超过上限"))</f>
@@ -5153,7 +5183,7 @@
       </c>
       <c r="AB38" s="7">
         <f>IF(OR(A38="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC38" s="8" t="str">
         <f>IF(OR(AB38="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB38,"低于上限","达到或超过上限"))</f>
@@ -5250,7 +5280,7 @@
       </c>
       <c r="AB39" s="7">
         <f>IF(OR(A39="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC39" s="8" t="str">
         <f>IF(OR(AB39="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB39,"低于上限","达到或超过上限"))</f>
@@ -5344,7 +5374,7 @@
       </c>
       <c r="AB40" s="7">
         <f>IF(OR(A40="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC40" s="8" t="str">
         <f>IF(OR(AB40="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB40,"低于上限","达到或超过上限"))</f>
@@ -5438,7 +5468,7 @@
       </c>
       <c r="AB41" s="7">
         <f>IF(OR(A41="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC41" s="8" t="str">
         <f>IF(OR(AB41="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB41,"低于上限","达到或超过上限"))</f>
@@ -5532,7 +5562,7 @@
       </c>
       <c r="AB42" s="7">
         <f>IF(OR(A42="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC42" s="8" t="str">
         <f>IF(OR(AB42="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB42,"低于上限","达到或超过上限"))</f>
@@ -5626,7 +5656,7 @@
       </c>
       <c r="AB43" s="7">
         <f>IF(OR(A43="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC43" s="8" t="str">
         <f>IF(OR(AB43="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB43,"低于上限","达到或超过上限"))</f>
@@ -5720,7 +5750,7 @@
       </c>
       <c r="AB44" s="7">
         <f>IF(OR(A44="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC44" s="8" t="str">
         <f>IF(OR(AB44="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB44,"低于上限","达到或超过上限"))</f>
@@ -5814,7 +5844,7 @@
       </c>
       <c r="AB45" s="7">
         <f>IF(OR(A45="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC45" s="8" t="str">
         <f>IF(OR(AB45="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB45,"低于上限","达到或超过上限"))</f>
@@ -5908,7 +5938,7 @@
       </c>
       <c r="AB46" s="7">
         <f>IF(OR(A46="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC46" s="8" t="str">
         <f>IF(OR(AB46="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB46,"低于上限","达到或超过上限"))</f>
@@ -6002,7 +6032,7 @@
       </c>
       <c r="AB47" s="7">
         <f>IF(OR(A47="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC47" s="8" t="str">
         <f>IF(OR(AB47="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB47,"低于上限","达到或超过上限"))</f>
@@ -6099,7 +6129,7 @@
       </c>
       <c r="AB48" s="7">
         <f>IF(OR(A48="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC48" s="8" t="str">
         <f>IF(OR(AB48="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB48,"低于上限","达到或超过上限"))</f>
@@ -6193,7 +6223,7 @@
       </c>
       <c r="AB49" s="7">
         <f>IF(OR(A49="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC49" s="8" t="str">
         <f>IF(OR(AB49="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB49,"低于上限","达到或超过上限"))</f>
@@ -6290,7 +6320,7 @@
       </c>
       <c r="AB50" s="7">
         <f>IF(OR(A50="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC50" s="8" t="str">
         <f>IF(OR(AB50="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB50,"低于上限","达到或超过上限"))</f>
@@ -6387,7 +6417,7 @@
       </c>
       <c r="AB51" s="7">
         <f>IF(OR(A51="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC51" s="8" t="str">
         <f>IF(OR(AB51="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB51,"低于上限","达到或超过上限"))</f>
@@ -6481,7 +6511,7 @@
       </c>
       <c r="AB52" s="7">
         <f>IF(OR(A52="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC52" s="8" t="str">
         <f>IF(OR(AB52="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB52,"低于上限","达到或超过上限"))</f>
@@ -6575,7 +6605,7 @@
       </c>
       <c r="AB53" s="7">
         <f>IF(OR(A53="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC53" s="8" t="str">
         <f>IF(OR(AB53="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB53,"低于上限","达到或超过上限"))</f>
@@ -6669,7 +6699,7 @@
       </c>
       <c r="AB54" s="7">
         <f>IF(OR(A54="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC54" s="8" t="str">
         <f>IF(OR(AB54="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB54,"低于上限","达到或超过上限"))</f>
@@ -6763,7 +6793,7 @@
       </c>
       <c r="AB55" s="7">
         <f>IF(OR(A55="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC55" s="8" t="str">
         <f>IF(OR(AB55="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB55,"低于上限","达到或超过上限"))</f>
@@ -6857,7 +6887,7 @@
       </c>
       <c r="AB56" s="7">
         <f>IF(OR(A56="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC56" s="8" t="str">
         <f>IF(OR(AB56="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB56,"低于上限","达到或超过上限"))</f>
@@ -6951,7 +6981,7 @@
       </c>
       <c r="AB57" s="7">
         <f>IF(OR(A57="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC57" s="8" t="str">
         <f>IF(OR(AB57="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB57,"低于上限","达到或超过上限"))</f>
@@ -7045,7 +7075,7 @@
       </c>
       <c r="AB58" s="7">
         <f>IF(OR(A58="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC58" s="8" t="str">
         <f>IF(OR(AB58="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB58,"低于上限","达到或超过上限"))</f>
@@ -7139,7 +7169,7 @@
       </c>
       <c r="AB59" s="7">
         <f>IF(OR(A59="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC59" s="8" t="str">
         <f>IF(OR(AB59="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB59,"低于上限","达到或超过上限"))</f>
@@ -7233,7 +7263,7 @@
       </c>
       <c r="AB60" s="7">
         <f>IF(OR(A60="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC60" s="8" t="str">
         <f>IF(OR(AB60="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB60,"低于上限","达到或超过上限"))</f>
@@ -7327,7 +7357,7 @@
       </c>
       <c r="AB61" s="7">
         <f>IF(OR(A61="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC61" s="8" t="str">
         <f>IF(OR(AB61="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB61,"低于上限","达到或超过上限"))</f>
@@ -7421,7 +7451,7 @@
       </c>
       <c r="AB62" s="7">
         <f>IF(OR(A62="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC62" s="8" t="str">
         <f>IF(OR(AB62="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB62,"低于上限","达到或超过上限"))</f>
@@ -7518,7 +7548,7 @@
       </c>
       <c r="AB63" s="7">
         <f>IF(OR(A63="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC63" s="8" t="str">
         <f>IF(OR(AB63="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB63,"低于上限","达到或超过上限"))</f>
@@ -7612,7 +7642,7 @@
       </c>
       <c r="AB64" s="7">
         <f>IF(OR(A64="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC64" s="8" t="str">
         <f>IF(OR(AB64="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB64,"低于上限","达到或超过上限"))</f>
@@ -7706,7 +7736,7 @@
       </c>
       <c r="AB65" s="7">
         <f>IF(OR(A65="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC65" s="8" t="str">
         <f>IF(OR(AB65="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB65,"低于上限","达到或超过上限"))</f>
@@ -7800,7 +7830,7 @@
       </c>
       <c r="AB66" s="7">
         <f>IF(OR(A66="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC66" s="8" t="str">
         <f>IF(OR(AB66="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB66,"低于上限","达到或超过上限"))</f>
@@ -7894,7 +7924,7 @@
       </c>
       <c r="AB67" s="7">
         <f>IF(OR(A67="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC67" s="8" t="str">
         <f>IF(OR(AB67="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB67,"低于上限","达到或超过上限"))</f>
@@ -7988,7 +8018,7 @@
       </c>
       <c r="AB68" s="7">
         <f>IF(OR(A68="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC68" s="8" t="str">
         <f>IF(OR(AB68="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB68,"低于上限","达到或超过上限"))</f>
@@ -8082,7 +8112,7 @@
       </c>
       <c r="AB69" s="7">
         <f>IF(OR(A69="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC69" s="8" t="str">
         <f>IF(OR(AB69="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB69,"低于上限","达到或超过上限"))</f>
@@ -8176,7 +8206,7 @@
       </c>
       <c r="AB70" s="7">
         <f>IF(OR(A70="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC70" s="8" t="str">
         <f>IF(OR(AB70="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB70,"低于上限","达到或超过上限"))</f>
@@ -8270,7 +8300,7 @@
       </c>
       <c r="AB71" s="7">
         <f>IF(OR(A71="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC71" s="8" t="str">
         <f>IF(OR(AB71="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB71,"低于上限","达到或超过上限"))</f>
@@ -8364,7 +8394,7 @@
       </c>
       <c r="AB72" s="7">
         <f>IF(OR(A72="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC72" s="8" t="str">
         <f>IF(OR(AB72="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB72,"低于上限","达到或超过上限"))</f>
@@ -8458,7 +8488,7 @@
       </c>
       <c r="AB73" s="7">
         <f>IF(OR(A73="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC73" s="8" t="str">
         <f>IF(OR(AB73="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB73,"低于上限","达到或超过上限"))</f>
@@ -8552,7 +8582,7 @@
       </c>
       <c r="AB74" s="7">
         <f>IF(OR(A74="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC74" s="8" t="str">
         <f>IF(OR(AB74="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB74,"低于上限","达到或超过上限"))</f>
@@ -8646,7 +8676,7 @@
       </c>
       <c r="AB75" s="7">
         <f>IF(OR(A75="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC75" s="8" t="str">
         <f>IF(OR(AB75="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB75,"低于上限","达到或超过上限"))</f>
@@ -8668,7 +8698,7 @@
         <v>75</v>
       </c>
       <c r="B76" s="15" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="C76" s="9">
         <v>161618</v>
@@ -8676,23 +8706,38 @@
       <c r="D76" s="6">
         <v>0.02</v>
       </c>
-      <c r="E76" s="9"/>
-      <c r="F76" s="8"/>
+      <c r="E76" s="9">
+        <v>18.75</v>
+      </c>
+      <c r="F76" s="8">
+        <f t="shared" si="9"/>
+        <v>1800</v>
+      </c>
       <c r="G76" s="8" t="str">
         <f>IF(OR(A76="",F76="",E76="",N76="",E76&lt;=N76,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H76="",F76*(E76-N76),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H76" s="2"/>
-      <c r="I76" s="10"/>
-      <c r="J76" s="9"/>
-      <c r="K76" s="9"/>
-      <c r="L76" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H76" s="2">
+        <v>1800</v>
+      </c>
+      <c r="I76" s="10">
+        <v>44032</v>
+      </c>
+      <c r="J76" s="9">
+        <v>24</v>
+      </c>
+      <c r="K76" s="9">
+        <v>16.88</v>
+      </c>
+      <c r="L76" s="8">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="M76" s="10"/>
+        <v>1800</v>
+      </c>
+      <c r="M76" s="10">
+        <v>44299</v>
+      </c>
       <c r="N76" s="9">
-        <v>33.5</v>
+        <v>17</v>
       </c>
       <c r="O76" s="9"/>
       <c r="P76" s="9"/>
@@ -8700,118 +8745,150 @@
       <c r="R76" s="2"/>
       <c r="S76" s="2"/>
       <c r="T76" s="2"/>
-      <c r="U76" s="7" t="str">
+      <c r="U76" s="7">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="V76" s="7" t="str">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="V76" s="7">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="W76" s="13" t="str">
+        <v>9.3333333333333338E-2</v>
+      </c>
+      <c r="W76" s="13">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="X76" s="5" t="str">
+        <v>3</v>
+      </c>
+      <c r="X76" s="5">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="Y76" s="7" t="str">
+        <v>-3366</v>
+      </c>
+      <c r="Y76" s="7">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="Z76" s="7" t="str">
+        <v>-9.9733333333333327E-2</v>
+      </c>
+      <c r="Z76" s="7">
         <f>IF(OR(AE76="",多次统计数据!$B$8=""),"",AE76-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA76" s="14" t="str">
+        <v>-7.9366710631524395E-2</v>
+      </c>
+      <c r="AA76" s="14">
         <f t="shared" si="16"/>
-        <v/>
+        <v>267</v>
       </c>
       <c r="AB76" s="7">
         <f>IF(OR(A76="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>4.210270769616864E-2</v>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC76" s="8" t="str">
         <f>IF(OR(AB76="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB76,"低于上限","达到或超过上限"))</f>
         <v>低于上限</v>
       </c>
-      <c r="AD76" s="2"/>
-      <c r="AE76" s="7" t="str">
+      <c r="AD76" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="AE76" s="7">
         <f t="shared" si="17"/>
-        <v/>
+        <v>-2.0826888094147931E-2</v>
+      </c>
+      <c r="AF76" s="16" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="77" spans="1:32" x14ac:dyDescent="0.15">
-      <c r="A77" s="2"/>
-      <c r="B77" s="2"/>
-      <c r="C77" s="9"/>
-      <c r="D77" s="6"/>
-      <c r="E77" s="9"/>
-      <c r="F77" s="8" t="str">
+      <c r="A77" s="2">
+        <v>76</v>
+      </c>
+      <c r="B77" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="C77" s="9">
+        <v>158252</v>
+      </c>
+      <c r="D77" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E77" s="9">
+        <v>26.05</v>
+      </c>
+      <c r="F77" s="8">
         <f t="shared" si="9"/>
-        <v/>
+        <v>1500</v>
       </c>
       <c r="G77" s="8" t="str">
         <f>IF(OR(A77="",F77="",E77="",N77="",E77&lt;=N77,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H77="",F77*(E77-N77),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H77" s="2"/>
-      <c r="I77" s="10"/>
-      <c r="J77" s="9"/>
-      <c r="K77" s="9"/>
-      <c r="L77" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H77" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I77" s="10">
+        <v>44399</v>
+      </c>
+      <c r="J77" s="9">
+        <v>30</v>
+      </c>
+      <c r="K77" s="9">
+        <v>23.4</v>
+      </c>
+      <c r="L77" s="8">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="M77" s="10"/>
-      <c r="N77" s="9"/>
+        <v>1500</v>
+      </c>
+      <c r="M77" s="10">
+        <v>44428</v>
+      </c>
+      <c r="N77" s="9">
+        <v>24</v>
+      </c>
       <c r="O77" s="9"/>
       <c r="P77" s="9"/>
       <c r="Q77" s="2"/>
       <c r="R77" s="2"/>
       <c r="S77" s="2"/>
       <c r="T77" s="2"/>
-      <c r="U77" s="7" t="str">
+      <c r="U77" s="7">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="V77" s="7" t="str">
+        <v>0.1516314779270633</v>
+      </c>
+      <c r="V77" s="7">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="W77" s="13" t="str">
+        <v>7.8694817658349348E-2</v>
+      </c>
+      <c r="W77" s="13">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="X77" s="5" t="str">
+        <v>1.926829268292682</v>
+      </c>
+      <c r="X77" s="5">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="Y77" s="7" t="str">
+        <v>-3975</v>
+      </c>
+      <c r="Y77" s="7">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="Z77" s="7" t="str">
+        <v>-0.1017274472168906</v>
+      </c>
+      <c r="Z77" s="7">
         <f>IF(OR(AE77="",多次统计数据!$B$8=""),"",AE77-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA77" s="14" t="str">
+        <v>-8.3657988500523861E-2</v>
+      </c>
+      <c r="AA77" s="14">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="AB77" s="7" t="str">
+        <v>29</v>
+      </c>
+      <c r="AB77" s="7">
         <f>IF(OR(A77="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>4.0184339021102522E-2</v>
       </c>
       <c r="AC77" s="8" t="str">
         <f>IF(OR(AB77="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB77,"低于上限","达到或超过上限"))</f>
-        <v/>
-      </c>
-      <c r="AD77" s="2"/>
-      <c r="AE77" s="7" t="str">
+        <v>低于上限</v>
+      </c>
+      <c r="AD77" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="AE77" s="7">
         <f t="shared" si="17"/>
-        <v/>
+        <v>-2.5118165963147386E-2</v>
+      </c>
+      <c r="AF77" s="16" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="78" spans="1:32" x14ac:dyDescent="0.15">
@@ -18900,7 +18977,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:11" ht="54" x14ac:dyDescent="0.15">
       <c r="A71" s="2">
         <v>73</v>
       </c>
@@ -18911,10 +18988,14 @@
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
       <c r="H71" s="2"/>
-      <c r="I71" s="2"/>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A72" s="2"/>
+      <c r="I71" s="15" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" ht="54" x14ac:dyDescent="0.15">
+      <c r="A72" s="2">
+        <v>74</v>
+      </c>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
       <c r="D72" s="2"/>
@@ -18922,10 +19003,14 @@
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
       <c r="H72" s="2"/>
-      <c r="I72" s="2"/>
+      <c r="I72" s="15" t="s">
+        <v>257</v>
+      </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.15">
-      <c r="A73" s="2"/>
+      <c r="A73" s="2">
+        <v>75</v>
+      </c>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
       <c r="D73" s="2"/>
@@ -23691,7 +23776,7 @@
       </c>
       <c r="B2" s="8">
         <f>COUNT(单次交易!M2:M201)</f>
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>137</v>
@@ -23715,7 +23800,7 @@
       </c>
       <c r="B4" s="8">
         <f>COUNTIF(单次交易!X2:X201,"&lt;0")</f>
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>141</v>
@@ -23739,7 +23824,7 @@
       </c>
       <c r="B6" s="7">
         <f>IFERROR(B3/(B3+B4),"")</f>
-        <v>0.43055555555555558</v>
+        <v>0.41891891891891891</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>145</v>
@@ -23751,7 +23836,7 @@
       </c>
       <c r="B7" s="7">
         <f>IFERROR(B4/(B3+B4),"")</f>
-        <v>0.56944444444444442</v>
+        <v>0.58108108108108103</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>147</v>
@@ -23775,7 +23860,7 @@
       </c>
       <c r="B9" s="7">
         <f>IFERROR(-AVERAGEIF(单次交易!X2:X201,"&lt;0",单次交易!AE2:AE201),"")</f>
-        <v>2.9727820386723097E-2</v>
+        <v>2.9413622191577421E-2</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>151</v>
@@ -23799,7 +23884,7 @@
       </c>
       <c r="B11" s="8">
         <f>SUMIF(单次交易!X2:X201,"&lt;0",单次交易!AA2:AA201)</f>
-        <v>514</v>
+        <v>810</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>153</v>
@@ -23811,7 +23896,7 @@
       </c>
       <c r="B12" s="5">
         <f>IFERROR(SUMPRODUCT(单次交易!E2:E201,单次交易!H2:H201)/COUNT(单次交易!H2:H201),"")</f>
-        <v>65740.722222222219</v>
+        <v>64948.067567567567</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>156</v>
@@ -23823,7 +23908,7 @@
       </c>
       <c r="B13" s="7">
         <f>IF(OR(B6="",B7="",B8="",B9=""),"",B6*B8-B7*B9)</f>
-        <v>8.2763036500419947E-3</v>
+        <v>7.4317397894708322E-3</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>158</v>
@@ -23885,7 +23970,7 @@
       </c>
       <c r="B3" s="5">
         <f>IF(B2="","",B2+SUM(单次交易!X2:X201))</f>
-        <v>161617.99999999997</v>
+        <v>154276.99999999997</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>166</v>
@@ -23908,7 +23993,7 @@
       </c>
       <c r="B5" s="5">
         <f>IF(B3="","",B3*B4)</f>
-        <v>3232.3599999999997</v>
+        <v>3085.5399999999995</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>170</v>
@@ -23931,7 +24016,7 @@
       </c>
       <c r="B7" s="5">
         <f>IF(B3="","",B3*B6)</f>
-        <v>9697.0799999999981</v>
+        <v>9256.6199999999972</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>174</v>
@@ -23967,7 +24052,7 @@
       </c>
       <c r="B10" s="5">
         <f>IF(OR(B7="",B9=""),"",B7-B9)</f>
-        <v>9697.0799999999981</v>
+        <v>9256.6199999999972</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>180</v>
@@ -23979,7 +24064,7 @@
       </c>
       <c r="B11" s="7">
         <f>IF(OR(B2="",B3="",B2&lt;=0),"",B3/B2-1)</f>
-        <v>0.61617999999999973</v>
+        <v>0.54276999999999975</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>182</v>
@@ -24037,7 +24122,7 @@
       </c>
       <c r="B2" s="5">
         <f>账户数据!B3</f>
-        <v>161617.99999999997</v>
+        <v>154276.99999999997</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>184</v>
@@ -24060,7 +24145,7 @@
       </c>
       <c r="B4" s="5">
         <f>IF(OR(B2="",B3=""),"",B2*B3)</f>
-        <v>16161.799999999997</v>
+        <v>15427.699999999997</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>188</v>
@@ -24072,7 +24157,7 @@
       </c>
       <c r="B5" s="5">
         <f>多次统计数据!B12</f>
-        <v>65740.722222222219</v>
+        <v>64948.067567567567</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>189</v>
@@ -24084,7 +24169,7 @@
       </c>
       <c r="B6" s="7">
         <f>多次统计数据!B13</f>
-        <v>8.2763036500419947E-3</v>
+        <v>7.4317397894708322E-3</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>191</v>
@@ -24096,7 +24181,7 @@
       </c>
       <c r="B7" s="8">
         <f>IF(OR(B3="",B6="",B3&lt;=0,B6&lt;=0),"暂不可计算",ROUNDUP(LN(1+B3)/LN(1+B6),0))</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>193</v>

--- a/交易管理系统.xlsx
+++ b/交易管理系统.xlsx
@@ -151,7 +151,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="300">
   <si>
     <t>交易编号</t>
   </si>
@@ -406,6 +406,12 @@
   </si>
   <si>
     <t>完美预测</t>
+  </si>
+  <si>
+    <t>保护了本金</t>
+  </si>
+  <si>
+    <t>不能建立假设要实时分析，还是要一个一个分析</t>
   </si>
   <si>
     <t>所属板块</t>
@@ -719,6 +725,15 @@
   </si>
   <si>
     <t>1.底部放量吸收了，昨天的是震仓，，连续两次试探了支撑，5.5左右支撑强力，6.5左右压力大，前面压力也大，可能要长期震仓，或者吸筹，上方交易量太大了，除非有更大的交易量过来，现在的交易量还是大，位这波不贪大，买一个反弹。不长期持有，因为上方供应天亮，除非看到特别多的需求</t>
+  </si>
+  <si>
+    <t>1.建立派发区间，至少要8～9块区间，CM盈利20%左右，2.继续吸筹拉升，单曲的同样的需求，没有造成比前面更高的涨幅,差10%但是供应少了一些，明显需求更旺盛，供应增大就会冲9～10，不足就是8～9，但是CM盈利更小，需要拿出更大的供应，吸引其它的CM与公众，拉伸，让人看到希望，让人狂热，如果更大额交易量出现就持有，没有的话，到达8左右就可以抛掉</t>
+  </si>
+  <si>
+    <t>1.供应站上方，上方没有供应，很容易就突破派发已经结束了，很奇怪上方为什么没有供应，按道理很多人被派发了，它们如果不卖，以后会成为供应，CM拉不上去，所以得让它们抛掉，所以解释之前并不是派发而是吸筹，之前是大震仓，都被吸收了，所以上方没有压力，那一定会突破之前的12.74拉到很大的位置已经没有供应了，继续往上不要贪，感受到大的压力就抛，但是除非CM派发，否则不会有抛盘基本都是盈利，散户不会抛，第一次供应，不要慌，看是否有供应吸收</t>
+  </si>
+  <si>
+    <t>1.我还是觉得当前可能是派发，但是不能假设，因为价格上来了，块接近20，而且没有特别大的波动2卖盘逐渐没有了，后面交易量上来就是突破20，入股没上来可能接下来就下跌了，如果遇到放量下跌就赶快跑，如果没遇到看到20，超过20把20作为支撑</t>
   </si>
   <si>
     <t>指标</t>
@@ -2433,7 +2448,7 @@
       </c>
       <c r="Z2" s="7">
         <f>IF(OR(AE2="",多次统计数据!$B$8=""),"",AE2-多次统计数据!$B$8)</f>
-        <v>-0.0985455440282548</v>
+        <v>-0.0998622441581622</v>
       </c>
       <c r="AA2" s="16">
         <f t="shared" ref="AA2:AA65" si="7">IF(OR(I2="",M2="",M2&lt;I2),"",M2-I2)</f>
@@ -2441,7 +2456,7 @@
       </c>
       <c r="AB2" s="7">
         <f>IF(OR(A2="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC2" s="8" t="str">
         <f>IF(OR(AB2="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB2,"低于上限","达到或超过上限"))</f>
@@ -2462,7 +2477,7 @@
       </c>
       <c r="C3" s="5">
         <f>IF(C2="","",C2+SUM(单次交易!Y2:Y201))</f>
-        <v>100002.926686518</v>
+        <v>100003.424182063</v>
       </c>
       <c r="D3" s="6">
         <v>0.02</v>
@@ -2528,7 +2543,7 @@
       </c>
       <c r="Z3" s="7">
         <f>IF(OR(AE3="",多次统计数据!$B$8=""),"",AE3-多次统计数据!$B$8)</f>
-        <v>-0.0892746095645987</v>
+        <v>-0.0905911508542663</v>
       </c>
       <c r="AA3" s="16">
         <f t="shared" si="7"/>
@@ -2536,7 +2551,7 @@
       </c>
       <c r="AB3" s="7">
         <f>IF(OR(A3="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC3" s="8" t="str">
         <f>IF(OR(AB3="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB3,"低于上限","达到或超过上限"))</f>
@@ -2545,7 +2560,7 @@
       <c r="AD3" s="2"/>
       <c r="AE3" s="7">
         <f t="shared" si="8"/>
-        <v>-0.0319290655363439</v>
+        <v>-0.031928906696104</v>
       </c>
     </row>
     <row r="4" ht="17" spans="1:32">
@@ -2626,7 +2641,7 @@
       </c>
       <c r="Z4" s="7">
         <f>IF(OR(AE4="",多次统计数据!$B$8=""),"",AE4-多次统计数据!$B$8)</f>
-        <v>0.0042812213217943</v>
+        <v>0.00296452119188684</v>
       </c>
       <c r="AA4" s="16">
         <f t="shared" si="7"/>
@@ -2634,7 +2649,7 @@
       </c>
       <c r="AB4" s="7">
         <f>IF(OR(A4="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC4" s="8" t="str">
         <f>IF(OR(AB4="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB4,"低于上限","达到或超过上限"))</f>
@@ -2724,7 +2739,7 @@
       </c>
       <c r="Z5" s="7">
         <f>IF(OR(AE5="",多次统计数据!$B$8=""),"",AE5-多次统计数据!$B$8)</f>
-        <v>-0.0852929825184833</v>
+        <v>-0.0866096826483908</v>
       </c>
       <c r="AA5" s="16">
         <f t="shared" si="7"/>
@@ -2732,7 +2747,7 @@
       </c>
       <c r="AB5" s="7">
         <f>IF(OR(A5="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC5" s="8" t="str">
         <f>IF(OR(AB5="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB5,"低于上限","达到或超过上限"))</f>
@@ -2822,7 +2837,7 @@
       </c>
       <c r="Z6" s="7">
         <f>IF(OR(AE6="",多次统计数据!$B$8=""),"",AE6-多次统计数据!$B$8)</f>
-        <v>-0.0870792579196703</v>
+        <v>-0.0883959580495777</v>
       </c>
       <c r="AA6" s="16">
         <f t="shared" si="7"/>
@@ -2830,7 +2845,7 @@
       </c>
       <c r="AB6" s="7">
         <f>IF(OR(A6="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC6" s="8" t="str">
         <f>IF(OR(AB6="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB6,"低于上限","达到或超过上限"))</f>
@@ -2916,7 +2931,7 @@
       </c>
       <c r="Z7" s="7">
         <f>IF(OR(AE7="",多次统计数据!$B$8=""),"",AE7-多次统计数据!$B$8)</f>
-        <v>-0.0964598158886071</v>
+        <v>-0.0977765160185146</v>
       </c>
       <c r="AA7" s="16">
         <f t="shared" si="7"/>
@@ -2924,7 +2939,7 @@
       </c>
       <c r="AB7" s="7">
         <f>IF(OR(A7="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC7" s="8" t="str">
         <f>IF(OR(AB7="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB7,"低于上限","达到或超过上限"))</f>
@@ -3158,7 +3173,7 @@
       </c>
       <c r="Z10" s="7">
         <f>IF(OR(AE10="",多次统计数据!$B$8=""),"",AE10-多次统计数据!$B$8)</f>
-        <v>0.0773558857446636</v>
+        <v>0.0760391856147562</v>
       </c>
       <c r="AA10" s="16">
         <f t="shared" si="7"/>
@@ -3166,7 +3181,7 @@
       </c>
       <c r="AB10" s="7">
         <f>IF(OR(A10="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC10" s="8" t="str">
         <f>IF(OR(AB10="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB10,"低于上限","达到或超过上限"))</f>
@@ -3252,7 +3267,7 @@
       </c>
       <c r="Z11" s="7">
         <f>IF(OR(AE11="",多次统计数据!$B$8=""),"",AE11-多次统计数据!$B$8)</f>
-        <v>-0.0790479366280947</v>
+        <v>-0.0803646367580022</v>
       </c>
       <c r="AA11" s="16">
         <f t="shared" si="7"/>
@@ -3260,7 +3275,7 @@
       </c>
       <c r="AB11" s="7">
         <f>IF(OR(A11="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC11" s="8" t="str">
         <f>IF(OR(AB11="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB11,"低于上限","达到或超过上限"))</f>
@@ -3350,7 +3365,7 @@
       </c>
       <c r="Z12" s="7">
         <f>IF(OR(AE12="",多次统计数据!$B$8=""),"",AE12-多次统计数据!$B$8)</f>
-        <v>-0.0504560288198015</v>
+        <v>-0.051772728949709</v>
       </c>
       <c r="AA12" s="16">
         <f t="shared" si="7"/>
@@ -3358,7 +3373,7 @@
       </c>
       <c r="AB12" s="7">
         <f>IF(OR(A12="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC12" s="8" t="str">
         <f>IF(OR(AB12="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB12,"低于上限","达到或超过上限"))</f>
@@ -3448,7 +3463,7 @@
       </c>
       <c r="Z13" s="7">
         <f>IF(OR(AE13="",多次统计数据!$B$8=""),"",AE13-多次统计数据!$B$8)</f>
-        <v>-0.0756654501211786</v>
+        <v>-0.0769821502510861</v>
       </c>
       <c r="AA13" s="16">
         <f t="shared" si="7"/>
@@ -3456,7 +3471,7 @@
       </c>
       <c r="AB13" s="7">
         <f>IF(OR(A13="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC13" s="8" t="str">
         <f>IF(OR(AB13="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB13,"低于上限","达到或超过上限"))</f>
@@ -3546,7 +3561,7 @@
       </c>
       <c r="Z14" s="7">
         <f>IF(OR(AE14="",多次统计数据!$B$8=""),"",AE14-多次统计数据!$B$8)</f>
-        <v>-0.0477795890168594</v>
+        <v>-0.0490962891467669</v>
       </c>
       <c r="AA14" s="16">
         <f t="shared" si="7"/>
@@ -3554,7 +3569,7 @@
       </c>
       <c r="AB14" s="7">
         <f>IF(OR(A14="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC14" s="8" t="str">
         <f>IF(OR(AB14="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB14,"低于上限","达到或超过上限"))</f>
@@ -3640,7 +3655,7 @@
       </c>
       <c r="Z15" s="7">
         <f>IF(OR(AE15="",多次统计数据!$B$8=""),"",AE15-多次统计数据!$B$8)</f>
-        <v>0.00794909168841711</v>
+        <v>0.00663239155850964</v>
       </c>
       <c r="AA15" s="16">
         <f t="shared" si="7"/>
@@ -3648,7 +3663,7 @@
       </c>
       <c r="AB15" s="7">
         <f>IF(OR(A15="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC15" s="8" t="str">
         <f>IF(OR(AB15="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB15,"低于上限","达到或超过上限"))</f>
@@ -3734,7 +3749,7 @@
       </c>
       <c r="Z16" s="7">
         <f>IF(OR(AE16="",多次统计数据!$B$8=""),"",AE16-多次统计数据!$B$8)</f>
-        <v>-0.0744504445822635</v>
+        <v>-0.075767144712171</v>
       </c>
       <c r="AA16" s="16">
         <f t="shared" si="7"/>
@@ -3742,7 +3757,7 @@
       </c>
       <c r="AB16" s="7">
         <f>IF(OR(A16="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC16" s="8" t="str">
         <f>IF(OR(AB16="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB16,"低于上限","达到或超过上限"))</f>
@@ -3828,7 +3843,7 @@
       </c>
       <c r="Z17" s="7">
         <f>IF(OR(AE17="",多次统计数据!$B$8=""),"",AE17-多次统计数据!$B$8)</f>
-        <v>-0.0483542163088616</v>
+        <v>-0.049670916438769</v>
       </c>
       <c r="AA17" s="16">
         <f t="shared" si="7"/>
@@ -3836,7 +3851,7 @@
       </c>
       <c r="AB17" s="7">
         <f>IF(OR(A17="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC17" s="8" t="str">
         <f>IF(OR(AB17="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB17,"低于上限","达到或超过上限"))</f>
@@ -3922,7 +3937,7 @@
       </c>
       <c r="Z18" s="7">
         <f>IF(OR(AE18="",多次统计数据!$B$8=""),"",AE18-多次统计数据!$B$8)</f>
-        <v>0.0245792576274886</v>
+        <v>0.0232625574975811</v>
       </c>
       <c r="AA18" s="16">
         <f t="shared" si="7"/>
@@ -3930,7 +3945,7 @@
       </c>
       <c r="AB18" s="7">
         <f>IF(OR(A18="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC18" s="8" t="str">
         <f>IF(OR(AB18="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB18,"低于上限","达到或超过上限"))</f>
@@ -4016,7 +4031,7 @@
       </c>
       <c r="Z19" s="7">
         <f>IF(OR(AE19="",多次统计数据!$B$8=""),"",AE19-多次统计数据!$B$8)</f>
-        <v>-0.0786008467834734</v>
+        <v>-0.0799175469133809</v>
       </c>
       <c r="AA19" s="16">
         <f t="shared" si="7"/>
@@ -4024,7 +4039,7 @@
       </c>
       <c r="AB19" s="7">
         <f>IF(OR(A19="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC19" s="8" t="str">
         <f>IF(OR(AB19="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB19,"低于上限","达到或超过上限"))</f>
@@ -4110,7 +4125,7 @@
       </c>
       <c r="Z20" s="7">
         <f>IF(OR(AE20="",多次统计数据!$B$8=""),"",AE20-多次统计数据!$B$8)</f>
-        <v>-0.0402434836371696</v>
+        <v>-0.041560183767077</v>
       </c>
       <c r="AA20" s="16">
         <f t="shared" si="7"/>
@@ -4118,7 +4133,7 @@
       </c>
       <c r="AB20" s="7">
         <f>IF(OR(A20="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC20" s="8" t="str">
         <f>IF(OR(AB20="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB20,"低于上限","达到或超过上限"))</f>
@@ -4204,7 +4219,7 @@
       </c>
       <c r="Z21" s="7">
         <f>IF(OR(AE21="",多次统计数据!$B$8=""),"",AE21-多次统计数据!$B$8)</f>
-        <v>0.124500136247183</v>
+        <v>0.123183436117275</v>
       </c>
       <c r="AA21" s="16">
         <f t="shared" si="7"/>
@@ -4212,7 +4227,7 @@
       </c>
       <c r="AB21" s="7">
         <f>IF(OR(A21="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC21" s="8" t="str">
         <f>IF(OR(AB21="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB21,"低于上限","达到或超过上限"))</f>
@@ -4298,7 +4313,7 @@
       </c>
       <c r="Z22" s="7">
         <f>IF(OR(AE22="",多次统计数据!$B$8=""),"",AE22-多次统计数据!$B$8)</f>
-        <v>-0.0895263890859545</v>
+        <v>-0.0908430892158619</v>
       </c>
       <c r="AA22" s="16">
         <f t="shared" si="7"/>
@@ -4306,7 +4321,7 @@
       </c>
       <c r="AB22" s="7">
         <f>IF(OR(A22="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC22" s="8" t="str">
         <f>IF(OR(AB22="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB22,"低于上限","达到或超过上限"))</f>
@@ -4392,7 +4407,7 @@
       </c>
       <c r="Z23" s="7">
         <f>IF(OR(AE23="",多次统计数据!$B$8=""),"",AE23-多次统计数据!$B$8)</f>
-        <v>-0.0775683055241169</v>
+        <v>-0.0788850056540244</v>
       </c>
       <c r="AA23" s="16">
         <f t="shared" si="7"/>
@@ -4400,7 +4415,7 @@
       </c>
       <c r="AB23" s="7">
         <f>IF(OR(A23="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC23" s="8" t="str">
         <f>IF(OR(AB23="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB23,"低于上限","达到或超过上限"))</f>
@@ -4486,7 +4501,7 @@
       </c>
       <c r="Z24" s="7">
         <f>IF(OR(AE24="",多次统计数据!$B$8=""),"",AE24-多次统计数据!$B$8)</f>
-        <v>-0.00606267853860662</v>
+        <v>-0.00737937866851408</v>
       </c>
       <c r="AA24" s="16">
         <f t="shared" si="7"/>
@@ -4494,7 +4509,7 @@
       </c>
       <c r="AB24" s="7">
         <f>IF(OR(A24="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC24" s="8" t="str">
         <f>IF(OR(AB24="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB24,"低于上限","达到或超过上限"))</f>
@@ -4580,7 +4595,7 @@
       </c>
       <c r="Z25" s="7">
         <f>IF(OR(AE25="",多次统计数据!$B$8=""),"",AE25-多次统计数据!$B$8)</f>
-        <v>-0.0816077846420223</v>
+        <v>-0.0829244847719297</v>
       </c>
       <c r="AA25" s="16">
         <f t="shared" si="7"/>
@@ -4588,7 +4603,7 @@
       </c>
       <c r="AB25" s="7">
         <f>IF(OR(A25="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC25" s="8" t="str">
         <f>IF(OR(AB25="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB25,"低于上限","达到或超过上限"))</f>
@@ -4674,7 +4689,7 @@
       </c>
       <c r="Z26" s="7">
         <f>IF(OR(AE26="",多次统计数据!$B$8=""),"",AE26-多次统计数据!$B$8)</f>
-        <v>0.0694199243771161</v>
+        <v>0.0681032242472086</v>
       </c>
       <c r="AA26" s="16">
         <f t="shared" si="7"/>
@@ -4682,7 +4697,7 @@
       </c>
       <c r="AB26" s="7">
         <f>IF(OR(A26="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC26" s="8" t="str">
         <f>IF(OR(AB26="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB26,"低于上限","达到或超过上限"))</f>
@@ -4768,7 +4783,7 @@
       </c>
       <c r="Z27" s="7">
         <f>IF(OR(AE27="",多次统计数据!$B$8=""),"",AE27-多次统计数据!$B$8)</f>
-        <v>0.00979275055603726</v>
+        <v>0.0084760504261298</v>
       </c>
       <c r="AA27" s="16">
         <f t="shared" si="7"/>
@@ -4776,7 +4791,7 @@
       </c>
       <c r="AB27" s="7">
         <f>IF(OR(A27="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC27" s="8" t="str">
         <f>IF(OR(AB27="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB27,"低于上限","达到或超过上限"))</f>
@@ -4862,7 +4877,7 @@
       </c>
       <c r="Z28" s="7">
         <f>IF(OR(AE28="",多次统计数据!$B$8=""),"",AE28-多次统计数据!$B$8)</f>
-        <v>-0.0487145341807939</v>
+        <v>-0.0500312343107013</v>
       </c>
       <c r="AA28" s="16">
         <f t="shared" si="7"/>
@@ -4870,7 +4885,7 @@
       </c>
       <c r="AB28" s="7">
         <f>IF(OR(A28="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC28" s="8" t="str">
         <f>IF(OR(AB28="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB28,"低于上限","达到或超过上限"))</f>
@@ -4956,7 +4971,7 @@
       </c>
       <c r="Z29" s="7">
         <f>IF(OR(AE29="",多次统计数据!$B$8=""),"",AE29-多次统计数据!$B$8)</f>
-        <v>-0.0896342793435805</v>
+        <v>-0.0909509794734879</v>
       </c>
       <c r="AA29" s="16">
         <f t="shared" si="7"/>
@@ -4964,7 +4979,7 @@
       </c>
       <c r="AB29" s="7">
         <f>IF(OR(A29="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC29" s="8" t="str">
         <f>IF(OR(AB29="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB29,"低于上限","达到或超过上限"))</f>
@@ -5050,7 +5065,7 @@
       </c>
       <c r="Z30" s="7">
         <f>IF(OR(AE30="",多次统计数据!$B$8=""),"",AE30-多次统计数据!$B$8)</f>
-        <v>-0.0798709477512767</v>
+        <v>-0.0811876478811842</v>
       </c>
       <c r="AA30" s="16">
         <f t="shared" si="7"/>
@@ -5058,7 +5073,7 @@
       </c>
       <c r="AB30" s="7">
         <f>IF(OR(A30="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC30" s="8" t="str">
         <f>IF(OR(AB30="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB30,"低于上限","达到或超过上限"))</f>
@@ -5144,7 +5159,7 @@
       </c>
       <c r="Z31" s="7">
         <f>IF(OR(AE31="",多次统计数据!$B$8=""),"",AE31-多次统计数据!$B$8)</f>
-        <v>-0.119260746240958</v>
+        <v>-0.120577446370865</v>
       </c>
       <c r="AA31" s="16">
         <f t="shared" si="7"/>
@@ -5152,7 +5167,7 @@
       </c>
       <c r="AB31" s="7">
         <f>IF(OR(A31="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC31" s="8" t="str">
         <f>IF(OR(AB31="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB31,"低于上限","达到或超过上限"))</f>
@@ -5241,7 +5256,7 @@
       </c>
       <c r="Z32" s="7">
         <f>IF(OR(AE32="",多次统计数据!$B$8=""),"",AE32-多次统计数据!$B$8)</f>
-        <v>-0.0790920220912074</v>
+        <v>-0.0804087222211149</v>
       </c>
       <c r="AA32" s="16">
         <f t="shared" si="7"/>
@@ -5249,7 +5264,7 @@
       </c>
       <c r="AB32" s="7">
         <f>IF(OR(A32="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC32" s="8" t="str">
         <f>IF(OR(AB32="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB32,"低于上限","达到或超过上限"))</f>
@@ -5335,7 +5350,7 @@
       </c>
       <c r="Z33" s="7">
         <f>IF(OR(AE33="",多次统计数据!$B$8=""),"",AE33-多次统计数据!$B$8)</f>
-        <v>-0.0893377812059984</v>
+        <v>-0.0906544813359059</v>
       </c>
       <c r="AA33" s="16">
         <f t="shared" si="7"/>
@@ -5343,7 +5358,7 @@
       </c>
       <c r="AB33" s="7">
         <f>IF(OR(A33="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC33" s="8" t="str">
         <f>IF(OR(AB33="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB33,"低于上限","达到或超过上限"))</f>
@@ -5429,7 +5444,7 @@
       </c>
       <c r="Z34" s="7">
         <f>IF(OR(AE34="",多次统计数据!$B$8=""),"",AE34-多次统计数据!$B$8)</f>
-        <v>-0.0794595923723591</v>
+        <v>-0.0807762925022666</v>
       </c>
       <c r="AA34" s="16">
         <f t="shared" si="7"/>
@@ -5437,7 +5452,7 @@
       </c>
       <c r="AB34" s="7">
         <f>IF(OR(A34="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC34" s="8" t="str">
         <f>IF(OR(AB34="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB34,"低于上限","达到或超过上限"))</f>
@@ -5523,7 +5538,7 @@
       </c>
       <c r="Z35" s="7">
         <f>IF(OR(AE35="",多次统计数据!$B$8=""),"",AE35-多次统计数据!$B$8)</f>
-        <v>-0.0477780238953035</v>
+        <v>-0.049094724025211</v>
       </c>
       <c r="AA35" s="16">
         <f t="shared" si="7"/>
@@ -5531,7 +5546,7 @@
       </c>
       <c r="AB35" s="7">
         <f>IF(OR(A35="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC35" s="8" t="str">
         <f>IF(OR(AB35="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB35,"低于上限","达到或超过上限"))</f>
@@ -5617,7 +5632,7 @@
       </c>
       <c r="Z36" s="7">
         <f>IF(OR(AE36="",多次统计数据!$B$8=""),"",AE36-多次统计数据!$B$8)</f>
-        <v>0.0169308076921165</v>
+        <v>0.0156141075622091</v>
       </c>
       <c r="AA36" s="16">
         <f t="shared" si="7"/>
@@ -5625,7 +5640,7 @@
       </c>
       <c r="AB36" s="7">
         <f>IF(OR(A36="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC36" s="8" t="str">
         <f>IF(OR(AB36="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB36,"低于上限","达到或超过上限"))</f>
@@ -5711,7 +5726,7 @@
       </c>
       <c r="Z37" s="7">
         <f>IF(OR(AE37="",多次统计数据!$B$8=""),"",AE37-多次统计数据!$B$8)</f>
-        <v>-0.0875910741484779</v>
+        <v>-0.0889077742783854</v>
       </c>
       <c r="AA37" s="16">
         <f t="shared" si="7"/>
@@ -5719,7 +5734,7 @@
       </c>
       <c r="AB37" s="7">
         <f>IF(OR(A37="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC37" s="8" t="str">
         <f>IF(OR(AB37="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB37,"低于上限","达到或超过上限"))</f>
@@ -5805,7 +5820,7 @@
       </c>
       <c r="Z38" s="7">
         <f>IF(OR(AE38="",多次统计数据!$B$8=""),"",AE38-多次统计数据!$B$8)</f>
-        <v>-0.11077417663626</v>
+        <v>-0.112090876766168</v>
       </c>
       <c r="AA38" s="16">
         <f t="shared" si="7"/>
@@ -5813,7 +5828,7 @@
       </c>
       <c r="AB38" s="7">
         <f>IF(OR(A38="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC38" s="8" t="str">
         <f>IF(OR(AB38="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB38,"低于上限","达到或超过上限"))</f>
@@ -5902,7 +5917,7 @@
       </c>
       <c r="Z39" s="7">
         <f>IF(OR(AE39="",多次统计数据!$B$8=""),"",AE39-多次统计数据!$B$8)</f>
-        <v>-0.10845438432873</v>
+        <v>-0.109771084458637</v>
       </c>
       <c r="AA39" s="16">
         <f t="shared" si="7"/>
@@ -5910,7 +5925,7 @@
       </c>
       <c r="AB39" s="7">
         <f>IF(OR(A39="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC39" s="8" t="str">
         <f>IF(OR(AB39="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB39,"低于上限","达到或超过上限"))</f>
@@ -5996,7 +6011,7 @@
       </c>
       <c r="Z40" s="7">
         <f>IF(OR(AE40="",多次统计数据!$B$8=""),"",AE40-多次统计数据!$B$8)</f>
-        <v>-0.0898992864755399</v>
+        <v>-0.0912159866054473</v>
       </c>
       <c r="AA40" s="16">
         <f t="shared" si="7"/>
@@ -6004,7 +6019,7 @@
       </c>
       <c r="AB40" s="7">
         <f>IF(OR(A40="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC40" s="8" t="str">
         <f>IF(OR(AB40="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB40,"低于上限","达到或超过上限"))</f>
@@ -6090,7 +6105,7 @@
       </c>
       <c r="Z41" s="7">
         <f>IF(OR(AE41="",多次统计数据!$B$8=""),"",AE41-多次统计数据!$B$8)</f>
-        <v>-0.0818176517735069</v>
+        <v>-0.0831343519034144</v>
       </c>
       <c r="AA41" s="16">
         <f t="shared" si="7"/>
@@ -6098,7 +6113,7 @@
       </c>
       <c r="AB41" s="7">
         <f>IF(OR(A41="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC41" s="8" t="str">
         <f>IF(OR(AB41="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB41,"低于上限","达到或超过上限"))</f>
@@ -6184,7 +6199,7 @@
       </c>
       <c r="Z42" s="7">
         <f>IF(OR(AE42="",多次统计数据!$B$8=""),"",AE42-多次统计数据!$B$8)</f>
-        <v>-0.0855673113728826</v>
+        <v>-0.0868840115027901</v>
       </c>
       <c r="AA42" s="16">
         <f t="shared" si="7"/>
@@ -6192,7 +6207,7 @@
       </c>
       <c r="AB42" s="7">
         <f>IF(OR(A42="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC42" s="8" t="str">
         <f>IF(OR(AB42="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB42,"低于上限","达到或超过上限"))</f>
@@ -6278,7 +6293,7 @@
       </c>
       <c r="Z43" s="7">
         <f>IF(OR(AE43="",多次统计数据!$B$8=""),"",AE43-多次统计数据!$B$8)</f>
-        <v>-0.0925447552504123</v>
+        <v>-0.0938614553803197</v>
       </c>
       <c r="AA43" s="16">
         <f t="shared" si="7"/>
@@ -6286,7 +6301,7 @@
       </c>
       <c r="AB43" s="7">
         <f>IF(OR(A43="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC43" s="8" t="str">
         <f>IF(OR(AB43="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB43,"低于上限","达到或超过上限"))</f>
@@ -6372,7 +6387,7 @@
       </c>
       <c r="Z44" s="7">
         <f>IF(OR(AE44="",多次统计数据!$B$8=""),"",AE44-多次统计数据!$B$8)</f>
-        <v>-0.00210482978235649</v>
+        <v>-0.00342152991226396</v>
       </c>
       <c r="AA44" s="16">
         <f t="shared" si="7"/>
@@ -6380,7 +6395,7 @@
       </c>
       <c r="AB44" s="7">
         <f>IF(OR(A44="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC44" s="8" t="str">
         <f>IF(OR(AB44="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB44,"低于上限","达到或超过上限"))</f>
@@ -6466,7 +6481,7 @@
       </c>
       <c r="Z45" s="7">
         <f>IF(OR(AE45="",多次统计数据!$B$8=""),"",AE45-多次统计数据!$B$8)</f>
-        <v>-0.0165739564807129</v>
+        <v>-0.0178906566106203</v>
       </c>
       <c r="AA45" s="16">
         <f t="shared" si="7"/>
@@ -6474,7 +6489,7 @@
       </c>
       <c r="AB45" s="7">
         <f>IF(OR(A45="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC45" s="8" t="str">
         <f>IF(OR(AB45="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB45,"低于上限","达到或超过上限"))</f>
@@ -6560,7 +6575,7 @@
       </c>
       <c r="Z46" s="7">
         <f>IF(OR(AE46="",多次统计数据!$B$8=""),"",AE46-多次统计数据!$B$8)</f>
-        <v>-0.101553131897814</v>
+        <v>-0.102869832027722</v>
       </c>
       <c r="AA46" s="16">
         <f t="shared" si="7"/>
@@ -6568,7 +6583,7 @@
       </c>
       <c r="AB46" s="7">
         <f>IF(OR(A46="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC46" s="8" t="str">
         <f>IF(OR(AB46="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB46,"低于上限","达到或超过上限"))</f>
@@ -6654,7 +6669,7 @@
       </c>
       <c r="Z47" s="7">
         <f>IF(OR(AE47="",多次统计数据!$B$8=""),"",AE47-多次统计数据!$B$8)</f>
-        <v>-0.100358580695541</v>
+        <v>-0.101675280825448</v>
       </c>
       <c r="AA47" s="16">
         <f t="shared" si="7"/>
@@ -6662,7 +6677,7 @@
       </c>
       <c r="AB47" s="7">
         <f>IF(OR(A47="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC47" s="8" t="str">
         <f>IF(OR(AB47="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB47,"低于上限","达到或超过上限"))</f>
@@ -6751,7 +6766,7 @@
       </c>
       <c r="Z48" s="7">
         <f>IF(OR(AE48="",多次统计数据!$B$8=""),"",AE48-多次统计数据!$B$8)</f>
-        <v>0.00104767148284769</v>
+        <v>-0.000269028647059771</v>
       </c>
       <c r="AA48" s="16">
         <f t="shared" si="7"/>
@@ -6759,7 +6774,7 @@
       </c>
       <c r="AB48" s="7">
         <f>IF(OR(A48="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC48" s="8" t="str">
         <f>IF(OR(AB48="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB48,"低于上限","达到或超过上限"))</f>
@@ -6845,7 +6860,7 @@
       </c>
       <c r="Z49" s="7">
         <f>IF(OR(AE49="",多次统计数据!$B$8=""),"",AE49-多次统计数据!$B$8)</f>
-        <v>-0.10885169515484</v>
+        <v>-0.110168395284747</v>
       </c>
       <c r="AA49" s="16">
         <f t="shared" si="7"/>
@@ -6853,7 +6868,7 @@
       </c>
       <c r="AB49" s="7">
         <f>IF(OR(A49="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC49" s="8" t="str">
         <f>IF(OR(AB49="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB49,"低于上限","达到或超过上限"))</f>
@@ -6942,7 +6957,7 @@
       </c>
       <c r="Z50" s="7">
         <f>IF(OR(AE50="",多次统计数据!$B$8=""),"",AE50-多次统计数据!$B$8)</f>
-        <v>-0.0881839251741006</v>
+        <v>-0.089500625304008</v>
       </c>
       <c r="AA50" s="16">
         <f t="shared" si="7"/>
@@ -6950,7 +6965,7 @@
       </c>
       <c r="AB50" s="7">
         <f>IF(OR(A50="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC50" s="8" t="str">
         <f>IF(OR(AB50="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB50,"低于上限","达到或超过上限"))</f>
@@ -7039,7 +7054,7 @@
       </c>
       <c r="Z51" s="7">
         <f>IF(OR(AE51="",多次统计数据!$B$8=""),"",AE51-多次统计数据!$B$8)</f>
-        <v>0.187936758435959</v>
+        <v>0.186620058306052</v>
       </c>
       <c r="AA51" s="16">
         <f t="shared" si="7"/>
@@ -7047,7 +7062,7 @@
       </c>
       <c r="AB51" s="7">
         <f>IF(OR(A51="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC51" s="8" t="str">
         <f>IF(OR(AB51="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB51,"低于上限","达到或超过上限"))</f>
@@ -7133,7 +7148,7 @@
       </c>
       <c r="Z52" s="7">
         <f>IF(OR(AE52="",多次统计数据!$B$8=""),"",AE52-多次统计数据!$B$8)</f>
-        <v>0.117411293487372</v>
+        <v>0.116094593357464</v>
       </c>
       <c r="AA52" s="16">
         <f t="shared" si="7"/>
@@ -7141,7 +7156,7 @@
       </c>
       <c r="AB52" s="7">
         <f>IF(OR(A52="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC52" s="8" t="str">
         <f>IF(OR(AB52="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB52,"低于上限","达到或超过上限"))</f>
@@ -7227,7 +7242,7 @@
       </c>
       <c r="Z53" s="7">
         <f>IF(OR(AE53="",多次统计数据!$B$8=""),"",AE53-多次统计数据!$B$8)</f>
-        <v>-0.0783689422918778</v>
+        <v>-0.0796856424217853</v>
       </c>
       <c r="AA53" s="16">
         <f t="shared" si="7"/>
@@ -7235,7 +7250,7 @@
       </c>
       <c r="AB53" s="7">
         <f>IF(OR(A53="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC53" s="8" t="str">
         <f>IF(OR(AB53="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB53,"低于上限","达到或超过上限"))</f>
@@ -7321,7 +7336,7 @@
       </c>
       <c r="Z54" s="7">
         <f>IF(OR(AE54="",多次统计数据!$B$8=""),"",AE54-多次统计数据!$B$8)</f>
-        <v>-0.0347571590182464</v>
+        <v>-0.0360738591481539</v>
       </c>
       <c r="AA54" s="16">
         <f t="shared" si="7"/>
@@ -7329,7 +7344,7 @@
       </c>
       <c r="AB54" s="7">
         <f>IF(OR(A54="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC54" s="8" t="str">
         <f>IF(OR(AB54="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB54,"低于上限","达到或超过上限"))</f>
@@ -7415,7 +7430,7 @@
       </c>
       <c r="Z55" s="7">
         <f>IF(OR(AE55="",多次统计数据!$B$8=""),"",AE55-多次统计数据!$B$8)</f>
-        <v>-0.0269272191426557</v>
+        <v>-0.0282439192725632</v>
       </c>
       <c r="AA55" s="16">
         <f t="shared" si="7"/>
@@ -7423,7 +7438,7 @@
       </c>
       <c r="AB55" s="7">
         <f>IF(OR(A55="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC55" s="8" t="str">
         <f>IF(OR(AB55="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB55,"低于上限","达到或超过上限"))</f>
@@ -7509,7 +7524,7 @@
       </c>
       <c r="Z56" s="7">
         <f>IF(OR(AE56="",多次统计数据!$B$8=""),"",AE56-多次统计数据!$B$8)</f>
-        <v>-0.0685422730737022</v>
+        <v>-0.0698589732036096</v>
       </c>
       <c r="AA56" s="16">
         <f t="shared" si="7"/>
@@ -7517,7 +7532,7 @@
       </c>
       <c r="AB56" s="7">
         <f>IF(OR(A56="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC56" s="8" t="str">
         <f>IF(OR(AB56="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB56,"低于上限","达到或超过上限"))</f>
@@ -7603,7 +7618,7 @@
       </c>
       <c r="Z57" s="7">
         <f>IF(OR(AE57="",多次统计数据!$B$8=""),"",AE57-多次统计数据!$B$8)</f>
-        <v>-0.0280189115017749</v>
+        <v>-0.0293356116316824</v>
       </c>
       <c r="AA57" s="16">
         <f t="shared" si="7"/>
@@ -7611,7 +7626,7 @@
       </c>
       <c r="AB57" s="7">
         <f>IF(OR(A57="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC57" s="8" t="str">
         <f>IF(OR(AB57="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB57,"低于上限","达到或超过上限"))</f>
@@ -7697,7 +7712,7 @@
       </c>
       <c r="Z58" s="7">
         <f>IF(OR(AE58="",多次统计数据!$B$8=""),"",AE58-多次统计数据!$B$8)</f>
-        <v>-0.0232304054355043</v>
+        <v>-0.0245471055654117</v>
       </c>
       <c r="AA58" s="16">
         <f t="shared" si="7"/>
@@ -7705,7 +7720,7 @@
       </c>
       <c r="AB58" s="7">
         <f>IF(OR(A58="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC58" s="8" t="str">
         <f>IF(OR(AB58="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB58,"低于上限","达到或超过上限"))</f>
@@ -7791,7 +7806,7 @@
       </c>
       <c r="Z59" s="7">
         <f>IF(OR(AE59="",多次统计数据!$B$8=""),"",AE59-多次统计数据!$B$8)</f>
-        <v>-0.0537597080802494</v>
+        <v>-0.0550764082101569</v>
       </c>
       <c r="AA59" s="16">
         <f t="shared" si="7"/>
@@ -7799,7 +7814,7 @@
       </c>
       <c r="AB59" s="7">
         <f>IF(OR(A59="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC59" s="8" t="str">
         <f>IF(OR(AB59="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB59,"低于上限","达到或超过上限"))</f>
@@ -7885,7 +7900,7 @@
       </c>
       <c r="Z60" s="7">
         <f>IF(OR(AE60="",多次统计数据!$B$8=""),"",AE60-多次统计数据!$B$8)</f>
-        <v>-0.0408619948247413</v>
+        <v>-0.0421786949546488</v>
       </c>
       <c r="AA60" s="16">
         <f t="shared" si="7"/>
@@ -7893,7 +7908,7 @@
       </c>
       <c r="AB60" s="7">
         <f>IF(OR(A60="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC60" s="8" t="str">
         <f>IF(OR(AB60="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB60,"低于上限","达到或超过上限"))</f>
@@ -7979,7 +7994,7 @@
       </c>
       <c r="Z61" s="7">
         <f>IF(OR(AE61="",多次统计数据!$B$8=""),"",AE61-多次统计数据!$B$8)</f>
-        <v>-0.0627939221105429</v>
+        <v>-0.0641106222404504</v>
       </c>
       <c r="AA61" s="16">
         <f t="shared" si="7"/>
@@ -7987,7 +8002,7 @@
       </c>
       <c r="AB61" s="7">
         <f>IF(OR(A61="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC61" s="8" t="str">
         <f>IF(OR(AB61="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB61,"低于上限","达到或超过上限"))</f>
@@ -8073,7 +8088,7 @@
       </c>
       <c r="Z62" s="7">
         <f>IF(OR(AE62="",多次统计数据!$B$8=""),"",AE62-多次统计数据!$B$8)</f>
-        <v>-0.0804012157588439</v>
+        <v>-0.0817179158887514</v>
       </c>
       <c r="AA62" s="16">
         <f t="shared" si="7"/>
@@ -8081,7 +8096,7 @@
       </c>
       <c r="AB62" s="7">
         <f>IF(OR(A62="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC62" s="8" t="str">
         <f>IF(OR(AB62="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB62,"低于上限","达到或超过上限"))</f>
@@ -8170,7 +8185,7 @@
       </c>
       <c r="Z63" s="7">
         <f>IF(OR(AE63="",多次统计数据!$B$8=""),"",AE63-多次统计数据!$B$8)</f>
-        <v>-0.072009485324253</v>
+        <v>-0.0733261854541604</v>
       </c>
       <c r="AA63" s="16">
         <f t="shared" si="7"/>
@@ -8178,7 +8193,7 @@
       </c>
       <c r="AB63" s="7">
         <f>IF(OR(A63="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC63" s="8" t="str">
         <f>IF(OR(AB63="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB63,"低于上限","达到或超过上限"))</f>
@@ -8264,7 +8279,7 @@
       </c>
       <c r="Z64" s="7">
         <f>IF(OR(AE64="",多次统计数据!$B$8=""),"",AE64-多次统计数据!$B$8)</f>
-        <v>0.00326014571026691</v>
+        <v>0.00194344558035945</v>
       </c>
       <c r="AA64" s="16">
         <f t="shared" si="7"/>
@@ -8272,7 +8287,7 @@
       </c>
       <c r="AB64" s="7">
         <f>IF(OR(A64="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC64" s="8" t="str">
         <f>IF(OR(AB64="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB64,"低于上限","达到或超过上限"))</f>
@@ -8358,7 +8373,7 @@
       </c>
       <c r="Z65" s="7">
         <f>IF(OR(AE65="",多次统计数据!$B$8=""),"",AE65-多次统计数据!$B$8)</f>
-        <v>-0.0381153295706876</v>
+        <v>-0.0394320297005951</v>
       </c>
       <c r="AA65" s="16">
         <f t="shared" si="7"/>
@@ -8366,7 +8381,7 @@
       </c>
       <c r="AB65" s="7">
         <f>IF(OR(A65="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC65" s="8" t="str">
         <f>IF(OR(AB65="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB65,"低于上限","达到或超过上限"))</f>
@@ -8452,7 +8467,7 @@
       </c>
       <c r="Z66" s="7">
         <f>IF(OR(AE66="",多次统计数据!$B$8=""),"",AE66-多次统计数据!$B$8)</f>
-        <v>-0.036638398987667</v>
+        <v>-0.0379550991175744</v>
       </c>
       <c r="AA66" s="16">
         <f t="shared" ref="AA66:AA129" si="16">IF(OR(I66="",M66="",M66&lt;I66),"",M66-I66)</f>
@@ -8460,7 +8475,7 @@
       </c>
       <c r="AB66" s="7">
         <f>IF(OR(A66="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC66" s="8" t="str">
         <f>IF(OR(AB66="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB66,"低于上限","达到或超过上限"))</f>
@@ -8546,7 +8561,7 @@
       </c>
       <c r="Z67" s="7">
         <f>IF(OR(AE67="",多次统计数据!$B$8=""),"",AE67-多次统计数据!$B$8)</f>
-        <v>0.00255063592649032</v>
+        <v>0.00123393579658286</v>
       </c>
       <c r="AA67" s="16">
         <f t="shared" si="16"/>
@@ -8554,7 +8569,7 @@
       </c>
       <c r="AB67" s="7">
         <f>IF(OR(A67="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC67" s="8" t="str">
         <f>IF(OR(AB67="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB67,"低于上限","达到或超过上限"))</f>
@@ -8640,7 +8655,7 @@
       </c>
       <c r="Z68" s="7">
         <f>IF(OR(AE68="",多次统计数据!$B$8=""),"",AE68-多次统计数据!$B$8)</f>
-        <v>-0.106421478558792</v>
+        <v>-0.107738178688699</v>
       </c>
       <c r="AA68" s="16">
         <f t="shared" si="16"/>
@@ -8648,7 +8663,7 @@
       </c>
       <c r="AB68" s="7">
         <f>IF(OR(A68="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC68" s="8" t="str">
         <f>IF(OR(AB68="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB68,"低于上限","达到或超过上限"))</f>
@@ -8734,7 +8749,7 @@
       </c>
       <c r="Z69" s="7">
         <f>IF(OR(AE69="",多次统计数据!$B$8=""),"",AE69-多次统计数据!$B$8)</f>
-        <v>-0.084467750782119</v>
+        <v>-0.0857844509120264</v>
       </c>
       <c r="AA69" s="16">
         <f t="shared" si="16"/>
@@ -8742,7 +8757,7 @@
       </c>
       <c r="AB69" s="7">
         <f>IF(OR(A69="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC69" s="8" t="str">
         <f>IF(OR(AB69="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB69,"低于上限","达到或超过上限"))</f>
@@ -8828,7 +8843,7 @@
       </c>
       <c r="Z70" s="7">
         <f>IF(OR(AE70="",多次统计数据!$B$8=""),"",AE70-多次统计数据!$B$8)</f>
-        <v>-0.0918866177596183</v>
+        <v>-0.0932033178895258</v>
       </c>
       <c r="AA70" s="16">
         <f t="shared" si="16"/>
@@ -8836,7 +8851,7 @@
       </c>
       <c r="AB70" s="7">
         <f>IF(OR(A70="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC70" s="8" t="str">
         <f>IF(OR(AB70="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB70,"低于上限","达到或超过上限"))</f>
@@ -8922,7 +8937,7 @@
       </c>
       <c r="Z71" s="7">
         <f>IF(OR(AE71="",多次统计数据!$B$8=""),"",AE71-多次统计数据!$B$8)</f>
-        <v>-0.0777676955599162</v>
+        <v>-0.0790843956898236</v>
       </c>
       <c r="AA71" s="16">
         <f t="shared" si="16"/>
@@ -8930,7 +8945,7 @@
       </c>
       <c r="AB71" s="7">
         <f>IF(OR(A71="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC71" s="8" t="str">
         <f>IF(OR(AB71="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB71,"低于上限","达到或超过上限"))</f>
@@ -9016,7 +9031,7 @@
       </c>
       <c r="Z72" s="7">
         <f>IF(OR(AE72="",多次统计数据!$B$8=""),"",AE72-多次统计数据!$B$8)</f>
-        <v>-0.0820149736710414</v>
+        <v>-0.0833316738009489</v>
       </c>
       <c r="AA72" s="16">
         <f t="shared" si="16"/>
@@ -9024,7 +9039,7 @@
       </c>
       <c r="AB72" s="7">
         <f>IF(OR(A72="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC72" s="8" t="str">
         <f>IF(OR(AB72="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB72,"低于上限","达到或超过上限"))</f>
@@ -9110,7 +9125,7 @@
       </c>
       <c r="Z73" s="7">
         <f>IF(OR(AE73="",多次统计数据!$B$8=""),"",AE73-多次统计数据!$B$8)</f>
-        <v>-0.0964905350146056</v>
+        <v>-0.097807235144513</v>
       </c>
       <c r="AA73" s="16">
         <f t="shared" si="16"/>
@@ -9118,7 +9133,7 @@
       </c>
       <c r="AB73" s="7">
         <f>IF(OR(A73="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC73" s="8" t="str">
         <f>IF(OR(AB73="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB73,"低于上限","达到或超过上限"))</f>
@@ -9204,7 +9219,7 @@
       </c>
       <c r="Z74" s="7">
         <f>IF(OR(AE74="",多次统计数据!$B$8=""),"",AE74-多次统计数据!$B$8)</f>
-        <v>-0.0634718219315362</v>
+        <v>-0.0647885220614436</v>
       </c>
       <c r="AA74" s="16">
         <f t="shared" si="16"/>
@@ -9212,7 +9227,7 @@
       </c>
       <c r="AB74" s="7">
         <f>IF(OR(A74="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC74" s="8" t="str">
         <f>IF(OR(AB74="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB74,"低于上限","达到或超过上限"))</f>
@@ -9298,7 +9313,7 @@
       </c>
       <c r="Z75" s="7">
         <f>IF(OR(AE75="",多次统计数据!$B$8=""),"",AE75-多次统计数据!$B$8)</f>
-        <v>-0.0196164792929875</v>
+        <v>-0.020933179422895</v>
       </c>
       <c r="AA75" s="16">
         <f t="shared" si="16"/>
@@ -9306,7 +9321,7 @@
       </c>
       <c r="AB75" s="7">
         <f>IF(OR(A75="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC75" s="8" t="str">
         <f>IF(OR(AB75="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB75,"低于上限","达到或超过上限"))</f>
@@ -9397,7 +9412,7 @@
       </c>
       <c r="Z76" s="7">
         <f>IF(OR(AE76="",多次统计数据!$B$8=""),"",AE76-多次统计数据!$B$8)</f>
-        <v>-0.0781724321224027</v>
+        <v>-0.0794891322523102</v>
       </c>
       <c r="AA76" s="16">
         <f t="shared" si="16"/>
@@ -9405,7 +9420,7 @@
       </c>
       <c r="AB76" s="7">
         <f>IF(OR(A76="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC76" s="8" t="str">
         <f>IF(OR(AB76="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB76,"低于上限","达到或超过上限"))</f>
@@ -9496,7 +9511,7 @@
       </c>
       <c r="Z77" s="7">
         <f>IF(OR(AE77="",多次统计数据!$B$8=""),"",AE77-多次统计数据!$B$8)</f>
-        <v>-0.0824637099914022</v>
+        <v>-0.0837804101213096</v>
       </c>
       <c r="AA77" s="16">
         <f t="shared" si="16"/>
@@ -9504,7 +9519,7 @@
       </c>
       <c r="AB77" s="7">
         <f>IF(OR(A77="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC77" s="8" t="str">
         <f>IF(OR(AB77="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB77,"低于上限","达到或超过上限"))</f>
@@ -9595,7 +9610,7 @@
       </c>
       <c r="Z78" s="7">
         <f>IF(OR(AE78="",多次统计数据!$B$8=""),"",AE78-多次统计数据!$B$8)</f>
-        <v>-0.0525619405099079</v>
+        <v>-0.0538786406398154</v>
       </c>
       <c r="AA78" s="16">
         <f t="shared" si="16"/>
@@ -9603,7 +9618,7 @@
       </c>
       <c r="AB78" s="7">
         <f>IF(OR(A78="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC78" s="8" t="str">
         <f>IF(OR(AB78="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB78,"低于上限","达到或超过上限"))</f>
@@ -9694,7 +9709,7 @@
       </c>
       <c r="Z79" s="7">
         <f>IF(OR(AE79="",多次统计数据!$B$8=""),"",AE79-多次统计数据!$B$8)</f>
-        <v>-0.00720846052020718</v>
+        <v>-0.00852516065011464</v>
       </c>
       <c r="AA79" s="16">
         <f t="shared" si="16"/>
@@ -9702,7 +9717,7 @@
       </c>
       <c r="AB79" s="7">
         <f>IF(OR(A79="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC79" s="8" t="str">
         <f>IF(OR(AB79="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB79,"低于上限","达到或超过上限"))</f>
@@ -9793,7 +9808,7 @@
       </c>
       <c r="Z80" s="7">
         <f>IF(OR(AE80="",多次统计数据!$B$8=""),"",AE80-多次统计数据!$B$8)</f>
-        <v>0.0162967001312911</v>
+        <v>0.0149800000013837</v>
       </c>
       <c r="AA80" s="16">
         <f t="shared" si="16"/>
@@ -9801,7 +9816,7 @@
       </c>
       <c r="AB80" s="7">
         <f>IF(OR(A80="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC80" s="8" t="str">
         <f>IF(OR(AB80="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB80,"低于上限","达到或超过上限"))</f>
@@ -9892,7 +9907,7 @@
       </c>
       <c r="Z81" s="7">
         <f>IF(OR(AE81="",多次统计数据!$B$8=""),"",AE81-多次统计数据!$B$8)</f>
-        <v>-0.0835277783294992</v>
+        <v>-0.0848444784594067</v>
       </c>
       <c r="AA81" s="16">
         <f t="shared" si="16"/>
@@ -9900,7 +9915,7 @@
       </c>
       <c r="AB81" s="7">
         <f>IF(OR(A81="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC81" s="8" t="str">
         <f>IF(OR(AB81="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB81,"低于上限","达到或超过上限"))</f>
@@ -9991,7 +10006,7 @@
       </c>
       <c r="Z82" s="7">
         <f>IF(OR(AE82="",多次统计数据!$B$8=""),"",AE82-多次统计数据!$B$8)</f>
-        <v>-0.0782387337649747</v>
+        <v>-0.0795554338948822</v>
       </c>
       <c r="AA82" s="16">
         <f t="shared" si="16"/>
@@ -9999,7 +10014,7 @@
       </c>
       <c r="AB82" s="7">
         <f>IF(OR(A82="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC82" s="8" t="str">
         <f>IF(OR(AB82="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB82,"低于上限","达到或超过上限"))</f>
@@ -10090,7 +10105,7 @@
       </c>
       <c r="Z83" s="7">
         <f>IF(OR(AE83="",多次统计数据!$B$8=""),"",AE83-多次统计数据!$B$8)</f>
-        <v>-0.0475521533667809</v>
+        <v>-0.0488688534966883</v>
       </c>
       <c r="AA83" s="16">
         <f t="shared" si="16"/>
@@ -10098,7 +10113,7 @@
       </c>
       <c r="AB83" s="7">
         <f>IF(OR(A83="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC83" s="8" t="str">
         <f>IF(OR(AB83="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB83,"低于上限","达到或超过上限"))</f>
@@ -10189,7 +10204,7 @@
       </c>
       <c r="Z84" s="7">
         <f>IF(OR(AE84="",多次统计数据!$B$8=""),"",AE84-多次统计数据!$B$8)</f>
-        <v>-0.0512602669520403</v>
+        <v>-0.0525769670819477</v>
       </c>
       <c r="AA84" s="16">
         <f t="shared" si="16"/>
@@ -10197,7 +10212,7 @@
       </c>
       <c r="AB84" s="7">
         <f>IF(OR(A84="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC84" s="8" t="str">
         <f>IF(OR(AB84="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB84,"低于上限","达到或超过上限"))</f>
@@ -10288,7 +10303,7 @@
       </c>
       <c r="Z85" s="7">
         <f>IF(OR(AE85="",多次统计数据!$B$8=""),"",AE85-多次统计数据!$B$8)</f>
-        <v>0.0241906729606229</v>
+        <v>0.0228739728307154</v>
       </c>
       <c r="AA85" s="16">
         <f t="shared" si="16"/>
@@ -10296,7 +10311,7 @@
       </c>
       <c r="AB85" s="7">
         <f>IF(OR(A85="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC85" s="8" t="str">
         <f>IF(OR(AB85="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB85,"低于上限","达到或超过上限"))</f>
@@ -10387,7 +10402,7 @@
       </c>
       <c r="Z86" s="7">
         <f>IF(OR(AE86="",多次统计数据!$B$8=""),"",AE86-多次统计数据!$B$8)</f>
-        <v>-0.0800649970137329</v>
+        <v>-0.0813816971436404</v>
       </c>
       <c r="AA86" s="16">
         <f t="shared" si="16"/>
@@ -10395,7 +10410,7 @@
       </c>
       <c r="AB86" s="7">
         <f>IF(OR(A86="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC86" s="8" t="str">
         <f>IF(OR(AB86="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB86,"低于上限","达到或超过上限"))</f>
@@ -10486,7 +10501,7 @@
       </c>
       <c r="Z87" s="7">
         <f>IF(OR(AE87="",多次统计数据!$B$8=""),"",AE87-多次统计数据!$B$8)</f>
-        <v>-0.0548587186145756</v>
+        <v>-0.056175418744483</v>
       </c>
       <c r="AA87" s="16">
         <f t="shared" si="16"/>
@@ -10494,7 +10509,7 @@
       </c>
       <c r="AB87" s="7">
         <f>IF(OR(A87="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC87" s="8" t="str">
         <f>IF(OR(AB87="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB87,"低于上限","达到或超过上限"))</f>
@@ -10580,7 +10595,7 @@
       </c>
       <c r="Z88" s="7">
         <f>IF(OR(AE88="",多次统计数据!$B$8=""),"",AE88-多次统计数据!$B$8)</f>
-        <v>-0.0237424044648503</v>
+        <v>-0.0250591045947578</v>
       </c>
       <c r="AA88" s="16">
         <f t="shared" si="16"/>
@@ -10588,7 +10603,7 @@
       </c>
       <c r="AB88" s="7">
         <f>IF(OR(A88="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC88" s="8" t="str">
         <f>IF(OR(AB88="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB88,"低于上限","达到或超过上限"))</f>
@@ -10676,7 +10691,7 @@
       </c>
       <c r="Z89" s="7">
         <f>IF(OR(AE89="",多次统计数据!$B$8=""),"",AE89-多次统计数据!$B$8)</f>
-        <v>-0.11624013780657</v>
+        <v>-0.117556837936477</v>
       </c>
       <c r="AA89" s="16">
         <f t="shared" si="16"/>
@@ -10684,7 +10699,7 @@
       </c>
       <c r="AB89" s="7">
         <f>IF(OR(A89="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC89" s="8" t="str">
         <f>IF(OR(AB89="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB89,"低于上限","达到或超过上限"))</f>
@@ -10775,7 +10790,7 @@
       </c>
       <c r="Z90" s="7">
         <f>IF(OR(AE90="",多次统计数据!$B$8=""),"",AE90-多次统计数据!$B$8)</f>
-        <v>-0.0752485332085225</v>
+        <v>-0.07656523333843</v>
       </c>
       <c r="AA90" s="16">
         <f t="shared" si="16"/>
@@ -10783,7 +10798,7 @@
       </c>
       <c r="AB90" s="7">
         <f>IF(OR(A90="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC90" s="8" t="str">
         <f>IF(OR(AB90="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB90,"低于上限","达到或超过上限"))</f>
@@ -10871,7 +10886,7 @@
       </c>
       <c r="Z91" s="7">
         <f>IF(OR(AE91="",多次统计数据!$B$8=""),"",AE91-多次统计数据!$B$8)</f>
-        <v>-0.0804998516164255</v>
+        <v>-0.081816551746333</v>
       </c>
       <c r="AA91" s="16">
         <f t="shared" si="16"/>
@@ -10879,7 +10894,7 @@
       </c>
       <c r="AB91" s="7">
         <f>IF(OR(A91="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC91" s="8" t="str">
         <f>IF(OR(AB91="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB91,"低于上限","达到或超过上限"))</f>
@@ -10970,7 +10985,7 @@
       </c>
       <c r="Z92" s="7">
         <f>IF(OR(AE92="",多次统计数据!$B$8=""),"",AE92-多次统计数据!$B$8)</f>
-        <v>0.169877222452833</v>
+        <v>0.168560522322925</v>
       </c>
       <c r="AA92" s="16">
         <f t="shared" si="16"/>
@@ -10978,7 +10993,7 @@
       </c>
       <c r="AB92" s="7">
         <f>IF(OR(A92="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC92" s="8" t="str">
         <f>IF(OR(AB92="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB92,"低于上限","达到或超过上限"))</f>
@@ -11069,7 +11084,7 @@
       </c>
       <c r="Z93" s="7">
         <f>IF(OR(AE93="",多次统计数据!$B$8=""),"",AE93-多次统计数据!$B$8)</f>
-        <v>-0.0102032848991575</v>
+        <v>-0.011519985029065</v>
       </c>
       <c r="AA93" s="16">
         <f t="shared" si="16"/>
@@ -11077,7 +11092,7 @@
       </c>
       <c r="AB93" s="7">
         <f>IF(OR(A93="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v>0.0455859002225864</v>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC93" s="8" t="str">
         <f>IF(OR(AB93="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB93,"低于上限","达到或超过上限"))</f>
@@ -11095,219 +11110,300 @@
       </c>
     </row>
     <row r="94" ht="17" spans="1:32">
-      <c r="A94" s="2"/>
-      <c r="B94" s="2"/>
-      <c r="C94" s="9"/>
-      <c r="D94" s="6"/>
-      <c r="E94" s="9"/>
-      <c r="F94" s="8" t="str">
+      <c r="A94" s="2">
+        <v>93</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C94" s="9">
+        <v>215127</v>
+      </c>
+      <c r="D94" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E94" s="9">
+        <v>6.86</v>
+      </c>
+      <c r="F94" s="8">
         <f t="shared" si="9"/>
-        <v/>
+        <v>5000</v>
       </c>
       <c r="G94" s="8" t="str">
         <f>IF(OR(A94="",F94="",E94="",N94="",E94&lt;=N94,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H94="",F94*(E94-N94),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H94" s="2"/>
-      <c r="I94" s="10"/>
-      <c r="J94" s="9"/>
-      <c r="K94" s="9"/>
-      <c r="L94" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H94" s="2">
+        <v>5000</v>
+      </c>
+      <c r="I94" s="10">
+        <v>44678</v>
+      </c>
+      <c r="J94" s="9">
+        <v>9</v>
+      </c>
+      <c r="K94" s="9">
+        <v>7.74</v>
+      </c>
+      <c r="L94" s="8">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="M94" s="10"/>
-      <c r="N94" s="9"/>
+        <v>5000</v>
+      </c>
+      <c r="M94" s="10">
+        <v>44692</v>
+      </c>
+      <c r="N94" s="9">
+        <v>6</v>
+      </c>
       <c r="O94" s="9"/>
       <c r="P94" s="9"/>
       <c r="Q94" s="2"/>
       <c r="R94" s="2"/>
       <c r="S94" s="2"/>
       <c r="T94" s="2"/>
-      <c r="U94" s="7" t="str">
+      <c r="U94" s="7">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="V94" s="7" t="str">
+        <v>0.311953352769679</v>
+      </c>
+      <c r="V94" s="7">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="W94" s="15" t="str">
+        <v>0.125364431486881</v>
+      </c>
+      <c r="W94" s="15">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="X94" s="5" t="str">
+        <v>2.48837209302325</v>
+      </c>
+      <c r="X94" s="5">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="Y94" s="7" t="str">
+        <v>4400</v>
+      </c>
+      <c r="Y94" s="7">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="Z94" s="7" t="str">
+        <v>0.128279883381924</v>
+      </c>
+      <c r="Z94" s="7">
         <f>IF(OR(AE94="",多次统计数据!$B$8=""),"",AE94-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA94" s="16" t="str">
+        <v>-0.0382092094391358</v>
+      </c>
+      <c r="AA94" s="16">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="AB94" s="7" t="str">
+        <v>14</v>
+      </c>
+      <c r="AB94" s="7">
         <f>IF(OR(A94="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC94" s="8" t="str">
         <f>IF(OR(AB94="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB94,"低于上限","达到或超过上限"))</f>
-        <v/>
-      </c>
-      <c r="AD94" s="2"/>
-      <c r="AE94" s="7" t="str">
+        <v>低于上限</v>
+      </c>
+      <c r="AD94" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="AE94" s="7">
         <f t="shared" si="17"/>
-        <v/>
+        <v>0.0204530347190264</v>
+      </c>
+      <c r="AF94" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="95" ht="17" spans="1:32">
-      <c r="A95" s="2"/>
-      <c r="B95" s="2"/>
-      <c r="C95" s="9"/>
-      <c r="D95" s="6"/>
-      <c r="E95" s="9"/>
-      <c r="F95" s="8" t="str">
+      <c r="A95" s="2">
+        <v>94</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C95" s="9">
+        <v>219527</v>
+      </c>
+      <c r="D95" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E95" s="9">
+        <v>12.26</v>
+      </c>
+      <c r="F95" s="8">
         <f t="shared" si="9"/>
-        <v/>
+        <v>5700</v>
       </c>
       <c r="G95" s="8" t="str">
         <f>IF(OR(A95="",F95="",E95="",N95="",E95&lt;=N95,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H95="",F95*(E95-N95),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H95" s="2"/>
-      <c r="I95" s="10"/>
-      <c r="J95" s="9"/>
-      <c r="K95" s="9"/>
-      <c r="L95" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H95" s="2">
+        <v>5700</v>
+      </c>
+      <c r="I95" s="10">
+        <v>44992</v>
+      </c>
+      <c r="J95" s="9">
+        <v>14</v>
+      </c>
+      <c r="K95" s="9">
+        <v>18.07</v>
+      </c>
+      <c r="L95" s="8">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="M95" s="10"/>
-      <c r="N95" s="9"/>
+        <v>5700</v>
+      </c>
+      <c r="M95" s="10">
+        <v>45034</v>
+      </c>
+      <c r="N95" s="9">
+        <v>11.5</v>
+      </c>
       <c r="O95" s="9"/>
       <c r="P95" s="9"/>
       <c r="Q95" s="2"/>
       <c r="R95" s="2"/>
       <c r="S95" s="2"/>
       <c r="T95" s="2"/>
-      <c r="U95" s="7" t="str">
+      <c r="U95" s="7">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="V95" s="7" t="str">
+        <v>0.141924959216966</v>
+      </c>
+      <c r="V95" s="7">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="W95" s="15" t="str">
+        <v>0.0619902120717781</v>
+      </c>
+      <c r="W95" s="15">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="X95" s="5" t="str">
+        <v>2.28947368421053</v>
+      </c>
+      <c r="X95" s="5">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="Y95" s="7" t="str">
+        <v>33117</v>
+      </c>
+      <c r="Y95" s="7">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="Z95" s="7" t="str">
+        <v>0.473898858075041</v>
+      </c>
+      <c r="Z95" s="7">
         <f>IF(OR(AE95="",多次统计数据!$B$8=""),"",AE95-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA95" s="16" t="str">
+        <v>0.0921939147653415</v>
+      </c>
+      <c r="AA95" s="16">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="AB95" s="7" t="str">
+        <v>42</v>
+      </c>
+      <c r="AB95" s="7">
         <f>IF(OR(A95="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC95" s="8" t="str">
         <f>IF(OR(AB95="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB95,"低于上限","达到或超过上限"))</f>
-        <v/>
-      </c>
-      <c r="AD95" s="2"/>
-      <c r="AE95" s="7" t="str">
+        <v>低于上限</v>
+      </c>
+      <c r="AD95" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="AE95" s="7">
         <f t="shared" si="17"/>
-        <v/>
+        <v>0.150856158923504</v>
+      </c>
+      <c r="AF95" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="96" ht="17" spans="1:32">
-      <c r="A96" s="2"/>
-      <c r="B96" s="2"/>
-      <c r="C96" s="9"/>
-      <c r="D96" s="6"/>
-      <c r="E96" s="9"/>
-      <c r="F96" s="8" t="str">
+      <c r="A96" s="2">
+        <v>95</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C96" s="9">
+        <v>252644</v>
+      </c>
+      <c r="D96" s="6">
+        <v>0.02</v>
+      </c>
+      <c r="E96" s="9">
+        <v>18.15</v>
+      </c>
+      <c r="F96" s="8">
         <f t="shared" si="9"/>
-        <v/>
+        <v>3800</v>
       </c>
       <c r="G96" s="8" t="str">
         <f>IF(OR(A96="",F96="",E96="",N96="",E96&lt;=N96,账户数据!$B$7=""),"",IF(账户数据!$B$9+IF(H96="",F96*(E96-N96),0)&gt;=账户数据!$B$7,"禁止开仓","允许开仓"))</f>
-        <v/>
-      </c>
-      <c r="H96" s="2"/>
-      <c r="I96" s="10"/>
-      <c r="J96" s="9"/>
-      <c r="K96" s="9"/>
-      <c r="L96" s="8" t="str">
+        <v>允许开仓</v>
+      </c>
+      <c r="H96" s="2">
+        <v>3800</v>
+      </c>
+      <c r="I96" s="10">
+        <v>45306</v>
+      </c>
+      <c r="J96" s="9">
+        <v>20</v>
+      </c>
+      <c r="K96" s="9">
+        <v>16.25</v>
+      </c>
+      <c r="L96" s="8">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="M96" s="10"/>
-      <c r="N96" s="9"/>
+        <v>3800</v>
+      </c>
+      <c r="M96" s="10">
+        <v>45313</v>
+      </c>
+      <c r="N96" s="9">
+        <v>16.83</v>
+      </c>
       <c r="O96" s="9"/>
       <c r="P96" s="9"/>
       <c r="Q96" s="2"/>
       <c r="R96" s="2"/>
       <c r="S96" s="2"/>
       <c r="T96" s="2"/>
-      <c r="U96" s="7" t="str">
+      <c r="U96" s="7">
         <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="V96" s="7" t="str">
+        <v>0.101928374655647</v>
+      </c>
+      <c r="V96" s="7">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="W96" s="15" t="str">
+        <v>0.0727272727272728</v>
+      </c>
+      <c r="W96" s="15">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="X96" s="5" t="str">
+        <v>1.40151515151515</v>
+      </c>
+      <c r="X96" s="5">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="Y96" s="7" t="str">
+        <v>-7220</v>
+      </c>
+      <c r="Y96" s="7">
         <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="Z96" s="7" t="str">
+        <v>-0.104683195592287</v>
+      </c>
+      <c r="Z96" s="7">
         <f>IF(OR(AE96="",多次统计数据!$B$8=""),"",AE96-多次统计数据!$B$8)</f>
-        <v/>
-      </c>
-      <c r="AA96" s="16" t="str">
+        <v>-0.0872400057515506</v>
+      </c>
+      <c r="AA96" s="16">
         <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="AB96" s="7" t="str">
+        <v>7</v>
+      </c>
+      <c r="AB96" s="7">
         <f>IF(OR(A96="",多次统计数据!$B$8="",多次统计数据!$B$6&lt;=0,多次统计数据!$B$6&gt;=1),"",1-POWER(1+多次统计数据!$B$8,-多次统计数据!$B$6/(1-多次统计数据!$B$6)))</f>
-        <v/>
+        <v>0.0478428901548558</v>
       </c>
       <c r="AC96" s="8" t="str">
         <f>IF(OR(AB96="",多次统计数据!$B$9=""),"",IF(多次统计数据!$B$9&lt;AB96,"低于上限","达到或超过上限"))</f>
-        <v/>
-      </c>
-      <c r="AD96" s="2"/>
-      <c r="AE96" s="7" t="str">
+        <v>低于上限</v>
+      </c>
+      <c r="AD96" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="AE96" s="7">
         <f t="shared" si="17"/>
-        <v/>
+        <v>-0.0285777615933883</v>
+      </c>
+      <c r="AF96" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="97" ht="17" spans="1:31">
@@ -18976,31 +19072,31 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J1" t="s">
         <v>31</v>
       </c>
       <c r="K1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" ht="34" spans="1:11">
@@ -19015,7 +19111,7 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" ht="51" spans="1:11">
@@ -19028,7 +19124,7 @@
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" ht="34" spans="1:11">
@@ -19041,7 +19137,7 @@
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" ht="34" spans="1:11">
@@ -19054,7 +19150,7 @@
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="11" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" ht="34" spans="1:11">
@@ -19067,10 +19163,10 @@
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="11" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" ht="17" spans="1:11">
@@ -19083,7 +19179,7 @@
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="11" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -19120,7 +19216,7 @@
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="11" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11" ht="34" spans="1:11">
@@ -19135,7 +19231,7 @@
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="11" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12" ht="51" spans="1:11">
@@ -19150,7 +19246,7 @@
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" ht="34" spans="1:11">
@@ -19165,7 +19261,7 @@
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="14" ht="34" spans="1:11">
@@ -19180,7 +19276,7 @@
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="15" ht="34" spans="1:11">
@@ -19195,7 +19291,7 @@
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="16" ht="51" spans="1:11">
@@ -19210,7 +19306,7 @@
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17" ht="34" spans="1:9">
@@ -19225,7 +19321,7 @@
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="18" ht="34" spans="1:9">
@@ -19240,7 +19336,7 @@
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="19" ht="34" spans="1:9">
@@ -19255,7 +19351,7 @@
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20" ht="34" spans="1:9">
@@ -19270,7 +19366,7 @@
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="21" ht="34" spans="1:9">
@@ -19285,7 +19381,7 @@
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="22" ht="34" spans="1:9">
@@ -19300,7 +19396,7 @@
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="23" ht="51" spans="1:9">
@@ -19315,7 +19411,7 @@
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="24" ht="34" spans="1:9">
@@ -19330,7 +19426,7 @@
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="25" ht="34" spans="1:9">
@@ -19345,7 +19441,7 @@
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="26" ht="51" spans="1:9">
@@ -19360,7 +19456,7 @@
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="27" ht="51" spans="1:9">
@@ -19375,7 +19471,7 @@
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="28" ht="34" spans="1:9">
@@ -19390,7 +19486,7 @@
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
       <c r="I28" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="29" ht="34" spans="1:9">
@@ -19405,7 +19501,7 @@
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
       <c r="I29" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="30" ht="51" spans="1:9">
@@ -19420,7 +19516,7 @@
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="31" ht="34" spans="1:9">
@@ -19435,7 +19531,7 @@
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="32" ht="34" spans="1:9">
@@ -19450,7 +19546,7 @@
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
       <c r="I32" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="33" ht="17" spans="1:9">
@@ -19465,7 +19561,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
       <c r="I33" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="34" ht="34" spans="1:9">
@@ -19480,7 +19576,7 @@
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="35" ht="34" spans="1:9">
@@ -19495,7 +19591,7 @@
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="36" ht="51" spans="1:9">
@@ -19510,7 +19606,7 @@
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
       <c r="I36" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="37" ht="17" spans="1:9">
@@ -19525,7 +19621,7 @@
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
       <c r="I37" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="38" ht="34" spans="1:9">
@@ -19540,7 +19636,7 @@
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
       <c r="I38" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="39" ht="17" spans="1:9">
@@ -19555,7 +19651,7 @@
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
       <c r="I39" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="40" ht="34" spans="1:9">
@@ -19570,7 +19666,7 @@
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
       <c r="I40" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="41" ht="17" spans="1:9">
@@ -19585,7 +19681,7 @@
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
       <c r="I41" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="42" ht="34" spans="1:9">
@@ -19600,7 +19696,7 @@
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
       <c r="I42" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="43" ht="34" spans="1:9">
@@ -19615,7 +19711,7 @@
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
       <c r="I43" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="44" ht="34" spans="1:9">
@@ -19630,7 +19726,7 @@
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
       <c r="I44" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="45" ht="17" spans="1:9">
@@ -19645,7 +19741,7 @@
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
       <c r="I45" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="46" ht="17" spans="1:9">
@@ -19660,7 +19756,7 @@
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
       <c r="I46" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="47" ht="17" spans="1:9">
@@ -19675,7 +19771,7 @@
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
       <c r="I47" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="48" ht="17" spans="1:9">
@@ -19690,7 +19786,7 @@
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
       <c r="I48" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="49" ht="34" spans="1:9">
@@ -19705,7 +19801,7 @@
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
       <c r="I49" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="50" ht="34" spans="1:9">
@@ -19720,7 +19816,7 @@
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
       <c r="I50" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="51" ht="34" spans="1:9">
@@ -19735,7 +19831,7 @@
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
       <c r="I51" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="52" ht="34" spans="1:9">
@@ -19750,7 +19846,7 @@
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
       <c r="I52" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="53" ht="34" spans="1:9">
@@ -19765,7 +19861,7 @@
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
       <c r="I53" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="54" ht="34" spans="1:9">
@@ -19780,7 +19876,7 @@
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
       <c r="I54" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="55" ht="51" spans="1:9">
@@ -19795,7 +19891,7 @@
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
       <c r="I55" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="56" ht="34" spans="1:9">
@@ -19810,7 +19906,7 @@
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
       <c r="I56" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="57" ht="34" spans="1:9">
@@ -19825,7 +19921,7 @@
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
       <c r="I57" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="58" ht="17" spans="1:9">
@@ -19840,7 +19936,7 @@
       <c r="G58" s="2"/>
       <c r="H58" s="2"/>
       <c r="I58" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="59" ht="34" spans="1:9">
@@ -19855,7 +19951,7 @@
       <c r="G59" s="2"/>
       <c r="H59" s="2"/>
       <c r="I59" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="60" ht="34" spans="1:9">
@@ -19870,7 +19966,7 @@
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
       <c r="I60" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="61" ht="34" spans="1:9">
@@ -19885,7 +19981,7 @@
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
       <c r="I61" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="62" ht="34" spans="1:9">
@@ -19900,7 +19996,7 @@
       <c r="G62" s="2"/>
       <c r="H62" s="2"/>
       <c r="I62" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="63" ht="34" spans="1:9">
@@ -19915,7 +20011,7 @@
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
       <c r="I63" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="64" ht="34" spans="1:9">
@@ -19930,7 +20026,7 @@
       <c r="G64" s="2"/>
       <c r="H64" s="2"/>
       <c r="I64" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="65" ht="34" spans="1:11">
@@ -19945,7 +20041,7 @@
       <c r="G65" s="2"/>
       <c r="H65" s="2"/>
       <c r="I65" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="66" ht="17" spans="1:11">
@@ -19960,7 +20056,7 @@
       <c r="G66" s="2"/>
       <c r="H66" s="2"/>
       <c r="I66" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="67" ht="17" spans="1:11">
@@ -19975,7 +20071,7 @@
       <c r="G67" s="2"/>
       <c r="H67" s="2"/>
       <c r="I67" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="68" ht="34" spans="1:11">
@@ -19990,7 +20086,7 @@
       <c r="G68" s="2"/>
       <c r="H68" s="2"/>
       <c r="I68" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="69" ht="17" spans="1:11">
@@ -20005,7 +20101,7 @@
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
       <c r="I69" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="70" ht="68" spans="1:11">
@@ -20020,13 +20116,13 @@
       <c r="G70" s="2"/>
       <c r="H70" s="2"/>
       <c r="I70" s="13" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="J70" s="14" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="K70" s="14" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="71" ht="84" spans="1:11">
@@ -20041,7 +20137,7 @@
       <c r="G71" s="2"/>
       <c r="H71" s="2"/>
       <c r="I71" s="13" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="72" ht="84" spans="1:11">
@@ -20056,7 +20152,7 @@
       <c r="G72" s="2"/>
       <c r="H72" s="2"/>
       <c r="I72" s="13" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="73" ht="101" spans="1:11">
@@ -20071,7 +20167,7 @@
       <c r="G73" s="2"/>
       <c r="H73" s="2"/>
       <c r="I73" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="74" ht="51" spans="1:11">
@@ -20086,7 +20182,7 @@
       <c r="G74" s="2"/>
       <c r="H74" s="2"/>
       <c r="I74" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="75" ht="135" spans="1:11">
@@ -20101,7 +20197,7 @@
       <c r="G75" s="2"/>
       <c r="H75" s="2"/>
       <c r="I75" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="76" ht="68" spans="1:11">
@@ -20116,10 +20212,10 @@
       <c r="G76" s="2"/>
       <c r="H76" s="2"/>
       <c r="I76" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="J76" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="77" ht="34" spans="1:11">
@@ -20134,10 +20230,10 @@
       <c r="G77" s="2"/>
       <c r="H77" s="2"/>
       <c r="I77" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="J77" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="78" ht="84" spans="1:11">
@@ -20152,7 +20248,7 @@
       <c r="G78" s="2"/>
       <c r="H78" s="2"/>
       <c r="I78" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="79" ht="17" spans="1:11">
@@ -20167,7 +20263,7 @@
       <c r="G79" s="2"/>
       <c r="H79" s="2"/>
       <c r="I79" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="80" ht="84" spans="1:11">
@@ -20182,7 +20278,7 @@
       <c r="G80" s="2"/>
       <c r="H80" s="2"/>
       <c r="I80" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="81" ht="68" spans="1:9">
@@ -20197,7 +20293,7 @@
       <c r="G81" s="2"/>
       <c r="H81" s="2"/>
       <c r="I81" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="82" ht="101" spans="1:9">
@@ -20212,7 +20308,7 @@
       <c r="G82" s="2"/>
       <c r="H82" s="2"/>
       <c r="I82" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="83" ht="51" spans="1:9">
@@ -20227,7 +20323,7 @@
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
       <c r="I83" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="84" ht="84" spans="1:9">
@@ -20242,7 +20338,7 @@
       <c r="G84" s="2"/>
       <c r="H84" s="2"/>
       <c r="I84" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="85" ht="34" spans="1:9">
@@ -20257,7 +20353,7 @@
       <c r="G85" s="2"/>
       <c r="H85" s="2"/>
       <c r="I85" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="86" ht="34" spans="1:9">
@@ -20272,7 +20368,7 @@
       <c r="G86" s="2"/>
       <c r="H86" s="2"/>
       <c r="I86" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="87" ht="84" spans="1:9">
@@ -20287,7 +20383,7 @@
       <c r="G87" s="2"/>
       <c r="H87" s="2"/>
       <c r="I87" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="88" ht="118" spans="1:9">
@@ -20302,11 +20398,13 @@
       <c r="G88" s="2"/>
       <c r="H88" s="2"/>
       <c r="I88" s="2" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9">
-      <c r="A89" s="2"/>
+        <v>184</v>
+      </c>
+    </row>
+    <row r="89" ht="135" spans="1:9">
+      <c r="A89" s="2">
+        <v>92</v>
+      </c>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
       <c r="D89" s="2"/>
@@ -20314,10 +20412,14 @@
       <c r="F89" s="2"/>
       <c r="G89" s="2"/>
       <c r="H89" s="2"/>
-      <c r="I89" s="2"/>
-    </row>
-    <row r="90" spans="1:9">
-      <c r="A90" s="2"/>
+      <c r="I89" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="90" ht="168" spans="1:9">
+      <c r="A90" s="2">
+        <v>93</v>
+      </c>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
       <c r="D90" s="2"/>
@@ -20325,10 +20427,14 @@
       <c r="F90" s="2"/>
       <c r="G90" s="2"/>
       <c r="H90" s="2"/>
-      <c r="I90" s="2"/>
-    </row>
-    <row r="91" spans="1:9">
-      <c r="A91" s="2"/>
+      <c r="I90" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="91" ht="101" spans="1:9">
+      <c r="A91" s="2">
+        <v>94</v>
+      </c>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
       <c r="D91" s="2"/>
@@ -20336,7 +20442,9 @@
       <c r="F91" s="2"/>
       <c r="G91" s="2"/>
       <c r="H91" s="2"/>
-      <c r="I91" s="2"/>
+      <c r="I91" s="2" t="s">
+        <v>187</v>
+      </c>
     </row>
     <row r="92" spans="1:9">
       <c r="A92" s="2"/>
@@ -24882,169 +24990,169 @@
   <sheetData>
     <row r="1" ht="17" spans="1:3">
       <c r="A1" s="3" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
     </row>
     <row r="2" ht="17" spans="1:3">
       <c r="A2" s="4" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B2" s="8">
         <f>COUNT(单次交易!M2:M201)</f>
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3" ht="17" spans="1:3">
       <c r="A3" s="4" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B3" s="8">
         <f>COUNTIF(单次交易!X2:X201,"&gt;0")</f>
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
     </row>
     <row r="4" ht="17" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B4" s="8">
         <f>COUNTIF(单次交易!X2:X201,"&lt;0")</f>
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5" ht="17" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B5" s="8">
         <f>COUNTIFS(单次交易!M2:M201,"&lt;&gt;",单次交易!X2:X201,"=0")</f>
         <v>0</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="6" ht="17" spans="1:3">
       <c r="A6" s="4" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="B6" s="7">
         <f>IFERROR(B3/(B3+B4),"")</f>
-        <v>0.455555555555556</v>
+        <v>0.462365591397849</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
     </row>
     <row r="7" ht="17" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B7" s="7">
         <f>IFERROR(B4/(B3+B4),"")</f>
-        <v>0.544444444444444</v>
+        <v>0.537634408602151</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
     </row>
     <row r="8" ht="17" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="B8" s="7">
         <f>IFERROR(AVERAGEIF(单次交易!X2:X201,"&gt;0",单次交易!AE2:AE201),"")</f>
-        <v>0.0573455440282548</v>
+        <v>0.0586622441581622</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
     </row>
     <row r="9" ht="17" spans="1:3">
       <c r="A9" s="4" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B9" s="7">
         <f>IFERROR(-AVERAGEIF(单次交易!X2:X201,"&lt;0",单次交易!AE2:AE201),"")</f>
-        <v>0.0292761619899203</v>
+        <v>0.0292621908051849</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
     </row>
     <row r="10" ht="17" spans="1:3">
       <c r="A10" s="4" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B10" s="8">
         <f>SUMIF(单次交易!X2:X201,"&gt;0",单次交易!AA2:AA201)</f>
-        <v>1785</v>
+        <v>1841</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11" ht="17" spans="1:3">
       <c r="A11" s="4" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B11" s="8">
         <f>SUMIF(单次交易!X2:X201,"&lt;0",单次交易!AA2:AA201)</f>
-        <v>917</v>
+        <v>924</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12" ht="17" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B12" s="5">
         <f>IFERROR(SUMPRODUCT(单次交易!E2:E201,单次交易!H2:H201)/COUNT(单次交易!H2:H201),"")</f>
-        <v>61767.8</v>
+        <v>61637.1397849462</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13" ht="17" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B13" s="7">
         <f>IF(OR(B6="",B7="",B8="",B9=""),"",B6*B8-B7*B9)</f>
-        <v>0.0101848374183594</v>
+        <v>0.0113910425649649</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
     </row>
     <row r="14" ht="17" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="B14" s="7">
         <f>IF(COUNT(单次交易!AE2:AE201)=0,"",EXP(SUMPRODUCT(IFERROR(LN(1+单次交易!AE2:AE201),0)))-1)</f>
-        <v>1.15131819740595</v>
+        <v>1.45429538789412</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
     </row>
   </sheetData>
@@ -25066,130 +25174,130 @@
   <sheetData>
     <row r="1" ht="17" spans="1:3">
       <c r="A1" s="3" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
     </row>
     <row r="2" ht="17" spans="1:3">
       <c r="A2" s="4" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="B2" s="9">
         <v>100000</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
     </row>
     <row r="3" ht="17" spans="1:3">
       <c r="A3" s="4" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="B3" s="5">
         <f>IF(B2="","",B2+SUM(单次交易!X2:X201))</f>
-        <v>215127</v>
+        <v>245424</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4" ht="17" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B4" s="6">
         <v>0.02</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="5" ht="17" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="B5" s="5">
         <f>IF(B3="","",B3*B4)</f>
-        <v>4302.54</v>
+        <v>4908.48</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
     </row>
     <row r="6" ht="17" spans="1:3">
       <c r="A6" s="4" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="B6" s="6">
         <v>0.06</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
     </row>
     <row r="7" ht="17" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B7" s="5">
         <f>IF(B3="","",B3*B6)</f>
-        <v>12907.62</v>
+        <v>14725.44</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
     </row>
     <row r="8" ht="17" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B8" s="5">
         <f ca="1">SUMIFS(单次交易!X2:X201,单次交易!X2:X201,"&lt;0",单次交易!M2:M201,"&gt;="&amp;EOMONTH(TODAY(),-1)+1,单次交易!M2:M201,"&lt;="&amp;EOMONTH(TODAY(),0))</f>
         <v>0</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
     </row>
     <row r="9" ht="17" spans="1:3">
       <c r="A9" s="4" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="B9" s="5">
         <f>IFERROR(SUMPRODUCT((单次交易!M2:M201="")*(单次交易!H2:H201&gt;0)*(单次交易!E2:E201&gt;单次交易!N2:N201)*单次交易!H2:H201*(单次交易!E2:E201-单次交易!N2:N201)),0)</f>
         <v>0</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
     </row>
     <row r="10" ht="17" spans="1:3">
       <c r="A10" s="4" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="B10" s="5">
         <f>IF(OR(B7="",B9=""),"",B7-B9)</f>
-        <v>12907.62</v>
+        <v>14725.44</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11" ht="17" spans="1:3">
       <c r="A11" s="4" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="B11" s="7">
         <f>IF(OR(B2="",B3="",B2&lt;=0),"",B3/B2-1)</f>
-        <v>1.15127</v>
+        <v>1.45424</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -25230,84 +25338,84 @@
   <sheetData>
     <row r="1" ht="17" spans="1:3">
       <c r="A1" s="3" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
     </row>
     <row r="2" ht="17" spans="1:3">
       <c r="A2" s="4" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="B2" s="5">
         <f>账户数据!B3</f>
-        <v>215127</v>
+        <v>245424</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3" ht="17" spans="1:3">
       <c r="A3" s="4" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="B3" s="6">
         <v>0.1</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
     </row>
     <row r="4" ht="17" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="B4" s="5">
         <f>IF(OR(B2="",B3=""),"",B2*B3)</f>
-        <v>21512.7</v>
+        <v>24542.4</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" ht="17" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B5" s="5">
         <f>多次统计数据!B12</f>
-        <v>61767.8</v>
+        <v>61637.1397849462</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" ht="17" spans="1:3">
       <c r="A6" s="4" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="B6" s="7">
         <f>多次统计数据!B13</f>
-        <v>0.0101848374183594</v>
+        <v>0.0113910425649649</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
     </row>
     <row r="7" ht="17" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B7" s="8">
         <f>IF(OR(B3="",B6="",B3&lt;=0,B6&lt;=0),"暂不可计算",ROUNDUP(LN(1+B3)/LN(1+B6),0))</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
   </sheetData>
@@ -25334,233 +25442,233 @@
   <sheetData>
     <row r="1" ht="42" customHeight="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
     </row>
     <row r="2" ht="17" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
     </row>
     <row r="3" ht="17" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
     </row>
     <row r="4" ht="17" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
     </row>
     <row r="5" ht="17" spans="1:3">
       <c r="A5" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>251</v>
-      </c>
       <c r="C5" s="2" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
     </row>
     <row r="6" ht="17" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
     </row>
     <row r="7" ht="17" spans="1:3">
       <c r="A7" s="2" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
     </row>
     <row r="8" ht="17" spans="1:3">
       <c r="A8" s="2" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
     </row>
     <row r="9" ht="17" spans="1:3">
       <c r="A9" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" ht="17" spans="1:3">
       <c r="A10" s="2" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" ht="17" spans="1:3">
       <c r="A11" s="2" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" ht="17" spans="1:3">
       <c r="A12" s="2" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
     </row>
     <row r="13" ht="17" spans="1:3">
       <c r="A13" s="2" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
     </row>
     <row r="14" ht="17" spans="1:3">
       <c r="A14" s="2" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
     </row>
     <row r="15" ht="17" spans="1:3">
       <c r="A15" s="2" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
     </row>
     <row r="16" ht="17" spans="1:3">
       <c r="A16" s="2" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
     </row>
     <row r="17" ht="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
     </row>
     <row r="18" ht="17" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
     </row>
     <row r="19" ht="17" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
     </row>
     <row r="20" ht="17" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
     </row>
     <row r="21" ht="17" spans="1:3">
       <c r="A21" s="2" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="22" spans="1:3">
